--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1762" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F93B24DE-9406-4876-B3D1-B91A799CFBC3}"/>
+  <xr:revisionPtr revIDLastSave="1785" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{423A2AAE-749C-441A-9ABF-9BC9616783CF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$127</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="579">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1746,6 +1746,39 @@
   </si>
   <si>
     <t xml:space="preserve">Fundraising with confidence </t>
+  </si>
+  <si>
+    <t>第十届理事会第一次会议</t>
+  </si>
+  <si>
+    <t>Tenth Management Committee 1st Meeting</t>
+  </si>
+  <si>
+    <t>ExCo Meeting</t>
+  </si>
+  <si>
+    <t>Tenth Management Committee 2nd Meeting</t>
+  </si>
+  <si>
+    <t>第十届理事会第二次会议</t>
+  </si>
+  <si>
+    <t>Ninth Management Committee 9th Meeting</t>
+  </si>
+  <si>
+    <t>第九届理事会第九次会议</t>
+  </si>
+  <si>
+    <t>Hari Raya Puasa (Public Holiday) - date subject to sighting of the moon</t>
+  </si>
+  <si>
+    <t>Ninth Management Committee 10th Meeting</t>
+  </si>
+  <si>
+    <t>开斋节（公共假期）－日期以观月为准</t>
+  </si>
+  <si>
+    <t>第九届理事会第十次会议</t>
   </si>
 </sst>
 </file>
@@ -1997,7 +2030,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2084,6 +2117,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2527,7 +2561,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -2585,7 +2619,7 @@
         <v>46023</v>
       </c>
       <c r="B3" s="32" t="str">
-        <f t="shared" ref="B3:B81" si="0">TEXT($A3,"ddd")</f>
+        <f t="shared" ref="B3:B85" si="0">TEXT($A3,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C3" s="33" t="s">
@@ -2602,531 +2636,531 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="35">
+      <c r="A4" s="31">
+        <f>DATE(2026,1,25)</f>
+        <v>46047</v>
+      </c>
+      <c r="B4" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>573</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>574</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="35">
         <f>DATE(2026,2,8)</f>
         <v>46061</v>
       </c>
-      <c r="B4" s="36" t="str">
+      <c r="B5" s="36" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C5" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D5" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E5" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F5" s="25" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="35">
         <f>DATE(2026,2,17)</f>
         <v>46070</v>
       </c>
-      <c r="B5" s="36" t="str">
-        <f>TEXT($A5,"ddd")</f>
+      <c r="B6" s="36" t="str">
+        <f>TEXT($A6,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C6" s="37" t="s">
         <v>485</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D6" s="37" t="s">
         <v>486</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E6" s="39" t="s">
         <v>469</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F6" s="25" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="12">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="12">
         <f>DATE(2026,2,18)</f>
         <v>46071</v>
       </c>
-      <c r="B6" s="13" t="str">
-        <f>TEXT($A6,"ddd")</f>
+      <c r="B7" s="13" t="str">
+        <f>TEXT($A7,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C7" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D7" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E7" s="38" t="s">
         <v>469</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F7" s="25" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="31">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="31">
         <f>DATE(2026,2,26)</f>
         <v>46079</v>
       </c>
-      <c r="B7" s="32" t="str">
+      <c r="B8" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C8" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D8" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E8" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F8" s="25" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="12">
         <f>DATE(2026,2,27)</f>
         <v>46080</v>
       </c>
-      <c r="B8" s="13" t="str">
+      <c r="B9" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C9" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D9" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F9" s="25" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="12">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="12">
         <f>DATE(2026,3,7)</f>
         <v>46088</v>
       </c>
-      <c r="B9" s="13" t="str">
+      <c r="B10" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C10" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D10" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F10" s="25" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="35">
         <f>DATE(2026,3,20)</f>
         <v>46101</v>
       </c>
-      <c r="B10" s="36" t="str">
+      <c r="B11" s="36" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C11" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D11" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E11" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F11" s="25" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="12">
         <f>DATE(2026,3,21)</f>
         <v>46102</v>
       </c>
-      <c r="B11" s="13" t="str">
-        <f>TEXT($A11,"ddd")</f>
+      <c r="B12" s="13" t="str">
+        <f>TEXT($A12,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>483</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="E11" s="38" t="s">
+      <c r="C12" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="E12" s="38" t="s">
         <v>480</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F12" s="25" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="31">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="12">
+        <f>DATE(2026,3,21)</f>
+        <v>46102</v>
+      </c>
+      <c r="B13" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>576</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>578</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="31">
         <f>DATE(2026,3,23)</f>
         <v>46104</v>
       </c>
-      <c r="B12" s="32" t="str">
+      <c r="B14" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C14" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D14" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E14" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F14" s="25" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="12">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="12">
         <f>DATE(2026,3,24)</f>
         <v>46105</v>
       </c>
-      <c r="B13" s="13" t="str">
+      <c r="B15" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D15" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E15" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F15" s="25" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="35">
         <f>DATE(2026,3,27)</f>
         <v>46108</v>
       </c>
-      <c r="B14" s="36" t="str">
+      <c r="B16" s="36" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C16" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D16" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E16" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F16" s="25" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="12">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="12">
         <f>DATE(2026,4,3)</f>
         <v>46115</v>
-      </c>
-      <c r="B15" s="13" t="str">
-        <f>TEXT($A15,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>481</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>482</v>
-      </c>
-      <c r="E15" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="41">
-        <f>DATE(2026,4,20)</f>
-        <v>46132</v>
-      </c>
-      <c r="B16" s="42" t="str">
-        <f t="shared" si="0"/>
-        <v>Mon</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="12">
-        <f>DATE(2026,5,1)</f>
-        <v>46143</v>
       </c>
       <c r="B17" s="13" t="str">
         <f>TEXT($A17,"ddd")</f>
         <v>Fri</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E17" s="38" t="s">
         <v>469</v>
       </c>
       <c r="F17" s="25" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="41">
+        <f>DATE(2026,4,20)</f>
+        <v>46132</v>
+      </c>
+      <c r="B18" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="12">
+        <f>DATE(2026,5,1)</f>
+        <v>46143</v>
+      </c>
+      <c r="B19" s="13" t="str">
+        <f>TEXT($A19,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>469</v>
+      </c>
+      <c r="F19" s="25" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="31">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="31">
         <f>DATE(2026,5,4)</f>
         <v>46146</v>
       </c>
-      <c r="B18" s="32" t="str">
+      <c r="B20" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C20" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D20" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="E18" s="33" t="s">
+      <c r="E20" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F20" s="25" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="12">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="12">
         <f>DATE(2026,5,15)</f>
         <v>46157</v>
       </c>
-      <c r="B19" s="13" t="str">
+      <c r="B21" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C21" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D21" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E21" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="F21" s="25" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="12">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="12">
         <f>DATE(2026,5,24)</f>
         <v>46166</v>
       </c>
-      <c r="B20" s="13" t="str">
+      <c r="B22" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C22" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D22" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="F22" s="25" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="35">
         <f>DATE(2026,5,25)</f>
         <v>46167</v>
       </c>
-      <c r="B21" s="36" t="str">
+      <c r="B23" s="36" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C23" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D23" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="E23" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F23" s="25" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="12">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="12">
         <f>DATE(2026,5,27)</f>
         <v>46169</v>
       </c>
-      <c r="B22" s="13" t="str">
-        <f>TEXT($A22,"ddd")</f>
+      <c r="B24" s="13" t="str">
+        <f>TEXT($A24,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C24" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D24" s="11" t="s">
         <v>514</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E24" s="38" t="s">
         <v>480</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F24" s="25" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="31">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="31">
         <f>DATE(2026,5,29)</f>
         <v>46171</v>
       </c>
-      <c r="B23" s="32" t="str">
+      <c r="B25" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C25" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="D23" s="33" t="s">
+      <c r="D25" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="E23" s="33" t="s">
+      <c r="E25" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F25" s="25" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="35">
         <f>DATE(2026,5,30)</f>
         <v>46172</v>
       </c>
-      <c r="B24" s="36" t="str">
+      <c r="B26" s="36" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C26" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D26" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="E24" s="37" t="s">
+      <c r="E26" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F26" s="25" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="35">
         <f>DATE(2026,5,31)</f>
         <v>46173</v>
       </c>
-      <c r="B25" s="36" t="str">
-        <f>TEXT($A25,"ddd")</f>
+      <c r="B27" s="36" t="str">
+        <f>TEXT($A27,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C27" s="37" t="s">
         <v>474</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D27" s="37" t="s">
         <v>475</v>
       </c>
-      <c r="E25" s="39" t="s">
+      <c r="E27" s="39" t="s">
         <v>469</v>
       </c>
-      <c r="F25" s="25" t="s">
+      <c r="F27" s="25" t="s">
         <v>505</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="12">
-        <f>DATE(2026,6,1)</f>
-        <v>46174</v>
-      </c>
-      <c r="B26" s="13" t="str">
-        <f>TEXT($A26,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>498</v>
-      </c>
-      <c r="E26" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="31">
-        <f>DATE(2026,5,31)</f>
-        <v>46173</v>
-      </c>
-      <c r="B27" s="32" t="str">
-        <f t="shared" si="0"/>
-        <v>Sun</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3135,2092 +3169,2180 @@
         <v>46174</v>
       </c>
       <c r="B28" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT($A28,"ddd")</f>
         <v>Mon</v>
       </c>
       <c r="C28" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>469</v>
+      </c>
+      <c r="F28" s="25" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="31">
+        <f>DATE(2026,5,31)</f>
+        <v>46173</v>
+      </c>
+      <c r="B29" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="12">
+        <f>DATE(2026,6,1)</f>
+        <v>46174</v>
+      </c>
+      <c r="B30" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D30" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F28" s="25" t="s">
+      <c r="F30" s="25" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="12">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="12">
         <f>DATE(2026,6,12)</f>
         <v>46185</v>
       </c>
-      <c r="B29" s="13" t="str">
+      <c r="B31" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C31" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E31" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="F31" s="25" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="12">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="12">
         <f>DATE(2026,6,13)</f>
         <v>46186</v>
       </c>
-      <c r="B30" s="13" t="str">
+      <c r="B32" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C32" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D32" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E32" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F30" s="25" t="s">
+      <c r="F32" s="25" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="12">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="12">
         <f>DATE(2026,6,20)</f>
         <v>46193</v>
       </c>
-      <c r="B31" s="13" t="str">
+      <c r="B33" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C33" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D33" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E33" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F31" s="25" t="s">
+      <c r="F33" s="25" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="12">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="12">
         <f>DATE(2026,7,3)</f>
         <v>46206</v>
       </c>
-      <c r="B32" s="13" t="str">
+      <c r="B34" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C34" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D34" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E34" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F32" s="25" t="s">
+      <c r="F34" s="25" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="12">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="12">
+        <f>DATE(2026,7,6)</f>
+        <v>46209</v>
+      </c>
+      <c r="B35" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>569</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>568</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
       </c>
-      <c r="B33" s="13" t="str">
+      <c r="B36" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C36" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D36" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E36" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F33" s="25" t="s">
+      <c r="F36" s="25" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="12">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
       </c>
-      <c r="B34" s="13" t="str">
+      <c r="B37" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C37" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D37" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E37" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F34" s="25" t="s">
+      <c r="F37" s="25" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="12">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="12">
         <f>DATE(2026,7,25)</f>
         <v>46228</v>
       </c>
-      <c r="B35" s="13" t="str">
+      <c r="B38" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C38" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D38" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E38" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F35" s="25" t="s">
+      <c r="F38" s="25" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="12">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="12">
         <f>DATE(2026,8,1)</f>
         <v>46235</v>
       </c>
-      <c r="B36" s="13" t="str">
+      <c r="B39" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C39" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D39" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E39" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F36" s="25" t="s">
+      <c r="F39" s="25" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="12">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="12">
         <f>DATE(2026,8,5)</f>
         <v>46239</v>
       </c>
-      <c r="B37" s="13" t="str">
-        <f t="shared" ref="B37:B52" si="1">TEXT($A37,"ddd")</f>
+      <c r="B40" s="13" t="str">
+        <f t="shared" ref="B40:B55" si="1">TEXT($A40,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C40" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D40" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E40" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F37" s="25" t="s">
+      <c r="F40" s="25" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="35">
         <f>DATE(2026,8,8)</f>
         <v>46242</v>
       </c>
-      <c r="B38" s="36" t="str">
+      <c r="B41" s="36" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C38" s="37" t="s">
+      <c r="C41" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="D38" s="40" t="s">
+      <c r="D41" s="40" t="s">
         <v>221</v>
       </c>
-      <c r="E38" s="37" t="s">
+      <c r="E41" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F38" s="25" t="s">
+      <c r="F41" s="25" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="35">
         <f>DATE(2026,8,9)</f>
         <v>46243</v>
       </c>
-      <c r="B39" s="36" t="str">
-        <f>TEXT($A39,"ddd")</f>
+      <c r="B42" s="36" t="str">
+        <f>TEXT($A42,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C42" s="37" t="s">
         <v>472</v>
       </c>
-      <c r="D39" s="37" t="s">
+      <c r="D42" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="E39" s="39" t="s">
+      <c r="E42" s="39" t="s">
         <v>469</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F42" s="25" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="12">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="12">
         <f>DATE(2026,8,10)</f>
         <v>46244</v>
       </c>
-      <c r="B40" s="13" t="str">
-        <f>TEXT($A40,"ddd")</f>
+      <c r="B43" s="13" t="str">
+        <f>TEXT($A43,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C43" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D43" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="E40" s="38" t="s">
+      <c r="E43" s="38" t="s">
         <v>469</v>
       </c>
-      <c r="F40" s="25" t="s">
+      <c r="F43" s="25" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="31">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="31">
         <f>DATE(2026,8,14)</f>
         <v>46248</v>
       </c>
-      <c r="B41" s="32" t="str">
+      <c r="B44" s="32" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
-      <c r="C41" s="33" t="s">
+      <c r="C44" s="33" t="s">
         <v>523</v>
       </c>
-      <c r="D41" s="43" t="s">
+      <c r="D44" s="43" t="s">
         <v>524</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E44" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="25" t="s">
+      <c r="F44" s="25" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="12">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
         <f>DATE(2026,8,15)</f>
         <v>46249</v>
       </c>
-      <c r="B42" s="13" t="str">
+      <c r="B45" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C45" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D45" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E45" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="F42" s="25" t="s">
+      <c r="F45" s="25" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
         <f>DATE(2026,8,19)</f>
         <v>46253</v>
       </c>
-      <c r="B43" s="13" t="str">
+      <c r="B46" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Wed</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C46" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D46" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E46" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F43" s="25" t="s">
+      <c r="F46" s="25" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2026,8,23)</f>
         <v>46257</v>
       </c>
-      <c r="B44" s="13" t="str">
+      <c r="B47" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sun</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C47" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D47" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E47" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F44" s="25" t="s">
+      <c r="F47" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
         <f>DATE(2026,8,28)</f>
         <v>46262</v>
       </c>
-      <c r="B45" s="13" t="str">
-        <f>TEXT($A45,"ddd")</f>
+      <c r="B48" s="13" t="str">
+        <f>TEXT($A48,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C48" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D48" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E48" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F45" s="25" t="s">
+      <c r="F48" s="25" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="F46" s="25" t="s">
+      <c r="F49" s="25" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="12">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
       </c>
-      <c r="B47" s="13" t="str">
+      <c r="B50" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C50" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D50" s="11" t="s">
         <v>458</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E50" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F47" s="25" t="s">
+      <c r="F50" s="25" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="12">
         <f>DATE(2026,8,31)</f>
         <v>46265</v>
       </c>
-      <c r="B48" s="13" t="str">
-        <f>TEXT($A48,"ddd")</f>
+      <c r="B51" s="13" t="str">
+        <f>TEXT($A51,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C51" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D51" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E51" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F48" s="25" t="s">
+      <c r="F51" s="25" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="B49" s="13" t="str">
+      <c r="B52" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C52" s="11" t="s">
         <v>554</v>
       </c>
-      <c r="D49" s="21"/>
-      <c r="E49" s="11" t="s">
+      <c r="D52" s="21"/>
+      <c r="E52" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="F49" s="25" t="s">
+      <c r="F52" s="25" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="B50" s="13" t="str">
+      <c r="B53" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C53" s="11" t="s">
         <v>525</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D53" s="16" t="s">
         <v>526</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E53" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F50" s="25" t="s">
+      <c r="F53" s="25" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
       </c>
-      <c r="B51" s="13" t="str">
+      <c r="B54" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C54" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D54" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E54" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F51" s="25" t="s">
+      <c r="F54" s="25" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
       </c>
-      <c r="B52" s="13" t="str">
+      <c r="B55" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C55" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D55" s="16" t="s">
         <v>528</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E55" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F52" s="25" t="s">
+      <c r="F55" s="25" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
         <f>DATE(2026,9,4)</f>
         <v>46269</v>
       </c>
-      <c r="B53" s="13" t="str">
-        <f>TEXT($A53,"ddd")</f>
+      <c r="B56" s="13" t="str">
+        <f>TEXT($A56,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C56" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D56" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E56" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F53" s="25" t="s">
+      <c r="F56" s="25" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="12">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="12">
         <f>DATE(2026,9,4)</f>
         <v>46269</v>
       </c>
-      <c r="B54" s="13" t="str">
-        <f>TEXT($A54,"ddd")</f>
+      <c r="B57" s="13" t="str">
+        <f>TEXT($A57,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C57" s="11" t="s">
         <v>530</v>
       </c>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11" t="s">
+      <c r="D57" s="11"/>
+      <c r="E57" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="F54" s="25" t="s">
+      <c r="F57" s="25" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" s="12">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
       </c>
-      <c r="B55" s="13" t="str">
+      <c r="B58" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C58" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D58" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F55" s="25" t="s">
+      <c r="F58" s="25" t="s">
         <v>433</v>
       </c>
-      <c r="G55" s="19"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
+      <c r="G58" s="19"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
       </c>
-      <c r="B56" s="13" t="str">
+      <c r="B59" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C59" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11" t="s">
+      <c r="D59" s="11"/>
+      <c r="E59" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="F56" s="25" t="s">
+      <c r="F59" s="25" t="s">
         <v>540</v>
       </c>
-      <c r="G56" s="19"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
+      <c r="G59" s="19"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="12">
         <f>DATE(2026,9,7)</f>
         <v>46272</v>
       </c>
-      <c r="B57" s="13" t="str">
-        <f>TEXT($A57,"ddd")</f>
+      <c r="B60" s="13" t="str">
+        <f>TEXT($A60,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C60" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="D57" s="16" t="s">
+      <c r="D60" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E60" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F57" s="25" t="s">
+      <c r="F60" s="25" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="12">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="12">
         <f>DATE(2026,9,8)</f>
         <v>46273</v>
       </c>
-      <c r="B58" s="13" t="str">
-        <f>TEXT($A58,"ddd")</f>
+      <c r="B61" s="13" t="str">
+        <f>TEXT($A61,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C61" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="D58" s="16" t="s">
+      <c r="D61" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E61" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F58" s="25" t="s">
+      <c r="F61" s="25" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="12">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="12">
         <f>DATE(2026,9,8)</f>
         <v>46273</v>
       </c>
-      <c r="B59" s="13" t="str">
-        <f>TEXT($A59,"ddd")</f>
+      <c r="B62" s="13" t="str">
+        <f>TEXT($A62,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C62" s="11" t="s">
         <v>542</v>
-      </c>
-      <c r="D59" s="16"/>
-      <c r="E59" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="F59" s="25" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="12">
-        <f>DATE(2026,9,9)</f>
-        <v>46274</v>
-      </c>
-      <c r="B60" s="13" t="str">
-        <f>TEXT($A60,"ddd")</f>
-        <v>Wed</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>561</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>562</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="F60" s="25" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="12">
-        <f>DATE(2026,9,9)</f>
-        <v>46274</v>
-      </c>
-      <c r="B61" s="13" t="str">
-        <f>TEXT($A61,"ddd")</f>
-        <v>Wed</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>552</v>
-      </c>
-      <c r="D61" s="16"/>
-      <c r="E61" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F61" s="25" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
-        <f>DATE(2026,9,15)</f>
-        <v>46280</v>
-      </c>
-      <c r="B62" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Tue</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>248</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="11" t="s">
         <v>240</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>436</v>
+        <v>543</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="12">
-        <f>DATE(2026,9,16)</f>
-        <v>46281</v>
+        <f>DATE(2026,9,9)</f>
+        <v>46274</v>
       </c>
       <c r="B63" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT($A63,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C63" s="11" t="s">
-        <v>230</v>
+      <c r="C63" s="16" t="s">
+        <v>561</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>229</v>
+        <v>562</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>121</v>
+        <v>232</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
-        <f>DATE(2026,9,16)</f>
-        <v>46281</v>
+        <f>DATE(2026,9,9)</f>
+        <v>46274</v>
       </c>
       <c r="B64" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT($A64,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C64" s="11" t="s">
-        <v>555</v>
+      <c r="C64" s="16" t="s">
+        <v>552</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>556</v>
+        <v>519</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
+        <f>DATE(2026,9,15)</f>
+        <v>46280</v>
+      </c>
+      <c r="B65" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D65" s="16"/>
+      <c r="E65" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F65" s="25" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="12">
+        <f>DATE(2026,9,16)</f>
+        <v>46281</v>
+      </c>
+      <c r="B66" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F66" s="25" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="12">
+        <f>DATE(2026,9,16)</f>
+        <v>46281</v>
+      </c>
+      <c r="B67" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>555</v>
+      </c>
+      <c r="D67" s="16"/>
+      <c r="E67" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F67" s="25" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="12">
         <f>DATE(2026,9,17)</f>
         <v>46282</v>
       </c>
-      <c r="B65" s="13" t="str">
+      <c r="B68" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C68" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11" t="s">
+      <c r="D68" s="11"/>
+      <c r="E68" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F65" s="25" t="s">
+      <c r="F68" s="25" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" s="12">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="12">
         <f>DATE(2026,9,18)</f>
         <v>46283</v>
       </c>
-      <c r="B66" s="13" t="str">
+      <c r="B69" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C69" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11" t="s">
+      <c r="D69" s="11"/>
+      <c r="E69" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="F66" s="25" t="s">
+      <c r="F69" s="25" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="12">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="12">
         <f>DATE(2026,9,18)</f>
         <v>46283</v>
       </c>
-      <c r="B67" s="13" t="str">
+      <c r="B70" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C70" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11" t="s">
+      <c r="D70" s="11"/>
+      <c r="E70" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F67" s="25" t="s">
+      <c r="F70" s="25" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="12">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="12">
         <f>DATE(2026,9,19)</f>
         <v>46284</v>
       </c>
-      <c r="B68" s="13" t="str">
+      <c r="B71" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C71" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D71" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E71" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F68" s="25" t="s">
+      <c r="F71" s="25" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69" s="12">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="12">
         <f>DATE(2026,9,19)</f>
         <v>46284</v>
       </c>
-      <c r="B69" s="13" t="str">
+      <c r="B72" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C72" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D72" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E72" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F69" s="25" t="s">
+      <c r="F72" s="25" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="12">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="12">
         <f>DATE(2026,9,20)</f>
         <v>46285</v>
       </c>
-      <c r="B70" s="13" t="str">
+      <c r="B73" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C73" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D73" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E73" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F70" s="25" t="s">
+      <c r="F73" s="25" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" s="12">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="12">
         <f>DATE(2026,9,23)</f>
         <v>46288</v>
       </c>
-      <c r="B71" s="13" t="str">
+      <c r="B74" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C74" s="11" t="s">
         <v>557</v>
       </c>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11" t="s">
+      <c r="D74" s="11"/>
+      <c r="E74" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F71" s="25" t="s">
+      <c r="F74" s="25" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" s="12">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="12">
         <f>DATE(2026,9,23)</f>
         <v>46288</v>
       </c>
-      <c r="B72" s="13" t="str">
+      <c r="B75" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C75" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11" t="s">
+      <c r="D75" s="11"/>
+      <c r="E75" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F72" s="25" t="s">
+      <c r="F75" s="25" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="12">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="12">
         <f>DATE(2026,9,25)</f>
         <v>46290</v>
       </c>
-      <c r="B73" s="13" t="str">
+      <c r="B76" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C76" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11" t="s">
+      <c r="D76" s="11"/>
+      <c r="E76" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="F73" s="25" t="s">
+      <c r="F76" s="25" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="12">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
       </c>
-      <c r="B74" s="13" t="str">
+      <c r="B77" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C77" s="11" t="s">
         <v>536</v>
       </c>
-      <c r="D74" s="11" t="s">
+      <c r="D77" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E77" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F74" s="25" t="s">
+      <c r="F77" s="25" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="51" x14ac:dyDescent="0.35">
-      <c r="A75" s="12">
+    <row r="78" spans="1:6" ht="51" x14ac:dyDescent="0.35">
+      <c r="A78" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
       </c>
-      <c r="B75" s="13" t="str">
+      <c r="B78" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C75" s="20" t="s">
+      <c r="C78" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D78" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E78" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="F75" s="25" t="s">
+      <c r="F78" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" s="12">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
-      <c r="B76" s="13" t="str">
+      <c r="B79" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C79" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D79" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E79" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F76" s="25" t="s">
+      <c r="F79" s="25" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="12">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B77" s="13" t="str">
+      <c r="B80" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C80" s="11" t="s">
         <v>549</v>
       </c>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11" t="s">
+      <c r="D80" s="11"/>
+      <c r="E80" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F77" s="25" t="s">
+      <c r="F80" s="25" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" s="12">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B78" s="13" t="str">
+      <c r="B81" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C81" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="D78" s="11" t="s">
+      <c r="D81" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E81" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F78" s="25" t="s">
+      <c r="F81" s="25" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="12">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B79" s="13" t="str">
+      <c r="B82" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C82" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="D82" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E82" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F79" s="25" t="s">
+      <c r="F82" s="25" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="12">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B80" s="13" t="str">
+      <c r="B83" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C83" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="D80" s="11" t="s">
+      <c r="D83" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E83" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F80" s="25" t="s">
+      <c r="F83" s="25" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A81" s="12">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="12">
         <f>DATE(2026,10,15)</f>
         <v>46310</v>
       </c>
-      <c r="B81" s="13" t="str">
+      <c r="B84" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="C81" s="37" t="s">
+      <c r="C84" s="37" t="s">
         <v>550</v>
       </c>
-      <c r="D81" s="37"/>
-      <c r="E81" s="37" t="s">
+      <c r="D84" s="37"/>
+      <c r="E84" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="F81" s="25" t="s">
+      <c r="F84" s="25" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" s="35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="12">
+        <f>DATE(2026,10,20)</f>
+        <v>46315</v>
+      </c>
+      <c r="B85" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>571</v>
+      </c>
+      <c r="D85" s="25" t="s">
+        <v>572</v>
+      </c>
+      <c r="E85" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F85" s="25" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="35">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
       </c>
-      <c r="B82" s="36" t="str">
-        <f t="shared" ref="B82:B122" si="2">TEXT($A82,"ddd")</f>
+      <c r="B86" s="36" t="str">
+        <f t="shared" ref="B86:B126" si="2">TEXT($A86,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C82" s="40" t="s">
+      <c r="C86" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="D82" s="37" t="s">
+      <c r="D86" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="E82" s="37" t="s">
+      <c r="E86" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F82" s="25" t="s">
+      <c r="F86" s="25" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" s="35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="35">
         <f>DATE(2026,11,8)</f>
         <v>46334</v>
       </c>
-      <c r="B83" s="36" t="str">
-        <f>TEXT($A83,"ddd")</f>
+      <c r="B87" s="36" t="str">
+        <f>TEXT($A87,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C83" s="37" t="s">
+      <c r="C87" s="37" t="s">
         <v>470</v>
       </c>
-      <c r="D83" s="37" t="s">
+      <c r="D87" s="37" t="s">
         <v>471</v>
       </c>
-      <c r="E83" s="39" t="s">
+      <c r="E87" s="39" t="s">
         <v>469</v>
       </c>
-      <c r="F83" s="25" t="s">
+      <c r="F87" s="25" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="12">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="12">
         <f>DATE(2026,11,9)</f>
         <v>46335</v>
       </c>
-      <c r="B84" s="13" t="str">
-        <f>TEXT($A84,"ddd")</f>
+      <c r="B88" s="13" t="str">
+        <f>TEXT($A88,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C88" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="D84" s="11" t="s">
+      <c r="D88" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="E84" s="38" t="s">
+      <c r="E88" s="38" t="s">
         <v>469</v>
       </c>
-      <c r="F84" s="25" t="s">
+      <c r="F88" s="25" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="31">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="31">
         <f>DATE(2026,11,10)</f>
         <v>46336</v>
       </c>
-      <c r="B85" s="32" t="str">
+      <c r="B89" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C85" s="43" t="s">
+      <c r="C89" s="43" t="s">
         <v>463</v>
       </c>
-      <c r="D85" s="33" t="s">
+      <c r="D89" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E85" s="33" t="s">
+      <c r="E89" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F85" s="25" t="s">
+      <c r="F89" s="25" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="12">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="12">
         <f>DATE(2026,11,24)</f>
         <v>46350</v>
       </c>
-      <c r="B86" s="13" t="str">
+      <c r="B90" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C86" s="16" t="s">
+      <c r="C90" s="16" t="s">
         <v>538</v>
       </c>
-      <c r="D86" s="11" t="s">
+      <c r="D90" s="11" t="s">
         <v>539</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E90" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F86" s="25" t="s">
+      <c r="F90" s="25" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="35">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B87" s="36" t="str">
+      <c r="B91" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C87" s="40" t="s">
+      <c r="C91" s="40" t="s">
         <v>462</v>
       </c>
-      <c r="D87" s="40" t="s">
+      <c r="D91" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="E87" s="37" t="s">
+      <c r="E91" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F87" s="25" t="s">
+      <c r="F91" s="25" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="35">
         <f>DATE(2026,12,25)</f>
         <v>46381</v>
       </c>
-      <c r="B88" s="36" t="str">
-        <f>TEXT($A88,"ddd")</f>
+      <c r="B92" s="36" t="str">
+        <f>TEXT($A92,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C88" s="37" t="s">
+      <c r="C92" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="D88" s="37" t="s">
+      <c r="D92" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="E88" s="39" t="s">
+      <c r="E92" s="39" t="s">
         <v>469</v>
       </c>
-      <c r="F88" s="25" t="s">
+      <c r="F92" s="25" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="12">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B89" s="13" t="str">
-        <f>TEXT($A89,"ddd")</f>
+      <c r="B93" s="13" t="str">
+        <f>TEXT($A93,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C93" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D93" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="E89" s="38" t="s">
+      <c r="E93" s="38" t="s">
         <v>469</v>
       </c>
-      <c r="F89" s="25" t="s">
+      <c r="F93" s="25" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="31">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="31">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B90" s="32" t="str">
+      <c r="B94" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C90" s="43" t="s">
+      <c r="C94" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="D90" s="33" t="s">
+      <c r="D94" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="E90" s="33" t="s">
+      <c r="E94" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F90" s="25" t="s">
+      <c r="F94" s="25" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="35">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B91" s="36" t="str">
+      <c r="B95" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C91" s="37" t="s">
+      <c r="C95" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D91" s="37" t="s">
+      <c r="D95" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="E91" s="37" t="s">
+      <c r="E95" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F91" s="25" t="s">
+      <c r="F95" s="25" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="35">
         <f>DATE(2027,2,6)</f>
         <v>46424</v>
       </c>
-      <c r="B92" s="36" t="str">
-        <f>TEXT($A92,"ddd")</f>
+      <c r="B96" s="36" t="str">
+        <f>TEXT($A96,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C92" s="37" t="s">
+      <c r="C96" s="37" t="s">
         <v>485</v>
       </c>
-      <c r="D92" s="37" t="s">
+      <c r="D96" s="37" t="s">
         <v>486</v>
       </c>
-      <c r="E92" s="39" t="s">
+      <c r="E96" s="39" t="s">
         <v>469</v>
       </c>
-      <c r="F92" s="25" t="s">
+      <c r="F96" s="25" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="35">
         <f>DATE(2027,2,7)</f>
         <v>46425</v>
       </c>
-      <c r="B93" s="36" t="str">
-        <f>TEXT($A93,"ddd")</f>
+      <c r="B97" s="36" t="str">
+        <f>TEXT($A97,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C93" s="37" t="s">
+      <c r="C97" s="37" t="s">
         <v>487</v>
       </c>
-      <c r="D93" s="37" t="s">
+      <c r="D97" s="37" t="s">
         <v>488</v>
       </c>
-      <c r="E93" s="39" t="s">
+      <c r="E97" s="39" t="s">
         <v>469</v>
       </c>
-      <c r="F93" s="25" t="s">
+      <c r="F97" s="25" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="12">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B94" s="13" t="str">
-        <f>TEXT($A94,"ddd")</f>
+      <c r="B98" s="13" t="str">
+        <f>TEXT($A98,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C98" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D98" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="E94" s="38" t="s">
+      <c r="E98" s="38" t="s">
         <v>469</v>
       </c>
-      <c r="F94" s="25" t="s">
+      <c r="F98" s="25" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="41">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B95" s="42" t="str">
+      <c r="B99" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C95" s="25" t="s">
+      <c r="C99" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="D95" s="25" t="s">
+      <c r="D99" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="E95" s="25" t="s">
+      <c r="E99" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="F95" s="26" t="s">
+      <c r="F99" s="26" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="12">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="12">
         <f>DATE(2027,3,10)</f>
         <v>46456</v>
       </c>
-      <c r="B96" s="13" t="str">
-        <f>TEXT($A96,"ddd")</f>
+      <c r="B100" s="13" t="str">
+        <f>TEXT($A100,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C96" s="11" t="s">
+      <c r="C100" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="D96" s="11" t="s">
+      <c r="D100" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="E96" s="38" t="s">
+      <c r="E100" s="38" t="s">
         <v>480</v>
       </c>
-      <c r="F96" s="25" t="s">
+      <c r="F100" s="25" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="31">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="31">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B97" s="32" t="str">
+      <c r="B101" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C97" s="33" t="s">
+      <c r="C101" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="D97" s="33" t="s">
+      <c r="D101" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="E97" s="33" t="s">
+      <c r="E101" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F97" s="26" t="s">
+      <c r="F101" s="26" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="35">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B98" s="36" t="str">
+      <c r="B102" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C98" s="37" t="s">
+      <c r="C102" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="D98" s="37" t="s">
+      <c r="D102" s="37" t="s">
         <v>210</v>
       </c>
-      <c r="E98" s="37" t="s">
+      <c r="E102" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F98" s="26" t="s">
+      <c r="F102" s="26" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="12">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="12">
         <f>DATE(2027,3,26)</f>
         <v>46472</v>
       </c>
-      <c r="B99" s="13" t="str">
-        <f>TEXT($A99,"ddd")</f>
+      <c r="B103" s="13" t="str">
+        <f>TEXT($A103,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C99" s="11" t="s">
+      <c r="C103" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D99" s="11" t="s">
+      <c r="D103" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="E99" s="38" t="s">
+      <c r="E103" s="38" t="s">
         <v>469</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="F103" s="25" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="31">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="31">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B100" s="32" t="str">
+      <c r="B104" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C100" s="43" t="s">
+      <c r="C104" s="43" t="s">
         <v>222</v>
       </c>
-      <c r="D100" s="33" t="s">
+      <c r="D104" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="E100" s="33" t="s">
+      <c r="E104" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="F100" s="26" t="s">
+      <c r="F104" s="26" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="35">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B101" s="36" t="str">
+      <c r="B105" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C101" s="37" t="s">
+      <c r="C105" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="D101" s="37" t="s">
+      <c r="D105" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="E101" s="37" t="s">
+      <c r="E105" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F101" s="26" t="s">
+      <c r="F105" s="26" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="35">
         <f>DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="B102" s="36" t="str">
-        <f>TEXT($A102,"ddd")</f>
+      <c r="B106" s="36" t="str">
+        <f>TEXT($A106,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C102" s="37" t="s">
+      <c r="C106" s="37" t="s">
         <v>476</v>
       </c>
-      <c r="D102" s="37" t="s">
+      <c r="D106" s="37" t="s">
         <v>477</v>
       </c>
-      <c r="E102" s="39" t="s">
+      <c r="E106" s="39" t="s">
         <v>469</v>
       </c>
-      <c r="F102" s="25" t="s">
+      <c r="F106" s="25" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="12">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="12">
         <f>DATE(2027,5,17)</f>
         <v>46524</v>
       </c>
-      <c r="B103" s="13" t="str">
-        <f>TEXT($A103,"ddd")</f>
+      <c r="B107" s="13" t="str">
+        <f>TEXT($A107,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C107" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="D103" s="11" t="s">
+      <c r="D107" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="E103" s="38" t="s">
+      <c r="E107" s="38" t="s">
         <v>480</v>
       </c>
-      <c r="F103" s="25" t="s">
+      <c r="F107" s="25" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="41">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="41">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B104" s="42" t="str">
+      <c r="B108" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C104" s="25" t="s">
+      <c r="C108" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="D104" s="25" t="s">
+      <c r="D108" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="E104" s="25" t="s">
+      <c r="E108" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="F104" s="26" t="s">
+      <c r="F108" s="26" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="12">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B105" s="13" t="str">
-        <f>TEXT($A105,"ddd")</f>
+      <c r="B109" s="13" t="str">
+        <f>TEXT($A109,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C109" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="D105" s="11" t="s">
+      <c r="D109" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="E105" s="38" t="s">
+      <c r="E109" s="38" t="s">
         <v>469</v>
       </c>
-      <c r="F105" s="25" t="s">
+      <c r="F109" s="25" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="31">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="31">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B106" s="32" t="str">
+      <c r="B110" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C106" s="33" t="s">
+      <c r="C110" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="D106" s="33" t="s">
+      <c r="D110" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="E106" s="33" t="s">
+      <c r="E110" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="F106" s="26" t="s">
+      <c r="F110" s="26" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="12">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
       </c>
-      <c r="B107" s="13" t="str">
+      <c r="B111" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C111" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D107" s="11" t="s">
+      <c r="D111" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E107" s="11" t="s">
+      <c r="E111" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F107" s="26" t="s">
+      <c r="F111" s="26" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="12">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="12">
         <f>DATE(2027,5,28)</f>
         <v>46535</v>
       </c>
-      <c r="B108" s="13" t="str">
+      <c r="B112" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C112" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="D108" s="11" t="s">
+      <c r="D112" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="E108" s="11" t="s">
+      <c r="E112" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F108" s="26" t="s">
+      <c r="F112" s="26" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="12">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="12">
         <f>DATE(2027,6,11)</f>
         <v>46549</v>
       </c>
-      <c r="B109" s="13" t="str">
+      <c r="B113" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C113" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="D109" s="11" t="s">
+      <c r="D113" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="E109" s="11" t="s">
+      <c r="E113" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F109" s="26" t="s">
+      <c r="F113" s="26" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="12">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="12">
         <f>DATE(2027,7,9)</f>
         <v>46577</v>
-      </c>
-      <c r="B110" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C110" s="16" t="s">
-        <v>454</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>455</v>
-      </c>
-      <c r="E110" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F110" s="25" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="35">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
-      </c>
-      <c r="B111" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C111" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="D111" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="E111" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F111" s="26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="12">
-        <f>DATE(2027,8,9)</f>
-        <v>46608</v>
-      </c>
-      <c r="B112" s="13" t="str">
-        <f>TEXT($A112,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C112" s="11" t="s">
-        <v>472</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>473</v>
-      </c>
-      <c r="E112" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F112" s="25" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="31">
-        <f>DATE(2027,8,16)</f>
-        <v>46615</v>
-      </c>
-      <c r="B113" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Mon</v>
-      </c>
-      <c r="C113" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="D113" s="33" t="s">
-        <v>217</v>
-      </c>
-      <c r="E113" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="F113" s="26" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="12">
-        <f>DATE(2027,8,20)</f>
-        <v>46619</v>
       </c>
       <c r="B114" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C114" s="11" t="s">
-        <v>177</v>
+      <c r="C114" s="16" t="s">
+        <v>454</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>218</v>
+        <v>455</v>
       </c>
       <c r="E114" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F114" s="26" t="s">
+      <c r="F114" s="25" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="35">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B115" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C115" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="D115" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="E115" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="F115" s="26" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="12">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="12">
+        <f>DATE(2027,8,9)</f>
+        <v>46608</v>
+      </c>
+      <c r="B116" s="13" t="str">
+        <f>TEXT($A116,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="E116" s="38" t="s">
+        <v>469</v>
+      </c>
+      <c r="F116" s="25" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="31">
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
+      </c>
+      <c r="B117" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C117" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D117" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="E117" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F117" s="26" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="12">
+        <f>DATE(2027,8,20)</f>
+        <v>46619</v>
+      </c>
+      <c r="B118" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F118" s="26" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
       </c>
-      <c r="B115" s="13" t="str">
+      <c r="B119" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C119" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="D115" s="11" t="s">
+      <c r="D119" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="E115" s="11" t="s">
+      <c r="E119" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F115" s="26" t="s">
+      <c r="F119" s="26" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="12">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B116" s="13" t="str">
+      <c r="B120" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C120" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D116" s="11" t="s">
+      <c r="D120" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="E116" s="11" t="s">
+      <c r="E120" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F116" s="26" t="s">
+      <c r="F120" s="26" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="12">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
-      </c>
-      <c r="B117" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="E117" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F117" s="26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="35">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
-      </c>
-      <c r="B118" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C118" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="D118" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="E118" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="12">
-        <f>DATE(2027,10,28)</f>
-        <v>46688</v>
-      </c>
-      <c r="B119" s="13" t="str">
-        <f>TEXT($A119,"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>470</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="E119" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F119" s="25" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="31">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
-      </c>
-      <c r="B120" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C120" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="D120" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="E120" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="F120" s="26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
       </c>
       <c r="B121" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C121" s="16" t="s">
-        <v>454</v>
+      <c r="C121" s="11" t="s">
+        <v>169</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>455</v>
+        <v>209</v>
       </c>
       <c r="E121" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F121" s="25" t="s">
-        <v>456</v>
+      <c r="F121" s="26" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="35">
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
+      </c>
+      <c r="B122" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C122" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="D122" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="E122" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="12">
+        <f>DATE(2027,10,28)</f>
+        <v>46688</v>
+      </c>
+      <c r="B123" s="13" t="str">
+        <f>TEXT($A123,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="E123" s="38" t="s">
+        <v>469</v>
+      </c>
+      <c r="F123" s="25" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="31">
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
+      </c>
+      <c r="B124" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C124" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="D124" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="E124" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="F124" s="26" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B125" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C125" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="E125" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F125" s="25" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B122" s="36" t="str">
+      <c r="B126" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C122" s="37" t="s">
+      <c r="C126" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="D122" s="40" t="s">
+      <c r="D126" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="E122" s="37" t="s">
+      <c r="E126" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F122" s="26" t="s">
+      <c r="F126" s="26" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="12">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B123" s="13" t="str">
-        <f>TEXT($A123,"ddd")</f>
+      <c r="B127" s="13" t="str">
+        <f>TEXT($A127,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C127" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="D123" s="11" t="s">
+      <c r="D127" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="E123" s="38" t="s">
+      <c r="E127" s="38" t="s">
         <v>469</v>
       </c>
-      <c r="F123" s="25" t="s">
+      <c r="F127" s="25" t="s">
         <v>511</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E123" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E127" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="D48" r:id="rId1" xr:uid="{DF6FA8D1-34EA-46D0-A461-22B2F51DB446}"/>
+    <hyperlink ref="D51" r:id="rId1" xr:uid="{DF6FA8D1-34EA-46D0-A461-22B2F51DB446}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7282,7 +7404,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7307,12 +7429,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7557,20 +7681,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7596,14 +7723,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1785" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{423A2AAE-749C-441A-9ABF-9BC9616783CF}"/>
+  <xr:revisionPtr revIDLastSave="1787" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21B379F9-8161-47BE-88FD-C715BB34FFC2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$126</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="577">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -788,9 +788,6 @@
     <t>南凤福利协会 Nam Hong Welfare Service Society · For committee members reference 仅供理事参考</t>
   </si>
   <si>
-    <t>Charity Governance Conference 2026. 9.30am to 3.30pm. Raffles City Convention Centre. Conference 9.30am - 12pm, Workshop 2pm - 3.30pm. (Attendees: GMO staff)</t>
-  </si>
-  <si>
     <t>Lunar July (ZhongYuan Festival) - 7 Gambas Crescent, ARK@Gambas Level 2 (Representative: Doran, Pei Yuen, Chi Hwee, Agnes - all to arrive by 7pm)</t>
   </si>
   <si>
@@ -1352,9 +1349,6 @@
     <t>中元会 - Blk 838</t>
   </si>
   <si>
-    <t>Charity Conference</t>
-  </si>
-  <si>
     <t>North West District Meeting</t>
   </si>
   <si>
@@ -1694,9 +1688,6 @@
     <t>Microsoft AI forum, 8am-5pm (Representative: Jin Hoa)</t>
   </si>
   <si>
-    <t>Charity Governance Conference 2026, 9am-5pm, Raffles City Convention Centre (Representative: Jin Hoa, Kathy)</t>
-  </si>
-  <si>
     <t>Charity Governance Conference 2026</t>
   </si>
   <si>
@@ -1779,6 +1770,9 @@
   </si>
   <si>
     <t>第九届理事会第十次会议</t>
+  </si>
+  <si>
+    <t>Charity Governance Conference 2026. 9.30am to 3.30pm. Raffles City Convention Centre. Conference 9.30am - 12pm, Workshop 2pm - 3.30pm. (Representative: Jin Hoa, Kathy)</t>
   </si>
 </sst>
 </file>
@@ -2561,7 +2555,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -2588,7 +2582,7 @@
         <v>134</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2601,16 +2595,16 @@
         <v>Thu</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2619,7 +2613,7 @@
         <v>46023</v>
       </c>
       <c r="B3" s="32" t="str">
-        <f t="shared" ref="B3:B85" si="0">TEXT($A3,"ddd")</f>
+        <f t="shared" ref="B3:B84" si="0">TEXT($A3,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C3" s="33" t="s">
@@ -2632,7 +2626,7 @@
         <v>124</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2645,16 +2639,16 @@
         <v>Sun</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2676,7 +2670,7 @@
         <v>121</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2689,16 +2683,16 @@
         <v>Tue</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2711,16 +2705,16 @@
         <v>Wed</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2742,7 +2736,7 @@
         <v>131</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2764,7 +2758,7 @@
         <v>121</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2786,7 +2780,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2808,7 +2802,7 @@
         <v>124</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2821,16 +2815,16 @@
         <v>Sat</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2843,16 +2837,16 @@
         <v>Sat</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2874,7 +2868,7 @@
         <v>121</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2896,7 +2890,7 @@
         <v>121</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2918,7 +2912,7 @@
         <v>121</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2931,16 +2925,16 @@
         <v>Fri</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2962,7 +2956,7 @@
         <v>129</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -2975,16 +2969,16 @@
         <v>Fri</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -3006,7 +3000,7 @@
         <v>129</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3028,7 +3022,7 @@
         <v>131</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3050,7 +3044,7 @@
         <v>129</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -3072,7 +3066,7 @@
         <v>121</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -3085,16 +3079,16 @@
         <v>Wed</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -3116,7 +3110,7 @@
         <v>232</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -3138,7 +3132,7 @@
         <v>232</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -3151,16 +3145,16 @@
         <v>Sun</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3173,16 +3167,16 @@
         <v>Mon</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -3204,7 +3198,7 @@
         <v>232</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -3226,7 +3220,7 @@
         <v>232</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -3248,7 +3242,7 @@
         <v>121</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -3270,7 +3264,7 @@
         <v>121</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -3292,7 +3286,7 @@
         <v>121</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -3314,7 +3308,7 @@
         <v>124</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -3327,16 +3321,16 @@
         <v>Mon</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -3358,7 +3352,7 @@
         <v>124</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3380,7 +3374,7 @@
         <v>121</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3402,7 +3396,7 @@
         <v>121</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3424,7 +3418,7 @@
         <v>124</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3446,7 +3440,7 @@
         <v>121</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -3468,7 +3462,7 @@
         <v>232</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3481,16 +3475,16 @@
         <v>Sun</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3503,16 +3497,16 @@
         <v>Mon</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3525,16 +3519,16 @@
         <v>Fri</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E44" s="33" t="s">
         <v>232</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3550,13 +3544,13 @@
         <v>237</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>240</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3569,16 +3563,16 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="D46" s="16" t="s">
         <v>451</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>453</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3591,16 +3585,16 @@
         <v>Sun</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>232</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3613,7 +3607,7 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>162</v>
@@ -3622,7 +3616,7 @@
         <v>124</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3635,16 +3629,16 @@
         <v>Sat</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>240</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -3657,16 +3651,16 @@
         <v>Sat</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>232</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3679,16 +3673,16 @@
         <v>Mon</v>
       </c>
       <c r="C51" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D51" s="21" t="s">
         <v>249</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>250</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>232</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3701,14 +3695,14 @@
         <v>Tue</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="11" t="s">
         <v>240</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3721,16 +3715,16 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>232</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -3752,7 +3746,7 @@
         <v>232</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3765,16 +3759,16 @@
         <v>Thu</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>232</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3787,16 +3781,16 @@
         <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>232</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3809,14 +3803,14 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="11" t="s">
         <v>240</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3829,7 +3823,7 @@
         <v>Sat</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>163</v>
@@ -3838,7 +3832,7 @@
         <v>124</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G58" s="19"/>
     </row>
@@ -3852,14 +3846,14 @@
         <v>Sat</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11" t="s">
         <v>240</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G59" s="19"/>
     </row>
@@ -3873,16 +3867,16 @@
         <v>Mon</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>232</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3895,7 +3889,7 @@
         <v>Tue</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D61" s="16" t="s">
         <v>228</v>
@@ -3904,7 +3898,7 @@
         <v>232</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3917,14 +3911,14 @@
         <v>Tue</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="11" t="s">
         <v>240</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3937,16 +3931,16 @@
         <v>Wed</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>232</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3959,34 +3953,36 @@
         <v>Wed</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
-        <f>DATE(2026,9,15)</f>
-        <v>46280</v>
+        <f>DATE(2026,9,16)</f>
+        <v>46281</v>
       </c>
       <c r="B65" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Tue</v>
+        <v>Wed</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="D65" s="16"/>
+        <v>230</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>229</v>
+      </c>
       <c r="E65" s="11" t="s">
-        <v>240</v>
+        <v>121</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>436</v>
+        <v>411</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -3999,56 +3995,54 @@
         <v>Wed</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="D66" s="16" t="s">
-        <v>229</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="D66" s="16"/>
       <c r="E66" s="11" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>412</v>
+        <v>553</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
-        <f>DATE(2026,9,16)</f>
-        <v>46281</v>
+        <f>DATE(2026,9,17)</f>
+        <v>46282</v>
       </c>
       <c r="B67" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>555</v>
-      </c>
-      <c r="D67" s="16"/>
+        <v>542</v>
+      </c>
+      <c r="D67" s="11"/>
       <c r="E67" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>556</v>
+        <v>529</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
-        <f>DATE(2026,9,17)</f>
-        <v>46282</v>
+        <f>DATE(2026,9,18)</f>
+        <v>46283</v>
       </c>
       <c r="B68" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thu</v>
+        <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>544</v>
+        <v>239</v>
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="11" t="s">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="F68" s="25" t="s">
-        <v>531</v>
+        <v>435</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4061,34 +4055,36 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>239</v>
+        <v>515</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11" t="s">
-        <v>240</v>
+        <v>131</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>437</v>
+        <v>516</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
-        <f>DATE(2026,9,18)</f>
-        <v>46283</v>
+        <f>DATE(2026,9,19)</f>
+        <v>46284</v>
       </c>
       <c r="B70" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="D70" s="11"/>
+        <v>518</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>520</v>
+      </c>
       <c r="E70" s="11" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -4101,60 +4097,58 @@
         <v>Sat</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="12">
-        <f>DATE(2026,9,19)</f>
-        <v>46284</v>
+        <f>DATE(2026,9,20)</f>
+        <v>46285</v>
       </c>
       <c r="B72" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Sun</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>533</v>
+        <v>164</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="12">
-        <f>DATE(2026,9,20)</f>
-        <v>46285</v>
+        <f>DATE(2026,9,23)</f>
+        <v>46288</v>
       </c>
       <c r="B73" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Sun</v>
+        <v>Wed</v>
       </c>
       <c r="C73" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F73" s="25" t="s">
         <v>545</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F73" s="25" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -4167,57 +4161,59 @@
         <v>Wed</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
-        <f>DATE(2026,9,23)</f>
-        <v>46288</v>
+        <f>DATE(2026,9,25)</f>
+        <v>46290</v>
       </c>
       <c r="B75" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="11" t="s">
-        <v>129</v>
+        <v>563</v>
       </c>
       <c r="F75" s="25" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
-        <f>DATE(2026,9,25)</f>
-        <v>46290</v>
+        <f>DATE(2026,10,9)</f>
+        <v>46304</v>
       </c>
       <c r="B76" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="D76" s="11"/>
+        <v>534</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>535</v>
+      </c>
       <c r="E76" s="11" t="s">
-        <v>566</v>
+        <v>124</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="51" x14ac:dyDescent="0.35">
       <c r="A77" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
@@ -4226,61 +4222,59 @@
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C77" s="11" t="s">
-        <v>536</v>
+      <c r="C77" s="20" t="s">
+        <v>242</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>537</v>
+        <v>241</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>124</v>
+        <v>240</v>
       </c>
       <c r="F77" s="25" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="12">
+        <f>DATE(2026,10,10)</f>
+        <v>46305</v>
+      </c>
+      <c r="B78" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F78" s="25" t="s">
         <v>438</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="51" x14ac:dyDescent="0.35">
-      <c r="A78" s="12">
-        <f>DATE(2026,10,9)</f>
-        <v>46304</v>
-      </c>
-      <c r="B78" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Fri</v>
-      </c>
-      <c r="C78" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="D78" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="F78" s="25" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="12">
-        <f>DATE(2026,10,10)</f>
-        <v>46305</v>
+        <f>DATE(2026,10,12)</f>
+        <v>46307</v>
       </c>
       <c r="B79" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Mon</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>461</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>252</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="D79" s="11"/>
       <c r="E79" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>440</v>
+        <v>546</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -4293,1050 +4287,1030 @@
         <v>Mon</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="D80" s="11"/>
+        <v>196</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>201</v>
+      </c>
       <c r="E80" s="11" t="s">
-        <v>129</v>
+        <v>232</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>548</v>
+        <v>439</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="12">
-        <f>DATE(2026,10,12)</f>
-        <v>46307</v>
+        <f>DATE(2026,10,13)</f>
+        <v>46308</v>
       </c>
       <c r="B81" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>232</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="12">
-        <f>DATE(2026,10,13)</f>
-        <v>46308</v>
+        <f>DATE(2026,10,14)</f>
+        <v>46309</v>
       </c>
       <c r="B82" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Tue</v>
+        <v>Wed</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E82" s="11" t="s">
         <v>232</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="12">
-        <f>DATE(2026,10,14)</f>
-        <v>46309</v>
+        <f>DATE(2026,10,15)</f>
+        <v>46310</v>
       </c>
       <c r="B83" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="D83" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="E83" s="11" t="s">
-        <v>232</v>
+        <v>Thu</v>
+      </c>
+      <c r="C83" s="40" t="s">
+        <v>576</v>
+      </c>
+      <c r="D83" s="37"/>
+      <c r="E83" s="37" t="s">
+        <v>240</v>
       </c>
       <c r="F83" s="25" t="s">
-        <v>441</v>
+        <v>548</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="12">
-        <f>DATE(2026,10,15)</f>
-        <v>46310</v>
-      </c>
-      <c r="B84" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Thu</v>
-      </c>
-      <c r="C84" s="37" t="s">
-        <v>550</v>
-      </c>
-      <c r="D84" s="37"/>
-      <c r="E84" s="37" t="s">
-        <v>240</v>
-      </c>
-      <c r="F84" s="25" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="12">
         <f>DATE(2026,10,20)</f>
         <v>46315</v>
       </c>
-      <c r="B85" s="42" t="str">
+      <c r="B84" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C85" s="25" t="s">
-        <v>571</v>
-      </c>
-      <c r="D85" s="25" t="s">
-        <v>572</v>
-      </c>
-      <c r="E85" s="25" t="s">
+      <c r="C84" s="25" t="s">
+        <v>568</v>
+      </c>
+      <c r="D84" s="25" t="s">
+        <v>569</v>
+      </c>
+      <c r="E84" s="25" t="s">
         <v>129</v>
       </c>
+      <c r="F84" s="25" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="35">
+        <f>DATE(2026,11,3)</f>
+        <v>46329</v>
+      </c>
+      <c r="B85" s="36" t="str">
+        <f t="shared" ref="B85:B125" si="2">TEXT($A85,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C85" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="D85" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E85" s="37" t="s">
+        <v>121</v>
+      </c>
       <c r="F85" s="25" t="s">
-        <v>570</v>
+        <v>441</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="35">
-        <f>DATE(2026,11,3)</f>
-        <v>46329</v>
-      </c>
-      <c r="B86" s="36" t="str">
-        <f t="shared" ref="B86:B126" si="2">TEXT($A86,"ddd")</f>
-        <v>Tue</v>
-      </c>
-      <c r="C86" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="D86" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="E86" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F86" s="25" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="35">
         <f>DATE(2026,11,8)</f>
         <v>46334</v>
       </c>
-      <c r="B87" s="36" t="str">
-        <f>TEXT($A87,"ddd")</f>
+      <c r="B86" s="36" t="str">
+        <f>TEXT($A86,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C87" s="37" t="s">
-        <v>470</v>
-      </c>
-      <c r="D87" s="37" t="s">
-        <v>471</v>
-      </c>
-      <c r="E87" s="39" t="s">
+      <c r="C86" s="37" t="s">
+        <v>468</v>
+      </c>
+      <c r="D86" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="F87" s="25" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="12">
+      <c r="E86" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="F86" s="25" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="12">
         <f>DATE(2026,11,9)</f>
         <v>46335</v>
       </c>
-      <c r="B88" s="13" t="str">
-        <f>TEXT($A88,"ddd")</f>
+      <c r="B87" s="13" t="str">
+        <f>TEXT($A87,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C88" s="11" t="s">
-        <v>493</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="E88" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F88" s="25" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="31">
+      <c r="C87" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="E87" s="38" t="s">
+        <v>467</v>
+      </c>
+      <c r="F87" s="25" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="31">
         <f>DATE(2026,11,10)</f>
         <v>46336</v>
       </c>
-      <c r="B89" s="32" t="str">
+      <c r="B88" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C89" s="43" t="s">
-        <v>463</v>
-      </c>
-      <c r="D89" s="33" t="s">
+      <c r="C88" s="43" t="s">
+        <v>461</v>
+      </c>
+      <c r="D88" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E89" s="33" t="s">
+      <c r="E88" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F89" s="25" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="12">
+      <c r="F88" s="25" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="12">
         <f>DATE(2026,11,24)</f>
         <v>46350</v>
       </c>
-      <c r="B90" s="13" t="str">
+      <c r="B89" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C90" s="16" t="s">
-        <v>538</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>539</v>
-      </c>
-      <c r="E90" s="11" t="s">
+      <c r="C89" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>537</v>
+      </c>
+      <c r="E89" s="11" t="s">
         <v>124</v>
       </c>
+      <c r="F89" s="25" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="35">
+        <f>DATE(2026,12,16)</f>
+        <v>46372</v>
+      </c>
+      <c r="B90" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Wed</v>
+      </c>
+      <c r="C90" s="40" t="s">
+        <v>460</v>
+      </c>
+      <c r="D90" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="E90" s="37" t="s">
+        <v>131</v>
+      </c>
       <c r="F90" s="25" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="35">
-        <f>DATE(2026,12,16)</f>
-        <v>46372</v>
+        <f>DATE(2026,12,25)</f>
+        <v>46381</v>
       </c>
       <c r="B91" s="36" t="str">
+        <f>TEXT($A91,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C91" s="37" t="s">
+        <v>465</v>
+      </c>
+      <c r="D91" s="37" t="s">
+        <v>466</v>
+      </c>
+      <c r="E91" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="F91" s="25" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="12">
+        <f>DATE(2027,1,1)</f>
+        <v>46388</v>
+      </c>
+      <c r="B92" s="13" t="str">
+        <f>TEXT($A92,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E92" s="38" t="s">
+        <v>467</v>
+      </c>
+      <c r="F92" s="25" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="31">
+        <f>DATE(2027,1,1)</f>
+        <v>46388</v>
+      </c>
+      <c r="B93" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C93" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="D93" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E93" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F93" s="25" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="35">
+        <f>DATE(2027,1,30)</f>
+        <v>46417</v>
+      </c>
+      <c r="B94" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="C94" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="D94" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="E94" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F94" s="25" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="35">
+        <f>DATE(2027,2,6)</f>
+        <v>46424</v>
+      </c>
+      <c r="B95" s="36" t="str">
+        <f>TEXT($A95,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C95" s="37" t="s">
+        <v>483</v>
+      </c>
+      <c r="D95" s="37" t="s">
+        <v>484</v>
+      </c>
+      <c r="E95" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="F95" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="35">
+        <f>DATE(2027,2,7)</f>
+        <v>46425</v>
+      </c>
+      <c r="B96" s="36" t="str">
+        <f>TEXT($A96,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C96" s="37" t="s">
+        <v>485</v>
+      </c>
+      <c r="D96" s="37" t="s">
+        <v>486</v>
+      </c>
+      <c r="E96" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="F96" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="12">
+        <f>DATE(2027,2,8)</f>
+        <v>46426</v>
+      </c>
+      <c r="B97" s="13" t="str">
+        <f>TEXT($A97,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="E97" s="38" t="s">
+        <v>467</v>
+      </c>
+      <c r="F97" s="25" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="41">
+        <f>DATE(2027,2,18)</f>
+        <v>46436</v>
+      </c>
+      <c r="B98" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C98" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="D98" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="E98" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="F98" s="26" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="12">
+        <f>DATE(2027,3,10)</f>
+        <v>46456</v>
+      </c>
+      <c r="B99" s="13" t="str">
+        <f>TEXT($A99,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="E99" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="F99" s="25" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="31">
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
+      </c>
+      <c r="B100" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C100" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="D100" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="E100" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="F100" s="26" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="35">
+        <f>DATE(2027,3,25)</f>
+        <v>46471</v>
+      </c>
+      <c r="B101" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C101" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="D101" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F101" s="26" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="12">
+        <f>DATE(2027,3,26)</f>
+        <v>46472</v>
+      </c>
+      <c r="B102" s="13" t="str">
+        <f>TEXT($A102,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="E102" s="38" t="s">
+        <v>467</v>
+      </c>
+      <c r="F102" s="25" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="31">
+        <f>DATE(2027,4,3)</f>
+        <v>46480</v>
+      </c>
+      <c r="B103" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="C103" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="D103" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E103" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="F103" s="26" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="35">
+        <f>DATE(2027,4,9)</f>
+        <v>46486</v>
+      </c>
+      <c r="B104" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C104" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="D104" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="E104" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="F104" s="26" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="35">
+        <f>DATE(2027,5,1)</f>
+        <v>46508</v>
+      </c>
+      <c r="B105" s="36" t="str">
+        <f>TEXT($A105,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C105" s="37" t="s">
+        <v>474</v>
+      </c>
+      <c r="D105" s="37" t="s">
+        <v>475</v>
+      </c>
+      <c r="E105" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="F105" s="25" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="12">
+        <f>DATE(2027,5,17)</f>
+        <v>46524</v>
+      </c>
+      <c r="B106" s="13" t="str">
+        <f>TEXT($A106,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="E106" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="F106" s="25" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="41">
+        <f>DATE(2027,5,19)</f>
+        <v>46526</v>
+      </c>
+      <c r="B107" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C91" s="40" t="s">
-        <v>462</v>
-      </c>
-      <c r="D91" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="E91" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="F91" s="25" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="35">
-        <f>DATE(2026,12,25)</f>
-        <v>46381</v>
-      </c>
-      <c r="B92" s="36" t="str">
-        <f>TEXT($A92,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C92" s="37" t="s">
+      <c r="C107" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="D107" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="E107" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="F107" s="26" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="12">
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
+      </c>
+      <c r="B108" s="13" t="str">
+        <f>TEXT($A108,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="E108" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="D92" s="37" t="s">
-        <v>468</v>
-      </c>
-      <c r="E92" s="39" t="s">
-        <v>469</v>
-      </c>
-      <c r="F92" s="25" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="12">
-        <f>DATE(2027,1,1)</f>
-        <v>46388</v>
-      </c>
-      <c r="B93" s="13" t="str">
-        <f>TEXT($A93,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>491</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="E93" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F93" s="25" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="31">
-        <f>DATE(2027,1,1)</f>
-        <v>46388</v>
-      </c>
-      <c r="B94" s="32" t="str">
+      <c r="F108" s="25" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="31">
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
+      </c>
+      <c r="B109" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C109" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="D109" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="E109" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F109" s="26" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="12">
+        <f>DATE(2027,5,21)</f>
+        <v>46528</v>
+      </c>
+      <c r="B110" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C94" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="D94" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E94" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="F94" s="25" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="35">
-        <f>DATE(2027,1,30)</f>
-        <v>46417</v>
-      </c>
-      <c r="B95" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C95" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="D95" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="E95" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F95" s="25" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="35">
-        <f>DATE(2027,2,6)</f>
-        <v>46424</v>
-      </c>
-      <c r="B96" s="36" t="str">
-        <f>TEXT($A96,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C96" s="37" t="s">
-        <v>485</v>
-      </c>
-      <c r="D96" s="37" t="s">
-        <v>486</v>
-      </c>
-      <c r="E96" s="39" t="s">
-        <v>469</v>
-      </c>
-      <c r="F96" s="25" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="35">
-        <f>DATE(2027,2,7)</f>
-        <v>46425</v>
-      </c>
-      <c r="B97" s="36" t="str">
-        <f>TEXT($A97,"ddd")</f>
-        <v>Sun</v>
-      </c>
-      <c r="C97" s="37" t="s">
-        <v>487</v>
-      </c>
-      <c r="D97" s="37" t="s">
-        <v>488</v>
-      </c>
-      <c r="E97" s="39" t="s">
-        <v>469</v>
-      </c>
-      <c r="F97" s="25" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="12">
-        <f>DATE(2027,2,8)</f>
-        <v>46426</v>
-      </c>
-      <c r="B98" s="13" t="str">
-        <f>TEXT($A98,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>489</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="E98" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F98" s="25" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="41">
-        <f>DATE(2027,2,18)</f>
-        <v>46436</v>
-      </c>
-      <c r="B99" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C99" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="D99" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="E99" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="F99" s="26" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="12">
-        <f>DATE(2027,3,10)</f>
-        <v>46456</v>
-      </c>
-      <c r="B100" s="13" t="str">
-        <f>TEXT($A100,"ddd")</f>
-        <v>Wed</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>483</v>
-      </c>
-      <c r="D100" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="E100" s="38" t="s">
-        <v>480</v>
-      </c>
-      <c r="F100" s="25" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="31">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
-      </c>
-      <c r="B101" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C101" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="D101" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="E101" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="F101" s="26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="35">
-        <f>DATE(2027,3,25)</f>
-        <v>46471</v>
-      </c>
-      <c r="B102" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C102" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="D102" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E102" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F102" s="26" t="s">
+      <c r="C110" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E110" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F110" s="26" t="s">
         <v>414</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="12">
-        <f>DATE(2027,3,26)</f>
-        <v>46472</v>
-      </c>
-      <c r="B103" s="13" t="str">
-        <f>TEXT($A103,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>481</v>
-      </c>
-      <c r="D103" s="11" t="s">
-        <v>482</v>
-      </c>
-      <c r="E103" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F103" s="25" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="31">
-        <f>DATE(2027,4,3)</f>
-        <v>46480</v>
-      </c>
-      <c r="B104" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C104" s="43" t="s">
-        <v>222</v>
-      </c>
-      <c r="D104" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="E104" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="F104" s="26" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="35">
-        <f>DATE(2027,4,9)</f>
-        <v>46486</v>
-      </c>
-      <c r="B105" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C105" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="D105" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="E105" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F105" s="26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="35">
-        <f>DATE(2027,5,1)</f>
-        <v>46508</v>
-      </c>
-      <c r="B106" s="36" t="str">
-        <f>TEXT($A106,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C106" s="37" t="s">
-        <v>476</v>
-      </c>
-      <c r="D106" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="E106" s="39" t="s">
-        <v>469</v>
-      </c>
-      <c r="F106" s="25" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="12">
-        <f>DATE(2027,5,17)</f>
-        <v>46524</v>
-      </c>
-      <c r="B107" s="13" t="str">
-        <f>TEXT($A107,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>478</v>
-      </c>
-      <c r="D107" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="E107" s="38" t="s">
-        <v>480</v>
-      </c>
-      <c r="F107" s="25" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="41">
-        <f>DATE(2027,5,19)</f>
-        <v>46526</v>
-      </c>
-      <c r="B108" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Wed</v>
-      </c>
-      <c r="C108" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="D108" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="E108" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="F108" s="26" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="12">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
-      </c>
-      <c r="B109" s="13" t="str">
-        <f>TEXT($A109,"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="C109" s="11" t="s">
-        <v>474</v>
-      </c>
-      <c r="D109" s="11" t="s">
-        <v>475</v>
-      </c>
-      <c r="E109" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F109" s="25" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="31">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
-      </c>
-      <c r="B110" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C110" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D110" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="E110" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="F110" s="26" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="12">
-        <f>DATE(2027,5,21)</f>
-        <v>46528</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B111" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>232</v>
+        <v>121</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>415</v>
+        <v>446</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B112" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>174</v>
+        <v>250</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B113" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C113" s="11" t="s">
-        <v>251</v>
+      <c r="C113" s="16" t="s">
+        <v>452</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>209</v>
+        <v>453</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F113" s="26" t="s">
-        <v>442</v>
+      <c r="F113" s="25" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
-      </c>
-      <c r="B114" s="13" t="str">
+      <c r="A114" s="35">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B114" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C114" s="16" t="s">
-        <v>454</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>455</v>
-      </c>
-      <c r="E114" s="11" t="s">
+      <c r="C114" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="D114" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="E114" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F114" s="25" t="s">
-        <v>456</v>
+      <c r="F114" s="26" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="35">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
-      </c>
-      <c r="B115" s="36" t="str">
+      <c r="A115" s="12">
+        <f>DATE(2027,8,9)</f>
+        <v>46608</v>
+      </c>
+      <c r="B115" s="13" t="str">
+        <f>TEXT($A115,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="E115" s="38" t="s">
+        <v>467</v>
+      </c>
+      <c r="F115" s="25" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="31">
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
+      </c>
+      <c r="B116" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C116" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D116" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="E116" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F116" s="26" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="12">
+        <f>DATE(2027,8,20)</f>
+        <v>46619</v>
+      </c>
+      <c r="B117" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C115" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="D115" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="E115" s="37" t="s">
+      <c r="C117" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E117" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F115" s="26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="12">
-        <f>DATE(2027,8,9)</f>
-        <v>46608</v>
-      </c>
-      <c r="B116" s="13" t="str">
-        <f>TEXT($A116,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>472</v>
-      </c>
-      <c r="D116" s="11" t="s">
-        <v>473</v>
-      </c>
-      <c r="E116" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F116" s="25" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="31">
-        <f>DATE(2027,8,16)</f>
-        <v>46615</v>
-      </c>
-      <c r="B117" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Mon</v>
-      </c>
-      <c r="C117" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="D117" s="33" t="s">
-        <v>217</v>
-      </c>
-      <c r="E117" s="33" t="s">
-        <v>232</v>
-      </c>
       <c r="F117" s="26" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="12">
-        <f>DATE(2027,8,20)</f>
-        <v>46619</v>
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
       </c>
       <c r="B118" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F118" s="26" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
       </c>
       <c r="B119" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
       </c>
       <c r="B120" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
+        <v>Fri</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F120" s="26" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
-      </c>
-      <c r="B121" s="13" t="str">
+      <c r="A121" s="35">
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
+      </c>
+      <c r="B121" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="C121" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="D121" s="11" t="s">
+      <c r="D121" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="E121" s="11" t="s">
+      <c r="E121" s="37" t="s">
         <v>124</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="35">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
-      </c>
-      <c r="B122" s="36" t="str">
+      <c r="A122" s="12">
+        <f>DATE(2027,10,28)</f>
+        <v>46688</v>
+      </c>
+      <c r="B122" s="13" t="str">
+        <f>TEXT($A122,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="E122" s="38" t="s">
+        <v>467</v>
+      </c>
+      <c r="F122" s="25" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="31">
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
+      </c>
+      <c r="B123" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C122" s="37" t="s">
+      <c r="C123" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="D122" s="37" t="s">
+      <c r="D123" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="E122" s="37" t="s">
+      <c r="E123" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F122" s="26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="12">
-        <f>DATE(2027,10,28)</f>
-        <v>46688</v>
-      </c>
-      <c r="B123" s="13" t="str">
-        <f>TEXT($A123,"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="C123" s="11" t="s">
-        <v>470</v>
-      </c>
-      <c r="D123" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="E123" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F123" s="25" t="s">
-        <v>509</v>
+      <c r="F123" s="26" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="31">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
-      </c>
-      <c r="B124" s="32" t="str">
+      <c r="A124" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B124" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C124" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="D124" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="E124" s="33" t="s">
+      <c r="C124" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="E124" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F124" s="26" t="s">
-        <v>442</v>
+      <c r="F124" s="25" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
-      </c>
-      <c r="B125" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C125" s="16" t="s">
-        <v>454</v>
-      </c>
-      <c r="D125" s="11" t="s">
-        <v>455</v>
-      </c>
-      <c r="E125" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F125" s="25" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="35">
+      <c r="A125" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B126" s="36" t="str">
+      <c r="B125" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C126" s="37" t="s">
+      <c r="C125" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="D126" s="40" t="s">
+      <c r="D125" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="E126" s="37" t="s">
+      <c r="E125" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F126" s="26" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="12">
+      <c r="F125" s="26" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B127" s="13" t="str">
-        <f>TEXT($A127,"ddd")</f>
+      <c r="B126" s="13" t="str">
+        <f>TEXT($A126,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C127" s="11" t="s">
+      <c r="C126" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="E126" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="D127" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="E127" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="F127" s="25" t="s">
-        <v>511</v>
+      <c r="F126" s="25" t="s">
+        <v>509</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E127" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E126" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -5559,7 +5533,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>96</v>
@@ -6260,7 +6234,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -6539,839 +6513,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" t="s">
         <v>254</v>
       </c>
-      <c r="C2" t="s">
-        <v>255</v>
-      </c>
       <c r="D2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E2" t="s">
         <v>350</v>
-      </c>
-      <c r="E2" t="s">
-        <v>351</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E3" t="s">
         <v>352</v>
-      </c>
-      <c r="E3" t="s">
-        <v>353</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D4" t="s">
+        <v>353</v>
+      </c>
+      <c r="E4" t="s">
         <v>354</v>
       </c>
-      <c r="E4" t="s">
-        <v>355</v>
-      </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D14" t="s">
+        <v>364</v>
+      </c>
+      <c r="E14" t="s">
         <v>365</v>
       </c>
-      <c r="E14" t="s">
-        <v>366</v>
-      </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
       <c r="G14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H14" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D15" t="s">
+        <v>364</v>
+      </c>
+      <c r="E15" t="s">
         <v>365</v>
       </c>
-      <c r="E15" t="s">
-        <v>366</v>
-      </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
       <c r="G15" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H15" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D16" t="s">
+        <v>364</v>
+      </c>
+      <c r="E16" t="s">
         <v>365</v>
       </c>
-      <c r="E16" t="s">
-        <v>366</v>
-      </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
       <c r="G16" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D17" t="s">
+        <v>364</v>
+      </c>
+      <c r="E17" t="s">
         <v>365</v>
       </c>
-      <c r="E17" t="s">
-        <v>366</v>
-      </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
       <c r="G17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B18" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C18" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D18" t="s">
+        <v>364</v>
+      </c>
+      <c r="E18" t="s">
         <v>365</v>
       </c>
-      <c r="E18" t="s">
-        <v>366</v>
-      </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
       <c r="G18" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H18" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D19" t="s">
+        <v>364</v>
+      </c>
+      <c r="E19" t="s">
         <v>365</v>
       </c>
-      <c r="E19" t="s">
-        <v>366</v>
-      </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
       <c r="G19" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H19" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D20" t="s">
+        <v>364</v>
+      </c>
+      <c r="E20" t="s">
         <v>365</v>
       </c>
-      <c r="E20" t="s">
-        <v>366</v>
-      </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
       <c r="G20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E21" t="s">
         <v>365</v>
       </c>
-      <c r="E21" t="s">
-        <v>366</v>
-      </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
       <c r="G21" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H21" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D22" t="s">
+        <v>364</v>
+      </c>
+      <c r="E22" t="s">
         <v>365</v>
       </c>
-      <c r="E22" t="s">
-        <v>366</v>
-      </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
       <c r="G22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H22" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B23" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C23" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D23" t="s">
+        <v>364</v>
+      </c>
+      <c r="E23" t="s">
         <v>365</v>
       </c>
-      <c r="E23" t="s">
-        <v>366</v>
-      </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
       <c r="G23" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H23" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B24" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C24" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D24" t="s">
+        <v>364</v>
+      </c>
+      <c r="E24" t="s">
         <v>365</v>
       </c>
-      <c r="E24" t="s">
-        <v>366</v>
-      </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
       <c r="G24" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B25" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C25" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D25" t="s">
+        <v>366</v>
+      </c>
+      <c r="E25" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="F25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geokchin.jpg</v>
+      </c>
+      <c r="G25" t="s">
+        <v>392</v>
+      </c>
+      <c r="H25" t="s">
         <v>368</v>
-      </c>
-      <c r="F25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geokchin.jpg</v>
-      </c>
-      <c r="G25" t="s">
-        <v>393</v>
-      </c>
-      <c r="H25" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C26" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D26" t="s">
+        <v>366</v>
+      </c>
+      <c r="E26" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laysiew.jpg</v>
+      </c>
+      <c r="G26" t="s">
+        <v>393</v>
+      </c>
+      <c r="H26" t="s">
         <v>368</v>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laysiew.jpg</v>
-      </c>
-      <c r="G26" t="s">
-        <v>394</v>
-      </c>
-      <c r="H26" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C27" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D27" t="s">
+        <v>366</v>
+      </c>
+      <c r="E27" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="F27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>waiyee.jpg</v>
+      </c>
+      <c r="G27" t="s">
+        <v>394</v>
+      </c>
+      <c r="H27" t="s">
         <v>368</v>
-      </c>
-      <c r="F27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>waiyee.jpg</v>
-      </c>
-      <c r="G27" t="s">
-        <v>395</v>
-      </c>
-      <c r="H27" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D28" t="s">
+        <v>366</v>
+      </c>
+      <c r="E28" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>carol.jpg</v>
+      </c>
+      <c r="G28" t="s">
+        <v>395</v>
+      </c>
+      <c r="H28" t="s">
         <v>368</v>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>carol.jpg</v>
-      </c>
-      <c r="G28" t="s">
-        <v>396</v>
-      </c>
-      <c r="H28" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D29" t="s">
+        <v>366</v>
+      </c>
+      <c r="E29" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="F29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yokewant.jpg</v>
+      </c>
+      <c r="G29" t="s">
+        <v>396</v>
+      </c>
+      <c r="H29" t="s">
         <v>368</v>
-      </c>
-      <c r="F29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>yokewant.jpg</v>
-      </c>
-      <c r="G29" t="s">
-        <v>397</v>
-      </c>
-      <c r="H29" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D30" t="s">
+        <v>366</v>
+      </c>
+      <c r="E30" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pohcheng.jpg</v>
+      </c>
+      <c r="G30" t="s">
+        <v>397</v>
+      </c>
+      <c r="H30" t="s">
         <v>368</v>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>pohcheng.jpg</v>
-      </c>
-      <c r="G30" t="s">
-        <v>398</v>
-      </c>
-      <c r="H30" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C31" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D31" t="s">
+        <v>366</v>
+      </c>
+      <c r="E31" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="F31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geoklan.jpg</v>
+      </c>
+      <c r="G31" t="s">
+        <v>398</v>
+      </c>
+      <c r="H31" t="s">
         <v>368</v>
-      </c>
-      <c r="F31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geoklan.jpg</v>
-      </c>
-      <c r="G31" t="s">
-        <v>399</v>
-      </c>
-      <c r="H31" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B32" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C32" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D32" t="s">
+        <v>366</v>
+      </c>
+      <c r="E32" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laichee.jpg</v>
+      </c>
+      <c r="G32" t="s">
+        <v>399</v>
+      </c>
+      <c r="H32" t="s">
         <v>368</v>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laichee.jpg</v>
-      </c>
-      <c r="G32" t="s">
-        <v>400</v>
-      </c>
-      <c r="H32" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C33" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D33" t="s">
+        <v>366</v>
+      </c>
+      <c r="E33" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="F33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>beechoo.jpg</v>
+      </c>
+      <c r="G33" t="s">
+        <v>400</v>
+      </c>
+      <c r="H33" t="s">
         <v>368</v>
-      </c>
-      <c r="F33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>beechoo.jpg</v>
-      </c>
-      <c r="G33" t="s">
-        <v>401</v>
-      </c>
-      <c r="H33" t="s">
-        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1787" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21B379F9-8161-47BE-88FD-C715BB34FFC2}"/>
+  <xr:revisionPtr revIDLastSave="1798" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{040DA775-9C1C-47FD-A5FD-B09E96F5486D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$128</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="579">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1773,6 +1773,12 @@
   </si>
   <si>
     <t>Charity Governance Conference 2026. 9.30am to 3.30pm. Raffles City Convention Centre. Conference 9.30am - 12pm, Workshop 2pm - 3.30pm. (Representative: Jin Hoa, Kathy)</t>
+  </si>
+  <si>
+    <t>Visit from temple</t>
+  </si>
+  <si>
+    <t>Visit from China temple (TCM operations and Caring Heart) (Representative: Lim Soi Tee, Jin Hoa)</t>
   </si>
 </sst>
 </file>
@@ -2555,7 +2561,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -2613,7 +2619,7 @@
         <v>46023</v>
       </c>
       <c r="B3" s="32" t="str">
-        <f t="shared" ref="B3:B84" si="0">TEXT($A3,"ddd")</f>
+        <f t="shared" ref="B3:B86" si="0">TEXT($A3,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C3" s="33" t="s">
@@ -4386,779 +4392,775 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="35">
+      <c r="A85" s="12">
+        <f>DATE(2026,10,26)</f>
+        <v>46321</v>
+      </c>
+      <c r="B85" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>578</v>
+      </c>
+      <c r="D85" s="25"/>
+      <c r="E85" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="F85" s="25" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="12">
+        <f>DATE(2026,10,27)</f>
+        <v>46322</v>
+      </c>
+      <c r="B86" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="C86" s="25" t="s">
+        <v>578</v>
+      </c>
+      <c r="D86" s="25"/>
+      <c r="E86" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="F86" s="25" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="35">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
       </c>
-      <c r="B85" s="36" t="str">
-        <f t="shared" ref="B85:B125" si="2">TEXT($A85,"ddd")</f>
+      <c r="B87" s="36" t="str">
+        <f t="shared" ref="B87:B127" si="2">TEXT($A87,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C85" s="40" t="s">
+      <c r="C87" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="D85" s="37" t="s">
+      <c r="D87" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="E85" s="37" t="s">
+      <c r="E87" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F85" s="25" t="s">
+      <c r="F87" s="25" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="35">
         <f>DATE(2026,11,8)</f>
         <v>46334</v>
       </c>
-      <c r="B86" s="36" t="str">
-        <f>TEXT($A86,"ddd")</f>
+      <c r="B88" s="36" t="str">
+        <f>TEXT($A88,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C86" s="37" t="s">
+      <c r="C88" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="D86" s="37" t="s">
+      <c r="D88" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="E86" s="39" t="s">
+      <c r="E88" s="39" t="s">
         <v>467</v>
       </c>
-      <c r="F86" s="25" t="s">
+      <c r="F88" s="25" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="12">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="12">
         <f>DATE(2026,11,9)</f>
         <v>46335</v>
       </c>
-      <c r="B87" s="13" t="str">
-        <f>TEXT($A87,"ddd")</f>
+      <c r="B89" s="13" t="str">
+        <f>TEXT($A89,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C89" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D87" s="11" t="s">
+      <c r="D89" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="E87" s="38" t="s">
+      <c r="E89" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="F87" s="25" t="s">
+      <c r="F89" s="25" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="31">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="31">
         <f>DATE(2026,11,10)</f>
         <v>46336</v>
       </c>
-      <c r="B88" s="32" t="str">
+      <c r="B90" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C88" s="43" t="s">
+      <c r="C90" s="43" t="s">
         <v>461</v>
       </c>
-      <c r="D88" s="33" t="s">
+      <c r="D90" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E88" s="33" t="s">
+      <c r="E90" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F88" s="25" t="s">
+      <c r="F90" s="25" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="12">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="12">
         <f>DATE(2026,11,24)</f>
         <v>46350</v>
       </c>
-      <c r="B89" s="13" t="str">
+      <c r="B91" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C89" s="16" t="s">
+      <c r="C91" s="16" t="s">
         <v>536</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D91" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E91" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F89" s="25" t="s">
+      <c r="F91" s="25" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="35">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B90" s="36" t="str">
+      <c r="B92" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C90" s="40" t="s">
+      <c r="C92" s="40" t="s">
         <v>460</v>
       </c>
-      <c r="D90" s="40" t="s">
+      <c r="D92" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="E90" s="37" t="s">
+      <c r="E92" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F90" s="25" t="s">
+      <c r="F92" s="25" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="35">
         <f>DATE(2026,12,25)</f>
         <v>46381</v>
       </c>
-      <c r="B91" s="36" t="str">
-        <f>TEXT($A91,"ddd")</f>
+      <c r="B93" s="36" t="str">
+        <f>TEXT($A93,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C91" s="37" t="s">
+      <c r="C93" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="D91" s="37" t="s">
+      <c r="D93" s="37" t="s">
         <v>466</v>
       </c>
-      <c r="E91" s="39" t="s">
+      <c r="E93" s="39" t="s">
         <v>467</v>
       </c>
-      <c r="F91" s="25" t="s">
+      <c r="F93" s="25" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="12">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B92" s="13" t="str">
-        <f>TEXT($A92,"ddd")</f>
+      <c r="B94" s="13" t="str">
+        <f>TEXT($A94,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C94" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D94" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="E92" s="38" t="s">
+      <c r="E94" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="F92" s="25" t="s">
+      <c r="F94" s="25" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="31">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="31">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B93" s="32" t="str">
+      <c r="B95" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C93" s="43" t="s">
+      <c r="C95" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="D93" s="33" t="s">
+      <c r="D95" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="E93" s="33" t="s">
+      <c r="E95" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F93" s="25" t="s">
+      <c r="F95" s="25" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="35">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B94" s="36" t="str">
+      <c r="B96" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C94" s="37" t="s">
+      <c r="C96" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D94" s="37" t="s">
+      <c r="D96" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="E94" s="37" t="s">
+      <c r="E96" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F94" s="25" t="s">
+      <c r="F96" s="25" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="35">
         <f>DATE(2027,2,6)</f>
         <v>46424</v>
       </c>
-      <c r="B95" s="36" t="str">
-        <f>TEXT($A95,"ddd")</f>
+      <c r="B97" s="36" t="str">
+        <f>TEXT($A97,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C95" s="37" t="s">
+      <c r="C97" s="37" t="s">
         <v>483</v>
       </c>
-      <c r="D95" s="37" t="s">
+      <c r="D97" s="37" t="s">
         <v>484</v>
       </c>
-      <c r="E95" s="39" t="s">
+      <c r="E97" s="39" t="s">
         <v>467</v>
       </c>
-      <c r="F95" s="25" t="s">
+      <c r="F97" s="25" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="35">
         <f>DATE(2027,2,7)</f>
         <v>46425</v>
       </c>
-      <c r="B96" s="36" t="str">
-        <f>TEXT($A96,"ddd")</f>
+      <c r="B98" s="36" t="str">
+        <f>TEXT($A98,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C96" s="37" t="s">
+      <c r="C98" s="37" t="s">
         <v>485</v>
       </c>
-      <c r="D96" s="37" t="s">
+      <c r="D98" s="37" t="s">
         <v>486</v>
       </c>
-      <c r="E96" s="39" t="s">
+      <c r="E98" s="39" t="s">
         <v>467</v>
       </c>
-      <c r="F96" s="25" t="s">
+      <c r="F98" s="25" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="12">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B97" s="13" t="str">
-        <f>TEXT($A97,"ddd")</f>
+      <c r="B99" s="13" t="str">
+        <f>TEXT($A99,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C99" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D99" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="E97" s="38" t="s">
+      <c r="E99" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="F97" s="25" t="s">
+      <c r="F99" s="25" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="41">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B98" s="42" t="str">
+      <c r="B100" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C98" s="25" t="s">
+      <c r="C100" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="D98" s="25" t="s">
+      <c r="D100" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="E98" s="25" t="s">
+      <c r="E100" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="F98" s="26" t="s">
+      <c r="F100" s="26" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="12">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="12">
         <f>DATE(2027,3,10)</f>
         <v>46456</v>
       </c>
-      <c r="B99" s="13" t="str">
-        <f>TEXT($A99,"ddd")</f>
+      <c r="B101" s="13" t="str">
+        <f>TEXT($A101,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C99" s="11" t="s">
+      <c r="C101" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D99" s="11" t="s">
+      <c r="D101" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="E99" s="38" t="s">
+      <c r="E101" s="38" t="s">
         <v>478</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="F101" s="25" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="31">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="31">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B100" s="32" t="str">
+      <c r="B102" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C100" s="33" t="s">
+      <c r="C102" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="D100" s="33" t="s">
+      <c r="D102" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="E100" s="33" t="s">
+      <c r="E102" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F100" s="26" t="s">
+      <c r="F102" s="26" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="35">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B101" s="36" t="str">
+      <c r="B103" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C101" s="37" t="s">
+      <c r="C103" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="D101" s="37" t="s">
+      <c r="D103" s="37" t="s">
         <v>210</v>
       </c>
-      <c r="E101" s="37" t="s">
+      <c r="E103" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F101" s="26" t="s">
+      <c r="F103" s="26" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="12">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="12">
         <f>DATE(2027,3,26)</f>
         <v>46472</v>
       </c>
-      <c r="B102" s="13" t="str">
-        <f>TEXT($A102,"ddd")</f>
+      <c r="B104" s="13" t="str">
+        <f>TEXT($A104,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C102" s="11" t="s">
+      <c r="C104" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="D102" s="11" t="s">
+      <c r="D104" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="E102" s="38" t="s">
+      <c r="E104" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="F102" s="25" t="s">
+      <c r="F104" s="25" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="31">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="31">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B103" s="32" t="str">
+      <c r="B105" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C103" s="43" t="s">
+      <c r="C105" s="43" t="s">
         <v>222</v>
       </c>
-      <c r="D103" s="33" t="s">
+      <c r="D105" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="E103" s="33" t="s">
+      <c r="E105" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="F103" s="26" t="s">
+      <c r="F105" s="26" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="35">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B104" s="36" t="str">
+      <c r="B106" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C104" s="37" t="s">
+      <c r="C106" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="D104" s="37" t="s">
+      <c r="D106" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="E104" s="37" t="s">
+      <c r="E106" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F104" s="26" t="s">
+      <c r="F106" s="26" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="35">
         <f>DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="B105" s="36" t="str">
-        <f>TEXT($A105,"ddd")</f>
+      <c r="B107" s="36" t="str">
+        <f>TEXT($A107,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C105" s="37" t="s">
+      <c r="C107" s="37" t="s">
         <v>474</v>
       </c>
-      <c r="D105" s="37" t="s">
+      <c r="D107" s="37" t="s">
         <v>475</v>
       </c>
-      <c r="E105" s="39" t="s">
+      <c r="E107" s="39" t="s">
         <v>467</v>
       </c>
-      <c r="F105" s="25" t="s">
+      <c r="F107" s="25" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="12">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="12">
         <f>DATE(2027,5,17)</f>
         <v>46524</v>
       </c>
-      <c r="B106" s="13" t="str">
-        <f>TEXT($A106,"ddd")</f>
+      <c r="B108" s="13" t="str">
+        <f>TEXT($A108,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C106" s="11" t="s">
+      <c r="C108" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="D106" s="11" t="s">
+      <c r="D108" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="E106" s="38" t="s">
+      <c r="E108" s="38" t="s">
         <v>478</v>
       </c>
-      <c r="F106" s="25" t="s">
+      <c r="F108" s="25" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="41">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="41">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B107" s="42" t="str">
+      <c r="B109" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C107" s="25" t="s">
+      <c r="C109" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="D107" s="25" t="s">
+      <c r="D109" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="E107" s="25" t="s">
+      <c r="E109" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="F107" s="26" t="s">
+      <c r="F109" s="26" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="12">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B108" s="13" t="str">
-        <f>TEXT($A108,"ddd")</f>
+      <c r="B110" s="13" t="str">
+        <f>TEXT($A110,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C110" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="D108" s="11" t="s">
+      <c r="D110" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="E108" s="38" t="s">
+      <c r="E110" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="F108" s="25" t="s">
+      <c r="F110" s="25" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="31">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="31">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B109" s="32" t="str">
+      <c r="B111" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C109" s="33" t="s">
+      <c r="C111" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="D109" s="33" t="s">
+      <c r="D111" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="E109" s="33" t="s">
+      <c r="E111" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="F109" s="26" t="s">
+      <c r="F111" s="26" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="12">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B110" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C110" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="E110" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="F110" s="26" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
-      </c>
-      <c r="B111" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C111" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="E111" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F111" s="26" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
       </c>
       <c r="B112" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>250</v>
+        <v>173</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>124</v>
+        <v>232</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B113" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C113" s="16" t="s">
+      <c r="C113" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E113" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F113" s="26" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="12">
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
+      </c>
+      <c r="B114" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E114" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F114" s="26" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="12">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B115" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C115" s="16" t="s">
         <v>452</v>
       </c>
-      <c r="D113" s="11" t="s">
+      <c r="D115" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="E113" s="11" t="s">
+      <c r="E115" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F113" s="25" t="s">
+      <c r="F115" s="25" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="35">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B114" s="36" t="str">
+      <c r="B116" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C114" s="37" t="s">
+      <c r="C116" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="D114" s="37" t="s">
+      <c r="D116" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="E114" s="37" t="s">
+      <c r="E116" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F114" s="26" t="s">
+      <c r="F116" s="26" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="12">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="12">
         <f>DATE(2027,8,9)</f>
         <v>46608</v>
       </c>
-      <c r="B115" s="13" t="str">
-        <f>TEXT($A115,"ddd")</f>
+      <c r="B117" s="13" t="str">
+        <f>TEXT($A117,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C117" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="D115" s="11" t="s">
+      <c r="D117" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="E115" s="38" t="s">
+      <c r="E117" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="F115" s="25" t="s">
+      <c r="F117" s="25" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="31">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="31">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B116" s="32" t="str">
+      <c r="B118" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C116" s="33" t="s">
+      <c r="C118" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="D116" s="33" t="s">
+      <c r="D118" s="33" t="s">
         <v>217</v>
       </c>
-      <c r="E116" s="33" t="s">
+      <c r="E118" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="F116" s="26" t="s">
+      <c r="F118" s="26" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="12">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
       </c>
-      <c r="B117" s="13" t="str">
+      <c r="B119" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C119" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D117" s="11" t="s">
+      <c r="D119" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E117" s="11" t="s">
+      <c r="E119" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F117" s="26" t="s">
+      <c r="F119" s="26" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="12">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
-      </c>
-      <c r="B118" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C118" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="E118" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
-      </c>
-      <c r="B119" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="E119" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="F119" s="26" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
       </c>
       <c r="B120" s="13" t="str">
         <f t="shared" si="2"/>
@@ -5178,139 +5180,183 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="35">
+      <c r="A121" s="12">
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
+      </c>
+      <c r="B121" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E121" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F121" s="26" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="12">
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
+      </c>
+      <c r="B122" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="35">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B121" s="36" t="str">
+      <c r="B123" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C121" s="37" t="s">
+      <c r="C123" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="D121" s="37" t="s">
+      <c r="D123" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="E121" s="37" t="s">
+      <c r="E123" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F121" s="26" t="s">
+      <c r="F123" s="26" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="12">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="12">
         <f>DATE(2027,10,28)</f>
         <v>46688</v>
       </c>
-      <c r="B122" s="13" t="str">
-        <f>TEXT($A122,"ddd")</f>
+      <c r="B124" s="13" t="str">
+        <f>TEXT($A124,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C124" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="D122" s="11" t="s">
+      <c r="D124" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="E122" s="38" t="s">
+      <c r="E124" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="F122" s="25" t="s">
+      <c r="F124" s="25" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="31">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="31">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B123" s="32" t="str">
+      <c r="B125" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C123" s="33" t="s">
+      <c r="C125" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="D123" s="33" t="s">
+      <c r="D125" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="E123" s="33" t="s">
+      <c r="E125" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F123" s="26" t="s">
+      <c r="F125" s="26" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="12">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B124" s="13" t="str">
+      <c r="B126" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C124" s="16" t="s">
+      <c r="C126" s="16" t="s">
         <v>452</v>
       </c>
-      <c r="D124" s="11" t="s">
+      <c r="D126" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="E124" s="11" t="s">
+      <c r="E126" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F124" s="25" t="s">
+      <c r="F126" s="25" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B125" s="36" t="str">
+      <c r="B127" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C125" s="37" t="s">
+      <c r="C127" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="D125" s="40" t="s">
+      <c r="D127" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="E125" s="37" t="s">
+      <c r="E127" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F125" s="26" t="s">
+      <c r="F127" s="26" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="12">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B126" s="13" t="str">
-        <f>TEXT($A126,"ddd")</f>
+      <c r="B128" s="13" t="str">
+        <f>TEXT($A128,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C126" s="11" t="s">
+      <c r="C128" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="D126" s="11" t="s">
+      <c r="D128" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="E126" s="38" t="s">
+      <c r="E128" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="F126" s="25" t="s">
+      <c r="F128" s="25" t="s">
         <v>509</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E126" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E128" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -7378,7 +7424,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">

--- a/data.xlsx
+++ b/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1798" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{040DA775-9C1C-47FD-A5FD-B09E96F5486D}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1798" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{040DA775-9C1C-47FD-A5FD-B09E96F5486D}"/>
+  <xr:revisionPtr revIDLastSave="1808" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D82ED1C-674B-4728-BC30-7A80CF26BD7A}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="582">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1775,10 +1775,19 @@
     <t>Charity Governance Conference 2026. 9.30am to 3.30pm. Raffles City Convention Centre. Conference 9.30am - 12pm, Workshop 2pm - 3.30pm. (Representative: Jin Hoa, Kathy)</t>
   </si>
   <si>
-    <t>Visit from temple</t>
-  </si>
-  <si>
-    <t>Visit from China temple (TCM operations and Caring Heart) (Representative: Lim Soi Tee, Jin Hoa)</t>
+    <t>存心善堂 (中國潮汕)</t>
+  </si>
+  <si>
+    <t>Visit from 存心善堂 (中國潮汕). NHST at 10am, then NHWSS at 11am-12pm. Approximately 40 pax.</t>
+  </si>
+  <si>
+    <t>Visit from Nanyang Girls School, Secondary 1 students. NHST at 9.30am, then NHWSS at 10am. Approximately 60 pax.</t>
+  </si>
+  <si>
+    <t>Visit from 存心善堂 (中國潮汕)</t>
+  </si>
+  <si>
+    <t>Visit from Nanyang Girls School</t>
   </si>
 </sst>
 </file>
@@ -4403,12 +4412,14 @@
       <c r="C85" s="25" t="s">
         <v>578</v>
       </c>
-      <c r="D85" s="25"/>
+      <c r="D85" s="25" t="s">
+        <v>577</v>
+      </c>
       <c r="E85" s="25" t="s">
-        <v>232</v>
+        <v>124</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -4421,14 +4432,14 @@
         <v>Tue</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D86" s="25"/>
       <c r="E86" s="25" t="s">
-        <v>232</v>
+        <v>124</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -7449,14 +7460,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7701,23 +7710,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7743,9 +7749,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1808" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D82ED1C-674B-4728-BC30-7A80CF26BD7A}"/>
+  <xr:revisionPtr revIDLastSave="1811" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93EF90F9-4594-4A40-A0FE-0D7E0095BA75}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1781,13 +1781,13 @@
     <t>Visit from 存心善堂 (中國潮汕). NHST at 10am, then NHWSS at 11am-12pm. Approximately 40 pax.</t>
   </si>
   <si>
-    <t>Visit from Nanyang Girls School, Secondary 1 students. NHST at 9.30am, then NHWSS at 10am. Approximately 60 pax.</t>
-  </si>
-  <si>
     <t>Visit from 存心善堂 (中國潮汕)</t>
   </si>
   <si>
-    <t>Visit from Nanyang Girls School</t>
+    <t>Visit from Nanyang Girls' High School, Secondary 1 students - Heritage and cross-cultural learning journey. Approximately 60 pax, split into Group 1 (9.30am) and Group 2 (11.30am).</t>
+  </si>
+  <si>
+    <t>Visit from Nanyang Girls' High School</t>
   </si>
 </sst>
 </file>
@@ -4419,7 +4419,7 @@
         <v>124</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -4432,7 +4432,7 @@
         <v>Tue</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D86" s="25"/>
       <c r="E86" s="25" t="s">
@@ -7460,12 +7460,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7710,20 +7712,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7749,14 +7754,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1811" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93EF90F9-4594-4A40-A0FE-0D7E0095BA75}"/>
+  <xr:revisionPtr revIDLastSave="1813" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB1C9B1E-8F9A-40CD-837B-BB029D4B8E45}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1730,9 +1730,6 @@
     <t>南凤善堂中元会 (代表：南凤福利协会员工，晓晓）。筹款活动包括义标。</t>
   </si>
   <si>
-    <t>Fundraising with Confidence: Legal, Governance and Compliance Considerations for Non-Profits</t>
-  </si>
-  <si>
     <t xml:space="preserve">Governance </t>
   </si>
   <si>
@@ -1788,6 +1785,9 @@
   </si>
   <si>
     <t>Visit from Nanyang Girls' High School</t>
+  </si>
+  <si>
+    <t>Fundraising with Confidence: Legal, Governance and Compliance Considerations for Non-Profits. Level 3 Tembusu Canopy, Temasek Shophouse (28 Orchard Road, Singapore 238832). Representative: Bryan, Chi Hwee, Jin Hoa</t>
   </si>
 </sst>
 </file>
@@ -2654,16 +2654,16 @@
         <v>Sun</v>
       </c>
       <c r="C4" s="44" t="s">
+        <v>569</v>
+      </c>
+      <c r="D4" s="44" t="s">
         <v>570</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>571</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2830,10 +2830,10 @@
         <v>Sat</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E12" s="38" t="s">
         <v>478</v>
@@ -2852,16 +2852,16 @@
         <v>Sat</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -3336,16 +3336,16 @@
         <v>Mon</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -4196,14 +4196,14 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="F75" s="25" t="s">
         <v>563</v>
-      </c>
-      <c r="F75" s="25" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -4368,7 +4368,7 @@
         <v>Thu</v>
       </c>
       <c r="C83" s="40" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D83" s="37"/>
       <c r="E83" s="37" t="s">
@@ -4388,16 +4388,16 @@
         <v>Tue</v>
       </c>
       <c r="C84" s="25" t="s">
+        <v>567</v>
+      </c>
+      <c r="D84" s="25" t="s">
         <v>568</v>
-      </c>
-      <c r="D84" s="25" t="s">
-        <v>569</v>
       </c>
       <c r="E84" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
@@ -4410,16 +4410,16 @@
         <v>Mon</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E85" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -4432,14 +4432,14 @@
         <v>Tue</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D86" s="25"/>
       <c r="E86" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7460,14 +7460,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7712,23 +7710,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7754,9 +7749,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1813" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB1C9B1E-8F9A-40CD-837B-BB029D4B8E45}"/>
+  <xr:revisionPtr revIDLastSave="1846" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51B5A042-067B-43E5-B57D-0E6429D0E16D}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,9 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$130</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="588">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -488,9 +488,6 @@
     <t>25th Anniversary Charity Dinner, Golf @ Orchid Country Club, Magazine Launch</t>
   </si>
   <si>
-    <t>25周年慈善晚宴、高尔夫球赛（胡姬乡村俱乐部）暨特刊推介</t>
-  </si>
-  <si>
     <t>10th Term Management Committee Sworn In</t>
   </si>
   <si>
@@ -1788,6 +1785,27 @@
   </si>
   <si>
     <t>Fundraising with Confidence: Legal, Governance and Compliance Considerations for Non-Profits. Level 3 Tembusu Canopy, Temasek Shophouse (28 Orchard Road, Singapore 238832). Representative: Bryan, Chi Hwee, Jin Hoa</t>
+  </si>
+  <si>
+    <t>25周年慈善晚宴、高尔夫球赛，暨特刊推介</t>
+  </si>
+  <si>
+    <t>Nam Hong Siang Theon 65th Anniversary celebration dinner at Orchid Country Club, 7pm</t>
+  </si>
+  <si>
+    <t>南凤善堂65周年晚宴 Orchid Country Club, 7pm</t>
+  </si>
+  <si>
+    <t>南凤善堂65周年 NHST 65th anniversary</t>
+  </si>
+  <si>
+    <t>宋大峰祖师诞辰</t>
+  </si>
+  <si>
+    <t>Master Song Da Feng prayers at NHST, 10am</t>
+  </si>
+  <si>
+    <t>宋大峰祖师诞辰, 南凤善堂, 10am</t>
   </si>
 </sst>
 </file>
@@ -1810,21 +1828,25 @@
       <sz val="10"/>
       <color rgb="FF142F63"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1C2434"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1848,6 +1870,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2460,7 +2483,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2570,7 +2593,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -2597,7 +2620,7 @@
         <v>134</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2610,16 +2633,16 @@
         <v>Thu</v>
       </c>
       <c r="C2" s="30" t="s">
+        <v>488</v>
+      </c>
+      <c r="D2" s="30" t="s">
         <v>489</v>
       </c>
-      <c r="D2" s="30" t="s">
-        <v>490</v>
-      </c>
       <c r="E2" s="34" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2641,7 +2664,7 @@
         <v>124</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2654,16 +2677,16 @@
         <v>Sun</v>
       </c>
       <c r="C4" s="44" t="s">
+        <v>568</v>
+      </c>
+      <c r="D4" s="44" t="s">
         <v>569</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>570</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2685,7 +2708,7 @@
         <v>121</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2698,16 +2721,16 @@
         <v>Tue</v>
       </c>
       <c r="C6" s="37" t="s">
+        <v>482</v>
+      </c>
+      <c r="D6" s="37" t="s">
         <v>483</v>
       </c>
-      <c r="D6" s="37" t="s">
-        <v>484</v>
-      </c>
       <c r="E6" s="39" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2720,16 +2743,16 @@
         <v>Wed</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>486</v>
-      </c>
       <c r="E7" s="38" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2751,7 +2774,7 @@
         <v>131</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2773,7 +2796,7 @@
         <v>121</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2795,7 +2818,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2817,7 +2840,7 @@
         <v>124</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2830,16 +2853,16 @@
         <v>Sat</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2852,16 +2875,16 @@
         <v>Sat</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2883,7 +2906,7 @@
         <v>121</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2905,7 +2928,7 @@
         <v>121</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2921,13 +2944,13 @@
         <v>128</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E16" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2940,16 +2963,16 @@
         <v>Fri</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>480</v>
-      </c>
       <c r="E17" s="38" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2965,13 +2988,13 @@
         <v>130</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -2984,16 +3007,16 @@
         <v>Fri</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>475</v>
-      </c>
       <c r="E19" s="38" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -3015,7 +3038,7 @@
         <v>129</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3030,14 +3053,14 @@
       <c r="C21" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>148</v>
+      <c r="D21" s="16" t="s">
+        <v>581</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3050,16 +3073,16 @@
         <v>Sun</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -3075,13 +3098,13 @@
         <v>132</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E23" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -3094,16 +3117,16 @@
         <v>Wed</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>511</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>512</v>
-      </c>
       <c r="E24" s="38" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -3116,16 +3139,16 @@
         <v>Fri</v>
       </c>
       <c r="C25" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="D25" s="33" t="s">
-        <v>152</v>
-      </c>
       <c r="E25" s="33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -3138,16 +3161,16 @@
         <v>Sat</v>
       </c>
       <c r="C26" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>154</v>
-      </c>
       <c r="E26" s="37" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -3160,16 +3183,16 @@
         <v>Sun</v>
       </c>
       <c r="C27" s="37" t="s">
+        <v>471</v>
+      </c>
+      <c r="D27" s="37" t="s">
         <v>472</v>
       </c>
-      <c r="D27" s="37" t="s">
-        <v>473</v>
-      </c>
       <c r="E27" s="39" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3182,16 +3205,16 @@
         <v>Mon</v>
       </c>
       <c r="C28" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>496</v>
-      </c>
       <c r="E28" s="38" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -3204,16 +3227,16 @@
         <v>Sun</v>
       </c>
       <c r="C29" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="D29" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="D29" s="33" t="s">
-        <v>156</v>
-      </c>
       <c r="E29" s="33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -3226,16 +3249,16 @@
         <v>Mon</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="11" t="s">
-        <v>158</v>
-      </c>
       <c r="E30" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -3251,13 +3274,13 @@
         <v>128</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -3273,13 +3296,13 @@
         <v>133</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -3295,13 +3318,13 @@
         <v>128</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -3314,16 +3337,16 @@
         <v>Fri</v>
       </c>
       <c r="C34" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>160</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>161</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -3336,16 +3359,16 @@
         <v>Mon</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -3358,16 +3381,16 @@
         <v>Fri</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>199</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>200</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3383,13 +3406,13 @@
         <v>128</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3405,13 +3428,13 @@
         <v>128</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3424,16 +3447,16 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3446,16 +3469,16 @@
         <v>Wed</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -3468,16 +3491,16 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3490,16 +3513,16 @@
         <v>Sun</v>
       </c>
       <c r="C42" s="37" t="s">
+        <v>469</v>
+      </c>
+      <c r="D42" s="37" t="s">
         <v>470</v>
       </c>
-      <c r="D42" s="37" t="s">
-        <v>471</v>
-      </c>
       <c r="E42" s="39" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3512,16 +3535,16 @@
         <v>Mon</v>
       </c>
       <c r="C43" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="D43" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="D43" s="11" t="s">
-        <v>494</v>
-      </c>
       <c r="E43" s="38" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3534,16 +3557,16 @@
         <v>Fri</v>
       </c>
       <c r="C44" s="33" t="s">
+        <v>520</v>
+      </c>
+      <c r="D44" s="43" t="s">
         <v>521</v>
       </c>
-      <c r="D44" s="43" t="s">
-        <v>522</v>
-      </c>
       <c r="E44" s="33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3556,16 +3579,16 @@
         <v>Sat</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3578,16 +3601,16 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3600,16 +3623,16 @@
         <v>Sun</v>
       </c>
       <c r="C47" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="D47" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="D47" s="11" t="s">
-        <v>514</v>
-      </c>
       <c r="E47" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3622,16 +3645,16 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3644,16 +3667,16 @@
         <v>Sat</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -3666,16 +3689,16 @@
         <v>Sat</v>
       </c>
       <c r="C50" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="D50" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="D50" s="11" t="s">
-        <v>456</v>
-      </c>
       <c r="E50" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3688,16 +3711,16 @@
         <v>Mon</v>
       </c>
       <c r="C51" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D51" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="D51" s="21" t="s">
-        <v>249</v>
-      </c>
       <c r="E51" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3710,14 +3733,14 @@
         <v>Tue</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3730,16 +3753,16 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="11" t="s">
+        <v>522</v>
+      </c>
+      <c r="D53" s="16" t="s">
         <v>523</v>
       </c>
-      <c r="D53" s="16" t="s">
-        <v>524</v>
-      </c>
       <c r="E53" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -3752,16 +3775,16 @@
         <v>Thu</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3774,16 +3797,16 @@
         <v>Thu</v>
       </c>
       <c r="C55" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="D55" s="16" t="s">
         <v>525</v>
       </c>
-      <c r="D55" s="16" t="s">
-        <v>526</v>
-      </c>
       <c r="E55" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3796,16 +3819,16 @@
         <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3818,14 +3841,14 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3838,16 +3861,16 @@
         <v>Sat</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G58" s="19"/>
     </row>
@@ -3861,14 +3884,14 @@
         <v>Sat</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G59" s="19"/>
     </row>
@@ -3882,16 +3905,16 @@
         <v>Mon</v>
       </c>
       <c r="C60" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="D60" s="16" t="s">
         <v>560</v>
       </c>
-      <c r="D60" s="16" t="s">
-        <v>561</v>
-      </c>
       <c r="E60" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3904,16 +3927,16 @@
         <v>Tue</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3926,14 +3949,14 @@
         <v>Tue</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3946,16 +3969,16 @@
         <v>Wed</v>
       </c>
       <c r="C63" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="D63" s="16" t="s">
         <v>558</v>
       </c>
-      <c r="D63" s="16" t="s">
-        <v>559</v>
-      </c>
       <c r="E63" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3968,14 +3991,14 @@
         <v>Wed</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -3988,16 +4011,16 @@
         <v>Wed</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -4010,14 +4033,14 @@
         <v>Wed</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -4030,14 +4053,14 @@
         <v>Thu</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -4050,14 +4073,14 @@
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F68" s="25" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4070,14 +4093,14 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4090,16 +4113,16 @@
         <v>Sat</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -4112,16 +4135,16 @@
         <v>Sat</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -4134,16 +4157,16 @@
         <v>Sun</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -4156,14 +4179,14 @@
         <v>Wed</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -4176,14 +4199,14 @@
         <v>Wed</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -4196,14 +4219,14 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="F75" s="25" t="s">
         <v>562</v>
-      </c>
-      <c r="F75" s="25" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -4216,16 +4239,16 @@
         <v>Fri</v>
       </c>
       <c r="C76" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="D76" s="11" t="s">
         <v>534</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>535</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="51" x14ac:dyDescent="0.35">
@@ -4238,16 +4261,16 @@
         <v>Fri</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -4260,16 +4283,16 @@
         <v>Sat</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -4282,14 +4305,14 @@
         <v>Mon</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D79" s="11"/>
       <c r="E79" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -4302,16 +4325,16 @@
         <v>Mon</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -4324,16 +4347,16 @@
         <v>Tue</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
@@ -4346,16 +4369,16 @@
         <v>Wed</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
@@ -4368,14 +4391,14 @@
         <v>Thu</v>
       </c>
       <c r="C83" s="40" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D83" s="37"/>
       <c r="E83" s="37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F83" s="25" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
@@ -4388,16 +4411,16 @@
         <v>Tue</v>
       </c>
       <c r="C84" s="25" t="s">
+        <v>566</v>
+      </c>
+      <c r="D84" s="25" t="s">
         <v>567</v>
-      </c>
-      <c r="D84" s="25" t="s">
-        <v>568</v>
       </c>
       <c r="E84" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
@@ -4410,16 +4433,16 @@
         <v>Mon</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E85" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -4432,14 +4455,14 @@
         <v>Tue</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D86" s="25"/>
       <c r="E86" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -4448,20 +4471,20 @@
         <v>46329</v>
       </c>
       <c r="B87" s="36" t="str">
-        <f t="shared" ref="B87:B127" si="2">TEXT($A87,"ddd")</f>
+        <f t="shared" ref="B87:B129" si="2">TEXT($A87,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="C87" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D87" s="37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E87" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
@@ -4474,16 +4497,16 @@
         <v>Sun</v>
       </c>
       <c r="C88" s="37" t="s">
+        <v>467</v>
+      </c>
+      <c r="D88" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="D88" s="37" t="s">
-        <v>469</v>
-      </c>
       <c r="E88" s="39" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F88" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -4496,16 +4519,16 @@
         <v>Mon</v>
       </c>
       <c r="C89" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="D89" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D89" s="11" t="s">
-        <v>492</v>
-      </c>
       <c r="E89" s="38" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F89" s="25" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
@@ -4518,16 +4541,16 @@
         <v>Tue</v>
       </c>
       <c r="C90" s="43" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D90" s="33" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E90" s="33" t="s">
         <v>124</v>
       </c>
       <c r="F90" s="25" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
@@ -4540,834 +4563,878 @@
         <v>Tue</v>
       </c>
       <c r="C91" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="D91" s="11" t="s">
         <v>536</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>537</v>
       </c>
       <c r="E91" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="35">
+        <f>DATE(2026,12,7)</f>
+        <v>46363</v>
+      </c>
+      <c r="B92" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C92" s="40" t="s">
+        <v>586</v>
+      </c>
+      <c r="D92" s="40" t="s">
+        <v>587</v>
+      </c>
+      <c r="E92" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="F92" s="40" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="35">
+        <f>DATE(2026,12,11)</f>
+        <v>46367</v>
+      </c>
+      <c r="B93" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C93" s="40" t="s">
+        <v>582</v>
+      </c>
+      <c r="D93" s="40" t="s">
+        <v>583</v>
+      </c>
+      <c r="E93" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="F93" s="44" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="35">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B92" s="36" t="str">
+      <c r="B94" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C92" s="40" t="s">
-        <v>460</v>
-      </c>
-      <c r="D92" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="E92" s="37" t="s">
+      <c r="C94" s="40" t="s">
+        <v>459</v>
+      </c>
+      <c r="D94" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="E94" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F92" s="25" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="35">
+      <c r="F94" s="25" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="35">
         <f>DATE(2026,12,25)</f>
         <v>46381</v>
       </c>
-      <c r="B93" s="36" t="str">
-        <f>TEXT($A93,"ddd")</f>
+      <c r="B95" s="36" t="str">
+        <f>TEXT($A95,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C93" s="37" t="s">
+      <c r="C95" s="37" t="s">
+        <v>464</v>
+      </c>
+      <c r="D95" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="D93" s="37" t="s">
+      <c r="E95" s="39" t="s">
         <v>466</v>
       </c>
-      <c r="E93" s="39" t="s">
-        <v>467</v>
-      </c>
-      <c r="F93" s="25" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="12">
+      <c r="F95" s="25" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B94" s="13" t="str">
-        <f>TEXT($A94,"ddd")</f>
+      <c r="B96" s="13" t="str">
+        <f>TEXT($A96,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C96" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="D96" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="D94" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="E94" s="38" t="s">
-        <v>467</v>
-      </c>
-      <c r="F94" s="25" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="31">
+      <c r="E96" s="38" t="s">
+        <v>466</v>
+      </c>
+      <c r="F96" s="25" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="31">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B95" s="32" t="str">
+      <c r="B97" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C95" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="D95" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E95" s="33" t="s">
+      <c r="C97" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="D97" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="E97" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F95" s="25" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="35">
+      <c r="F97" s="25" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="35">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B96" s="36" t="str">
+      <c r="B98" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C96" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="D96" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="E96" s="37" t="s">
+      <c r="C98" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="D98" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="E98" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F96" s="25" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="35">
+      <c r="F98" s="25" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="35">
         <f>DATE(2027,2,6)</f>
         <v>46424</v>
       </c>
-      <c r="B97" s="36" t="str">
-        <f>TEXT($A97,"ddd")</f>
+      <c r="B99" s="36" t="str">
+        <f>TEXT($A99,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C97" s="37" t="s">
+      <c r="C99" s="37" t="s">
+        <v>482</v>
+      </c>
+      <c r="D99" s="37" t="s">
         <v>483</v>
       </c>
-      <c r="D97" s="37" t="s">
-        <v>484</v>
-      </c>
-      <c r="E97" s="39" t="s">
-        <v>467</v>
-      </c>
-      <c r="F97" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="35">
+      <c r="E99" s="39" t="s">
+        <v>466</v>
+      </c>
+      <c r="F99" s="25" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="35">
         <f>DATE(2027,2,7)</f>
         <v>46425</v>
       </c>
-      <c r="B98" s="36" t="str">
-        <f>TEXT($A98,"ddd")</f>
+      <c r="B100" s="36" t="str">
+        <f>TEXT($A100,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C98" s="37" t="s">
+      <c r="C100" s="37" t="s">
+        <v>484</v>
+      </c>
+      <c r="D100" s="37" t="s">
         <v>485</v>
       </c>
-      <c r="D98" s="37" t="s">
-        <v>486</v>
-      </c>
-      <c r="E98" s="39" t="s">
-        <v>467</v>
-      </c>
-      <c r="F98" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="12">
+      <c r="E100" s="39" t="s">
+        <v>466</v>
+      </c>
+      <c r="F100" s="25" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B99" s="13" t="str">
-        <f>TEXT($A99,"ddd")</f>
+      <c r="B101" s="13" t="str">
+        <f>TEXT($A101,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C99" s="11" t="s">
+      <c r="C101" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="D101" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="D99" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E99" s="38" t="s">
-        <v>467</v>
-      </c>
-      <c r="F99" s="25" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="41">
+      <c r="E101" s="38" t="s">
+        <v>466</v>
+      </c>
+      <c r="F101" s="25" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B100" s="42" t="str">
+      <c r="B102" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C100" s="25" t="s">
+      <c r="C102" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="D102" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="D100" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="E100" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="F100" s="26" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="12">
+      <c r="E102" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="F102" s="26" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="12">
         <f>DATE(2027,3,10)</f>
         <v>46456</v>
       </c>
-      <c r="B101" s="13" t="str">
-        <f>TEXT($A101,"ddd")</f>
+      <c r="B103" s="13" t="str">
+        <f>TEXT($A103,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C103" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="D103" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D101" s="11" t="s">
-        <v>482</v>
-      </c>
-      <c r="E101" s="38" t="s">
-        <v>478</v>
-      </c>
-      <c r="F101" s="25" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="31">
+      <c r="E103" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F103" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="31">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B102" s="32" t="str">
+      <c r="B104" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C102" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="D102" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="E102" s="33" t="s">
+      <c r="C104" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="D104" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E104" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F102" s="26" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="35">
+      <c r="F104" s="26" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="35">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B103" s="36" t="str">
+      <c r="B105" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C103" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="D103" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E103" s="37" t="s">
+      <c r="C105" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="D105" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="E105" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F103" s="26" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="12">
+      <c r="F105" s="26" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="12">
         <f>DATE(2027,3,26)</f>
         <v>46472</v>
       </c>
-      <c r="B104" s="13" t="str">
-        <f>TEXT($A104,"ddd")</f>
+      <c r="B106" s="13" t="str">
+        <f>TEXT($A106,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C106" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="D106" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="D104" s="11" t="s">
-        <v>480</v>
-      </c>
-      <c r="E104" s="38" t="s">
-        <v>467</v>
-      </c>
-      <c r="F104" s="25" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="31">
+      <c r="E106" s="38" t="s">
+        <v>466</v>
+      </c>
+      <c r="F106" s="25" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="31">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B105" s="32" t="str">
+      <c r="B107" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C105" s="43" t="s">
-        <v>222</v>
-      </c>
-      <c r="D105" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="E105" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="F105" s="26" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="35">
+      <c r="C107" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="D107" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="E107" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F107" s="26" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="35">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B106" s="36" t="str">
+      <c r="B108" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C106" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="D106" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="E106" s="37" t="s">
+      <c r="C108" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="D108" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="E108" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F106" s="26" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="35">
+      <c r="F108" s="26" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="35">
         <f>DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="B107" s="36" t="str">
-        <f>TEXT($A107,"ddd")</f>
+      <c r="B109" s="36" t="str">
+        <f>TEXT($A109,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C107" s="37" t="s">
+      <c r="C109" s="37" t="s">
+        <v>473</v>
+      </c>
+      <c r="D109" s="37" t="s">
         <v>474</v>
       </c>
-      <c r="D107" s="37" t="s">
-        <v>475</v>
-      </c>
-      <c r="E107" s="39" t="s">
-        <v>467</v>
-      </c>
-      <c r="F107" s="25" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="12">
+      <c r="E109" s="39" t="s">
+        <v>466</v>
+      </c>
+      <c r="F109" s="25" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="12">
         <f>DATE(2027,5,17)</f>
         <v>46524</v>
       </c>
-      <c r="B108" s="13" t="str">
-        <f>TEXT($A108,"ddd")</f>
+      <c r="B110" s="13" t="str">
+        <f>TEXT($A110,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C110" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="D110" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="D108" s="11" t="s">
+      <c r="E110" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="E108" s="38" t="s">
-        <v>478</v>
-      </c>
-      <c r="F108" s="25" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="41">
+      <c r="F110" s="25" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="41">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B109" s="42" t="str">
+      <c r="B111" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C109" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="D109" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="E109" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="F109" s="26" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="12">
+      <c r="C111" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="D111" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="E111" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="F111" s="26" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B110" s="13" t="str">
-        <f>TEXT($A110,"ddd")</f>
+      <c r="B112" s="13" t="str">
+        <f>TEXT($A112,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C112" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="D112" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="D110" s="11" t="s">
-        <v>473</v>
-      </c>
-      <c r="E110" s="38" t="s">
-        <v>467</v>
-      </c>
-      <c r="F110" s="25" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="31">
+      <c r="E112" s="38" t="s">
+        <v>466</v>
+      </c>
+      <c r="F112" s="25" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="31">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B111" s="32" t="str">
+      <c r="B113" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C111" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D111" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="E111" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="F111" s="26" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="12">
+      <c r="C113" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="D113" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E113" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="F113" s="26" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B112" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C112" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="E112" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="F112" s="26" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
-      </c>
-      <c r="B113" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="E113" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F113" s="26" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
       </c>
       <c r="B114" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>124</v>
+        <v>231</v>
       </c>
       <c r="F114" s="26" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B115" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C115" s="16" t="s">
+      <c r="C115" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E115" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F115" s="26" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="12">
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
+      </c>
+      <c r="B116" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E116" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F116" s="26" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="12">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B117" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="D117" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D115" s="11" t="s">
+      <c r="E117" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F117" s="25" t="s">
         <v>453</v>
       </c>
-      <c r="E115" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F115" s="25" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="35">
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="35">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B116" s="36" t="str">
+      <c r="B118" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C116" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="D116" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="E116" s="37" t="s">
+      <c r="C118" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="D118" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="E118" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F116" s="26" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="12">
+      <c r="F118" s="26" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="12">
         <f>DATE(2027,8,9)</f>
         <v>46608</v>
       </c>
-      <c r="B117" s="13" t="str">
-        <f>TEXT($A117,"ddd")</f>
+      <c r="B119" s="13" t="str">
+        <f>TEXT($A119,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C119" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="D119" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="D117" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="E117" s="38" t="s">
-        <v>467</v>
-      </c>
-      <c r="F117" s="25" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="31">
+      <c r="E119" s="38" t="s">
+        <v>466</v>
+      </c>
+      <c r="F119" s="25" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="31">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B118" s="32" t="str">
+      <c r="B120" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C118" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="D118" s="33" t="s">
-        <v>217</v>
-      </c>
-      <c r="E118" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="12">
+      <c r="C120" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="D120" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E120" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="F120" s="26" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
       </c>
-      <c r="B119" s="13" t="str">
+      <c r="B121" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C119" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E119" s="11" t="s">
+      <c r="C121" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="E121" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F119" s="26" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="12">
+      <c r="F121" s="26" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
-      </c>
-      <c r="B120" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D120" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="E120" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F120" s="26" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
-      </c>
-      <c r="B121" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C121" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D121" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="E121" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="F121" s="26" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
       </c>
       <c r="B122" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E122" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="35">
+      <c r="A123" s="12">
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
+      </c>
+      <c r="B123" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E123" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F123" s="26" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="12">
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
+      </c>
+      <c r="B124" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E124" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F124" s="26" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="35">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B123" s="36" t="str">
+      <c r="B125" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C123" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="D123" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="E123" s="37" t="s">
+      <c r="C125" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="D125" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="E125" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F123" s="26" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="12">
+      <c r="F125" s="26" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="12">
         <f>DATE(2027,10,28)</f>
         <v>46688</v>
       </c>
-      <c r="B124" s="13" t="str">
-        <f>TEXT($A124,"ddd")</f>
+      <c r="B126" s="13" t="str">
+        <f>TEXT($A126,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C126" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="D126" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="D124" s="11" t="s">
-        <v>469</v>
-      </c>
-      <c r="E124" s="38" t="s">
-        <v>467</v>
-      </c>
-      <c r="F124" s="25" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="31">
+      <c r="E126" s="38" t="s">
+        <v>466</v>
+      </c>
+      <c r="F126" s="25" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="31">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B125" s="32" t="str">
+      <c r="B127" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C125" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="D125" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="E125" s="33" t="s">
+      <c r="C127" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="D127" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E127" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F125" s="26" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="12">
+      <c r="F127" s="26" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B126" s="13" t="str">
+      <c r="B128" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C126" s="16" t="s">
+      <c r="C128" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="D128" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D126" s="11" t="s">
+      <c r="E128" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F128" s="25" t="s">
         <v>453</v>
       </c>
-      <c r="E126" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F126" s="25" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="35">
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B127" s="36" t="str">
+      <c r="B129" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C127" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="D127" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="E127" s="37" t="s">
+      <c r="C129" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="D129" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="E129" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F127" s="26" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="12">
+      <c r="F129" s="26" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B128" s="13" t="str">
-        <f>TEXT($A128,"ddd")</f>
+      <c r="B130" s="13" t="str">
+        <f>TEXT($A130,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C130" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="D130" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="E130" s="38" t="s">
         <v>466</v>
       </c>
-      <c r="E128" s="38" t="s">
-        <v>467</v>
-      </c>
-      <c r="F128" s="25" t="s">
-        <v>509</v>
+      <c r="F130" s="25" t="s">
+        <v>508</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E128" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E130" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -5590,7 +5657,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>96</v>
@@ -5615,7 +5682,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>64</v>
@@ -5782,7 +5849,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>21</v>
@@ -5842,7 +5909,7 @@
         <v>109</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>93</v>
@@ -5862,7 +5929,7 @@
         <v>109</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>86</v>
@@ -5882,7 +5949,7 @@
         <v>109</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>101</v>
@@ -5902,7 +5969,7 @@
         <v>109</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>88</v>
@@ -5922,7 +5989,7 @@
         <v>109</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>90</v>
@@ -6053,10 +6120,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>180</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>181</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -6076,10 +6143,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>180</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>181</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -6097,16 +6164,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>180</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>181</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>64</v>
@@ -6120,10 +6187,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>180</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>181</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -6141,10 +6208,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>180</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>181</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -6164,10 +6231,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>182</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>183</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -6187,10 +6254,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>182</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>183</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -6210,10 +6277,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>184</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>185</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -6233,10 +6300,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>184</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>185</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -6256,10 +6323,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>187</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -6279,10 +6346,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>187</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -6291,7 +6358,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -6302,10 +6369,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>187</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -6325,10 +6392,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>187</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -6348,10 +6415,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>188</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>189</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -6371,10 +6438,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>188</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>189</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -6394,10 +6461,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>190</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>191</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -6417,10 +6484,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>190</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>191</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -6440,10 +6507,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>190</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>191</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -6463,10 +6530,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>192</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>193</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -6486,10 +6553,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>192</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>193</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -6509,10 +6576,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>192</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>193</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -6562,7 +6629,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>21</v>
@@ -6570,839 +6637,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" t="s">
         <v>253</v>
       </c>
-      <c r="C2" t="s">
-        <v>254</v>
-      </c>
       <c r="D2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E2" t="s">
         <v>349</v>
-      </c>
-      <c r="E2" t="s">
-        <v>350</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E3" t="s">
         <v>351</v>
-      </c>
-      <c r="E3" t="s">
-        <v>352</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E4" t="s">
         <v>353</v>
       </c>
-      <c r="E4" t="s">
-        <v>354</v>
-      </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D11" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D14" t="s">
+        <v>363</v>
+      </c>
+      <c r="E14" t="s">
         <v>364</v>
       </c>
-      <c r="E14" t="s">
-        <v>365</v>
-      </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
       <c r="G14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D15" t="s">
+        <v>363</v>
+      </c>
+      <c r="E15" t="s">
         <v>364</v>
       </c>
-      <c r="E15" t="s">
-        <v>365</v>
-      </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
       <c r="G15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H15" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D16" t="s">
+        <v>363</v>
+      </c>
+      <c r="E16" t="s">
         <v>364</v>
       </c>
-      <c r="E16" t="s">
-        <v>365</v>
-      </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
       <c r="G16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D17" t="s">
+        <v>363</v>
+      </c>
+      <c r="E17" t="s">
         <v>364</v>
       </c>
-      <c r="E17" t="s">
-        <v>365</v>
-      </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
       <c r="G17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D18" t="s">
+        <v>363</v>
+      </c>
+      <c r="E18" t="s">
         <v>364</v>
       </c>
-      <c r="E18" t="s">
-        <v>365</v>
-      </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
       <c r="G18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H18" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D19" t="s">
+        <v>363</v>
+      </c>
+      <c r="E19" t="s">
         <v>364</v>
       </c>
-      <c r="E19" t="s">
-        <v>365</v>
-      </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
       <c r="G19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H19" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D20" t="s">
+        <v>363</v>
+      </c>
+      <c r="E20" t="s">
         <v>364</v>
       </c>
-      <c r="E20" t="s">
-        <v>365</v>
-      </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
       <c r="G20" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D21" t="s">
+        <v>363</v>
+      </c>
+      <c r="E21" t="s">
         <v>364</v>
       </c>
-      <c r="E21" t="s">
-        <v>365</v>
-      </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
       <c r="G21" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H21" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D22" t="s">
+        <v>363</v>
+      </c>
+      <c r="E22" t="s">
         <v>364</v>
       </c>
-      <c r="E22" t="s">
-        <v>365</v>
-      </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
       <c r="G22" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H22" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C23" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D23" t="s">
+        <v>363</v>
+      </c>
+      <c r="E23" t="s">
         <v>364</v>
       </c>
-      <c r="E23" t="s">
-        <v>365</v>
-      </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
       <c r="G23" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H23" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B24" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D24" t="s">
+        <v>363</v>
+      </c>
+      <c r="E24" t="s">
         <v>364</v>
       </c>
-      <c r="E24" t="s">
-        <v>365</v>
-      </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
       <c r="G24" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H24" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B25" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C25" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D25" t="s">
+        <v>365</v>
+      </c>
+      <c r="E25" s="23" t="s">
         <v>366</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="F25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geokchin.jpg</v>
+      </c>
+      <c r="G25" t="s">
+        <v>391</v>
+      </c>
+      <c r="H25" t="s">
         <v>367</v>
-      </c>
-      <c r="F25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geokchin.jpg</v>
-      </c>
-      <c r="G25" t="s">
-        <v>392</v>
-      </c>
-      <c r="H25" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C26" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D26" t="s">
+        <v>365</v>
+      </c>
+      <c r="E26" s="23" t="s">
         <v>366</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laysiew.jpg</v>
+      </c>
+      <c r="G26" t="s">
+        <v>392</v>
+      </c>
+      <c r="H26" t="s">
         <v>367</v>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laysiew.jpg</v>
-      </c>
-      <c r="G26" t="s">
-        <v>393</v>
-      </c>
-      <c r="H26" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B27" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C27" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D27" t="s">
+        <v>365</v>
+      </c>
+      <c r="E27" s="23" t="s">
         <v>366</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="F27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>waiyee.jpg</v>
+      </c>
+      <c r="G27" t="s">
+        <v>393</v>
+      </c>
+      <c r="H27" t="s">
         <v>367</v>
-      </c>
-      <c r="F27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>waiyee.jpg</v>
-      </c>
-      <c r="G27" t="s">
-        <v>394</v>
-      </c>
-      <c r="H27" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D28" t="s">
+        <v>365</v>
+      </c>
+      <c r="E28" s="23" t="s">
         <v>366</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>carol.jpg</v>
+      </c>
+      <c r="G28" t="s">
+        <v>394</v>
+      </c>
+      <c r="H28" t="s">
         <v>367</v>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>carol.jpg</v>
-      </c>
-      <c r="G28" t="s">
-        <v>395</v>
-      </c>
-      <c r="H28" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D29" t="s">
+        <v>365</v>
+      </c>
+      <c r="E29" s="23" t="s">
         <v>366</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="F29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yokewant.jpg</v>
+      </c>
+      <c r="G29" t="s">
+        <v>395</v>
+      </c>
+      <c r="H29" t="s">
         <v>367</v>
-      </c>
-      <c r="F29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>yokewant.jpg</v>
-      </c>
-      <c r="G29" t="s">
-        <v>396</v>
-      </c>
-      <c r="H29" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D30" t="s">
+        <v>365</v>
+      </c>
+      <c r="E30" s="23" t="s">
         <v>366</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pohcheng.jpg</v>
+      </c>
+      <c r="G30" t="s">
+        <v>396</v>
+      </c>
+      <c r="H30" t="s">
         <v>367</v>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>pohcheng.jpg</v>
-      </c>
-      <c r="G30" t="s">
-        <v>397</v>
-      </c>
-      <c r="H30" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C31" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D31" t="s">
+        <v>365</v>
+      </c>
+      <c r="E31" s="23" t="s">
         <v>366</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="F31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geoklan.jpg</v>
+      </c>
+      <c r="G31" t="s">
+        <v>397</v>
+      </c>
+      <c r="H31" t="s">
         <v>367</v>
-      </c>
-      <c r="F31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geoklan.jpg</v>
-      </c>
-      <c r="G31" t="s">
-        <v>398</v>
-      </c>
-      <c r="H31" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C32" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D32" t="s">
+        <v>365</v>
+      </c>
+      <c r="E32" s="23" t="s">
         <v>366</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laichee.jpg</v>
+      </c>
+      <c r="G32" t="s">
+        <v>398</v>
+      </c>
+      <c r="H32" t="s">
         <v>367</v>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laichee.jpg</v>
-      </c>
-      <c r="G32" t="s">
-        <v>399</v>
-      </c>
-      <c r="H32" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C33" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D33" t="s">
+        <v>365</v>
+      </c>
+      <c r="E33" s="23" t="s">
         <v>366</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="F33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>beechoo.jpg</v>
+      </c>
+      <c r="G33" t="s">
+        <v>399</v>
+      </c>
+      <c r="H33" t="s">
         <v>367</v>
-      </c>
-      <c r="F33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>beechoo.jpg</v>
-      </c>
-      <c r="G33" t="s">
-        <v>400</v>
-      </c>
-      <c r="H33" t="s">
-        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -7435,7 +7502,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7443,15 +7510,15 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" t="s">
         <v>194</v>
-      </c>
-      <c r="B4" t="s">
-        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -7460,12 +7527,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7710,20 +7779,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7749,14 +7821,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1846" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51B5A042-067B-43E5-B57D-0E6429D0E16D}"/>
+  <xr:revisionPtr revIDLastSave="1851" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAA30EA4-B1D6-49B4-B551-A4D4347B7909}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$131</definedName>
   </definedNames>
   <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="590">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1806,6 +1806,12 @@
   </si>
   <si>
     <t>宋大峰祖师诞辰, 南凤善堂, 10am</t>
+  </si>
+  <si>
+    <t>Bursary award at NHST, 10.30am</t>
+  </si>
+  <si>
+    <t>Bursary Award at NHST</t>
   </si>
 </sst>
 </file>
@@ -2593,7 +2599,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -4471,7 +4477,7 @@
         <v>46329</v>
       </c>
       <c r="B87" s="36" t="str">
-        <f t="shared" ref="B87:B129" si="2">TEXT($A87,"ddd")</f>
+        <f t="shared" ref="B87:B130" si="2">TEXT($A87,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="C87" s="40" t="s">
@@ -4599,656 +4605,654 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="35">
+        <f>DATE(2026,12,7)</f>
+        <v>46363</v>
+      </c>
+      <c r="B93" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C93" s="40" t="s">
+        <v>588</v>
+      </c>
+      <c r="D93" s="40"/>
+      <c r="E93" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="F93" s="40" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="35">
         <f>DATE(2026,12,11)</f>
         <v>46367</v>
       </c>
-      <c r="B93" s="36" t="str">
+      <c r="B94" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C93" s="40" t="s">
+      <c r="C94" s="40" t="s">
         <v>582</v>
       </c>
-      <c r="D93" s="40" t="s">
+      <c r="D94" s="40" t="s">
         <v>583</v>
       </c>
-      <c r="E93" s="40" t="s">
+      <c r="E94" s="40" t="s">
         <v>231</v>
       </c>
-      <c r="F93" s="44" t="s">
+      <c r="F94" s="44" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="35">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B94" s="36" t="str">
+      <c r="B95" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C94" s="40" t="s">
+      <c r="C95" s="40" t="s">
         <v>459</v>
       </c>
-      <c r="D94" s="40" t="s">
+      <c r="D95" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="E94" s="37" t="s">
+      <c r="E95" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F94" s="25" t="s">
+      <c r="F95" s="25" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="35">
         <f>DATE(2026,12,25)</f>
         <v>46381</v>
       </c>
-      <c r="B95" s="36" t="str">
-        <f>TEXT($A95,"ddd")</f>
+      <c r="B96" s="36" t="str">
+        <f>TEXT($A96,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C95" s="37" t="s">
+      <c r="C96" s="37" t="s">
         <v>464</v>
       </c>
-      <c r="D95" s="37" t="s">
+      <c r="D96" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="E95" s="39" t="s">
+      <c r="E96" s="39" t="s">
         <v>466</v>
       </c>
-      <c r="F95" s="25" t="s">
+      <c r="F96" s="25" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="12">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B96" s="13" t="str">
-        <f>TEXT($A96,"ddd")</f>
+      <c r="B97" s="13" t="str">
+        <f>TEXT($A97,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C96" s="11" t="s">
+      <c r="C97" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="D96" s="11" t="s">
+      <c r="D97" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="E96" s="38" t="s">
+      <c r="E97" s="38" t="s">
         <v>466</v>
       </c>
-      <c r="F96" s="25" t="s">
+      <c r="F97" s="25" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="31">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="31">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B97" s="32" t="str">
+      <c r="B98" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C97" s="43" t="s">
+      <c r="C98" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="D97" s="33" t="s">
+      <c r="D98" s="33" t="s">
         <v>206</v>
       </c>
-      <c r="E97" s="33" t="s">
+      <c r="E98" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F97" s="25" t="s">
+      <c r="F98" s="25" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="35">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B98" s="36" t="str">
+      <c r="B99" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C98" s="37" t="s">
+      <c r="C99" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="D98" s="37" t="s">
+      <c r="D99" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="E98" s="37" t="s">
+      <c r="E99" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F98" s="25" t="s">
+      <c r="F99" s="25" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="35">
         <f>DATE(2027,2,6)</f>
         <v>46424</v>
       </c>
-      <c r="B99" s="36" t="str">
-        <f>TEXT($A99,"ddd")</f>
+      <c r="B100" s="36" t="str">
+        <f>TEXT($A100,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C99" s="37" t="s">
+      <c r="C100" s="37" t="s">
         <v>482</v>
       </c>
-      <c r="D99" s="37" t="s">
+      <c r="D100" s="37" t="s">
         <v>483</v>
       </c>
-      <c r="E99" s="39" t="s">
+      <c r="E100" s="39" t="s">
         <v>466</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="F100" s="25" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="35">
         <f>DATE(2027,2,7)</f>
         <v>46425</v>
       </c>
-      <c r="B100" s="36" t="str">
-        <f>TEXT($A100,"ddd")</f>
+      <c r="B101" s="36" t="str">
+        <f>TEXT($A101,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C100" s="37" t="s">
+      <c r="C101" s="37" t="s">
         <v>484</v>
       </c>
-      <c r="D100" s="37" t="s">
+      <c r="D101" s="37" t="s">
         <v>485</v>
       </c>
-      <c r="E100" s="39" t="s">
+      <c r="E101" s="39" t="s">
         <v>466</v>
       </c>
-      <c r="F100" s="25" t="s">
+      <c r="F101" s="25" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="12">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B101" s="13" t="str">
-        <f>TEXT($A101,"ddd")</f>
+      <c r="B102" s="13" t="str">
+        <f>TEXT($A102,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C102" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="D101" s="11" t="s">
+      <c r="D102" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="E101" s="38" t="s">
+      <c r="E102" s="38" t="s">
         <v>466</v>
       </c>
-      <c r="F101" s="25" t="s">
+      <c r="F102" s="25" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="41">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B102" s="42" t="str">
+      <c r="B103" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C102" s="25" t="s">
+      <c r="C103" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="D102" s="25" t="s">
+      <c r="D103" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="E102" s="25" t="s">
+      <c r="E103" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="F102" s="26" t="s">
+      <c r="F103" s="26" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="12">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="12">
         <f>DATE(2027,3,10)</f>
         <v>46456</v>
       </c>
-      <c r="B103" s="13" t="str">
-        <f>TEXT($A103,"ddd")</f>
+      <c r="B104" s="13" t="str">
+        <f>TEXT($A104,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C104" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="D103" s="11" t="s">
+      <c r="D104" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="E103" s="38" t="s">
+      <c r="E104" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="F103" s="25" t="s">
+      <c r="F104" s="25" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="31">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="31">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B104" s="32" t="str">
+      <c r="B105" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C104" s="33" t="s">
+      <c r="C105" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="D104" s="33" t="s">
+      <c r="D105" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="E104" s="33" t="s">
+      <c r="E105" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F104" s="26" t="s">
+      <c r="F105" s="26" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="35">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B105" s="36" t="str">
+      <c r="B106" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C105" s="37" t="s">
+      <c r="C106" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="D105" s="37" t="s">
+      <c r="D106" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="E105" s="37" t="s">
+      <c r="E106" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F105" s="26" t="s">
+      <c r="F106" s="26" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="12">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="12">
         <f>DATE(2027,3,26)</f>
         <v>46472</v>
       </c>
-      <c r="B106" s="13" t="str">
-        <f>TEXT($A106,"ddd")</f>
+      <c r="B107" s="13" t="str">
+        <f>TEXT($A107,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C106" s="11" t="s">
+      <c r="C107" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="D106" s="11" t="s">
+      <c r="D107" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="E106" s="38" t="s">
+      <c r="E107" s="38" t="s">
         <v>466</v>
       </c>
-      <c r="F106" s="25" t="s">
+      <c r="F107" s="25" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="31">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="31">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B107" s="32" t="str">
+      <c r="B108" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C107" s="43" t="s">
+      <c r="C108" s="43" t="s">
         <v>221</v>
       </c>
-      <c r="D107" s="33" t="s">
+      <c r="D108" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="E107" s="33" t="s">
+      <c r="E108" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="F107" s="26" t="s">
+      <c r="F108" s="26" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="35">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B108" s="36" t="str">
+      <c r="B109" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C108" s="37" t="s">
+      <c r="C109" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D108" s="37" t="s">
+      <c r="D109" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="E108" s="37" t="s">
+      <c r="E109" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F108" s="26" t="s">
+      <c r="F109" s="26" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="35">
         <f>DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="B109" s="36" t="str">
-        <f>TEXT($A109,"ddd")</f>
+      <c r="B110" s="36" t="str">
+        <f>TEXT($A110,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C109" s="37" t="s">
+      <c r="C110" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="D109" s="37" t="s">
+      <c r="D110" s="37" t="s">
         <v>474</v>
       </c>
-      <c r="E109" s="39" t="s">
+      <c r="E110" s="39" t="s">
         <v>466</v>
       </c>
-      <c r="F109" s="25" t="s">
+      <c r="F110" s="25" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="12">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="12">
         <f>DATE(2027,5,17)</f>
         <v>46524</v>
       </c>
-      <c r="B110" s="13" t="str">
-        <f>TEXT($A110,"ddd")</f>
+      <c r="B111" s="13" t="str">
+        <f>TEXT($A111,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C111" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="D110" s="11" t="s">
+      <c r="D111" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="E110" s="38" t="s">
+      <c r="E111" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="F110" s="25" t="s">
+      <c r="F111" s="25" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="41">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="41">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B111" s="42" t="str">
+      <c r="B112" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C111" s="25" t="s">
+      <c r="C112" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="D111" s="25" t="s">
+      <c r="D112" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="E111" s="25" t="s">
+      <c r="E112" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="F111" s="26" t="s">
+      <c r="F112" s="26" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="12">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B112" s="13" t="str">
-        <f>TEXT($A112,"ddd")</f>
+      <c r="B113" s="13" t="str">
+        <f>TEXT($A113,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C113" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="D112" s="11" t="s">
+      <c r="D113" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="E112" s="38" t="s">
+      <c r="E113" s="38" t="s">
         <v>466</v>
       </c>
-      <c r="F112" s="25" t="s">
+      <c r="F113" s="25" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="31">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="31">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B113" s="32" t="str">
+      <c r="B114" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C113" s="33" t="s">
+      <c r="C114" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="D113" s="33" t="s">
+      <c r="D114" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="E113" s="33" t="s">
+      <c r="E114" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="F113" s="26" t="s">
+      <c r="F114" s="26" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="12">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B114" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="E114" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="F114" s="26" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B115" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>121</v>
+        <v>231</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>445</v>
+        <v>413</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B116" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>249</v>
+        <v>173</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B117" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C117" s="16" t="s">
-        <v>451</v>
+      <c r="C117" s="11" t="s">
+        <v>249</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>452</v>
+        <v>208</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F117" s="25" t="s">
+      <c r="F117" s="26" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="12">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B118" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F118" s="25" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="35">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B118" s="36" t="str">
+      <c r="B119" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C118" s="37" t="s">
+      <c r="C119" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="D118" s="37" t="s">
+      <c r="D119" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="E118" s="37" t="s">
+      <c r="E119" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F118" s="26" t="s">
+      <c r="F119" s="26" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="12">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="12">
         <f>DATE(2027,8,9)</f>
         <v>46608</v>
       </c>
-      <c r="B119" s="13" t="str">
-        <f>TEXT($A119,"ddd")</f>
+      <c r="B120" s="13" t="str">
+        <f>TEXT($A120,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C119" s="11" t="s">
+      <c r="C120" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="D119" s="11" t="s">
+      <c r="D120" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="E119" s="38" t="s">
+      <c r="E120" s="38" t="s">
         <v>466</v>
       </c>
-      <c r="F119" s="25" t="s">
+      <c r="F120" s="25" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="31">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="31">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B120" s="32" t="str">
+      <c r="B121" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C120" s="33" t="s">
+      <c r="C121" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="D120" s="33" t="s">
+      <c r="D121" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="E120" s="33" t="s">
+      <c r="E121" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="F120" s="26" t="s">
+      <c r="F121" s="26" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="12">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
-      </c>
-      <c r="B121" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C121" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="D121" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="E121" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F121" s="26" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
       </c>
       <c r="B122" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E122" s="11" t="s">
         <v>124</v>
@@ -5259,182 +5263,204 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B123" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E123" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F123" s="26" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B123" s="13" t="str">
+      <c r="B124" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C124" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D123" s="11" t="s">
+      <c r="D124" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E123" s="11" t="s">
+      <c r="E124" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F123" s="26" t="s">
+      <c r="F124" s="26" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="12">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
       </c>
-      <c r="B124" s="13" t="str">
+      <c r="B125" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C125" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="D124" s="11" t="s">
+      <c r="D125" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="E124" s="11" t="s">
+      <c r="E125" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F124" s="26" t="s">
+      <c r="F125" s="26" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="35">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B125" s="36" t="str">
+      <c r="B126" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C125" s="37" t="s">
+      <c r="C126" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D125" s="37" t="s">
+      <c r="D126" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="E125" s="37" t="s">
+      <c r="E126" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F125" s="26" t="s">
+      <c r="F126" s="26" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="12">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="12">
         <f>DATE(2027,10,28)</f>
         <v>46688</v>
       </c>
-      <c r="B126" s="13" t="str">
-        <f>TEXT($A126,"ddd")</f>
+      <c r="B127" s="13" t="str">
+        <f>TEXT($A127,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C126" s="11" t="s">
+      <c r="C127" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="D126" s="11" t="s">
+      <c r="D127" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="E126" s="38" t="s">
+      <c r="E127" s="38" t="s">
         <v>466</v>
       </c>
-      <c r="F126" s="25" t="s">
+      <c r="F127" s="25" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="31">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="31">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B127" s="32" t="str">
+      <c r="B128" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C127" s="33" t="s">
+      <c r="C128" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="D127" s="33" t="s">
+      <c r="D128" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="E127" s="33" t="s">
+      <c r="E128" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F127" s="26" t="s">
+      <c r="F128" s="26" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="12">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B128" s="13" t="str">
+      <c r="B129" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C128" s="16" t="s">
+      <c r="C129" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D129" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="E128" s="11" t="s">
+      <c r="E129" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F128" s="25" t="s">
+      <c r="F129" s="25" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" s="35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B129" s="36" t="str">
+      <c r="B130" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C129" s="37" t="s">
+      <c r="C130" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D129" s="40" t="s">
+      <c r="D130" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="E129" s="37" t="s">
+      <c r="E130" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F129" s="26" t="s">
+      <c r="F130" s="26" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" s="12">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B130" s="13" t="str">
-        <f>TEXT($A130,"ddd")</f>
+      <c r="B131" s="13" t="str">
+        <f>TEXT($A131,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C130" s="11" t="s">
+      <c r="C131" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="D130" s="11" t="s">
+      <c r="D131" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="E130" s="38" t="s">
+      <c r="E131" s="38" t="s">
         <v>466</v>
       </c>
-      <c r="F130" s="25" t="s">
+      <c r="F131" s="25" t="s">
         <v>508</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E130" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E131" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1851" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAA30EA4-B1D6-49B4-B551-A4D4347B7909}"/>
+  <xr:revisionPtr revIDLastSave="1854" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F9423F7-D5FA-4268-8F19-733BFADDD9D1}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="589">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -656,9 +656,6 @@
     <t>[未确认] 屠妖节红包派发（AMS印族受惠者）</t>
   </si>
   <si>
-    <t>[未确认] MS项目物资派发（日期待定）</t>
-  </si>
-  <si>
     <t>[未确认] 「认捐拥抱・温暖长者」慈善运动（圣诞前实体推介）</t>
   </si>
   <si>
@@ -1424,9 +1421,6 @@
     <t>[Tentative] Sponsor a HUG Campaign (Physical Launch Closer to Christmas). (In charge: Chi Hwee, Jin Hoa)</t>
   </si>
   <si>
-    <t>[Tentative] MS Project Ration Distribution (Date Unconfirmed). (In charge: Chi Hwee)</t>
-  </si>
-  <si>
     <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon dinner for NHWSS elderly (200 pax) - all to arrive by 7pm</t>
   </si>
   <si>
@@ -1812,6 +1806,9 @@
   </si>
   <si>
     <t>Bursary Award at NHST</t>
+  </si>
+  <si>
+    <t>MS Project Ration Distribution (200 pax). (In charge: Bryan)</t>
   </si>
 </sst>
 </file>
@@ -2489,7 +2486,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2626,7 +2623,7 @@
         <v>134</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2639,16 +2636,16 @@
         <v>Thu</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2670,7 +2667,7 @@
         <v>124</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2683,16 +2680,16 @@
         <v>Sun</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2714,7 +2711,7 @@
         <v>121</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2727,16 +2724,16 @@
         <v>Tue</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2749,16 +2746,16 @@
         <v>Wed</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2780,7 +2777,7 @@
         <v>131</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2802,7 +2799,7 @@
         <v>121</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2824,7 +2821,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2846,7 +2843,7 @@
         <v>124</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2859,16 +2856,16 @@
         <v>Sat</v>
       </c>
       <c r="C12" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>570</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>572</v>
-      </c>
       <c r="E12" s="38" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2881,16 +2878,16 @@
         <v>Sat</v>
       </c>
       <c r="C13" s="44" t="s">
+        <v>569</v>
+      </c>
+      <c r="D13" s="44" t="s">
         <v>571</v>
-      </c>
-      <c r="D13" s="44" t="s">
-        <v>573</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2912,7 +2909,7 @@
         <v>121</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2934,7 +2931,7 @@
         <v>121</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2950,13 +2947,13 @@
         <v>128</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E16" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2969,16 +2966,16 @@
         <v>Fri</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2994,13 +2991,13 @@
         <v>130</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -3013,16 +3010,16 @@
         <v>Fri</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -3044,7 +3041,7 @@
         <v>129</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3060,13 +3057,13 @@
         <v>147</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3082,13 +3079,13 @@
         <v>148</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -3110,7 +3107,7 @@
         <v>121</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -3123,16 +3120,16 @@
         <v>Wed</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -3151,10 +3148,10 @@
         <v>151</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -3173,10 +3170,10 @@
         <v>153</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -3189,16 +3186,16 @@
         <v>Sun</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3211,16 +3208,16 @@
         <v>Mon</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -3239,10 +3236,10 @@
         <v>155</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -3261,10 +3258,10 @@
         <v>157</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -3280,13 +3277,13 @@
         <v>128</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -3308,7 +3305,7 @@
         <v>121</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -3324,13 +3321,13 @@
         <v>128</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -3352,7 +3349,7 @@
         <v>124</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -3365,16 +3362,16 @@
         <v>Mon</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -3396,7 +3393,7 @@
         <v>124</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3412,13 +3409,13 @@
         <v>128</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3434,13 +3431,13 @@
         <v>128</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3453,16 +3450,16 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>222</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>223</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3475,16 +3472,16 @@
         <v>Wed</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -3497,16 +3494,16 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3519,16 +3516,16 @@
         <v>Sun</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3541,16 +3538,16 @@
         <v>Mon</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3563,16 +3560,16 @@
         <v>Fri</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3585,16 +3582,16 @@
         <v>Sat</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3607,16 +3604,16 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3629,16 +3626,16 @@
         <v>Sun</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3651,7 +3648,7 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>161</v>
@@ -3660,7 +3657,7 @@
         <v>124</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3673,16 +3670,16 @@
         <v>Sat</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -3695,16 +3692,16 @@
         <v>Sat</v>
       </c>
       <c r="C50" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="D50" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="D50" s="11" t="s">
-        <v>455</v>
-      </c>
       <c r="E50" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3717,16 +3714,16 @@
         <v>Mon</v>
       </c>
       <c r="C51" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D51" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D51" s="21" t="s">
-        <v>248</v>
-      </c>
       <c r="E51" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3739,14 +3736,14 @@
         <v>Tue</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3759,16 +3756,16 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -3781,16 +3778,16 @@
         <v>Thu</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3803,16 +3800,16 @@
         <v>Thu</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3825,16 +3822,16 @@
         <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3847,14 +3844,14 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3867,7 +3864,7 @@
         <v>Sat</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>162</v>
@@ -3876,7 +3873,7 @@
         <v>124</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G58" s="19"/>
     </row>
@@ -3890,14 +3887,14 @@
         <v>Sat</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G59" s="19"/>
     </row>
@@ -3911,16 +3908,16 @@
         <v>Mon</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3933,16 +3930,16 @@
         <v>Tue</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3955,14 +3952,14 @@
         <v>Tue</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3975,16 +3972,16 @@
         <v>Wed</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3997,14 +3994,14 @@
         <v>Wed</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -4017,16 +4014,16 @@
         <v>Wed</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -4039,14 +4036,14 @@
         <v>Wed</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -4059,14 +4056,14 @@
         <v>Thu</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -4079,14 +4076,14 @@
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F68" s="25" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4099,14 +4096,14 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4119,16 +4116,16 @@
         <v>Sat</v>
       </c>
       <c r="C70" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="D70" s="11" t="s">
         <v>517</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>519</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -4141,16 +4138,16 @@
         <v>Sat</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -4163,7 +4160,7 @@
         <v>Sun</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>163</v>
@@ -4172,7 +4169,7 @@
         <v>124</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -4185,14 +4182,14 @@
         <v>Wed</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -4205,14 +4202,14 @@
         <v>Wed</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -4225,14 +4222,14 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="11" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F75" s="25" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -4245,16 +4242,16 @@
         <v>Fri</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="51" x14ac:dyDescent="0.35">
@@ -4267,16 +4264,16 @@
         <v>Fri</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -4289,16 +4286,16 @@
         <v>Sat</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -4311,14 +4308,14 @@
         <v>Mon</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D79" s="11"/>
       <c r="E79" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -4337,10 +4334,10 @@
         <v>200</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -4359,10 +4356,10 @@
         <v>201</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
@@ -4381,10 +4378,10 @@
         <v>202</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
@@ -4397,14 +4394,14 @@
         <v>Thu</v>
       </c>
       <c r="C83" s="40" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D83" s="37"/>
       <c r="E83" s="37" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F83" s="25" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
@@ -4417,16 +4414,16 @@
         <v>Tue</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E84" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
@@ -4439,16 +4436,16 @@
         <v>Mon</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E85" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -4461,14 +4458,14 @@
         <v>Tue</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D86" s="25"/>
       <c r="E86" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -4490,7 +4487,7 @@
         <v>121</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
@@ -4503,16 +4500,16 @@
         <v>Sun</v>
       </c>
       <c r="C88" s="37" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D88" s="37" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E88" s="39" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F88" s="25" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -4525,38 +4522,36 @@
         <v>Mon</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E89" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F89" s="25" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="31">
-        <f>DATE(2026,11,10)</f>
-        <v>46336</v>
+        <f>DATE(2026,11,28)</f>
+        <v>46354</v>
       </c>
       <c r="B90" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>Tue</v>
+        <v>Sat</v>
       </c>
       <c r="C90" s="43" t="s">
-        <v>460</v>
-      </c>
-      <c r="D90" s="33" t="s">
-        <v>204</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="D90" s="33"/>
       <c r="E90" s="33" t="s">
         <v>124</v>
       </c>
       <c r="F90" s="25" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
@@ -4569,16 +4564,16 @@
         <v>Tue</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E91" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
@@ -4591,16 +4586,16 @@
         <v>Mon</v>
       </c>
       <c r="C92" s="40" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D92" s="40" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F92" s="40" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
@@ -4613,14 +4608,14 @@
         <v>Mon</v>
       </c>
       <c r="C93" s="40" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D93" s="40"/>
       <c r="E93" s="40" t="s">
         <v>121</v>
       </c>
       <c r="F93" s="40" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
@@ -4633,16 +4628,16 @@
         <v>Fri</v>
       </c>
       <c r="C94" s="40" t="s">
+        <v>580</v>
+      </c>
+      <c r="D94" s="40" t="s">
+        <v>581</v>
+      </c>
+      <c r="E94" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="F94" s="44" t="s">
         <v>582</v>
-      </c>
-      <c r="D94" s="40" t="s">
-        <v>583</v>
-      </c>
-      <c r="E94" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="F94" s="44" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -4655,16 +4650,16 @@
         <v>Wed</v>
       </c>
       <c r="C95" s="40" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D95" s="40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E95" s="37" t="s">
         <v>131</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
@@ -4677,16 +4672,16 @@
         <v>Fri</v>
       </c>
       <c r="C96" s="37" t="s">
+        <v>462</v>
+      </c>
+      <c r="D96" s="37" t="s">
+        <v>463</v>
+      </c>
+      <c r="E96" s="39" t="s">
         <v>464</v>
       </c>
-      <c r="D96" s="37" t="s">
-        <v>465</v>
-      </c>
-      <c r="E96" s="39" t="s">
-        <v>466</v>
-      </c>
       <c r="F96" s="25" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
@@ -4699,16 +4694,16 @@
         <v>Fri</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E97" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
@@ -4721,16 +4716,16 @@
         <v>Fri</v>
       </c>
       <c r="C98" s="43" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D98" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E98" s="33" t="s">
         <v>131</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
@@ -4746,13 +4741,13 @@
         <v>167</v>
       </c>
       <c r="D99" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E99" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
@@ -4765,16 +4760,16 @@
         <v>Sat</v>
       </c>
       <c r="C100" s="37" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D100" s="37" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E100" s="39" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F100" s="25" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
@@ -4787,16 +4782,16 @@
         <v>Sun</v>
       </c>
       <c r="C101" s="37" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D101" s="37" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E101" s="39" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F101" s="25" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
@@ -4809,16 +4804,16 @@
         <v>Mon</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E102" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
@@ -4831,16 +4826,16 @@
         <v>Thu</v>
       </c>
       <c r="C103" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="D103" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="D103" s="25" t="s">
-        <v>234</v>
-      </c>
       <c r="E103" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
@@ -4853,16 +4848,16 @@
         <v>Wed</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E104" s="38" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F104" s="25" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
@@ -4878,13 +4873,13 @@
         <v>168</v>
       </c>
       <c r="D105" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E105" s="33" t="s">
         <v>124</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
@@ -4900,13 +4895,13 @@
         <v>169</v>
       </c>
       <c r="D106" s="37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E106" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
@@ -4919,16 +4914,16 @@
         <v>Fri</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E107" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F107" s="25" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
@@ -4941,16 +4936,16 @@
         <v>Sat</v>
       </c>
       <c r="C108" s="43" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D108" s="33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E108" s="33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -4966,13 +4961,13 @@
         <v>168</v>
       </c>
       <c r="D109" s="37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E109" s="37" t="s">
         <v>124</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -4985,16 +4980,16 @@
         <v>Sat</v>
       </c>
       <c r="C110" s="37" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D110" s="37" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E110" s="39" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F110" s="25" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -5007,16 +5002,16 @@
         <v>Mon</v>
       </c>
       <c r="C111" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="E111" s="38" t="s">
         <v>475</v>
       </c>
-      <c r="D111" s="11" t="s">
-        <v>476</v>
-      </c>
-      <c r="E111" s="38" t="s">
-        <v>477</v>
-      </c>
       <c r="F111" s="25" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
@@ -5032,13 +5027,13 @@
         <v>170</v>
       </c>
       <c r="D112" s="25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E112" s="25" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -5051,16 +5046,16 @@
         <v>Thu</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E113" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F113" s="25" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
@@ -5076,13 +5071,13 @@
         <v>171</v>
       </c>
       <c r="D114" s="33" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E114" s="33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F114" s="26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
@@ -5098,13 +5093,13 @@
         <v>172</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
@@ -5120,13 +5115,13 @@
         <v>173</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E116" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
@@ -5139,16 +5134,16 @@
         <v>Fri</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F117" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
@@ -5161,16 +5156,16 @@
         <v>Fri</v>
       </c>
       <c r="C118" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="D118" s="11" t="s">
         <v>451</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>452</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F118" s="25" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
@@ -5186,13 +5181,13 @@
         <v>174</v>
       </c>
       <c r="D119" s="37" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E119" s="37" t="s">
         <v>124</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
@@ -5205,16 +5200,16 @@
         <v>Mon</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E120" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F120" s="25" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
@@ -5230,13 +5225,13 @@
         <v>175</v>
       </c>
       <c r="D121" s="33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E121" s="33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
@@ -5252,13 +5247,13 @@
         <v>176</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E122" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
@@ -5274,13 +5269,13 @@
         <v>168</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E123" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F123" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -5296,13 +5291,13 @@
         <v>177</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E124" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -5318,13 +5313,13 @@
         <v>168</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E125" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
@@ -5340,13 +5335,13 @@
         <v>168</v>
       </c>
       <c r="D126" s="37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E126" s="37" t="s">
         <v>124</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5359,16 +5354,16 @@
         <v>Thu</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E127" s="38" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F127" s="25" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5384,13 +5379,13 @@
         <v>168</v>
       </c>
       <c r="D128" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E128" s="33" t="s">
         <v>124</v>
       </c>
       <c r="F128" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5403,16 +5398,16 @@
         <v>Fri</v>
       </c>
       <c r="C129" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="D129" s="11" t="s">
         <v>451</v>
-      </c>
-      <c r="D129" s="11" t="s">
-        <v>452</v>
       </c>
       <c r="E129" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F129" s="25" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
@@ -5428,13 +5423,13 @@
         <v>165</v>
       </c>
       <c r="D130" s="40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E130" s="37" t="s">
         <v>131</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
@@ -5447,16 +5442,16 @@
         <v>Sat</v>
       </c>
       <c r="C131" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="E131" s="38" t="s">
         <v>464</v>
       </c>
-      <c r="D131" s="11" t="s">
-        <v>465</v>
-      </c>
-      <c r="E131" s="38" t="s">
-        <v>466</v>
-      </c>
       <c r="F131" s="25" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -5683,7 +5678,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>96</v>
@@ -5935,7 +5930,7 @@
         <v>109</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>93</v>
@@ -5955,7 +5950,7 @@
         <v>109</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>86</v>
@@ -5975,7 +5970,7 @@
         <v>109</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>101</v>
@@ -5995,7 +5990,7 @@
         <v>109</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>88</v>
@@ -6015,7 +6010,7 @@
         <v>109</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>90</v>
@@ -6384,7 +6379,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -6663,839 +6658,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" t="s">
         <v>252</v>
       </c>
-      <c r="C2" t="s">
-        <v>253</v>
-      </c>
       <c r="D2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E2" t="s">
         <v>348</v>
-      </c>
-      <c r="E2" t="s">
-        <v>349</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" t="s">
         <v>350</v>
-      </c>
-      <c r="E3" t="s">
-        <v>351</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4" t="s">
         <v>352</v>
       </c>
-      <c r="E4" t="s">
-        <v>353</v>
-      </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D14" t="s">
+        <v>362</v>
+      </c>
+      <c r="E14" t="s">
         <v>363</v>
       </c>
-      <c r="E14" t="s">
-        <v>364</v>
-      </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
       <c r="G14" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D15" t="s">
+        <v>362</v>
+      </c>
+      <c r="E15" t="s">
         <v>363</v>
       </c>
-      <c r="E15" t="s">
-        <v>364</v>
-      </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
       <c r="G15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D16" t="s">
+        <v>362</v>
+      </c>
+      <c r="E16" t="s">
         <v>363</v>
       </c>
-      <c r="E16" t="s">
-        <v>364</v>
-      </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
       <c r="G16" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C17" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D17" t="s">
+        <v>362</v>
+      </c>
+      <c r="E17" t="s">
         <v>363</v>
       </c>
-      <c r="E17" t="s">
-        <v>364</v>
-      </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
       <c r="G17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C18" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D18" t="s">
+        <v>362</v>
+      </c>
+      <c r="E18" t="s">
         <v>363</v>
       </c>
-      <c r="E18" t="s">
-        <v>364</v>
-      </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
       <c r="G18" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H18" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D19" t="s">
+        <v>362</v>
+      </c>
+      <c r="E19" t="s">
         <v>363</v>
       </c>
-      <c r="E19" t="s">
-        <v>364</v>
-      </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
       <c r="G19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D20" t="s">
+        <v>362</v>
+      </c>
+      <c r="E20" t="s">
         <v>363</v>
       </c>
-      <c r="E20" t="s">
-        <v>364</v>
-      </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
       <c r="G20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D21" t="s">
+        <v>362</v>
+      </c>
+      <c r="E21" t="s">
         <v>363</v>
       </c>
-      <c r="E21" t="s">
-        <v>364</v>
-      </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
       <c r="G21" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H21" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D22" t="s">
+        <v>362</v>
+      </c>
+      <c r="E22" t="s">
         <v>363</v>
       </c>
-      <c r="E22" t="s">
-        <v>364</v>
-      </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
       <c r="G22" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H22" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C23" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D23" t="s">
+        <v>362</v>
+      </c>
+      <c r="E23" t="s">
         <v>363</v>
       </c>
-      <c r="E23" t="s">
-        <v>364</v>
-      </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
       <c r="G23" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H23" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D24" t="s">
+        <v>362</v>
+      </c>
+      <c r="E24" t="s">
         <v>363</v>
       </c>
-      <c r="E24" t="s">
-        <v>364</v>
-      </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
       <c r="G24" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H24" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B25" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C25" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D25" t="s">
+        <v>364</v>
+      </c>
+      <c r="E25" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="F25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geokchin.jpg</v>
+      </c>
+      <c r="G25" t="s">
+        <v>390</v>
+      </c>
+      <c r="H25" t="s">
         <v>366</v>
-      </c>
-      <c r="F25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geokchin.jpg</v>
-      </c>
-      <c r="G25" t="s">
-        <v>391</v>
-      </c>
-      <c r="H25" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C26" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D26" t="s">
+        <v>364</v>
+      </c>
+      <c r="E26" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laysiew.jpg</v>
+      </c>
+      <c r="G26" t="s">
+        <v>391</v>
+      </c>
+      <c r="H26" t="s">
         <v>366</v>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laysiew.jpg</v>
-      </c>
-      <c r="G26" t="s">
-        <v>392</v>
-      </c>
-      <c r="H26" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C27" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D27" t="s">
+        <v>364</v>
+      </c>
+      <c r="E27" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="F27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>waiyee.jpg</v>
+      </c>
+      <c r="G27" t="s">
+        <v>392</v>
+      </c>
+      <c r="H27" t="s">
         <v>366</v>
-      </c>
-      <c r="F27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>waiyee.jpg</v>
-      </c>
-      <c r="G27" t="s">
-        <v>393</v>
-      </c>
-      <c r="H27" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C28" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D28" t="s">
+        <v>364</v>
+      </c>
+      <c r="E28" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>carol.jpg</v>
+      </c>
+      <c r="G28" t="s">
+        <v>393</v>
+      </c>
+      <c r="H28" t="s">
         <v>366</v>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>carol.jpg</v>
-      </c>
-      <c r="G28" t="s">
-        <v>394</v>
-      </c>
-      <c r="H28" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C29" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D29" t="s">
+        <v>364</v>
+      </c>
+      <c r="E29" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="F29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yokewant.jpg</v>
+      </c>
+      <c r="G29" t="s">
+        <v>394</v>
+      </c>
+      <c r="H29" t="s">
         <v>366</v>
-      </c>
-      <c r="F29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>yokewant.jpg</v>
-      </c>
-      <c r="G29" t="s">
-        <v>395</v>
-      </c>
-      <c r="H29" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D30" t="s">
+        <v>364</v>
+      </c>
+      <c r="E30" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pohcheng.jpg</v>
+      </c>
+      <c r="G30" t="s">
+        <v>395</v>
+      </c>
+      <c r="H30" t="s">
         <v>366</v>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>pohcheng.jpg</v>
-      </c>
-      <c r="G30" t="s">
-        <v>396</v>
-      </c>
-      <c r="H30" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D31" t="s">
+        <v>364</v>
+      </c>
+      <c r="E31" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="F31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geoklan.jpg</v>
+      </c>
+      <c r="G31" t="s">
+        <v>396</v>
+      </c>
+      <c r="H31" t="s">
         <v>366</v>
-      </c>
-      <c r="F31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geoklan.jpg</v>
-      </c>
-      <c r="G31" t="s">
-        <v>397</v>
-      </c>
-      <c r="H31" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B32" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C32" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D32" t="s">
+        <v>364</v>
+      </c>
+      <c r="E32" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laichee.jpg</v>
+      </c>
+      <c r="G32" t="s">
+        <v>397</v>
+      </c>
+      <c r="H32" t="s">
         <v>366</v>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laichee.jpg</v>
-      </c>
-      <c r="G32" t="s">
-        <v>398</v>
-      </c>
-      <c r="H32" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B33" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C33" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D33" t="s">
+        <v>364</v>
+      </c>
+      <c r="E33" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="F33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>beechoo.jpg</v>
+      </c>
+      <c r="G33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H33" t="s">
         <v>366</v>
-      </c>
-      <c r="F33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>beechoo.jpg</v>
-      </c>
-      <c r="G33" t="s">
-        <v>399</v>
-      </c>
-      <c r="H33" t="s">
-        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -7528,7 +7523,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7536,7 +7531,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -7553,14 +7548,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7805,23 +7798,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7847,9 +7837,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1854" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F9423F7-D5FA-4268-8F19-733BFADDD9D1}"/>
+  <xr:revisionPtr revIDLastSave="1869" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE9DBFA3-E7E1-489D-A463-7773509FA6BB}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$130</definedName>
   </definedNames>
   <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="587">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -542,9 +542,6 @@
     <t>[Tentative] Sponsor a HUG Campaign (Physical Launch Closer to Christmas)</t>
   </si>
   <si>
-    <t>[Tentative] Deepavali Ang Pao Distribution (AMS Hindus)</t>
-  </si>
-  <si>
     <t>[Tentative] CNY Ration + Ang Bao</t>
   </si>
   <si>
@@ -629,33 +626,12 @@
     <t>NHWSS2026</t>
   </si>
   <si>
-    <t>[Tentative] Nine Emperor Gods Festival Fundraiser – Day 1</t>
-  </si>
-  <si>
-    <t>[Tentative] Nine Emperor Gods Festival Fundraiser – Day 2</t>
-  </si>
-  <si>
-    <t>[Tentative] Nine Emperor Gods Festival Fundraiser – Day 3</t>
-  </si>
-  <si>
     <t>Naval Base Secondary School Outing</t>
   </si>
   <si>
     <t>海军部中学户外活动</t>
   </si>
   <si>
-    <t>[未确认] 九皇爷诞筹款第一天</t>
-  </si>
-  <si>
-    <t>[未确认] 九皇爷诞筹款第二天</t>
-  </si>
-  <si>
-    <t>[未确认] 九皇爷诞筹款第三天</t>
-  </si>
-  <si>
-    <t>[未确认] 屠妖节红包派发（AMS印族受惠者）</t>
-  </si>
-  <si>
     <t>[未确认] 「认捐拥抱・温暖长者」慈善运动（圣诞前实体推介）</t>
   </si>
   <si>
@@ -1643,12 +1619,6 @@
     <t>Wee Guan Construction 企业社会责任（80人）</t>
   </si>
   <si>
-    <t>[Tentative] CSR Partnership - Corporate (open slot)</t>
-  </si>
-  <si>
-    <t>[未确认]  企业社会责任合作</t>
-  </si>
-  <si>
     <t>Integrative Chinese &amp; Western Medicine Model of Care Symposium</t>
   </si>
   <si>
@@ -1809,6 +1779,30 @@
   </si>
   <si>
     <t>MS Project Ration Distribution (200 pax). (In charge: Bryan)</t>
+  </si>
+  <si>
+    <t>屠妖节红包派发（AMS印族受惠者）</t>
+  </si>
+  <si>
+    <t>Deepavali Ang Pao Distribution (AMS Hindus), actual day 9 Nov</t>
+  </si>
+  <si>
+    <t>Nine Emperor Gods Festival Fundraiser – Day 1</t>
+  </si>
+  <si>
+    <t>Nine Emperor Gods Festival Fundraiser – Day 2</t>
+  </si>
+  <si>
+    <t>Nine Emperor Gods Festival Fundraiser – Day 3</t>
+  </si>
+  <si>
+    <t>九皇爷诞筹款第一天</t>
+  </si>
+  <si>
+    <t>九皇爷诞筹款第二天</t>
+  </si>
+  <si>
+    <t>九皇爷诞筹款第三天</t>
   </si>
 </sst>
 </file>
@@ -2486,7 +2480,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2596,7 +2590,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -2623,7 +2617,7 @@
         <v>134</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2636,16 +2630,16 @@
         <v>Thu</v>
       </c>
       <c r="C2" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="F2" s="27" t="s">
         <v>486</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>487</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>464</v>
-      </c>
-      <c r="F2" s="27" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2667,7 +2661,7 @@
         <v>124</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2680,16 +2674,16 @@
         <v>Sun</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2711,7 +2705,7 @@
         <v>121</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2724,16 +2718,16 @@
         <v>Tue</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2746,16 +2740,16 @@
         <v>Wed</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2777,7 +2771,7 @@
         <v>131</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2799,7 +2793,7 @@
         <v>121</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2821,7 +2815,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2843,7 +2837,7 @@
         <v>124</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2856,16 +2850,16 @@
         <v>Sat</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2878,16 +2872,16 @@
         <v>Sat</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2909,7 +2903,7 @@
         <v>121</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2931,7 +2925,7 @@
         <v>121</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2947,13 +2941,13 @@
         <v>128</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E16" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2966,16 +2960,16 @@
         <v>Fri</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2991,13 +2985,13 @@
         <v>130</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -3010,16 +3004,16 @@
         <v>Fri</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -3041,7 +3035,7 @@
         <v>129</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3057,13 +3051,13 @@
         <v>147</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3079,13 +3073,13 @@
         <v>148</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -3107,7 +3101,7 @@
         <v>121</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -3120,16 +3114,16 @@
         <v>Wed</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -3148,10 +3142,10 @@
         <v>151</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -3170,10 +3164,10 @@
         <v>153</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -3186,16 +3180,16 @@
         <v>Sun</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3208,16 +3202,16 @@
         <v>Mon</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="D28" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>456</v>
+      </c>
+      <c r="F28" s="25" t="s">
         <v>493</v>
-      </c>
-      <c r="E28" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -3236,10 +3230,10 @@
         <v>155</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -3258,10 +3252,10 @@
         <v>157</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -3277,13 +3271,13 @@
         <v>128</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -3305,7 +3299,7 @@
         <v>121</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -3321,13 +3315,13 @@
         <v>128</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -3349,7 +3343,7 @@
         <v>124</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -3362,16 +3356,16 @@
         <v>Mon</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -3384,16 +3378,16 @@
         <v>Fri</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3409,13 +3403,13 @@
         <v>128</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3431,13 +3425,13 @@
         <v>128</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3450,16 +3444,16 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3472,16 +3466,16 @@
         <v>Wed</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -3494,16 +3488,16 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3516,16 +3510,16 @@
         <v>Sun</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3538,16 +3532,16 @@
         <v>Mon</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3560,16 +3554,16 @@
         <v>Fri</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3582,16 +3576,16 @@
         <v>Sat</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3604,16 +3598,16 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3626,16 +3620,16 @@
         <v>Sun</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3648,7 +3642,7 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>161</v>
@@ -3657,7 +3651,7 @@
         <v>124</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3670,16 +3664,16 @@
         <v>Sat</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -3692,16 +3686,16 @@
         <v>Sat</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3714,16 +3708,16 @@
         <v>Mon</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3736,14 +3730,14 @@
         <v>Tue</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="11" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3756,16 +3750,16 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -3778,16 +3772,16 @@
         <v>Thu</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3800,16 +3794,16 @@
         <v>Thu</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3822,16 +3816,16 @@
         <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3844,14 +3838,14 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="11" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3864,7 +3858,7 @@
         <v>Sat</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>162</v>
@@ -3873,7 +3867,7 @@
         <v>124</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="G58" s="19"/>
     </row>
@@ -3887,14 +3881,14 @@
         <v>Sat</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="G59" s="19"/>
     </row>
@@ -3908,16 +3902,16 @@
         <v>Mon</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3930,16 +3924,16 @@
         <v>Tue</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3952,14 +3946,14 @@
         <v>Tue</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="11" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3972,16 +3966,16 @@
         <v>Wed</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3994,14 +3988,14 @@
         <v>Wed</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -4014,16 +4008,16 @@
         <v>Wed</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -4036,14 +4030,14 @@
         <v>Wed</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -4056,14 +4050,14 @@
         <v>Thu</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -4076,14 +4070,14 @@
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="11" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F68" s="25" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4096,14 +4090,14 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4116,16 +4110,16 @@
         <v>Sat</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -4138,16 +4132,16 @@
         <v>Sat</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -4160,7 +4154,7 @@
         <v>Sun</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>163</v>
@@ -4169,7 +4163,7 @@
         <v>124</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -4182,14 +4176,14 @@
         <v>Wed</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -4202,14 +4196,14 @@
         <v>Wed</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -4222,14 +4216,14 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="11" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="F75" s="25" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -4242,16 +4236,16 @@
         <v>Fri</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="51" x14ac:dyDescent="0.35">
@@ -4264,16 +4258,16 @@
         <v>Fri</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -4286,16 +4280,16 @@
         <v>Sat</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -4308,14 +4302,14 @@
         <v>Mon</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="D79" s="11"/>
       <c r="E79" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -4327,17 +4321,17 @@
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C80" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="D80" s="11" t="s">
-        <v>200</v>
+      <c r="C80" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>584</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -4349,17 +4343,17 @@
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C81" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D81" s="11" t="s">
-        <v>201</v>
+      <c r="C81" s="16" t="s">
+        <v>582</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>585</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
@@ -4371,17 +4365,17 @@
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C82" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>202</v>
+      <c r="C82" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>586</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
@@ -4394,14 +4388,14 @@
         <v>Thu</v>
       </c>
       <c r="C83" s="40" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="D83" s="37"/>
       <c r="E83" s="37" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F83" s="25" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
@@ -4414,16 +4408,16 @@
         <v>Tue</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="E84" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
@@ -4436,16 +4430,16 @@
         <v>Mon</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="E85" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -4458,14 +4452,14 @@
         <v>Tue</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="D86" s="25"/>
       <c r="E86" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -4474,20 +4468,20 @@
         <v>46329</v>
       </c>
       <c r="B87" s="36" t="str">
-        <f t="shared" ref="B87:B130" si="2">TEXT($A87,"ddd")</f>
+        <f t="shared" ref="B87:B129" si="2">TEXT($A87,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="C87" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="D87" s="37" t="s">
-        <v>203</v>
+        <v>580</v>
+      </c>
+      <c r="D87" s="40" t="s">
+        <v>579</v>
       </c>
       <c r="E87" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
@@ -4500,16 +4494,16 @@
         <v>Sun</v>
       </c>
       <c r="C88" s="37" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="D88" s="37" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="E88" s="39" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F88" s="25" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -4522,16 +4516,16 @@
         <v>Mon</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E89" s="38" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F89" s="25" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
@@ -4544,36 +4538,36 @@
         <v>Sat</v>
       </c>
       <c r="C90" s="43" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="D90" s="33"/>
       <c r="E90" s="33" t="s">
         <v>124</v>
       </c>
       <c r="F90" s="25" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="12">
-        <f>DATE(2026,11,24)</f>
-        <v>46350</v>
-      </c>
-      <c r="B91" s="13" t="str">
+      <c r="A91" s="35">
+        <f>DATE(2026,12,7)</f>
+        <v>46363</v>
+      </c>
+      <c r="B91" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>Tue</v>
-      </c>
-      <c r="C91" s="16" t="s">
-        <v>533</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>534</v>
-      </c>
-      <c r="E91" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F91" s="25" t="s">
-        <v>438</v>
+        <v>Mon</v>
+      </c>
+      <c r="C91" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="D91" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="E91" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="F91" s="40" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
@@ -4586,504 +4580,504 @@
         <v>Mon</v>
       </c>
       <c r="C92" s="40" t="s">
-        <v>584</v>
-      </c>
-      <c r="D92" s="40" t="s">
-        <v>585</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="D92" s="40"/>
       <c r="E92" s="40" t="s">
-        <v>230</v>
+        <v>121</v>
       </c>
       <c r="F92" s="40" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="35">
-        <f>DATE(2026,12,7)</f>
-        <v>46363</v>
+        <f>DATE(2026,12,11)</f>
+        <v>46367</v>
       </c>
       <c r="B93" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="C93" s="40" t="s">
-        <v>586</v>
-      </c>
-      <c r="D93" s="40"/>
+        <v>570</v>
+      </c>
+      <c r="D93" s="40" t="s">
+        <v>571</v>
+      </c>
       <c r="E93" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F93" s="40" t="s">
-        <v>587</v>
+        <v>222</v>
+      </c>
+      <c r="F93" s="44" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="35">
-        <f>DATE(2026,12,11)</f>
-        <v>46367</v>
+        <f>DATE(2026,12,16)</f>
+        <v>46372</v>
       </c>
       <c r="B94" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Wed</v>
       </c>
       <c r="C94" s="40" t="s">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="D94" s="40" t="s">
-        <v>581</v>
-      </c>
-      <c r="E94" s="40" t="s">
-        <v>230</v>
-      </c>
-      <c r="F94" s="44" t="s">
-        <v>582</v>
+        <v>196</v>
+      </c>
+      <c r="E94" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F94" s="25" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="35">
-        <f>DATE(2026,12,16)</f>
-        <v>46372</v>
+        <f>DATE(2026,12,25)</f>
+        <v>46381</v>
       </c>
       <c r="B95" s="36" t="str">
+        <f>TEXT($A95,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C95" s="37" t="s">
+        <v>454</v>
+      </c>
+      <c r="D95" s="37" t="s">
+        <v>455</v>
+      </c>
+      <c r="E95" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="F95" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="12">
+        <f>DATE(2027,1,1)</f>
+        <v>46388</v>
+      </c>
+      <c r="B96" s="13" t="str">
+        <f>TEXT($A96,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="E96" s="38" t="s">
+        <v>456</v>
+      </c>
+      <c r="F96" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="31">
+        <f>DATE(2027,1,1)</f>
+        <v>46388</v>
+      </c>
+      <c r="B97" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C97" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="D97" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="E97" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F97" s="25" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="35">
+        <f>DATE(2027,1,30)</f>
+        <v>46417</v>
+      </c>
+      <c r="B98" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="C98" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="D98" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="E98" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F98" s="25" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="35">
+        <f>DATE(2027,2,6)</f>
+        <v>46424</v>
+      </c>
+      <c r="B99" s="36" t="str">
+        <f>TEXT($A99,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C99" s="37" t="s">
+        <v>472</v>
+      </c>
+      <c r="D99" s="37" t="s">
+        <v>473</v>
+      </c>
+      <c r="E99" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="F99" s="25" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="35">
+        <f>DATE(2027,2,7)</f>
+        <v>46425</v>
+      </c>
+      <c r="B100" s="36" t="str">
+        <f>TEXT($A100,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C100" s="37" t="s">
+        <v>474</v>
+      </c>
+      <c r="D100" s="37" t="s">
+        <v>475</v>
+      </c>
+      <c r="E100" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="F100" s="25" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="12">
+        <f>DATE(2027,2,8)</f>
+        <v>46426</v>
+      </c>
+      <c r="B101" s="13" t="str">
+        <f>TEXT($A101,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="E101" s="38" t="s">
+        <v>456</v>
+      </c>
+      <c r="F101" s="25" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="41">
+        <f>DATE(2027,2,18)</f>
+        <v>46436</v>
+      </c>
+      <c r="B102" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C102" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="D102" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="E102" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="F102" s="26" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="12">
+        <f>DATE(2027,3,10)</f>
+        <v>46456</v>
+      </c>
+      <c r="B103" s="13" t="str">
+        <f>TEXT($A103,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="E103" s="38" t="s">
+        <v>467</v>
+      </c>
+      <c r="F103" s="25" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="31">
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
+      </c>
+      <c r="B104" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C104" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="D104" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="E104" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="F104" s="26" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="35">
+        <f>DATE(2027,3,25)</f>
+        <v>46471</v>
+      </c>
+      <c r="B105" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C105" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="D105" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="E105" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F105" s="26" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="12">
+        <f>DATE(2027,3,26)</f>
+        <v>46472</v>
+      </c>
+      <c r="B106" s="13" t="str">
+        <f>TEXT($A106,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="E106" s="38" t="s">
+        <v>456</v>
+      </c>
+      <c r="F106" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="31">
+        <f>DATE(2027,4,3)</f>
+        <v>46480</v>
+      </c>
+      <c r="B107" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="C107" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="D107" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="E107" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="F107" s="26" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="35">
+        <f>DATE(2027,4,9)</f>
+        <v>46486</v>
+      </c>
+      <c r="B108" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C108" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="D108" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="E108" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="F108" s="26" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="35">
+        <f>DATE(2027,5,1)</f>
+        <v>46508</v>
+      </c>
+      <c r="B109" s="36" t="str">
+        <f>TEXT($A109,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C109" s="37" t="s">
+        <v>463</v>
+      </c>
+      <c r="D109" s="37" t="s">
+        <v>464</v>
+      </c>
+      <c r="E109" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="F109" s="25" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="12">
+        <f>DATE(2027,5,17)</f>
+        <v>46524</v>
+      </c>
+      <c r="B110" s="13" t="str">
+        <f>TEXT($A110,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C110" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="E110" s="38" t="s">
+        <v>467</v>
+      </c>
+      <c r="F110" s="25" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="41">
+        <f>DATE(2027,5,19)</f>
+        <v>46526</v>
+      </c>
+      <c r="B111" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C95" s="40" t="s">
-        <v>458</v>
-      </c>
-      <c r="D95" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="E95" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="F95" s="25" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="35">
-        <f>DATE(2026,12,25)</f>
-        <v>46381</v>
-      </c>
-      <c r="B96" s="36" t="str">
-        <f>TEXT($A96,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C96" s="37" t="s">
+      <c r="C111" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="D111" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="E111" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="F111" s="26" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="12">
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
+      </c>
+      <c r="B112" s="13" t="str">
+        <f>TEXT($A112,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="D112" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="D96" s="37" t="s">
-        <v>463</v>
-      </c>
-      <c r="E96" s="39" t="s">
-        <v>464</v>
-      </c>
-      <c r="F96" s="25" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="12">
-        <f>DATE(2027,1,1)</f>
-        <v>46388</v>
-      </c>
-      <c r="B97" s="13" t="str">
-        <f>TEXT($A97,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="E97" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="F97" s="25" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="31">
-        <f>DATE(2027,1,1)</f>
-        <v>46388</v>
-      </c>
-      <c r="B98" s="32" t="str">
+      <c r="E112" s="38" t="s">
+        <v>456</v>
+      </c>
+      <c r="F112" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="31">
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
+      </c>
+      <c r="B113" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C113" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="D113" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="E113" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="F113" s="26" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="12">
+        <f>DATE(2027,5,21)</f>
+        <v>46528</v>
+      </c>
+      <c r="B114" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C98" s="43" t="s">
-        <v>229</v>
-      </c>
-      <c r="D98" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="E98" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="F98" s="25" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="35">
-        <f>DATE(2027,1,30)</f>
-        <v>46417</v>
-      </c>
-      <c r="B99" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C99" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="D99" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="E99" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F99" s="25" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="35">
-        <f>DATE(2027,2,6)</f>
-        <v>46424</v>
-      </c>
-      <c r="B100" s="36" t="str">
-        <f>TEXT($A100,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C100" s="37" t="s">
-        <v>480</v>
-      </c>
-      <c r="D100" s="37" t="s">
-        <v>481</v>
-      </c>
-      <c r="E100" s="39" t="s">
-        <v>464</v>
-      </c>
-      <c r="F100" s="25" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="35">
-        <f>DATE(2027,2,7)</f>
-        <v>46425</v>
-      </c>
-      <c r="B101" s="36" t="str">
-        <f>TEXT($A101,"ddd")</f>
-        <v>Sun</v>
-      </c>
-      <c r="C101" s="37" t="s">
-        <v>482</v>
-      </c>
-      <c r="D101" s="37" t="s">
-        <v>483</v>
-      </c>
-      <c r="E101" s="39" t="s">
-        <v>464</v>
-      </c>
-      <c r="F101" s="25" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="12">
-        <f>DATE(2027,2,8)</f>
-        <v>46426</v>
-      </c>
-      <c r="B102" s="13" t="str">
-        <f>TEXT($A102,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="D102" s="11" t="s">
-        <v>485</v>
-      </c>
-      <c r="E102" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="F102" s="25" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="41">
-        <f>DATE(2027,2,18)</f>
-        <v>46436</v>
-      </c>
-      <c r="B103" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C103" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="D103" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="E103" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="F103" s="26" t="s">
+      <c r="C114" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E114" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="F114" s="26" t="s">
         <v>404</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="12">
-        <f>DATE(2027,3,10)</f>
-        <v>46456</v>
-      </c>
-      <c r="B104" s="13" t="str">
-        <f>TEXT($A104,"ddd")</f>
-        <v>Wed</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>478</v>
-      </c>
-      <c r="D104" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="E104" s="38" t="s">
-        <v>475</v>
-      </c>
-      <c r="F104" s="25" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="31">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
-      </c>
-      <c r="B105" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C105" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="D105" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E105" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="F105" s="26" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="35">
-        <f>DATE(2027,3,25)</f>
-        <v>46471</v>
-      </c>
-      <c r="B106" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C106" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="D106" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="E106" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F106" s="26" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="12">
-        <f>DATE(2027,3,26)</f>
-        <v>46472</v>
-      </c>
-      <c r="B107" s="13" t="str">
-        <f>TEXT($A107,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>476</v>
-      </c>
-      <c r="D107" s="11" t="s">
-        <v>477</v>
-      </c>
-      <c r="E107" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="F107" s="25" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="31">
-        <f>DATE(2027,4,3)</f>
-        <v>46480</v>
-      </c>
-      <c r="B108" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C108" s="43" t="s">
-        <v>220</v>
-      </c>
-      <c r="D108" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="E108" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="F108" s="26" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="35">
-        <f>DATE(2027,4,9)</f>
-        <v>46486</v>
-      </c>
-      <c r="B109" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C109" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="D109" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="E109" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F109" s="26" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="35">
-        <f>DATE(2027,5,1)</f>
-        <v>46508</v>
-      </c>
-      <c r="B110" s="36" t="str">
-        <f>TEXT($A110,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C110" s="37" t="s">
-        <v>471</v>
-      </c>
-      <c r="D110" s="37" t="s">
-        <v>472</v>
-      </c>
-      <c r="E110" s="39" t="s">
-        <v>464</v>
-      </c>
-      <c r="F110" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="12">
-        <f>DATE(2027,5,17)</f>
-        <v>46524</v>
-      </c>
-      <c r="B111" s="13" t="str">
-        <f>TEXT($A111,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C111" s="11" t="s">
-        <v>473</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>474</v>
-      </c>
-      <c r="E111" s="38" t="s">
-        <v>475</v>
-      </c>
-      <c r="F111" s="25" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="41">
-        <f>DATE(2027,5,19)</f>
-        <v>46526</v>
-      </c>
-      <c r="B112" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Wed</v>
-      </c>
-      <c r="C112" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="D112" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="E112" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="F112" s="26" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="12">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
-      </c>
-      <c r="B113" s="13" t="str">
-        <f>TEXT($A113,"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>469</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>470</v>
-      </c>
-      <c r="E113" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="F113" s="25" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="31">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
-      </c>
-      <c r="B114" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C114" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="D114" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="E114" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="F114" s="26" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="12">
-        <f>DATE(2027,5,21)</f>
-        <v>46528</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B115" s="13" t="str">
         <f t="shared" si="2"/>
@@ -5093,369 +5087,347 @@
         <v>172</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>230</v>
+        <v>121</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B116" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B117" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C117" s="11" t="s">
-        <v>248</v>
+      <c r="C117" s="16" t="s">
+        <v>442</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>207</v>
+        <v>443</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F117" s="26" t="s">
-        <v>438</v>
+      <c r="F117" s="25" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
-      </c>
-      <c r="B118" s="13" t="str">
+      <c r="A118" s="35">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B118" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C118" s="16" t="s">
-        <v>450</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>451</v>
-      </c>
-      <c r="E118" s="11" t="s">
+      <c r="C118" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="D118" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="E118" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F118" s="25" t="s">
-        <v>452</v>
+      <c r="F118" s="26" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="35">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
-      </c>
-      <c r="B119" s="36" t="str">
+      <c r="A119" s="12">
+        <f>DATE(2027,8,9)</f>
+        <v>46608</v>
+      </c>
+      <c r="B119" s="13" t="str">
+        <f>TEXT($A119,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="E119" s="38" t="s">
+        <v>456</v>
+      </c>
+      <c r="F119" s="25" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="31">
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
+      </c>
+      <c r="B120" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C120" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D120" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E120" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="F120" s="26" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="12">
+        <f>DATE(2027,8,20)</f>
+        <v>46619</v>
+      </c>
+      <c r="B121" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C119" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="D119" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="E119" s="37" t="s">
+      <c r="C121" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E121" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F119" s="26" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="12">
-        <f>DATE(2027,8,9)</f>
-        <v>46608</v>
-      </c>
-      <c r="B120" s="13" t="str">
-        <f>TEXT($A120,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="D120" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="E120" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="F120" s="25" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="31">
-        <f>DATE(2027,8,16)</f>
-        <v>46615</v>
-      </c>
-      <c r="B121" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Mon</v>
-      </c>
-      <c r="C121" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="D121" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="E121" s="33" t="s">
-        <v>230</v>
-      </c>
       <c r="F121" s="26" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="12">
-        <f>DATE(2027,8,20)</f>
-        <v>46619</v>
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
       </c>
       <c r="B122" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="E122" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
       </c>
       <c r="B123" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F123" s="26" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
       </c>
       <c r="B124" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
+        <v>Fri</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
-      </c>
-      <c r="B125" s="13" t="str">
+      <c r="A125" s="35">
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
+      </c>
+      <c r="B125" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C125" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D125" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="E125" s="11" t="s">
+      <c r="C125" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="D125" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="E125" s="37" t="s">
         <v>124</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="35">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
-      </c>
-      <c r="B126" s="36" t="str">
+      <c r="A126" s="12">
+        <f>DATE(2027,10,28)</f>
+        <v>46688</v>
+      </c>
+      <c r="B126" s="13" t="str">
+        <f>TEXT($A126,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="E126" s="38" t="s">
+        <v>456</v>
+      </c>
+      <c r="F126" s="25" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="31">
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
+      </c>
+      <c r="B127" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C126" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="D126" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="E126" s="37" t="s">
+      <c r="C127" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="D127" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="E127" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F126" s="26" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="12">
-        <f>DATE(2027,10,28)</f>
-        <v>46688</v>
-      </c>
-      <c r="B127" s="13" t="str">
-        <f>TEXT($A127,"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="C127" s="11" t="s">
-        <v>465</v>
-      </c>
-      <c r="D127" s="11" t="s">
-        <v>466</v>
-      </c>
-      <c r="E127" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="F127" s="25" t="s">
-        <v>504</v>
+      <c r="F127" s="26" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="31">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
-      </c>
-      <c r="B128" s="32" t="str">
+      <c r="A128" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B128" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C128" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="D128" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E128" s="33" t="s">
+      <c r="C128" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="E128" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F128" s="26" t="s">
-        <v>438</v>
+      <c r="F128" s="25" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
-      </c>
-      <c r="B129" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C129" s="16" t="s">
-        <v>450</v>
-      </c>
-      <c r="D129" s="11" t="s">
-        <v>451</v>
-      </c>
-      <c r="E129" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F129" s="25" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" s="35">
+      <c r="A129" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B130" s="36" t="str">
+      <c r="B129" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C130" s="37" t="s">
+      <c r="C129" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D130" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="E130" s="37" t="s">
+      <c r="D129" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="E129" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F130" s="26" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A131" s="12">
+      <c r="F129" s="26" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B131" s="13" t="str">
-        <f>TEXT($A131,"ddd")</f>
+      <c r="B130" s="13" t="str">
+        <f>TEXT($A130,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C131" s="11" t="s">
-        <v>462</v>
-      </c>
-      <c r="D131" s="11" t="s">
-        <v>463</v>
-      </c>
-      <c r="E131" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="F131" s="25" t="s">
-        <v>506</v>
+      <c r="C130" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="E130" s="38" t="s">
+        <v>456</v>
+      </c>
+      <c r="F130" s="25" t="s">
+        <v>498</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E131" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E130" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -5678,7 +5650,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>96</v>
@@ -5703,7 +5675,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>64</v>
@@ -5930,7 +5902,7 @@
         <v>109</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>93</v>
@@ -5950,7 +5922,7 @@
         <v>109</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>86</v>
@@ -5970,7 +5942,7 @@
         <v>109</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>101</v>
@@ -5990,7 +5962,7 @@
         <v>109</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>88</v>
@@ -6010,7 +5982,7 @@
         <v>109</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>90</v>
@@ -6141,10 +6113,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>179</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>180</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -6164,10 +6136,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>179</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>180</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -6185,16 +6157,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>179</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>180</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>64</v>
@@ -6208,10 +6180,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>179</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>180</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -6229,10 +6201,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>179</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>180</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -6252,10 +6224,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>181</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>182</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -6275,10 +6247,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>181</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>182</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -6298,10 +6270,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>183</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>184</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -6321,10 +6293,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>183</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>184</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -6344,10 +6316,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>186</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -6367,10 +6339,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>186</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -6379,7 +6351,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -6390,10 +6362,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>186</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -6413,10 +6385,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>186</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -6436,10 +6408,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>187</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -6459,10 +6431,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>187</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -6482,10 +6454,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>190</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -6505,10 +6477,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>190</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -6528,10 +6500,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>190</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -6551,10 +6523,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>191</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>192</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -6574,10 +6546,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>191</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>192</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -6597,10 +6569,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>191</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>192</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -6658,839 +6630,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D2" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="H2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="D3" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E3" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="H3" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B4" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C4" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D4" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="E4" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="H4" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C5" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D5" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="H5" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B6" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D6" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="H6" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B7" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C7" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D7" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="H7" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B8" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C8" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D8" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H8" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B9" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C9" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D9" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="H9" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B10" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="D10" t="s">
+        <v>350</v>
+      </c>
+      <c r="F10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>crystal.jpg</v>
+      </c>
+      <c r="G10" t="s">
+        <v>367</v>
+      </c>
+      <c r="H10" t="s">
         <v>358</v>
-      </c>
-      <c r="F10" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>crystal.jpg</v>
-      </c>
-      <c r="G10" t="s">
-        <v>375</v>
-      </c>
-      <c r="H10" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B11" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C11" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D11" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="H11" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B12" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C12" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D12" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="H12" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B13" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C13" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D13" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="H13" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="B14" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C14" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="D14" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E14" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
       <c r="G14" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="H14" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B15" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C15" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D15" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E15" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
       <c r="G15" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="H15" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B16" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C16" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="D16" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E16" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
       <c r="G16" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="H16" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B17" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C17" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D17" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
       <c r="G17" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="H17" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B18" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C18" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D18" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E18" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
       <c r="G18" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="H18" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B19" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C19" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D19" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E19" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
       <c r="G19" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="H19" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B20" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D20" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E20" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
       <c r="G20" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="H20" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B21" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="C21" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D21" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E21" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
       <c r="G21" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="H21" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B22" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C22" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D22" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E22" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
       <c r="G22" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="H22" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B23" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C23" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D23" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E23" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
       <c r="G23" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="H23" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B24" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C24" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="D24" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E24" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
       <c r="G24" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="H24" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B25" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C25" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D25" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geokchin.jpg</v>
       </c>
       <c r="G25" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="H25" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B26" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C26" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D26" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laysiew.jpg</v>
       </c>
       <c r="G26" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="H26" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B27" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C27" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D27" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>waiyee.jpg</v>
       </c>
       <c r="G27" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="H27" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B28" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="C28" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D28" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>carol.jpg</v>
       </c>
       <c r="G28" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="H28" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B29" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C29" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D29" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F29" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yokewant.jpg</v>
       </c>
       <c r="G29" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="H29" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B30" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C30" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D30" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F30" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pohcheng.jpg</v>
       </c>
       <c r="G30" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="H30" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B31" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C31" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D31" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F31" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geoklan.jpg</v>
       </c>
       <c r="G31" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="H31" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B32" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C32" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D32" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F32" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laichee.jpg</v>
       </c>
       <c r="G32" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="H32" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B33" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C33" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D33" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F33" s="4" t="str">
         <f t="shared" si="0"/>
         <v>beechoo.jpg</v>
       </c>
       <c r="G33" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="H33" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -7531,15 +7503,15 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" t="s">
         <v>193</v>
-      </c>
-      <c r="B4" t="s">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -7548,12 +7520,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7798,20 +7772,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7837,14 +7814,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1869" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE9DBFA3-E7E1-489D-A463-7773509FA6BB}"/>
+  <xr:revisionPtr revIDLastSave="1879" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76B6F803-9CF7-4034-B439-E77A7E94AA83}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$130</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1796,13 +1796,13 @@
     <t>Nine Emperor Gods Festival Fundraiser – Day 3</t>
   </si>
   <si>
-    <t>九皇爷诞筹款第一天</t>
-  </si>
-  <si>
-    <t>九皇爷诞筹款第二天</t>
-  </si>
-  <si>
-    <t>九皇爷诞筹款第三天</t>
+    <t>九皇爷诞筹款第一天 (理事會的宴會)</t>
+  </si>
+  <si>
+    <t>九皇爷诞筹款第二天(香友會)</t>
+  </si>
+  <si>
+    <t>九皇爷诞筹款第三天(诚敬會)</t>
   </si>
 </sst>
 </file>
@@ -4314,40 +4314,38 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="12">
-        <f>DATE(2026,10,12)</f>
-        <v>46307</v>
+        <f>DATE(2026,10,15)</f>
+        <v>46310</v>
       </c>
       <c r="B80" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Mon</v>
-      </c>
-      <c r="C80" s="16" t="s">
-        <v>581</v>
-      </c>
-      <c r="D80" s="16" t="s">
-        <v>584</v>
-      </c>
-      <c r="E80" s="11" t="s">
-        <v>222</v>
+        <f>TEXT($A80,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C80" s="40" t="s">
+        <v>562</v>
+      </c>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37" t="s">
+        <v>230</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>429</v>
+        <v>535</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="12">
-        <f>DATE(2026,10,13)</f>
-        <v>46308</v>
+        <f>DATE(2026,10,19)</f>
+        <v>46314</v>
       </c>
       <c r="B81" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Tue</v>
+        <v>Mon</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>222</v>
@@ -4358,66 +4356,68 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="12">
-        <f>DATE(2026,10,14)</f>
-        <v>46309</v>
-      </c>
-      <c r="B82" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Wed</v>
-      </c>
-      <c r="C82" s="16" t="s">
-        <v>583</v>
-      </c>
-      <c r="D82" s="16" t="s">
-        <v>586</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>222</v>
+        <f>DATE(2026,10,20)</f>
+        <v>46315</v>
+      </c>
+      <c r="B82" s="42" t="str">
+        <f>TEXT($A82,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C82" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="D82" s="25" t="s">
+        <v>555</v>
+      </c>
+      <c r="E82" s="25" t="s">
+        <v>129</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>429</v>
+        <v>553</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="12">
-        <f>DATE(2026,10,15)</f>
-        <v>46310</v>
+        <f>DATE(2026,10,23)</f>
+        <v>46318</v>
       </c>
       <c r="B83" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Thu</v>
-      </c>
-      <c r="C83" s="40" t="s">
-        <v>562</v>
-      </c>
-      <c r="D83" s="37"/>
-      <c r="E83" s="37" t="s">
-        <v>230</v>
+        <v>Fri</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>582</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>222</v>
       </c>
       <c r="F83" s="25" t="s">
-        <v>535</v>
+        <v>429</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="12">
-        <f>DATE(2026,10,20)</f>
-        <v>46315</v>
-      </c>
-      <c r="B84" s="42" t="str">
-        <f t="shared" si="0"/>
-        <v>Tue</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>554</v>
-      </c>
-      <c r="D84" s="25" t="s">
-        <v>555</v>
-      </c>
-      <c r="E84" s="25" t="s">
-        <v>129</v>
+        <f>DATE(2026,10,24)</f>
+        <v>46319</v>
+      </c>
+      <c r="B84" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>586</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>222</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>553</v>
+        <v>429</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46290</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7520,14 +7520,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7772,23 +7770,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7814,9 +7809,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1879" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76B6F803-9CF7-4034-B439-E77A7E94AA83}"/>
+  <xr:revisionPtr revIDLastSave="1882" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0D0328C-C2C8-499F-86FF-83A2C8D03164}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16110" yWindow="-16335" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -2648,7 +2648,7 @@
         <v>46023</v>
       </c>
       <c r="B3" s="32" t="str">
-        <f t="shared" ref="B3:B86" si="0">TEXT($A3,"ddd")</f>
+        <f t="shared" ref="B3:B85" si="0">TEXT($A3,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C3" s="33" t="s">
@@ -4226,7 +4226,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="51" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
@@ -4235,317 +4235,317 @@
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C76" s="11" t="s">
-        <v>523</v>
+      <c r="C76" s="20" t="s">
+        <v>232</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>524</v>
+        <v>231</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="51" x14ac:dyDescent="0.35">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="12">
-        <f>DATE(2026,10,9)</f>
-        <v>46304</v>
+        <f>DATE(2026,10,10)</f>
+        <v>46305</v>
       </c>
       <c r="B77" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
-      </c>
-      <c r="C77" s="20" t="s">
-        <v>232</v>
+        <v>Sat</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>449</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>230</v>
+        <v>131</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="12">
-        <f>DATE(2026,10,10)</f>
-        <v>46305</v>
+        <f>DATE(2026,10,12)</f>
+        <v>46307</v>
       </c>
       <c r="B78" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Mon</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>449</v>
-      </c>
-      <c r="D78" s="11" t="s">
-        <v>241</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="D78" s="11"/>
       <c r="E78" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>428</v>
+        <v>533</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="12">
-        <f>DATE(2026,10,12)</f>
-        <v>46307</v>
+        <f>DATE(2026,10,15)</f>
+        <v>46310</v>
       </c>
       <c r="B79" s="13" t="str">
+        <f>TEXT($A79,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C79" s="40" t="s">
+        <v>562</v>
+      </c>
+      <c r="D79" s="37"/>
+      <c r="E79" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="F79" s="25" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="12">
+        <f>DATE(2026,10,19)</f>
+        <v>46314</v>
+      </c>
+      <c r="B80" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C79" s="11" t="s">
-        <v>534</v>
-      </c>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F79" s="25" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="12">
-        <f>DATE(2026,10,15)</f>
-        <v>46310</v>
-      </c>
-      <c r="B80" s="13" t="str">
-        <f>TEXT($A80,"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="C80" s="40" t="s">
-        <v>562</v>
-      </c>
-      <c r="D80" s="37"/>
-      <c r="E80" s="37" t="s">
-        <v>230</v>
+      <c r="C80" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>222</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>535</v>
+        <v>429</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="12">
-        <f>DATE(2026,10,19)</f>
-        <v>46314</v>
-      </c>
-      <c r="B81" s="13" t="str">
+        <f>DATE(2026,10,20)</f>
+        <v>46315</v>
+      </c>
+      <c r="B81" s="42" t="str">
+        <f>TEXT($A81,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="D81" s="25" t="s">
+        <v>555</v>
+      </c>
+      <c r="E81" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F81" s="25" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="12">
+        <f>DATE(2026,10,23)</f>
+        <v>46318</v>
+      </c>
+      <c r="B82" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>582</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="F82" s="25" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="12">
+        <f>DATE(2026,10,24)</f>
+        <v>46319</v>
+      </c>
+      <c r="B83" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>586</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="F83" s="25" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="12">
+        <f>DATE(2026,10,26)</f>
+        <v>46321</v>
+      </c>
+      <c r="B84" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C81" s="16" t="s">
-        <v>581</v>
-      </c>
-      <c r="D81" s="16" t="s">
-        <v>584</v>
-      </c>
-      <c r="E81" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="F81" s="25" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" s="12">
-        <f>DATE(2026,10,20)</f>
-        <v>46315</v>
-      </c>
-      <c r="B82" s="42" t="str">
-        <f>TEXT($A82,"ddd")</f>
-        <v>Tue</v>
-      </c>
-      <c r="C82" s="25" t="s">
-        <v>554</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>555</v>
-      </c>
-      <c r="E82" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="F82" s="25" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" s="12">
-        <f>DATE(2026,10,23)</f>
-        <v>46318</v>
-      </c>
-      <c r="B83" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Fri</v>
-      </c>
-      <c r="C83" s="16" t="s">
-        <v>582</v>
-      </c>
-      <c r="D83" s="16" t="s">
-        <v>585</v>
-      </c>
-      <c r="E83" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="F83" s="25" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="12">
-        <f>DATE(2026,10,24)</f>
-        <v>46319</v>
-      </c>
-      <c r="B84" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Sat</v>
-      </c>
-      <c r="C84" s="16" t="s">
-        <v>583</v>
-      </c>
-      <c r="D84" s="16" t="s">
-        <v>586</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>222</v>
+      <c r="C84" s="25" t="s">
+        <v>564</v>
+      </c>
+      <c r="D84" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="E84" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>429</v>
+        <v>565</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="12">
-        <f>DATE(2026,10,26)</f>
-        <v>46321</v>
+        <f>DATE(2026,10,27)</f>
+        <v>46322</v>
       </c>
       <c r="B85" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>564</v>
-      </c>
-      <c r="D85" s="25" t="s">
-        <v>563</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="D85" s="25"/>
       <c r="E85" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="12">
-        <f>DATE(2026,10,27)</f>
-        <v>46322</v>
-      </c>
-      <c r="B86" s="42" t="str">
-        <f t="shared" si="0"/>
+      <c r="A86" s="35">
+        <f>DATE(2026,11,3)</f>
+        <v>46329</v>
+      </c>
+      <c r="B86" s="36" t="str">
+        <f t="shared" ref="B86:B129" si="2">TEXT($A86,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C86" s="25" t="s">
-        <v>566</v>
-      </c>
-      <c r="D86" s="25"/>
-      <c r="E86" s="25" t="s">
-        <v>124</v>
+      <c r="C86" s="40" t="s">
+        <v>580</v>
+      </c>
+      <c r="D86" s="40" t="s">
+        <v>579</v>
+      </c>
+      <c r="E86" s="37" t="s">
+        <v>121</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>567</v>
+        <v>431</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="35">
-        <f>DATE(2026,11,3)</f>
-        <v>46329</v>
-      </c>
-      <c r="B87" s="36" t="str">
-        <f t="shared" ref="B87:B129" si="2">TEXT($A87,"ddd")</f>
-        <v>Tue</v>
-      </c>
-      <c r="C87" s="40" t="s">
-        <v>580</v>
-      </c>
-      <c r="D87" s="40" t="s">
-        <v>579</v>
-      </c>
-      <c r="E87" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F87" s="25" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="35">
         <f>DATE(2026,11,8)</f>
         <v>46334</v>
       </c>
-      <c r="B88" s="36" t="str">
-        <f>TEXT($A88,"ddd")</f>
+      <c r="B87" s="36" t="str">
+        <f>TEXT($A87,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C88" s="37" t="s">
+      <c r="C87" s="37" t="s">
         <v>457</v>
       </c>
-      <c r="D88" s="37" t="s">
+      <c r="D87" s="37" t="s">
         <v>458</v>
       </c>
-      <c r="E88" s="39" t="s">
+      <c r="E87" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="F88" s="25" t="s">
+      <c r="F87" s="25" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="12">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="12">
         <f>DATE(2026,11,9)</f>
         <v>46335</v>
       </c>
-      <c r="B89" s="13" t="str">
-        <f>TEXT($A89,"ddd")</f>
+      <c r="B88" s="13" t="str">
+        <f>TEXT($A88,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C88" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D88" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="E89" s="38" t="s">
+      <c r="E88" s="38" t="s">
         <v>456</v>
       </c>
-      <c r="F89" s="25" t="s">
+      <c r="F88" s="25" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="31">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="31">
         <f>DATE(2026,11,28)</f>
         <v>46354</v>
       </c>
-      <c r="B90" s="32" t="str">
+      <c r="B89" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C90" s="43" t="s">
+      <c r="C89" s="43" t="s">
         <v>578</v>
       </c>
-      <c r="D90" s="33"/>
-      <c r="E90" s="33" t="s">
+      <c r="D89" s="33"/>
+      <c r="E89" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F90" s="25" t="s">
+      <c r="F89" s="25" t="s">
         <v>432</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="35">
+        <f>DATE(2026,12,7)</f>
+        <v>46363</v>
+      </c>
+      <c r="B90" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C90" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="D90" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="E90" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="F90" s="40" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
@@ -4558,184 +4558,184 @@
         <v>Mon</v>
       </c>
       <c r="C91" s="40" t="s">
-        <v>574</v>
-      </c>
-      <c r="D91" s="40" t="s">
-        <v>575</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="D91" s="40"/>
       <c r="E91" s="40" t="s">
-        <v>222</v>
+        <v>121</v>
       </c>
       <c r="F91" s="40" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="35">
-        <f>DATE(2026,12,7)</f>
-        <v>46363</v>
+        <f>DATE(2026,12,11)</f>
+        <v>46367</v>
       </c>
       <c r="B92" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="C92" s="40" t="s">
-        <v>576</v>
-      </c>
-      <c r="D92" s="40"/>
+        <v>570</v>
+      </c>
+      <c r="D92" s="40" t="s">
+        <v>571</v>
+      </c>
       <c r="E92" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F92" s="40" t="s">
-        <v>577</v>
+        <v>222</v>
+      </c>
+      <c r="F92" s="44" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="35">
-        <f>DATE(2026,12,11)</f>
-        <v>46367</v>
+        <f>DATE(2026,12,16)</f>
+        <v>46372</v>
       </c>
       <c r="B93" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Wed</v>
       </c>
       <c r="C93" s="40" t="s">
-        <v>570</v>
+        <v>450</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>571</v>
-      </c>
-      <c r="E93" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="F93" s="44" t="s">
-        <v>572</v>
+        <v>196</v>
+      </c>
+      <c r="E93" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F93" s="25" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="35">
-        <f>DATE(2026,12,16)</f>
-        <v>46372</v>
-      </c>
-      <c r="B94" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Wed</v>
-      </c>
-      <c r="C94" s="40" t="s">
-        <v>450</v>
-      </c>
-      <c r="D94" s="40" t="s">
-        <v>196</v>
-      </c>
-      <c r="E94" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="F94" s="25" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="35">
         <f>DATE(2026,12,25)</f>
         <v>46381</v>
       </c>
-      <c r="B95" s="36" t="str">
+      <c r="B94" s="36" t="str">
+        <f>TEXT($A94,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C94" s="37" t="s">
+        <v>454</v>
+      </c>
+      <c r="D94" s="37" t="s">
+        <v>455</v>
+      </c>
+      <c r="E94" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="F94" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="12">
+        <f>DATE(2027,1,1)</f>
+        <v>46388</v>
+      </c>
+      <c r="B95" s="13" t="str">
         <f>TEXT($A95,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C95" s="37" t="s">
-        <v>454</v>
-      </c>
-      <c r="D95" s="37" t="s">
-        <v>455</v>
-      </c>
-      <c r="E95" s="39" t="s">
+      <c r="C95" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="E95" s="38" t="s">
         <v>456</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="12">
+      <c r="A96" s="31">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B96" s="13" t="str">
-        <f>TEXT($A96,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>478</v>
-      </c>
-      <c r="D96" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="E96" s="38" t="s">
-        <v>456</v>
-      </c>
-      <c r="F96" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="31">
-        <f>DATE(2027,1,1)</f>
-        <v>46388</v>
-      </c>
-      <c r="B97" s="32" t="str">
+      <c r="B96" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C97" s="43" t="s">
+      <c r="C96" s="43" t="s">
         <v>221</v>
       </c>
-      <c r="D97" s="33" t="s">
+      <c r="D96" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="E97" s="33" t="s">
+      <c r="E96" s="33" t="s">
         <v>131</v>
       </c>
+      <c r="F96" s="25" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="35">
+        <f>DATE(2027,1,30)</f>
+        <v>46417</v>
+      </c>
+      <c r="B97" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="C97" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="D97" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="E97" s="37" t="s">
+        <v>121</v>
+      </c>
       <c r="F97" s="25" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="35">
-        <f>DATE(2027,1,30)</f>
-        <v>46417</v>
+        <f>DATE(2027,2,6)</f>
+        <v>46424</v>
       </c>
       <c r="B98" s="36" t="str">
-        <f t="shared" si="2"/>
+        <f>TEXT($A98,"ddd")</f>
         <v>Sat</v>
       </c>
       <c r="C98" s="37" t="s">
-        <v>166</v>
+        <v>472</v>
       </c>
       <c r="D98" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="E98" s="37" t="s">
-        <v>121</v>
+        <v>473</v>
+      </c>
+      <c r="E98" s="39" t="s">
+        <v>456</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>395</v>
+        <v>487</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="35">
-        <f>DATE(2027,2,6)</f>
-        <v>46424</v>
+        <f>DATE(2027,2,7)</f>
+        <v>46425</v>
       </c>
       <c r="B99" s="36" t="str">
         <f>TEXT($A99,"ddd")</f>
-        <v>Sat</v>
+        <v>Sun</v>
       </c>
       <c r="C99" s="37" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D99" s="37" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E99" s="39" t="s">
         <v>456</v>
@@ -4745,69 +4745,69 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="35">
-        <f>DATE(2027,2,7)</f>
-        <v>46425</v>
-      </c>
-      <c r="B100" s="36" t="str">
-        <f>TEXT($A100,"ddd")</f>
-        <v>Sun</v>
-      </c>
-      <c r="C100" s="37" t="s">
-        <v>474</v>
-      </c>
-      <c r="D100" s="37" t="s">
-        <v>475</v>
-      </c>
-      <c r="E100" s="39" t="s">
-        <v>456</v>
-      </c>
-      <c r="F100" s="25" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="12">
+      <c r="A100" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B101" s="13" t="str">
-        <f>TEXT($A101,"ddd")</f>
+      <c r="B100" s="13" t="str">
+        <f>TEXT($A100,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C100" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="D101" s="11" t="s">
+      <c r="D100" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="E101" s="38" t="s">
+      <c r="E100" s="38" t="s">
         <v>456</v>
       </c>
-      <c r="F101" s="25" t="s">
+      <c r="F100" s="25" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="41">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B102" s="42" t="str">
+      <c r="B101" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C102" s="25" t="s">
+      <c r="C101" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="D102" s="25" t="s">
+      <c r="D101" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="E102" s="25" t="s">
+      <c r="E101" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="F102" s="26" t="s">
+      <c r="F101" s="26" t="s">
         <v>396</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="12">
+        <f>DATE(2027,3,6)</f>
+        <v>46452</v>
+      </c>
+      <c r="B102" s="13" t="str">
+        <f>TEXT($A102,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="E102" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F102" s="25" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7520,12 +7520,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7770,20 +7772,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7809,14 +7814,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1882" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0D0328C-C2C8-499F-86FF-83A2C8D03164}"/>
+  <xr:revisionPtr revIDLastSave="1893" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A9B1783-B392-4D61-BF83-E5DA8EF3E38F}"/>
   <bookViews>
-    <workbookView xWindow="16110" yWindow="-16335" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$127</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="585">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -569,9 +569,6 @@
     <t>[Tentative] 7th Month Fundraising Period (Actual Day 16 Aug, covering 2–30 Aug)</t>
   </si>
   <si>
-    <t>[Tentative] CSR Partnership – Corporate / School (Charity Concert)</t>
-  </si>
-  <si>
     <t>[Tentative] Charity Concert</t>
   </si>
   <si>
@@ -647,9 +644,6 @@
     <t>[未确认] 开斋节红包及礼包派发暨午宴</t>
   </si>
   <si>
-    <t>[未确认] 企业／学校社会责任合作（日出健走）</t>
-  </si>
-  <si>
     <t>[未确认] 卫塞节筹款（Ubin Thai）第一天</t>
   </si>
   <si>
@@ -668,9 +662,6 @@
     <t>[未确认] 七月筹款期（实际日期8月16日，涵盖8月2日至30日）</t>
   </si>
   <si>
-    <t>[未确认] 企业／学校社会责任合作（慈善演唱会）</t>
-  </si>
-  <si>
     <t>[未确认] 慈善演唱会</t>
   </si>
   <si>
@@ -680,9 +671,6 @@
     <t>元龙聖庙（关帝聖君兴诸众神诞）(代表：徐金声, Agnes, Bryan, Kathy, Jin Hoa）。筹款活动包括义标。</t>
   </si>
   <si>
-    <t>[Tentative] CSR Partnership – Corporate / School (Charity Walk)</t>
-  </si>
-  <si>
     <t>Asiatic Fire System CSR National Day Celebration (130 pax)</t>
   </si>
   <si>
@@ -1349,9 +1337,6 @@
     <t>7th Month Fundraising</t>
   </si>
   <si>
-    <t>Corporate - Charity Walk</t>
-  </si>
-  <si>
     <t>Dragon Board Festival</t>
   </si>
   <si>
@@ -1803,6 +1788,15 @@
   </si>
   <si>
     <t>九皇爷诞筹款第三天(诚敬會)</t>
+  </si>
+  <si>
+    <t>Sunrise Charity Walk 2027</t>
+  </si>
+  <si>
+    <t>日出义走2027</t>
+  </si>
+  <si>
+    <t>Sunrise Charity Walk</t>
   </si>
 </sst>
 </file>
@@ -2059,7 +2053,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2147,6 +2141,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2480,7 +2475,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2590,7 +2585,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -2617,7 +2612,7 @@
         <v>134</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2630,16 +2625,16 @@
         <v>Thu</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2661,7 +2656,7 @@
         <v>124</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2674,16 +2669,16 @@
         <v>Sun</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2705,7 +2700,7 @@
         <v>121</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2718,16 +2713,16 @@
         <v>Tue</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2740,16 +2735,16 @@
         <v>Wed</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2771,7 +2766,7 @@
         <v>131</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2793,7 +2788,7 @@
         <v>121</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2815,7 +2810,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2837,7 +2832,7 @@
         <v>124</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2850,16 +2845,16 @@
         <v>Sat</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2872,16 +2867,16 @@
         <v>Sat</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2903,7 +2898,7 @@
         <v>121</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2925,7 +2920,7 @@
         <v>121</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2941,13 +2936,13 @@
         <v>128</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E16" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2960,16 +2955,16 @@
         <v>Fri</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2985,13 +2980,13 @@
         <v>130</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -3004,16 +2999,16 @@
         <v>Fri</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -3035,7 +3030,7 @@
         <v>129</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3051,13 +3046,13 @@
         <v>147</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3073,13 +3068,13 @@
         <v>148</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -3101,7 +3096,7 @@
         <v>121</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -3114,16 +3109,16 @@
         <v>Wed</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -3142,10 +3137,10 @@
         <v>151</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -3164,10 +3159,10 @@
         <v>153</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -3180,16 +3175,16 @@
         <v>Sun</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3202,16 +3197,16 @@
         <v>Mon</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -3230,10 +3225,10 @@
         <v>155</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -3252,10 +3247,10 @@
         <v>157</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -3271,13 +3266,13 @@
         <v>128</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -3299,7 +3294,7 @@
         <v>121</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -3315,13 +3310,13 @@
         <v>128</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -3343,7 +3338,7 @@
         <v>124</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -3356,16 +3351,16 @@
         <v>Mon</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -3378,16 +3373,16 @@
         <v>Fri</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>194</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>195</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3403,13 +3398,13 @@
         <v>128</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3425,13 +3420,13 @@
         <v>128</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3444,16 +3439,16 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3466,16 +3461,16 @@
         <v>Wed</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -3488,16 +3483,16 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3510,16 +3505,16 @@
         <v>Sun</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3532,16 +3527,16 @@
         <v>Mon</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3554,16 +3549,16 @@
         <v>Fri</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3576,16 +3571,16 @@
         <v>Sat</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3598,16 +3593,16 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3620,16 +3615,16 @@
         <v>Sun</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3642,7 +3637,7 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>161</v>
@@ -3651,7 +3646,7 @@
         <v>124</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3664,16 +3659,16 @@
         <v>Sat</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -3686,16 +3681,16 @@
         <v>Sat</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3708,16 +3703,16 @@
         <v>Mon</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3730,14 +3725,14 @@
         <v>Tue</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3750,16 +3745,16 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -3772,16 +3767,16 @@
         <v>Thu</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3794,16 +3789,16 @@
         <v>Thu</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3816,16 +3811,16 @@
         <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3838,14 +3833,14 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3858,7 +3853,7 @@
         <v>Sat</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>162</v>
@@ -3867,7 +3862,7 @@
         <v>124</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="G58" s="19"/>
     </row>
@@ -3881,14 +3876,14 @@
         <v>Sat</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="G59" s="19"/>
     </row>
@@ -3902,16 +3897,16 @@
         <v>Mon</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3924,16 +3919,16 @@
         <v>Tue</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D61" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="E61" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E61" s="11" t="s">
-        <v>222</v>
-      </c>
       <c r="F61" s="25" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3946,14 +3941,14 @@
         <v>Tue</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3966,16 +3961,16 @@
         <v>Wed</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3988,14 +3983,14 @@
         <v>Wed</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -4008,16 +4003,16 @@
         <v>Wed</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -4030,14 +4025,14 @@
         <v>Wed</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -4050,14 +4045,14 @@
         <v>Thu</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -4070,14 +4065,14 @@
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F68" s="25" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4090,14 +4085,14 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4110,16 +4105,16 @@
         <v>Sat</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -4132,16 +4127,16 @@
         <v>Sat</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -4154,7 +4149,7 @@
         <v>Sun</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>163</v>
@@ -4163,7 +4158,7 @@
         <v>124</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -4176,14 +4171,14 @@
         <v>Wed</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -4196,14 +4191,14 @@
         <v>Wed</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -4216,14 +4211,14 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="11" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F75" s="25" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="51" x14ac:dyDescent="0.35">
@@ -4236,16 +4231,16 @@
         <v>Fri</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
@@ -4258,16 +4253,16 @@
         <v>Sat</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E77" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -4280,14 +4275,14 @@
         <v>Mon</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="D78" s="11"/>
       <c r="E78" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -4300,14 +4295,14 @@
         <v>Thu</v>
       </c>
       <c r="C79" s="40" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="D79" s="37"/>
       <c r="E79" s="37" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -4320,16 +4315,16 @@
         <v>Mon</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -4342,16 +4337,16 @@
         <v>Tue</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="D81" s="25" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="E81" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
@@ -4364,16 +4359,16 @@
         <v>Fri</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
@@ -4386,16 +4381,16 @@
         <v>Sat</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F83" s="25" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
@@ -4408,16 +4403,16 @@
         <v>Mon</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="E84" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
@@ -4430,14 +4425,14 @@
         <v>Tue</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="D85" s="25"/>
       <c r="E85" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -4446,20 +4441,20 @@
         <v>46329</v>
       </c>
       <c r="B86" s="36" t="str">
-        <f t="shared" ref="B86:B129" si="2">TEXT($A86,"ddd")</f>
+        <f t="shared" ref="B86:B126" si="2">TEXT($A86,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="C86" s="40" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E86" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -4472,16 +4467,16 @@
         <v>Sun</v>
       </c>
       <c r="C87" s="37" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="D87" s="37" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="E87" s="39" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
@@ -4494,16 +4489,16 @@
         <v>Mon</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="E88" s="38" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F88" s="25" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -4516,14 +4511,14 @@
         <v>Sat</v>
       </c>
       <c r="C89" s="43" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="D89" s="33"/>
       <c r="E89" s="33" t="s">
         <v>124</v>
       </c>
       <c r="F89" s="25" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
@@ -4536,16 +4531,16 @@
         <v>Mon</v>
       </c>
       <c r="C90" s="40" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="D90" s="40" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F90" s="40" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
@@ -4558,14 +4553,14 @@
         <v>Mon</v>
       </c>
       <c r="C91" s="40" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="D91" s="40"/>
       <c r="E91" s="40" t="s">
         <v>121</v>
       </c>
       <c r="F91" s="40" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
@@ -4578,16 +4573,16 @@
         <v>Fri</v>
       </c>
       <c r="C92" s="40" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="D92" s="40" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F92" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
@@ -4600,16 +4595,16 @@
         <v>Wed</v>
       </c>
       <c r="C93" s="40" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E93" s="37" t="s">
         <v>131</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
@@ -4622,16 +4617,16 @@
         <v>Fri</v>
       </c>
       <c r="C94" s="37" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="D94" s="37" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="E94" s="39" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -4644,16 +4639,16 @@
         <v>Fri</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E95" s="38" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
@@ -4666,16 +4661,16 @@
         <v>Fri</v>
       </c>
       <c r="C96" s="43" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D96" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E96" s="33" t="s">
         <v>131</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
@@ -4691,13 +4686,13 @@
         <v>166</v>
       </c>
       <c r="D97" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E97" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
@@ -4710,16 +4705,16 @@
         <v>Sat</v>
       </c>
       <c r="C98" s="37" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D98" s="37" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E98" s="39" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
@@ -4732,16 +4727,16 @@
         <v>Sun</v>
       </c>
       <c r="C99" s="37" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="D99" s="37" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="E99" s="39" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
@@ -4754,16 +4749,16 @@
         <v>Mon</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E100" s="38" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F100" s="25" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
@@ -4776,16 +4771,16 @@
         <v>Thu</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D101" s="25" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E101" s="25" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
@@ -4798,16 +4793,16 @@
         <v>Sat</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E102" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
@@ -4820,16 +4815,16 @@
         <v>Wed</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E103" s="38" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F103" s="25" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
@@ -4845,13 +4840,13 @@
         <v>167</v>
       </c>
       <c r="D104" s="33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E104" s="33" t="s">
         <v>124</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
@@ -4867,13 +4862,13 @@
         <v>168</v>
       </c>
       <c r="D105" s="37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E105" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
@@ -4886,548 +4881,482 @@
         <v>Fri</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="E106" s="38" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F106" s="25" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="31">
-        <f>DATE(2027,4,3)</f>
-        <v>46480</v>
+        <f>DATE(2027,4,17)</f>
+        <v>46494</v>
       </c>
       <c r="B107" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f>TEXT($A107,"ddd")</f>
         <v>Sat</v>
       </c>
       <c r="C107" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="D107" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E107" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="F107" s="26" t="s">
-        <v>435</v>
+        <v>582</v>
+      </c>
+      <c r="D107" s="43" t="s">
+        <v>583</v>
+      </c>
+      <c r="E107" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="F107" s="45" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="35">
-        <f>DATE(2027,4,9)</f>
-        <v>46486</v>
+        <f>DATE(2027,5,1)</f>
+        <v>46508</v>
       </c>
       <c r="B108" s="36" t="str">
+        <f>TEXT($A108,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C108" s="37" t="s">
+        <v>458</v>
+      </c>
+      <c r="D108" s="37" t="s">
+        <v>459</v>
+      </c>
+      <c r="E108" s="39" t="s">
+        <v>451</v>
+      </c>
+      <c r="F108" s="25" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="12">
+        <f>DATE(2027,5,17)</f>
+        <v>46524</v>
+      </c>
+      <c r="B109" s="13" t="str">
+        <f>TEXT($A109,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C109" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="E109" s="38" t="s">
+        <v>462</v>
+      </c>
+      <c r="F109" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="41">
+        <f>DATE(2027,5,19)</f>
+        <v>46526</v>
+      </c>
+      <c r="B110" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Wed</v>
+      </c>
+      <c r="C110" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="D110" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="E110" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="F110" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="12">
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
+      </c>
+      <c r="B111" s="13" t="str">
+        <f>TEXT($A111,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="E111" s="38" t="s">
+        <v>451</v>
+      </c>
+      <c r="F111" s="25" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="31">
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
+      </c>
+      <c r="B112" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C112" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="D112" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="E112" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="F112" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="12">
+        <f>DATE(2027,5,21)</f>
+        <v>46528</v>
+      </c>
+      <c r="B113" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C108" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="D108" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="E108" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F108" s="26" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="35">
-        <f>DATE(2027,5,1)</f>
-        <v>46508</v>
-      </c>
-      <c r="B109" s="36" t="str">
-        <f>TEXT($A109,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C109" s="37" t="s">
-        <v>463</v>
-      </c>
-      <c r="D109" s="37" t="s">
-        <v>464</v>
-      </c>
-      <c r="E109" s="39" t="s">
-        <v>456</v>
-      </c>
-      <c r="F109" s="25" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="12">
-        <f>DATE(2027,5,17)</f>
-        <v>46524</v>
-      </c>
-      <c r="B110" s="13" t="str">
-        <f>TEXT($A110,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C110" s="11" t="s">
-        <v>465</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>466</v>
-      </c>
-      <c r="E110" s="38" t="s">
-        <v>467</v>
-      </c>
-      <c r="F110" s="25" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="41">
-        <f>DATE(2027,5,19)</f>
-        <v>46526</v>
-      </c>
-      <c r="B111" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Wed</v>
-      </c>
-      <c r="C111" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="D111" s="25" t="s">
+      <c r="C113" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D113" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="E111" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="F111" s="26" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="12">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
-      </c>
-      <c r="B112" s="13" t="str">
-        <f>TEXT($A112,"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="C112" s="11" t="s">
-        <v>461</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>462</v>
-      </c>
-      <c r="E112" s="38" t="s">
-        <v>456</v>
-      </c>
-      <c r="F112" s="25" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="31">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
-      </c>
-      <c r="B113" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C113" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="D113" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="E113" s="33" t="s">
-        <v>222</v>
+      <c r="E113" s="11" t="s">
+        <v>218</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="12">
-        <f>DATE(2027,5,21)</f>
-        <v>46528</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B114" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>222</v>
+        <v>121</v>
       </c>
       <c r="F114" s="26" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B115" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B116" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C116" s="11" t="s">
-        <v>240</v>
+      <c r="C116" s="16" t="s">
+        <v>437</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>199</v>
+        <v>438</v>
       </c>
       <c r="E116" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F116" s="26" t="s">
-        <v>430</v>
+      <c r="F116" s="25" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
-      </c>
-      <c r="B117" s="13" t="str">
+      <c r="A117" s="35">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B117" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C117" s="16" t="s">
-        <v>442</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>443</v>
-      </c>
-      <c r="E117" s="11" t="s">
+      <c r="C117" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="D117" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E117" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F117" s="25" t="s">
-        <v>444</v>
+      <c r="F117" s="26" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="35">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
-      </c>
-      <c r="B118" s="36" t="str">
+      <c r="A118" s="12">
+        <f>DATE(2027,8,9)</f>
+        <v>46608</v>
+      </c>
+      <c r="B118" s="13" t="str">
+        <f>TEXT($A118,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="E118" s="38" t="s">
+        <v>451</v>
+      </c>
+      <c r="F118" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="31">
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
+      </c>
+      <c r="B119" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C119" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D119" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="E119" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="F119" s="26" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B120" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C118" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="D118" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="E118" s="37" t="s">
+      <c r="C120" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E120" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F118" s="26" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="12">
-        <f>DATE(2027,8,9)</f>
-        <v>46608</v>
-      </c>
-      <c r="B119" s="13" t="str">
-        <f>TEXT($A119,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>460</v>
-      </c>
-      <c r="E119" s="38" t="s">
-        <v>456</v>
-      </c>
-      <c r="F119" s="25" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="31">
-        <f>DATE(2027,8,16)</f>
-        <v>46615</v>
-      </c>
-      <c r="B120" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Mon</v>
-      </c>
-      <c r="C120" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="D120" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E120" s="33" t="s">
-        <v>222</v>
-      </c>
       <c r="F120" s="26" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="12">
-        <f>DATE(2027,8,20)</f>
-        <v>46619</v>
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
       </c>
       <c r="B121" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C121" s="11" t="s">
         <v>175</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
-      </c>
-      <c r="B122" s="13" t="str">
+      <c r="A122" s="35">
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
+      </c>
+      <c r="B122" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C122" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="D122" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="E122" s="11" t="s">
+      <c r="D122" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="E122" s="37" t="s">
         <v>124</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
+        <f>DATE(2027,10,28)</f>
+        <v>46688</v>
       </c>
       <c r="B123" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Sat</v>
+        <f>TEXT($A123,"ddd")</f>
+        <v>Thu</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>176</v>
+        <v>452</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="E123" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="F123" s="26" t="s">
-        <v>428</v>
+        <v>453</v>
+      </c>
+      <c r="E123" s="38" t="s">
+        <v>451</v>
+      </c>
+      <c r="F123" s="25" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
-      </c>
-      <c r="B124" s="13" t="str">
+      <c r="A124" s="31">
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
+      </c>
+      <c r="B124" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C124" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D124" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="E124" s="11" t="s">
+      <c r="D124" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="E124" s="33" t="s">
         <v>124</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="35">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
-      </c>
-      <c r="B125" s="36" t="str">
+      <c r="A125" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B125" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C125" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="D125" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="E125" s="37" t="s">
+      <c r="C125" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="E125" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F125" s="26" t="s">
-        <v>430</v>
+      <c r="F125" s="25" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="12">
-        <f>DATE(2027,10,28)</f>
-        <v>46688</v>
-      </c>
-      <c r="B126" s="13" t="str">
-        <f>TEXT($A126,"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="C126" s="11" t="s">
-        <v>457</v>
-      </c>
-      <c r="D126" s="11" t="s">
-        <v>458</v>
-      </c>
-      <c r="E126" s="38" t="s">
-        <v>456</v>
-      </c>
-      <c r="F126" s="25" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="31">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
-      </c>
-      <c r="B127" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C127" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="D127" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="E127" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="F127" s="26" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
-      </c>
-      <c r="B128" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C128" s="16" t="s">
-        <v>442</v>
-      </c>
-      <c r="D128" s="11" t="s">
-        <v>443</v>
-      </c>
-      <c r="E128" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F128" s="25" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" s="35">
+      <c r="A126" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B129" s="36" t="str">
+      <c r="B126" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C129" s="37" t="s">
+      <c r="C126" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D129" s="40" t="s">
-        <v>196</v>
-      </c>
-      <c r="E129" s="37" t="s">
+      <c r="D126" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="E126" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F129" s="26" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" s="12">
+      <c r="F126" s="26" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B130" s="13" t="str">
-        <f>TEXT($A130,"ddd")</f>
+      <c r="B127" s="13" t="str">
+        <f>TEXT($A127,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C130" s="11" t="s">
-        <v>454</v>
-      </c>
-      <c r="D130" s="11" t="s">
-        <v>455</v>
-      </c>
-      <c r="E130" s="38" t="s">
-        <v>456</v>
-      </c>
-      <c r="F130" s="25" t="s">
-        <v>498</v>
+      <c r="C127" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="E127" s="38" t="s">
+        <v>451</v>
+      </c>
+      <c r="F127" s="25" t="s">
+        <v>493</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E130" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E127" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -5650,7 +5579,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>96</v>
@@ -5675,7 +5604,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>64</v>
@@ -5902,7 +5831,7 @@
         <v>109</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>93</v>
@@ -5922,7 +5851,7 @@
         <v>109</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>86</v>
@@ -5942,7 +5871,7 @@
         <v>109</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>101</v>
@@ -5962,7 +5891,7 @@
         <v>109</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>88</v>
@@ -5982,7 +5911,7 @@
         <v>109</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>90</v>
@@ -6113,10 +6042,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>178</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>179</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -6136,10 +6065,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>178</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>179</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -6157,16 +6086,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>178</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>179</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>64</v>
@@ -6180,10 +6109,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>178</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>179</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -6201,10 +6130,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>178</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>179</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -6224,10 +6153,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>180</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>181</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -6247,10 +6176,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>180</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>181</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -6270,10 +6199,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>182</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>183</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -6293,10 +6222,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>182</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>183</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -6316,10 +6245,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>184</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>185</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -6339,10 +6268,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>184</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>185</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -6351,7 +6280,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -6362,10 +6291,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>184</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>185</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -6385,10 +6314,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>184</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>185</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -6408,10 +6337,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>187</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -6431,10 +6360,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>187</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -6454,10 +6383,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>188</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>189</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -6477,10 +6406,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>188</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>189</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -6500,10 +6429,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>188</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>189</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -6523,10 +6452,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>190</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>191</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -6546,10 +6475,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>190</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>191</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -6569,10 +6498,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>190</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>191</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -6630,839 +6559,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D4" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D5" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="H5" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C6" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H6" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C7" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H7" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C8" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D8" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="H8" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D9" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="H9" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B10" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C10" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D10" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="H10" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C11" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="H11" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B12" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C12" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D12" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="H12" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B13" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C13" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D13" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="H13" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B14" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C14" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D14" t="s">
+        <v>350</v>
+      </c>
+      <c r="E14" t="s">
+        <v>351</v>
+      </c>
+      <c r="F14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>keongeng.jpg</v>
+      </c>
+      <c r="G14" t="s">
+        <v>367</v>
+      </c>
+      <c r="H14" t="s">
         <v>354</v>
-      </c>
-      <c r="E14" t="s">
-        <v>355</v>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>keongeng.jpg</v>
-      </c>
-      <c r="G14" t="s">
-        <v>371</v>
-      </c>
-      <c r="H14" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B15" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C15" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D15" t="s">
+        <v>350</v>
+      </c>
+      <c r="E15" t="s">
+        <v>351</v>
+      </c>
+      <c r="F15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>siokteng.jpg</v>
+      </c>
+      <c r="G15" t="s">
+        <v>368</v>
+      </c>
+      <c r="H15" t="s">
         <v>354</v>
-      </c>
-      <c r="E15" t="s">
-        <v>355</v>
-      </c>
-      <c r="F15" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>siokteng.jpg</v>
-      </c>
-      <c r="G15" t="s">
-        <v>372</v>
-      </c>
-      <c r="H15" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B16" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C16" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D16" t="s">
+        <v>350</v>
+      </c>
+      <c r="E16" t="s">
+        <v>351</v>
+      </c>
+      <c r="F16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>vivian.jpg</v>
+      </c>
+      <c r="G16" t="s">
+        <v>369</v>
+      </c>
+      <c r="H16" t="s">
         <v>354</v>
-      </c>
-      <c r="E16" t="s">
-        <v>355</v>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>vivian.jpg</v>
-      </c>
-      <c r="G16" t="s">
-        <v>373</v>
-      </c>
-      <c r="H16" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B17" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C17" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D17" t="s">
+        <v>350</v>
+      </c>
+      <c r="E17" t="s">
+        <v>351</v>
+      </c>
+      <c r="F17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>bonteck.jpg</v>
+      </c>
+      <c r="G17" t="s">
+        <v>370</v>
+      </c>
+      <c r="H17" t="s">
         <v>354</v>
-      </c>
-      <c r="E17" t="s">
-        <v>355</v>
-      </c>
-      <c r="F17" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>bonteck.jpg</v>
-      </c>
-      <c r="G17" t="s">
-        <v>374</v>
-      </c>
-      <c r="H17" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B18" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C18" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D18" t="s">
+        <v>350</v>
+      </c>
+      <c r="E18" t="s">
+        <v>351</v>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>chinmee.jpg</v>
+      </c>
+      <c r="G18" t="s">
+        <v>371</v>
+      </c>
+      <c r="H18" t="s">
         <v>354</v>
-      </c>
-      <c r="E18" t="s">
-        <v>355</v>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>chinmee.jpg</v>
-      </c>
-      <c r="G18" t="s">
-        <v>375</v>
-      </c>
-      <c r="H18" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B19" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C19" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D19" t="s">
+        <v>350</v>
+      </c>
+      <c r="E19" t="s">
+        <v>351</v>
+      </c>
+      <c r="F19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>soonmeng.jpg</v>
+      </c>
+      <c r="G19" t="s">
+        <v>372</v>
+      </c>
+      <c r="H19" t="s">
         <v>354</v>
-      </c>
-      <c r="E19" t="s">
-        <v>355</v>
-      </c>
-      <c r="F19" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>soonmeng.jpg</v>
-      </c>
-      <c r="G19" t="s">
-        <v>376</v>
-      </c>
-      <c r="H19" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B20" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C20" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D20" t="s">
+        <v>350</v>
+      </c>
+      <c r="E20" t="s">
+        <v>351</v>
+      </c>
+      <c r="F20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yuehong.jpg</v>
+      </c>
+      <c r="G20" t="s">
+        <v>373</v>
+      </c>
+      <c r="H20" t="s">
         <v>354</v>
-      </c>
-      <c r="E20" t="s">
-        <v>355</v>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>yuehong.jpg</v>
-      </c>
-      <c r="G20" t="s">
-        <v>377</v>
-      </c>
-      <c r="H20" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B21" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C21" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E21" t="s">
+        <v>351</v>
+      </c>
+      <c r="F21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>choejang.jpg</v>
+      </c>
+      <c r="G21" t="s">
+        <v>374</v>
+      </c>
+      <c r="H21" t="s">
         <v>354</v>
-      </c>
-      <c r="E21" t="s">
-        <v>355</v>
-      </c>
-      <c r="F21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>choejang.jpg</v>
-      </c>
-      <c r="G21" t="s">
-        <v>378</v>
-      </c>
-      <c r="H21" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B22" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C22" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D22" t="s">
+        <v>350</v>
+      </c>
+      <c r="E22" t="s">
+        <v>351</v>
+      </c>
+      <c r="F22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>meichia.jpg</v>
+      </c>
+      <c r="G22" t="s">
+        <v>375</v>
+      </c>
+      <c r="H22" t="s">
         <v>354</v>
-      </c>
-      <c r="E22" t="s">
-        <v>355</v>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>meichia.jpg</v>
-      </c>
-      <c r="G22" t="s">
-        <v>379</v>
-      </c>
-      <c r="H22" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B23" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C23" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D23" t="s">
+        <v>350</v>
+      </c>
+      <c r="E23" t="s">
+        <v>351</v>
+      </c>
+      <c r="F23" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>gekhee.jpg</v>
+      </c>
+      <c r="G23" t="s">
+        <v>376</v>
+      </c>
+      <c r="H23" t="s">
         <v>354</v>
-      </c>
-      <c r="E23" t="s">
-        <v>355</v>
-      </c>
-      <c r="F23" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>gekhee.jpg</v>
-      </c>
-      <c r="G23" t="s">
-        <v>380</v>
-      </c>
-      <c r="H23" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B24" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C24" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D24" t="s">
+        <v>350</v>
+      </c>
+      <c r="E24" t="s">
+        <v>351</v>
+      </c>
+      <c r="F24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>aimee.jpg</v>
+      </c>
+      <c r="G24" t="s">
+        <v>377</v>
+      </c>
+      <c r="H24" t="s">
         <v>354</v>
-      </c>
-      <c r="E24" t="s">
-        <v>355</v>
-      </c>
-      <c r="F24" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>aimee.jpg</v>
-      </c>
-      <c r="G24" t="s">
-        <v>381</v>
-      </c>
-      <c r="H24" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B25" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C25" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D25" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geokchin.jpg</v>
       </c>
       <c r="G25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H25" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B26" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C26" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D26" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laysiew.jpg</v>
       </c>
       <c r="G26" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="H26" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B27" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C27" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D27" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>waiyee.jpg</v>
       </c>
       <c r="G27" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="H27" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C28" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D28" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>carol.jpg</v>
       </c>
       <c r="G28" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="H28" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B29" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C29" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D29" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F29" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yokewant.jpg</v>
       </c>
       <c r="G29" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="H29" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B30" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C30" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D30" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F30" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pohcheng.jpg</v>
       </c>
       <c r="G30" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="H30" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B31" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C31" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D31" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F31" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geoklan.jpg</v>
       </c>
       <c r="G31" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="H31" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B32" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C32" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D32" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F32" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laichee.jpg</v>
       </c>
       <c r="G32" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="H32" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B33" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C33" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D33" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F33" s="4" t="str">
         <f t="shared" si="0"/>
         <v>beechoo.jpg</v>
       </c>
       <c r="G33" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="H33" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -7495,7 +7424,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7503,15 +7432,15 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" t="s">
         <v>192</v>
-      </c>
-      <c r="B4" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -7520,14 +7449,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7772,23 +7699,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7814,9 +7738,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1893" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A9B1783-B392-4D61-BF83-E5DA8EF3E38F}"/>
+  <xr:revisionPtr revIDLastSave="1897" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07BEBD0B-6FFD-4200-9594-C29C5FC13A16}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$128</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="587">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1797,6 +1797,12 @@
   </si>
   <si>
     <t>Sunrise Charity Walk</t>
+  </si>
+  <si>
+    <t>Kopi Kaki session at Blk 123 coffee shop, 830am to 930am</t>
+  </si>
+  <si>
+    <t>咖啡老友，大牌123咖啡店，早上8点30分至9点30分</t>
   </si>
 </sst>
 </file>
@@ -2585,7 +2591,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -2643,7 +2649,7 @@
         <v>46023</v>
       </c>
       <c r="B3" s="32" t="str">
-        <f t="shared" ref="B3:B85" si="0">TEXT($A3,"ddd")</f>
+        <f t="shared" ref="B3:B86" si="0">TEXT($A3,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C3" s="33" t="s">
@@ -4351,196 +4357,196 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="12">
+        <f>DATE(2026,9,21)</f>
+        <v>46286</v>
+      </c>
+      <c r="B82" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>586</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F82" s="25" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="12">
         <f>DATE(2026,10,23)</f>
         <v>46318</v>
       </c>
-      <c r="B82" s="13" t="str">
+      <c r="B83" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C82" s="16" t="s">
+      <c r="C83" s="16" t="s">
         <v>577</v>
       </c>
-      <c r="D82" s="16" t="s">
+      <c r="D83" s="16" t="s">
         <v>580</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="E83" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F82" s="25" t="s">
+      <c r="F83" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" s="12">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="12">
         <f>DATE(2026,10,24)</f>
         <v>46319</v>
       </c>
-      <c r="B83" s="13" t="str">
+      <c r="B84" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C83" s="16" t="s">
+      <c r="C84" s="16" t="s">
         <v>578</v>
       </c>
-      <c r="D83" s="16" t="s">
+      <c r="D84" s="16" t="s">
         <v>581</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E84" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F83" s="25" t="s">
+      <c r="F84" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="12">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="12">
         <f>DATE(2026,10,26)</f>
         <v>46321</v>
       </c>
-      <c r="B84" s="42" t="str">
+      <c r="B85" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C84" s="25" t="s">
+      <c r="C85" s="25" t="s">
         <v>559</v>
       </c>
-      <c r="D84" s="25" t="s">
+      <c r="D85" s="25" t="s">
         <v>558</v>
       </c>
-      <c r="E84" s="25" t="s">
+      <c r="E85" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="F84" s="25" t="s">
+      <c r="F85" s="25" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="12">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="12">
         <f>DATE(2026,10,27)</f>
         <v>46322</v>
       </c>
-      <c r="B85" s="42" t="str">
+      <c r="B86" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C85" s="25" t="s">
+      <c r="C86" s="25" t="s">
         <v>561</v>
       </c>
-      <c r="D85" s="25"/>
-      <c r="E85" s="25" t="s">
+      <c r="D86" s="25"/>
+      <c r="E86" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="F85" s="25" t="s">
+      <c r="F86" s="25" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="35">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
       </c>
-      <c r="B86" s="36" t="str">
-        <f t="shared" ref="B86:B126" si="2">TEXT($A86,"ddd")</f>
+      <c r="B87" s="36" t="str">
+        <f t="shared" ref="B87:B127" si="2">TEXT($A87,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C86" s="40" t="s">
+      <c r="C87" s="40" t="s">
         <v>575</v>
       </c>
-      <c r="D86" s="40" t="s">
+      <c r="D87" s="40" t="s">
         <v>574</v>
       </c>
-      <c r="E86" s="37" t="s">
+      <c r="E87" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F86" s="25" t="s">
+      <c r="F87" s="25" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="35">
         <f>DATE(2026,11,8)</f>
         <v>46334</v>
       </c>
-      <c r="B87" s="36" t="str">
-        <f>TEXT($A87,"ddd")</f>
+      <c r="B88" s="36" t="str">
+        <f>TEXT($A88,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C87" s="37" t="s">
+      <c r="C88" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="D87" s="37" t="s">
+      <c r="D88" s="37" t="s">
         <v>453</v>
       </c>
-      <c r="E87" s="39" t="s">
+      <c r="E88" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F87" s="25" t="s">
+      <c r="F88" s="25" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="12">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="12">
         <f>DATE(2026,11,9)</f>
         <v>46335</v>
       </c>
-      <c r="B88" s="13" t="str">
-        <f>TEXT($A88,"ddd")</f>
+      <c r="B89" s="13" t="str">
+        <f>TEXT($A89,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C89" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="D88" s="11" t="s">
+      <c r="D89" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="E88" s="38" t="s">
+      <c r="E89" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F88" s="25" t="s">
+      <c r="F89" s="25" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="31">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="31">
         <f>DATE(2026,11,28)</f>
         <v>46354</v>
       </c>
-      <c r="B89" s="32" t="str">
+      <c r="B90" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C89" s="43" t="s">
+      <c r="C90" s="43" t="s">
         <v>573</v>
       </c>
-      <c r="D89" s="33"/>
-      <c r="E89" s="33" t="s">
+      <c r="D90" s="33"/>
+      <c r="E90" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F89" s="25" t="s">
+      <c r="F90" s="25" t="s">
         <v>428</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="35">
-        <f>DATE(2026,12,7)</f>
-        <v>46363</v>
-      </c>
-      <c r="B90" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Mon</v>
-      </c>
-      <c r="C90" s="40" t="s">
-        <v>569</v>
-      </c>
-      <c r="D90" s="40" t="s">
-        <v>570</v>
-      </c>
-      <c r="E90" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="F90" s="40" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
@@ -4553,810 +4559,832 @@
         <v>Mon</v>
       </c>
       <c r="C91" s="40" t="s">
-        <v>571</v>
-      </c>
-      <c r="D91" s="40"/>
+        <v>569</v>
+      </c>
+      <c r="D91" s="40" t="s">
+        <v>570</v>
+      </c>
       <c r="E91" s="40" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="F91" s="40" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="35">
+        <f>DATE(2026,12,7)</f>
+        <v>46363</v>
+      </c>
+      <c r="B92" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C92" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="D92" s="40"/>
+      <c r="E92" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="F92" s="40" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="35">
         <f>DATE(2026,12,11)</f>
         <v>46367</v>
       </c>
-      <c r="B92" s="36" t="str">
+      <c r="B93" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C92" s="40" t="s">
+      <c r="C93" s="40" t="s">
         <v>565</v>
       </c>
-      <c r="D92" s="40" t="s">
+      <c r="D93" s="40" t="s">
         <v>566</v>
       </c>
-      <c r="E92" s="40" t="s">
+      <c r="E93" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="F92" s="44" t="s">
+      <c r="F93" s="44" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="35">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B93" s="36" t="str">
+      <c r="B94" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C93" s="40" t="s">
+      <c r="C94" s="40" t="s">
         <v>445</v>
       </c>
-      <c r="D93" s="40" t="s">
+      <c r="D94" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E93" s="37" t="s">
+      <c r="E94" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F93" s="25" t="s">
+      <c r="F94" s="25" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="35">
         <f>DATE(2026,12,25)</f>
         <v>46381</v>
       </c>
-      <c r="B94" s="36" t="str">
-        <f>TEXT($A94,"ddd")</f>
+      <c r="B95" s="36" t="str">
+        <f>TEXT($A95,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C94" s="37" t="s">
+      <c r="C95" s="37" t="s">
         <v>449</v>
       </c>
-      <c r="D94" s="37" t="s">
+      <c r="D95" s="37" t="s">
         <v>450</v>
       </c>
-      <c r="E94" s="39" t="s">
+      <c r="E95" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F94" s="25" t="s">
+      <c r="F95" s="25" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="12">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B95" s="13" t="str">
-        <f>TEXT($A95,"ddd")</f>
+      <c r="B96" s="13" t="str">
+        <f>TEXT($A96,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C96" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="D95" s="11" t="s">
+      <c r="D96" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="E95" s="38" t="s">
+      <c r="E96" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F95" s="25" t="s">
+      <c r="F96" s="25" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="31">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="31">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B96" s="32" t="str">
+      <c r="B97" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C96" s="43" t="s">
+      <c r="C97" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="D96" s="33" t="s">
+      <c r="D97" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="E96" s="33" t="s">
+      <c r="E97" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F96" s="25" t="s">
+      <c r="F97" s="25" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="35">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B97" s="36" t="str">
+      <c r="B98" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C97" s="37" t="s">
+      <c r="C98" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="D97" s="37" t="s">
+      <c r="D98" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E97" s="37" t="s">
+      <c r="E98" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F97" s="25" t="s">
+      <c r="F98" s="25" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="35">
         <f>DATE(2027,2,6)</f>
         <v>46424</v>
       </c>
-      <c r="B98" s="36" t="str">
-        <f>TEXT($A98,"ddd")</f>
+      <c r="B99" s="36" t="str">
+        <f>TEXT($A99,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C98" s="37" t="s">
+      <c r="C99" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="D98" s="37" t="s">
+      <c r="D99" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="E98" s="39" t="s">
+      <c r="E99" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F98" s="25" t="s">
+      <c r="F99" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="35">
         <f>DATE(2027,2,7)</f>
         <v>46425</v>
       </c>
-      <c r="B99" s="36" t="str">
-        <f>TEXT($A99,"ddd")</f>
+      <c r="B100" s="36" t="str">
+        <f>TEXT($A100,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C99" s="37" t="s">
+      <c r="C100" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="D99" s="37" t="s">
+      <c r="D100" s="37" t="s">
         <v>470</v>
       </c>
-      <c r="E99" s="39" t="s">
+      <c r="E100" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="F100" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="12">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B100" s="13" t="str">
-        <f>TEXT($A100,"ddd")</f>
+      <c r="B101" s="13" t="str">
+        <f>TEXT($A101,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C100" s="11" t="s">
+      <c r="C101" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="D100" s="11" t="s">
+      <c r="D101" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="E100" s="38" t="s">
+      <c r="E101" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F100" s="25" t="s">
+      <c r="F101" s="25" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="41">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B101" s="42" t="str">
+      <c r="B102" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C101" s="25" t="s">
+      <c r="C102" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="D101" s="25" t="s">
+      <c r="D102" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="E101" s="25" t="s">
+      <c r="E102" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="F101" s="26" t="s">
+      <c r="F102" s="26" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="12">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="12">
         <f>DATE(2027,3,6)</f>
         <v>46452</v>
       </c>
-      <c r="B102" s="13" t="str">
-        <f>TEXT($A102,"ddd")</f>
+      <c r="B103" s="13" t="str">
+        <f>TEXT($A103,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C102" s="11" t="s">
+      <c r="C103" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="D102" s="11" t="s">
+      <c r="D103" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="E102" s="11" t="s">
+      <c r="E103" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F102" s="25" t="s">
+      <c r="F103" s="25" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="12">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="12">
         <f>DATE(2027,3,10)</f>
         <v>46456</v>
       </c>
-      <c r="B103" s="13" t="str">
-        <f>TEXT($A103,"ddd")</f>
+      <c r="B104" s="13" t="str">
+        <f>TEXT($A104,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C104" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="D103" s="11" t="s">
+      <c r="D104" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="E103" s="38" t="s">
+      <c r="E104" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F103" s="25" t="s">
+      <c r="F104" s="25" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="31">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="31">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B104" s="32" t="str">
+      <c r="B105" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C104" s="33" t="s">
+      <c r="C105" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D104" s="33" t="s">
+      <c r="D105" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E104" s="33" t="s">
+      <c r="E105" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F104" s="26" t="s">
+      <c r="F105" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="35">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B105" s="36" t="str">
+      <c r="B106" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C105" s="37" t="s">
+      <c r="C106" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D105" s="37" t="s">
+      <c r="D106" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="E105" s="37" t="s">
+      <c r="E106" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F105" s="26" t="s">
+      <c r="F106" s="26" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="12">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="12">
         <f>DATE(2027,3,26)</f>
         <v>46472</v>
       </c>
-      <c r="B106" s="13" t="str">
-        <f>TEXT($A106,"ddd")</f>
+      <c r="B107" s="13" t="str">
+        <f>TEXT($A107,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C106" s="11" t="s">
+      <c r="C107" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D106" s="11" t="s">
+      <c r="D107" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="E106" s="38" t="s">
+      <c r="E107" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F106" s="25" t="s">
+      <c r="F107" s="25" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="31">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="31">
         <f>DATE(2027,4,17)</f>
         <v>46494</v>
       </c>
-      <c r="B107" s="32" t="str">
-        <f>TEXT($A107,"ddd")</f>
+      <c r="B108" s="32" t="str">
+        <f>TEXT($A108,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C107" s="43" t="s">
+      <c r="C108" s="43" t="s">
         <v>582</v>
       </c>
-      <c r="D107" s="43" t="s">
+      <c r="D108" s="43" t="s">
         <v>583</v>
       </c>
-      <c r="E107" s="43" t="s">
+      <c r="E108" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F107" s="45" t="s">
+      <c r="F108" s="45" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="35">
         <f>DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="B108" s="36" t="str">
-        <f>TEXT($A108,"ddd")</f>
+      <c r="B109" s="36" t="str">
+        <f>TEXT($A109,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C108" s="37" t="s">
+      <c r="C109" s="37" t="s">
         <v>458</v>
       </c>
-      <c r="D108" s="37" t="s">
+      <c r="D109" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="E108" s="39" t="s">
+      <c r="E109" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F108" s="25" t="s">
+      <c r="F109" s="25" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="12">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="12">
         <f>DATE(2027,5,17)</f>
         <v>46524</v>
       </c>
-      <c r="B109" s="13" t="str">
-        <f>TEXT($A109,"ddd")</f>
+      <c r="B110" s="13" t="str">
+        <f>TEXT($A110,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C110" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D109" s="11" t="s">
+      <c r="D110" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="E109" s="38" t="s">
+      <c r="E110" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F109" s="25" t="s">
+      <c r="F110" s="25" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="41">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="41">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B110" s="42" t="str">
+      <c r="B111" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C110" s="25" t="s">
+      <c r="C111" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="D110" s="25" t="s">
+      <c r="D111" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="E110" s="25" t="s">
+      <c r="E111" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="F110" s="26" t="s">
+      <c r="F111" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="12">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B111" s="13" t="str">
-        <f>TEXT($A111,"ddd")</f>
+      <c r="B112" s="13" t="str">
+        <f>TEXT($A112,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C112" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="D111" s="11" t="s">
+      <c r="D112" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="E111" s="38" t="s">
+      <c r="E112" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F111" s="25" t="s">
+      <c r="F112" s="25" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="31">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="31">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B112" s="32" t="str">
+      <c r="B113" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C112" s="33" t="s">
+      <c r="C113" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="D112" s="33" t="s">
+      <c r="D113" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="E112" s="33" t="s">
+      <c r="E113" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F112" s="26" t="s">
+      <c r="F113" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="12">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B113" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E113" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="F113" s="26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B114" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="F114" s="26" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B115" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B116" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C116" s="16" t="s">
-        <v>437</v>
+      <c r="C116" s="11" t="s">
+        <v>236</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>438</v>
+        <v>198</v>
       </c>
       <c r="E116" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F116" s="25" t="s">
+      <c r="F116" s="26" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="12">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B117" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="E117" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F117" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="35">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B117" s="36" t="str">
+      <c r="B118" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C117" s="37" t="s">
+      <c r="C118" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="D117" s="37" t="s">
+      <c r="D118" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="E117" s="37" t="s">
+      <c r="E118" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F117" s="26" t="s">
+      <c r="F118" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="12">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="12">
         <f>DATE(2027,8,9)</f>
         <v>46608</v>
       </c>
-      <c r="B118" s="13" t="str">
-        <f>TEXT($A118,"ddd")</f>
+      <c r="B119" s="13" t="str">
+        <f>TEXT($A119,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C119" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="D118" s="11" t="s">
+      <c r="D119" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="E118" s="38" t="s">
+      <c r="E119" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F118" s="25" t="s">
+      <c r="F119" s="25" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="31">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="31">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B119" s="32" t="str">
+      <c r="B120" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C119" s="33" t="s">
+      <c r="C120" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="D119" s="33" t="s">
+      <c r="D120" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E119" s="33" t="s">
+      <c r="E120" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F119" s="26" t="s">
+      <c r="F120" s="26" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="12">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
       </c>
-      <c r="B120" s="13" t="str">
+      <c r="B121" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C120" s="11" t="s">
+      <c r="C121" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D120" s="11" t="s">
+      <c r="D121" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E120" s="11" t="s">
+      <c r="E121" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F120" s="26" t="s">
+      <c r="F121" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="12">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B121" s="13" t="str">
+      <c r="B122" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="C122" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D121" s="11" t="s">
+      <c r="D122" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E121" s="11" t="s">
+      <c r="E122" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F121" s="26" t="s">
+      <c r="F122" s="26" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="35">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B122" s="36" t="str">
+      <c r="B123" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C122" s="37" t="s">
+      <c r="C123" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="D122" s="37" t="s">
+      <c r="D123" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="E122" s="37" t="s">
+      <c r="E123" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F122" s="26" t="s">
+      <c r="F123" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="12">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="12">
         <f>DATE(2027,10,28)</f>
         <v>46688</v>
       </c>
-      <c r="B123" s="13" t="str">
-        <f>TEXT($A123,"ddd")</f>
+      <c r="B124" s="13" t="str">
+        <f>TEXT($A124,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C124" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D123" s="11" t="s">
+      <c r="D124" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="E123" s="38" t="s">
+      <c r="E124" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F123" s="25" t="s">
+      <c r="F124" s="25" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="31">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="31">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B124" s="32" t="str">
+      <c r="B125" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C124" s="33" t="s">
+      <c r="C125" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D124" s="33" t="s">
+      <c r="D125" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E124" s="33" t="s">
+      <c r="E125" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F124" s="26" t="s">
+      <c r="F125" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="12">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B125" s="13" t="str">
+      <c r="B126" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C125" s="16" t="s">
+      <c r="C126" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="D125" s="11" t="s">
+      <c r="D126" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E125" s="11" t="s">
+      <c r="E126" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F125" s="25" t="s">
+      <c r="F126" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B126" s="36" t="str">
+      <c r="B127" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C126" s="37" t="s">
+      <c r="C127" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D126" s="40" t="s">
+      <c r="D127" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E126" s="37" t="s">
+      <c r="E127" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F126" s="26" t="s">
+      <c r="F127" s="26" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="12">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B127" s="13" t="str">
-        <f>TEXT($A127,"ddd")</f>
+      <c r="B128" s="13" t="str">
+        <f>TEXT($A128,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C127" s="11" t="s">
+      <c r="C128" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D127" s="11" t="s">
+      <c r="D128" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="E127" s="38" t="s">
+      <c r="E128" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F127" s="25" t="s">
+      <c r="F128" s="25" t="s">
         <v>493</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E127" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E128" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -7424,7 +7452,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7449,12 +7477,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7699,20 +7729,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7738,14 +7771,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1897" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07BEBD0B-6FFD-4200-9594-C29C5FC13A16}"/>
+  <xr:revisionPtr revIDLastSave="1898" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C372AB16-2DCD-4057-A6E1-F032654189AB}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4357,12 +4357,12 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="12">
-        <f>DATE(2026,9,21)</f>
-        <v>46286</v>
+        <f>DATE(2026,10,21)</f>
+        <v>46316</v>
       </c>
       <c r="B82" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Wed</v>
       </c>
       <c r="C82" s="16" t="s">
         <v>585</v>
@@ -7477,14 +7477,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7729,23 +7727,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7771,9 +7766,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1898" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C372AB16-2DCD-4057-A6E1-F032654189AB}"/>
+  <xr:revisionPtr revIDLastSave="1908" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5906F873-5C84-4211-BB05-855715839F61}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$129</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="589">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1803,6 +1803,12 @@
   </si>
   <si>
     <t>咖啡老友，大牌123咖啡店，早上8点30分至9点30分</t>
+  </si>
+  <si>
+    <t>遗嘱规划</t>
+  </si>
+  <si>
+    <t>Will Writing by Mr Patrick Chang for 10-12pax elderly beneficiaries. 10am-12pm.</t>
   </si>
 </sst>
 </file>
@@ -2591,7 +2597,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -4469,7 +4475,7 @@
         <v>46329</v>
       </c>
       <c r="B87" s="36" t="str">
-        <f t="shared" ref="B87:B127" si="2">TEXT($A87,"ddd")</f>
+        <f t="shared" ref="B87:B128" si="2">TEXT($A87,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="C87" s="40" t="s">
@@ -4530,45 +4536,41 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="31">
+      <c r="A90" s="12">
+        <f>DATE(2026,11,19)</f>
+        <v>46345</v>
+      </c>
+      <c r="B90" s="13" t="str">
+        <f>TEXT($A90,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="E90" s="38"/>
+      <c r="F90" s="25"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="31">
         <f>DATE(2026,11,28)</f>
         <v>46354</v>
       </c>
-      <c r="B90" s="32" t="str">
+      <c r="B91" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C90" s="43" t="s">
+      <c r="C91" s="43" t="s">
         <v>573</v>
       </c>
-      <c r="D90" s="33"/>
-      <c r="E90" s="33" t="s">
+      <c r="D91" s="33"/>
+      <c r="E91" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F90" s="25" t="s">
+      <c r="F91" s="25" t="s">
         <v>428</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="35">
-        <f>DATE(2026,12,7)</f>
-        <v>46363</v>
-      </c>
-      <c r="B91" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Mon</v>
-      </c>
-      <c r="C91" s="40" t="s">
-        <v>569</v>
-      </c>
-      <c r="D91" s="40" t="s">
-        <v>570</v>
-      </c>
-      <c r="E91" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="F91" s="40" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
@@ -4581,810 +4583,832 @@
         <v>Mon</v>
       </c>
       <c r="C92" s="40" t="s">
-        <v>571</v>
-      </c>
-      <c r="D92" s="40"/>
+        <v>569</v>
+      </c>
+      <c r="D92" s="40" t="s">
+        <v>570</v>
+      </c>
       <c r="E92" s="40" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="F92" s="40" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="35">
+        <f>DATE(2026,12,7)</f>
+        <v>46363</v>
+      </c>
+      <c r="B93" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C93" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="D93" s="40"/>
+      <c r="E93" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="F93" s="40" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="35">
         <f>DATE(2026,12,11)</f>
         <v>46367</v>
       </c>
-      <c r="B93" s="36" t="str">
+      <c r="B94" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C93" s="40" t="s">
+      <c r="C94" s="40" t="s">
         <v>565</v>
       </c>
-      <c r="D93" s="40" t="s">
+      <c r="D94" s="40" t="s">
         <v>566</v>
       </c>
-      <c r="E93" s="40" t="s">
+      <c r="E94" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="F93" s="44" t="s">
+      <c r="F94" s="44" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="35">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B94" s="36" t="str">
+      <c r="B95" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C94" s="40" t="s">
+      <c r="C95" s="40" t="s">
         <v>445</v>
       </c>
-      <c r="D94" s="40" t="s">
+      <c r="D95" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E94" s="37" t="s">
+      <c r="E95" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F94" s="25" t="s">
+      <c r="F95" s="25" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="35">
         <f>DATE(2026,12,25)</f>
         <v>46381</v>
       </c>
-      <c r="B95" s="36" t="str">
-        <f>TEXT($A95,"ddd")</f>
+      <c r="B96" s="36" t="str">
+        <f>TEXT($A96,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C95" s="37" t="s">
+      <c r="C96" s="37" t="s">
         <v>449</v>
       </c>
-      <c r="D95" s="37" t="s">
+      <c r="D96" s="37" t="s">
         <v>450</v>
       </c>
-      <c r="E95" s="39" t="s">
+      <c r="E96" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F95" s="25" t="s">
+      <c r="F96" s="25" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="12">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B96" s="13" t="str">
-        <f>TEXT($A96,"ddd")</f>
+      <c r="B97" s="13" t="str">
+        <f>TEXT($A97,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C96" s="11" t="s">
+      <c r="C97" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="D96" s="11" t="s">
+      <c r="D97" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="E96" s="38" t="s">
+      <c r="E97" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F96" s="25" t="s">
+      <c r="F97" s="25" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="31">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="31">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B97" s="32" t="str">
+      <c r="B98" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C97" s="43" t="s">
+      <c r="C98" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="D97" s="33" t="s">
+      <c r="D98" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="E97" s="33" t="s">
+      <c r="E98" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F97" s="25" t="s">
+      <c r="F98" s="25" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="35">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B98" s="36" t="str">
+      <c r="B99" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C98" s="37" t="s">
+      <c r="C99" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="D98" s="37" t="s">
+      <c r="D99" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E98" s="37" t="s">
+      <c r="E99" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F98" s="25" t="s">
+      <c r="F99" s="25" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="35">
         <f>DATE(2027,2,6)</f>
         <v>46424</v>
       </c>
-      <c r="B99" s="36" t="str">
-        <f>TEXT($A99,"ddd")</f>
+      <c r="B100" s="36" t="str">
+        <f>TEXT($A100,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C99" s="37" t="s">
+      <c r="C100" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="D99" s="37" t="s">
+      <c r="D100" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="E99" s="39" t="s">
+      <c r="E100" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="F100" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="35">
         <f>DATE(2027,2,7)</f>
         <v>46425</v>
       </c>
-      <c r="B100" s="36" t="str">
-        <f>TEXT($A100,"ddd")</f>
+      <c r="B101" s="36" t="str">
+        <f>TEXT($A101,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C100" s="37" t="s">
+      <c r="C101" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="D100" s="37" t="s">
+      <c r="D101" s="37" t="s">
         <v>470</v>
       </c>
-      <c r="E100" s="39" t="s">
+      <c r="E101" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F100" s="25" t="s">
+      <c r="F101" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="12">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B101" s="13" t="str">
-        <f>TEXT($A101,"ddd")</f>
+      <c r="B102" s="13" t="str">
+        <f>TEXT($A102,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C102" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="D101" s="11" t="s">
+      <c r="D102" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="E101" s="38" t="s">
+      <c r="E102" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F101" s="25" t="s">
+      <c r="F102" s="25" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="41">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B102" s="42" t="str">
+      <c r="B103" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C102" s="25" t="s">
+      <c r="C103" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="D102" s="25" t="s">
+      <c r="D103" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="E102" s="25" t="s">
+      <c r="E103" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="F102" s="26" t="s">
+      <c r="F103" s="26" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="12">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="12">
         <f>DATE(2027,3,6)</f>
         <v>46452</v>
       </c>
-      <c r="B103" s="13" t="str">
-        <f>TEXT($A103,"ddd")</f>
+      <c r="B104" s="13" t="str">
+        <f>TEXT($A104,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C104" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="D103" s="11" t="s">
+      <c r="D104" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="E103" s="11" t="s">
+      <c r="E104" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F103" s="25" t="s">
+      <c r="F104" s="25" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="12">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="12">
         <f>DATE(2027,3,10)</f>
         <v>46456</v>
       </c>
-      <c r="B104" s="13" t="str">
-        <f>TEXT($A104,"ddd")</f>
+      <c r="B105" s="13" t="str">
+        <f>TEXT($A105,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C105" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="D104" s="11" t="s">
+      <c r="D105" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="E104" s="38" t="s">
+      <c r="E105" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F104" s="25" t="s">
+      <c r="F105" s="25" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="31">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="31">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B105" s="32" t="str">
+      <c r="B106" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C105" s="33" t="s">
+      <c r="C106" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D105" s="33" t="s">
+      <c r="D106" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E105" s="33" t="s">
+      <c r="E106" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F105" s="26" t="s">
+      <c r="F106" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="35">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B106" s="36" t="str">
+      <c r="B107" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C106" s="37" t="s">
+      <c r="C107" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D106" s="37" t="s">
+      <c r="D107" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="E106" s="37" t="s">
+      <c r="E107" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F106" s="26" t="s">
+      <c r="F107" s="26" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="12">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="12">
         <f>DATE(2027,3,26)</f>
         <v>46472</v>
       </c>
-      <c r="B107" s="13" t="str">
-        <f>TEXT($A107,"ddd")</f>
+      <c r="B108" s="13" t="str">
+        <f>TEXT($A108,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C108" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D107" s="11" t="s">
+      <c r="D108" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="E107" s="38" t="s">
+      <c r="E108" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F107" s="25" t="s">
+      <c r="F108" s="25" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="31">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="31">
         <f>DATE(2027,4,17)</f>
         <v>46494</v>
       </c>
-      <c r="B108" s="32" t="str">
-        <f>TEXT($A108,"ddd")</f>
+      <c r="B109" s="32" t="str">
+        <f>TEXT($A109,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C108" s="43" t="s">
+      <c r="C109" s="43" t="s">
         <v>582</v>
       </c>
-      <c r="D108" s="43" t="s">
+      <c r="D109" s="43" t="s">
         <v>583</v>
       </c>
-      <c r="E108" s="43" t="s">
+      <c r="E109" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F108" s="45" t="s">
+      <c r="F109" s="45" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="35">
         <f>DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="B109" s="36" t="str">
-        <f>TEXT($A109,"ddd")</f>
+      <c r="B110" s="36" t="str">
+        <f>TEXT($A110,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C109" s="37" t="s">
+      <c r="C110" s="37" t="s">
         <v>458</v>
       </c>
-      <c r="D109" s="37" t="s">
+      <c r="D110" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="E109" s="39" t="s">
+      <c r="E110" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F109" s="25" t="s">
+      <c r="F110" s="25" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="12">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="12">
         <f>DATE(2027,5,17)</f>
         <v>46524</v>
       </c>
-      <c r="B110" s="13" t="str">
-        <f>TEXT($A110,"ddd")</f>
+      <c r="B111" s="13" t="str">
+        <f>TEXT($A111,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C111" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D110" s="11" t="s">
+      <c r="D111" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="E110" s="38" t="s">
+      <c r="E111" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F110" s="25" t="s">
+      <c r="F111" s="25" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="41">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="41">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B111" s="42" t="str">
+      <c r="B112" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C111" s="25" t="s">
+      <c r="C112" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="D111" s="25" t="s">
+      <c r="D112" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="E111" s="25" t="s">
+      <c r="E112" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="F111" s="26" t="s">
+      <c r="F112" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="12">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B112" s="13" t="str">
-        <f>TEXT($A112,"ddd")</f>
+      <c r="B113" s="13" t="str">
+        <f>TEXT($A113,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C113" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="D112" s="11" t="s">
+      <c r="D113" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="E112" s="38" t="s">
+      <c r="E113" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F112" s="25" t="s">
+      <c r="F113" s="25" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="31">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="31">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B113" s="32" t="str">
+      <c r="B114" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C113" s="33" t="s">
+      <c r="C114" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="D113" s="33" t="s">
+      <c r="D114" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="E113" s="33" t="s">
+      <c r="E114" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F113" s="26" t="s">
+      <c r="F114" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="12">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B114" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E114" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="F114" s="26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B115" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B116" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B117" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C117" s="16" t="s">
-        <v>437</v>
+      <c r="C117" s="11" t="s">
+        <v>236</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>438</v>
+        <v>198</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F117" s="25" t="s">
+      <c r="F117" s="26" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="12">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B118" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F118" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="35">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B118" s="36" t="str">
+      <c r="B119" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C118" s="37" t="s">
+      <c r="C119" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="D118" s="37" t="s">
+      <c r="D119" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="E118" s="37" t="s">
+      <c r="E119" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F118" s="26" t="s">
+      <c r="F119" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="12">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="12">
         <f>DATE(2027,8,9)</f>
         <v>46608</v>
       </c>
-      <c r="B119" s="13" t="str">
-        <f>TEXT($A119,"ddd")</f>
+      <c r="B120" s="13" t="str">
+        <f>TEXT($A120,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C119" s="11" t="s">
+      <c r="C120" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="D119" s="11" t="s">
+      <c r="D120" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="E119" s="38" t="s">
+      <c r="E120" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F119" s="25" t="s">
+      <c r="F120" s="25" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="31">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="31">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B120" s="32" t="str">
+      <c r="B121" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C120" s="33" t="s">
+      <c r="C121" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="D120" s="33" t="s">
+      <c r="D121" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E120" s="33" t="s">
+      <c r="E121" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F120" s="26" t="s">
+      <c r="F121" s="26" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="12">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
       </c>
-      <c r="B121" s="13" t="str">
+      <c r="B122" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="C122" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D121" s="11" t="s">
+      <c r="D122" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E121" s="11" t="s">
+      <c r="E122" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F121" s="26" t="s">
+      <c r="F122" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="12">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B122" s="13" t="str">
+      <c r="B123" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C123" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D122" s="11" t="s">
+      <c r="D123" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E122" s="11" t="s">
+      <c r="E123" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F122" s="26" t="s">
+      <c r="F123" s="26" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="35">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B123" s="36" t="str">
+      <c r="B124" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C123" s="37" t="s">
+      <c r="C124" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="D123" s="37" t="s">
+      <c r="D124" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="E123" s="37" t="s">
+      <c r="E124" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F123" s="26" t="s">
+      <c r="F124" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="12">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="12">
         <f>DATE(2027,10,28)</f>
         <v>46688</v>
       </c>
-      <c r="B124" s="13" t="str">
-        <f>TEXT($A124,"ddd")</f>
+      <c r="B125" s="13" t="str">
+        <f>TEXT($A125,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C125" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D124" s="11" t="s">
+      <c r="D125" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="E124" s="38" t="s">
+      <c r="E125" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F124" s="25" t="s">
+      <c r="F125" s="25" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="31">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="31">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B125" s="32" t="str">
+      <c r="B126" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C125" s="33" t="s">
+      <c r="C126" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D125" s="33" t="s">
+      <c r="D126" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E125" s="33" t="s">
+      <c r="E126" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F125" s="26" t="s">
+      <c r="F126" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="12">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B126" s="13" t="str">
+      <c r="B127" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C126" s="16" t="s">
+      <c r="C127" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="D126" s="11" t="s">
+      <c r="D127" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E126" s="11" t="s">
+      <c r="E127" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F126" s="25" t="s">
+      <c r="F127" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B127" s="36" t="str">
+      <c r="B128" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C127" s="37" t="s">
+      <c r="C128" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D127" s="40" t="s">
+      <c r="D128" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E127" s="37" t="s">
+      <c r="E128" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F127" s="26" t="s">
+      <c r="F128" s="26" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="12">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B128" s="13" t="str">
-        <f>TEXT($A128,"ddd")</f>
+      <c r="B129" s="13" t="str">
+        <f>TEXT($A129,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C129" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D129" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="E128" s="38" t="s">
+      <c r="E129" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F128" s="25" t="s">
+      <c r="F129" s="25" t="s">
         <v>493</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E128" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E129" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -7477,12 +7501,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7727,20 +7753,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7766,14 +7795,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1908" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5906F873-5C84-4211-BB05-855715839F61}"/>
+  <xr:revisionPtr revIDLastSave="1920" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88703373-7D44-49FB-8EA4-28AE559CEF86}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$130</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="592">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1809,6 +1809,15 @@
   </si>
   <si>
     <t>Will Writing by Mr Patrick Chang for 10-12pax elderly beneficiaries. 10am-12pm.</t>
+  </si>
+  <si>
+    <t>Will writing training for beneficiaries</t>
+  </si>
+  <si>
+    <t>Kueh making at Gin Thye Cake Maker (锦泰西果饼家)</t>
+  </si>
+  <si>
+    <t>糕点自作 - 锦泰西果饼家</t>
   </si>
 </sst>
 </file>
@@ -2065,7 +2074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2154,6 +2163,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2597,7 +2607,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -4475,7 +4485,7 @@
         <v>46329</v>
       </c>
       <c r="B87" s="36" t="str">
-        <f t="shared" ref="B87:B128" si="2">TEXT($A87,"ddd")</f>
+        <f t="shared" ref="B87:B129" si="2">TEXT($A87,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="C87" s="40" t="s">
@@ -4550,8 +4560,12 @@
       <c r="D90" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="E90" s="38"/>
-      <c r="F90" s="25"/>
+      <c r="E90" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="F90" s="44" t="s">
+        <v>589</v>
+      </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="31">
@@ -4727,688 +4741,708 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="35">
+        <f>DATE(2027,1,15)</f>
+        <v>46402</v>
+      </c>
+      <c r="B99" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C99" s="40" t="s">
+        <v>590</v>
+      </c>
+      <c r="D99" s="40" t="s">
+        <v>591</v>
+      </c>
+      <c r="E99" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F99" s="25"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="35">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B99" s="36" t="str">
+      <c r="B100" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C99" s="37" t="s">
+      <c r="C100" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="D99" s="37" t="s">
+      <c r="D100" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E99" s="37" t="s">
+      <c r="E100" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="F100" s="25" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="35">
         <f>DATE(2027,2,6)</f>
         <v>46424</v>
       </c>
-      <c r="B100" s="36" t="str">
-        <f>TEXT($A100,"ddd")</f>
+      <c r="B101" s="36" t="str">
+        <f>TEXT($A101,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C100" s="37" t="s">
+      <c r="C101" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="D100" s="37" t="s">
+      <c r="D101" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="E100" s="39" t="s">
+      <c r="E101" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F100" s="25" t="s">
+      <c r="F101" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="35">
         <f>DATE(2027,2,7)</f>
         <v>46425</v>
       </c>
-      <c r="B101" s="36" t="str">
-        <f>TEXT($A101,"ddd")</f>
+      <c r="B102" s="36" t="str">
+        <f>TEXT($A102,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C101" s="37" t="s">
+      <c r="C102" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="D101" s="37" t="s">
+      <c r="D102" s="37" t="s">
         <v>470</v>
       </c>
-      <c r="E101" s="39" t="s">
+      <c r="E102" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F101" s="25" t="s">
+      <c r="F102" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="12">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B102" s="13" t="str">
-        <f>TEXT($A102,"ddd")</f>
+      <c r="B103" s="13" t="str">
+        <f>TEXT($A103,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C102" s="11" t="s">
+      <c r="C103" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="D102" s="11" t="s">
+      <c r="D103" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="E102" s="38" t="s">
+      <c r="E103" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F102" s="25" t="s">
+      <c r="F103" s="25" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="41">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B103" s="42" t="str">
+      <c r="B104" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C103" s="25" t="s">
+      <c r="C104" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="D103" s="25" t="s">
+      <c r="D104" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="E103" s="25" t="s">
+      <c r="E104" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="F103" s="26" t="s">
+      <c r="F104" s="26" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="12">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="12">
         <f>DATE(2027,3,6)</f>
         <v>46452</v>
       </c>
-      <c r="B104" s="13" t="str">
-        <f>TEXT($A104,"ddd")</f>
+      <c r="B105" s="13" t="str">
+        <f>TEXT($A105,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C105" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="D104" s="11" t="s">
+      <c r="D105" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="E104" s="11" t="s">
+      <c r="E105" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F104" s="25" t="s">
+      <c r="F105" s="25" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="12">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="12">
         <f>DATE(2027,3,10)</f>
         <v>46456</v>
       </c>
-      <c r="B105" s="13" t="str">
-        <f>TEXT($A105,"ddd")</f>
+      <c r="B106" s="13" t="str">
+        <f>TEXT($A106,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C106" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="D105" s="11" t="s">
+      <c r="D106" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="E105" s="38" t="s">
+      <c r="E106" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F105" s="25" t="s">
+      <c r="F106" s="25" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="31">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="31">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B106" s="32" t="str">
+      <c r="B107" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C106" s="33" t="s">
+      <c r="C107" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D106" s="33" t="s">
+      <c r="D107" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E106" s="33" t="s">
+      <c r="E107" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F106" s="26" t="s">
+      <c r="F107" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="35">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B107" s="36" t="str">
+      <c r="B108" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C107" s="37" t="s">
+      <c r="C108" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D107" s="37" t="s">
+      <c r="D108" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="E107" s="37" t="s">
+      <c r="E108" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F107" s="26" t="s">
+      <c r="F108" s="26" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="12">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="12">
         <f>DATE(2027,3,26)</f>
         <v>46472</v>
       </c>
-      <c r="B108" s="13" t="str">
-        <f>TEXT($A108,"ddd")</f>
+      <c r="B109" s="13" t="str">
+        <f>TEXT($A109,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C109" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D108" s="11" t="s">
+      <c r="D109" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="E108" s="38" t="s">
+      <c r="E109" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F108" s="25" t="s">
+      <c r="F109" s="25" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="31">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="31">
         <f>DATE(2027,4,17)</f>
         <v>46494</v>
       </c>
-      <c r="B109" s="32" t="str">
-        <f>TEXT($A109,"ddd")</f>
+      <c r="B110" s="32" t="str">
+        <f>TEXT($A110,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C109" s="43" t="s">
+      <c r="C110" s="43" t="s">
         <v>582</v>
       </c>
-      <c r="D109" s="43" t="s">
+      <c r="D110" s="43" t="s">
         <v>583</v>
       </c>
-      <c r="E109" s="43" t="s">
+      <c r="E110" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F109" s="45" t="s">
+      <c r="F110" s="45" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="35">
         <f>DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="B110" s="36" t="str">
-        <f>TEXT($A110,"ddd")</f>
+      <c r="B111" s="36" t="str">
+        <f>TEXT($A111,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C110" s="37" t="s">
+      <c r="C111" s="37" t="s">
         <v>458</v>
       </c>
-      <c r="D110" s="37" t="s">
+      <c r="D111" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="E110" s="39" t="s">
+      <c r="E111" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F110" s="25" t="s">
+      <c r="F111" s="25" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="12">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="12">
         <f>DATE(2027,5,17)</f>
         <v>46524</v>
       </c>
-      <c r="B111" s="13" t="str">
-        <f>TEXT($A111,"ddd")</f>
+      <c r="B112" s="13" t="str">
+        <f>TEXT($A112,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C112" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D111" s="11" t="s">
+      <c r="D112" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="E111" s="38" t="s">
+      <c r="E112" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F111" s="25" t="s">
+      <c r="F112" s="25" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="41">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="41">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B112" s="42" t="str">
+      <c r="B113" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C112" s="25" t="s">
+      <c r="C113" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="D112" s="25" t="s">
+      <c r="D113" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="E112" s="25" t="s">
+      <c r="E113" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="F112" s="26" t="s">
+      <c r="F113" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="12">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B113" s="13" t="str">
-        <f>TEXT($A113,"ddd")</f>
+      <c r="B114" s="13" t="str">
+        <f>TEXT($A114,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C113" s="11" t="s">
+      <c r="C114" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="D113" s="11" t="s">
+      <c r="D114" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="E113" s="38" t="s">
+      <c r="E114" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F113" s="25" t="s">
+      <c r="F114" s="25" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="31">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="31">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B114" s="32" t="str">
+      <c r="B115" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C114" s="33" t="s">
+      <c r="C115" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="D114" s="33" t="s">
+      <c r="D115" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="E114" s="33" t="s">
+      <c r="E115" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F114" s="26" t="s">
+      <c r="F115" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="12">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B115" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D115" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E115" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="F115" s="26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B116" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B117" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F117" s="26" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B118" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C118" s="16" t="s">
-        <v>437</v>
+      <c r="C118" s="11" t="s">
+        <v>236</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>438</v>
+        <v>198</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F118" s="25" t="s">
+      <c r="F118" s="26" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="12">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B119" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C119" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="E119" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F119" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="35">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B119" s="36" t="str">
+      <c r="B120" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C119" s="37" t="s">
+      <c r="C120" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="D119" s="37" t="s">
+      <c r="D120" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="E119" s="37" t="s">
+      <c r="E120" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F119" s="26" t="s">
+      <c r="F120" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="12">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="12">
         <f>DATE(2027,8,9)</f>
         <v>46608</v>
       </c>
-      <c r="B120" s="13" t="str">
-        <f>TEXT($A120,"ddd")</f>
+      <c r="B121" s="13" t="str">
+        <f>TEXT($A121,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C120" s="11" t="s">
+      <c r="C121" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="D120" s="11" t="s">
+      <c r="D121" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="E120" s="38" t="s">
+      <c r="E121" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F120" s="25" t="s">
+      <c r="F121" s="25" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="31">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="31">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B121" s="32" t="str">
+      <c r="B122" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C121" s="33" t="s">
+      <c r="C122" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="D121" s="33" t="s">
+      <c r="D122" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E121" s="33" t="s">
+      <c r="E122" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F121" s="26" t="s">
+      <c r="F122" s="26" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="12">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
       </c>
-      <c r="B122" s="13" t="str">
+      <c r="B123" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C123" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D122" s="11" t="s">
+      <c r="D123" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E122" s="11" t="s">
+      <c r="E123" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F122" s="26" t="s">
+      <c r="F123" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="12">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B123" s="13" t="str">
+      <c r="B124" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C124" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D123" s="11" t="s">
+      <c r="D124" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E123" s="11" t="s">
+      <c r="E124" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F123" s="26" t="s">
+      <c r="F124" s="26" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="35">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B124" s="36" t="str">
+      <c r="B125" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C124" s="37" t="s">
+      <c r="C125" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="D124" s="37" t="s">
+      <c r="D125" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="E124" s="37" t="s">
+      <c r="E125" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F124" s="26" t="s">
+      <c r="F125" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="12">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="12">
         <f>DATE(2027,10,28)</f>
         <v>46688</v>
       </c>
-      <c r="B125" s="13" t="str">
-        <f>TEXT($A125,"ddd")</f>
+      <c r="B126" s="13" t="str">
+        <f>TEXT($A126,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C125" s="11" t="s">
+      <c r="C126" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D125" s="11" t="s">
+      <c r="D126" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="E125" s="38" t="s">
+      <c r="E126" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F125" s="25" t="s">
+      <c r="F126" s="25" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="31">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="31">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B126" s="32" t="str">
+      <c r="B127" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C126" s="33" t="s">
+      <c r="C127" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D126" s="33" t="s">
+      <c r="D127" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E126" s="33" t="s">
+      <c r="E127" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F126" s="26" t="s">
+      <c r="F127" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="12">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B127" s="13" t="str">
+      <c r="B128" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C127" s="16" t="s">
+      <c r="C128" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="D127" s="11" t="s">
+      <c r="D128" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E127" s="11" t="s">
+      <c r="E128" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F127" s="25" t="s">
+      <c r="F128" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B128" s="36" t="str">
+      <c r="B129" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C128" s="37" t="s">
+      <c r="C129" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D128" s="40" t="s">
+      <c r="D129" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E128" s="37" t="s">
+      <c r="E129" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F128" s="26" t="s">
+      <c r="F129" s="26" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" s="12">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B129" s="13" t="str">
-        <f>TEXT($A129,"ddd")</f>
+      <c r="B130" s="13" t="str">
+        <f>TEXT($A130,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C129" s="11" t="s">
+      <c r="C130" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D129" s="11" t="s">
+      <c r="D130" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="E129" s="38" t="s">
+      <c r="E130" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F129" s="25" t="s">
+      <c r="F130" s="25" t="s">
         <v>493</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E129" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E130" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1920" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88703373-7D44-49FB-8EA4-28AE559CEF86}"/>
+  <xr:revisionPtr revIDLastSave="1933" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD8056A0-E378-48FD-8ED5-D732F0523BBA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$132</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="596">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1818,6 +1818,18 @@
   </si>
   <si>
     <t>糕点自作 - 锦泰西果饼家</t>
+  </si>
+  <si>
+    <t>Health Talk by TCM Physician. 2.30pm - 3.30pm</t>
+  </si>
+  <si>
+    <t>中医保健养生讲座</t>
+  </si>
+  <si>
+    <t>Health Talk 保健养生讲座</t>
+  </si>
+  <si>
+    <t>Health Talk by TCM Physician. 10.30am - 11.30am</t>
   </si>
 </sst>
 </file>
@@ -2607,7 +2619,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -4485,7 +4497,7 @@
         <v>46329</v>
       </c>
       <c r="B87" s="36" t="str">
-        <f t="shared" ref="B87:B129" si="2">TEXT($A87,"ddd")</f>
+        <f t="shared" ref="B87:B131" si="2">TEXT($A87,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="C87" s="40" t="s">
@@ -4503,946 +4515,990 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="35">
+        <f>DATE(2026,11,3)</f>
+        <v>46329</v>
+      </c>
+      <c r="B88" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="C88" s="40" t="s">
+        <v>592</v>
+      </c>
+      <c r="D88" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="E88" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F88" s="44" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="35">
+        <f>DATE(2026,11,7)</f>
+        <v>46333</v>
+      </c>
+      <c r="B89" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="C89" s="40" t="s">
+        <v>595</v>
+      </c>
+      <c r="D89" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F89" s="44" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="35">
         <f>DATE(2026,11,8)</f>
         <v>46334</v>
       </c>
-      <c r="B88" s="36" t="str">
-        <f>TEXT($A88,"ddd")</f>
+      <c r="B90" s="36" t="str">
+        <f>TEXT($A90,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C88" s="37" t="s">
+      <c r="C90" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="D88" s="37" t="s">
+      <c r="D90" s="37" t="s">
         <v>453</v>
       </c>
-      <c r="E88" s="39" t="s">
+      <c r="E90" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F88" s="25" t="s">
+      <c r="F90" s="25" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="12">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="12">
         <f>DATE(2026,11,9)</f>
         <v>46335</v>
       </c>
-      <c r="B89" s="13" t="str">
-        <f>TEXT($A89,"ddd")</f>
+      <c r="B91" s="13" t="str">
+        <f>TEXT($A91,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C91" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D91" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="E89" s="38" t="s">
+      <c r="E91" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F89" s="25" t="s">
+      <c r="F91" s="25" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="12">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="12">
         <f>DATE(2026,11,19)</f>
         <v>46345</v>
       </c>
-      <c r="B90" s="13" t="str">
-        <f>TEXT($A90,"ddd")</f>
+      <c r="B92" s="13" t="str">
+        <f>TEXT($A92,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C90" s="16" t="s">
+      <c r="C92" s="16" t="s">
         <v>588</v>
       </c>
-      <c r="D90" s="16" t="s">
+      <c r="D92" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="E90" s="46" t="s">
+      <c r="E92" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="F90" s="44" t="s">
+      <c r="F92" s="44" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="31">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="31">
         <f>DATE(2026,11,28)</f>
         <v>46354</v>
       </c>
-      <c r="B91" s="32" t="str">
+      <c r="B93" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C91" s="43" t="s">
+      <c r="C93" s="43" t="s">
         <v>573</v>
       </c>
-      <c r="D91" s="33"/>
-      <c r="E91" s="33" t="s">
+      <c r="D93" s="33"/>
+      <c r="E93" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F91" s="25" t="s">
+      <c r="F93" s="25" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="35">
         <f>DATE(2026,12,7)</f>
         <v>46363</v>
       </c>
-      <c r="B92" s="36" t="str">
+      <c r="B94" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C92" s="40" t="s">
+      <c r="C94" s="40" t="s">
         <v>569</v>
       </c>
-      <c r="D92" s="40" t="s">
+      <c r="D94" s="40" t="s">
         <v>570</v>
       </c>
-      <c r="E92" s="40" t="s">
+      <c r="E94" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="F92" s="40" t="s">
+      <c r="F94" s="40" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="35">
         <f>DATE(2026,12,7)</f>
         <v>46363</v>
       </c>
-      <c r="B93" s="36" t="str">
+      <c r="B95" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C93" s="40" t="s">
+      <c r="C95" s="40" t="s">
         <v>571</v>
       </c>
-      <c r="D93" s="40"/>
-      <c r="E93" s="40" t="s">
+      <c r="D95" s="40"/>
+      <c r="E95" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="F93" s="40" t="s">
+      <c r="F95" s="40" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="35">
         <f>DATE(2026,12,11)</f>
         <v>46367</v>
       </c>
-      <c r="B94" s="36" t="str">
+      <c r="B96" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C94" s="40" t="s">
+      <c r="C96" s="40" t="s">
         <v>565</v>
       </c>
-      <c r="D94" s="40" t="s">
+      <c r="D96" s="40" t="s">
         <v>566</v>
       </c>
-      <c r="E94" s="40" t="s">
+      <c r="E96" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="F94" s="44" t="s">
+      <c r="F96" s="44" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="35">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B95" s="36" t="str">
+      <c r="B97" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C95" s="40" t="s">
+      <c r="C97" s="40" t="s">
         <v>445</v>
       </c>
-      <c r="D95" s="40" t="s">
+      <c r="D97" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E95" s="37" t="s">
+      <c r="E97" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F95" s="25" t="s">
+      <c r="F97" s="25" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="35">
         <f>DATE(2026,12,25)</f>
         <v>46381</v>
       </c>
-      <c r="B96" s="36" t="str">
-        <f>TEXT($A96,"ddd")</f>
+      <c r="B98" s="36" t="str">
+        <f>TEXT($A98,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C96" s="37" t="s">
+      <c r="C98" s="37" t="s">
         <v>449</v>
       </c>
-      <c r="D96" s="37" t="s">
+      <c r="D98" s="37" t="s">
         <v>450</v>
       </c>
-      <c r="E96" s="39" t="s">
+      <c r="E98" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F96" s="25" t="s">
+      <c r="F98" s="25" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="12">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B97" s="13" t="str">
-        <f>TEXT($A97,"ddd")</f>
+      <c r="B99" s="13" t="str">
+        <f>TEXT($A99,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C99" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D99" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="E97" s="38" t="s">
+      <c r="E99" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F97" s="25" t="s">
+      <c r="F99" s="25" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="31">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="31">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B98" s="32" t="str">
+      <c r="B100" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C98" s="43" t="s">
+      <c r="C100" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="D98" s="33" t="s">
+      <c r="D100" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="E98" s="33" t="s">
+      <c r="E100" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F98" s="25" t="s">
+      <c r="F100" s="25" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="35">
         <f>DATE(2027,1,15)</f>
         <v>46402</v>
       </c>
-      <c r="B99" s="36" t="str">
+      <c r="B101" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C99" s="40" t="s">
+      <c r="C101" s="40" t="s">
         <v>590</v>
       </c>
-      <c r="D99" s="40" t="s">
+      <c r="D101" s="40" t="s">
         <v>591</v>
       </c>
-      <c r="E99" s="37" t="s">
+      <c r="E101" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F99" s="25"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="35">
+      <c r="F101" s="25"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="35">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B100" s="36" t="str">
+      <c r="B102" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C100" s="37" t="s">
+      <c r="C102" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="D100" s="37" t="s">
+      <c r="D102" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E100" s="37" t="s">
+      <c r="E102" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F100" s="25" t="s">
+      <c r="F102" s="25" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="35">
         <f>DATE(2027,2,6)</f>
         <v>46424</v>
       </c>
-      <c r="B101" s="36" t="str">
-        <f>TEXT($A101,"ddd")</f>
+      <c r="B103" s="36" t="str">
+        <f>TEXT($A103,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C101" s="37" t="s">
+      <c r="C103" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="D101" s="37" t="s">
+      <c r="D103" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="E101" s="39" t="s">
+      <c r="E103" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F101" s="25" t="s">
+      <c r="F103" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="35">
         <f>DATE(2027,2,7)</f>
         <v>46425</v>
       </c>
-      <c r="B102" s="36" t="str">
-        <f>TEXT($A102,"ddd")</f>
+      <c r="B104" s="36" t="str">
+        <f>TEXT($A104,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C102" s="37" t="s">
+      <c r="C104" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="D102" s="37" t="s">
+      <c r="D104" s="37" t="s">
         <v>470</v>
       </c>
-      <c r="E102" s="39" t="s">
+      <c r="E104" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F102" s="25" t="s">
+      <c r="F104" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="12">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B103" s="13" t="str">
-        <f>TEXT($A103,"ddd")</f>
+      <c r="B105" s="13" t="str">
+        <f>TEXT($A105,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C105" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="D103" s="11" t="s">
+      <c r="D105" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="E103" s="38" t="s">
+      <c r="E105" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F103" s="25" t="s">
+      <c r="F105" s="25" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="41">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B104" s="42" t="str">
+      <c r="B106" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C104" s="25" t="s">
+      <c r="C106" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="D104" s="25" t="s">
+      <c r="D106" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="E104" s="25" t="s">
+      <c r="E106" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="F104" s="26" t="s">
+      <c r="F106" s="26" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="12">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="12">
         <f>DATE(2027,3,6)</f>
         <v>46452</v>
       </c>
-      <c r="B105" s="13" t="str">
-        <f>TEXT($A105,"ddd")</f>
+      <c r="B107" s="13" t="str">
+        <f>TEXT($A107,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C107" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="D105" s="11" t="s">
+      <c r="D107" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="E105" s="11" t="s">
+      <c r="E107" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F105" s="25" t="s">
+      <c r="F107" s="25" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="12">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="12">
         <f>DATE(2027,3,10)</f>
         <v>46456</v>
       </c>
-      <c r="B106" s="13" t="str">
-        <f>TEXT($A106,"ddd")</f>
+      <c r="B108" s="13" t="str">
+        <f>TEXT($A108,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C106" s="11" t="s">
+      <c r="C108" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="D106" s="11" t="s">
+      <c r="D108" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="E106" s="38" t="s">
+      <c r="E108" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F106" s="25" t="s">
+      <c r="F108" s="25" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="31">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="31">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B107" s="32" t="str">
+      <c r="B109" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C107" s="33" t="s">
+      <c r="C109" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D107" s="33" t="s">
+      <c r="D109" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E107" s="33" t="s">
+      <c r="E109" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F107" s="26" t="s">
+      <c r="F109" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="35">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B108" s="36" t="str">
+      <c r="B110" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C108" s="37" t="s">
+      <c r="C110" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D108" s="37" t="s">
+      <c r="D110" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="E108" s="37" t="s">
+      <c r="E110" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F108" s="26" t="s">
+      <c r="F110" s="26" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="12">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="12">
         <f>DATE(2027,3,26)</f>
         <v>46472</v>
       </c>
-      <c r="B109" s="13" t="str">
-        <f>TEXT($A109,"ddd")</f>
+      <c r="B111" s="13" t="str">
+        <f>TEXT($A111,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C111" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D109" s="11" t="s">
+      <c r="D111" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="E109" s="38" t="s">
+      <c r="E111" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F109" s="25" t="s">
+      <c r="F111" s="25" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="31">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="31">
         <f>DATE(2027,4,17)</f>
         <v>46494</v>
       </c>
-      <c r="B110" s="32" t="str">
-        <f>TEXT($A110,"ddd")</f>
+      <c r="B112" s="32" t="str">
+        <f>TEXT($A112,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C110" s="43" t="s">
+      <c r="C112" s="43" t="s">
         <v>582</v>
       </c>
-      <c r="D110" s="43" t="s">
+      <c r="D112" s="43" t="s">
         <v>583</v>
       </c>
-      <c r="E110" s="43" t="s">
+      <c r="E112" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F110" s="45" t="s">
+      <c r="F112" s="45" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="35">
         <f>DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="B111" s="36" t="str">
-        <f>TEXT($A111,"ddd")</f>
+      <c r="B113" s="36" t="str">
+        <f>TEXT($A113,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C111" s="37" t="s">
+      <c r="C113" s="37" t="s">
         <v>458</v>
       </c>
-      <c r="D111" s="37" t="s">
+      <c r="D113" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="E111" s="39" t="s">
+      <c r="E113" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F111" s="25" t="s">
+      <c r="F113" s="25" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="12">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="12">
         <f>DATE(2027,5,17)</f>
         <v>46524</v>
       </c>
-      <c r="B112" s="13" t="str">
-        <f>TEXT($A112,"ddd")</f>
+      <c r="B114" s="13" t="str">
+        <f>TEXT($A114,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C114" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D112" s="11" t="s">
+      <c r="D114" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="E112" s="38" t="s">
+      <c r="E114" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F112" s="25" t="s">
+      <c r="F114" s="25" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="41">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="41">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B113" s="42" t="str">
+      <c r="B115" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C113" s="25" t="s">
+      <c r="C115" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="D113" s="25" t="s">
+      <c r="D115" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="E113" s="25" t="s">
+      <c r="E115" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="F113" s="26" t="s">
+      <c r="F115" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="12">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B114" s="13" t="str">
-        <f>TEXT($A114,"ddd")</f>
+      <c r="B116" s="13" t="str">
+        <f>TEXT($A116,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C114" s="11" t="s">
+      <c r="C116" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="D114" s="11" t="s">
+      <c r="D116" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="E114" s="38" t="s">
+      <c r="E116" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F114" s="25" t="s">
+      <c r="F116" s="25" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="31">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="31">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B115" s="32" t="str">
+      <c r="B117" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C115" s="33" t="s">
+      <c r="C117" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="D115" s="33" t="s">
+      <c r="D117" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="E115" s="33" t="s">
+      <c r="E117" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F115" s="26" t="s">
+      <c r="F117" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="12">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B116" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D116" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E116" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="F116" s="26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
-      </c>
-      <c r="B117" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="E117" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F117" s="26" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
       </c>
       <c r="B118" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>124</v>
+        <v>218</v>
       </c>
       <c r="F118" s="26" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B119" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C119" s="16" t="s">
+      <c r="C119" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E119" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F119" s="26" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="12">
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
+      </c>
+      <c r="B120" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E120" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F120" s="26" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="12">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B121" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C121" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="D119" s="11" t="s">
+      <c r="D121" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E119" s="11" t="s">
+      <c r="E121" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F119" s="25" t="s">
+      <c r="F121" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="35">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B120" s="36" t="str">
+      <c r="B122" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C120" s="37" t="s">
+      <c r="C122" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="D120" s="37" t="s">
+      <c r="D122" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="E120" s="37" t="s">
+      <c r="E122" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F120" s="26" t="s">
+      <c r="F122" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="12">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="12">
         <f>DATE(2027,8,9)</f>
         <v>46608</v>
       </c>
-      <c r="B121" s="13" t="str">
-        <f>TEXT($A121,"ddd")</f>
+      <c r="B123" s="13" t="str">
+        <f>TEXT($A123,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="C123" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="D121" s="11" t="s">
+      <c r="D123" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="E121" s="38" t="s">
+      <c r="E123" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F121" s="25" t="s">
+      <c r="F123" s="25" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="31">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="31">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B122" s="32" t="str">
+      <c r="B124" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C122" s="33" t="s">
+      <c r="C124" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="D122" s="33" t="s">
+      <c r="D124" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E122" s="33" t="s">
+      <c r="E124" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F122" s="26" t="s">
+      <c r="F124" s="26" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="12">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
       </c>
-      <c r="B123" s="13" t="str">
+      <c r="B125" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C125" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D123" s="11" t="s">
+      <c r="D125" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E123" s="11" t="s">
+      <c r="E125" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F123" s="26" t="s">
+      <c r="F125" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="12">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B124" s="13" t="str">
+      <c r="B126" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C126" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D124" s="11" t="s">
+      <c r="D126" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E124" s="11" t="s">
+      <c r="E126" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F124" s="26" t="s">
+      <c r="F126" s="26" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="35">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B125" s="36" t="str">
+      <c r="B127" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C125" s="37" t="s">
+      <c r="C127" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="D125" s="37" t="s">
+      <c r="D127" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="E125" s="37" t="s">
+      <c r="E127" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F125" s="26" t="s">
+      <c r="F127" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="12">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="12">
         <f>DATE(2027,10,28)</f>
         <v>46688</v>
       </c>
-      <c r="B126" s="13" t="str">
-        <f>TEXT($A126,"ddd")</f>
+      <c r="B128" s="13" t="str">
+        <f>TEXT($A128,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C126" s="11" t="s">
+      <c r="C128" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D126" s="11" t="s">
+      <c r="D128" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="E126" s="38" t="s">
+      <c r="E128" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F126" s="25" t="s">
+      <c r="F128" s="25" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="31">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="31">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B127" s="32" t="str">
+      <c r="B129" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C127" s="33" t="s">
+      <c r="C129" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D127" s="33" t="s">
+      <c r="D129" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E127" s="33" t="s">
+      <c r="E129" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F127" s="26" t="s">
+      <c r="F129" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="12">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B128" s="13" t="str">
+      <c r="B130" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C128" s="16" t="s">
+      <c r="C130" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D130" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E128" s="11" t="s">
+      <c r="E130" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F128" s="25" t="s">
+      <c r="F130" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" s="35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B129" s="36" t="str">
+      <c r="B131" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C129" s="37" t="s">
+      <c r="C131" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D129" s="40" t="s">
+      <c r="D131" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E129" s="37" t="s">
+      <c r="E131" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F129" s="26" t="s">
+      <c r="F131" s="26" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" s="12">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B130" s="13" t="str">
-        <f>TEXT($A130,"ddd")</f>
+      <c r="B132" s="13" t="str">
+        <f>TEXT($A132,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C130" s="11" t="s">
+      <c r="C132" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D130" s="11" t="s">
+      <c r="D132" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="E130" s="38" t="s">
+      <c r="E132" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F130" s="25" t="s">
+      <c r="F132" s="25" t="s">
         <v>493</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E130" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E132" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1933" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD8056A0-E378-48FD-8ED5-D732F0523BBA}"/>
+  <xr:revisionPtr revIDLastSave="1941" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62359A9E-1228-4689-B3FC-99BA4E4E6820}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$134</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="600">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1830,6 +1830,18 @@
   </si>
   <si>
     <t>Health Talk by TCM Physician. 10.30am - 11.30am</t>
+  </si>
+  <si>
+    <t>Charities Essentials : Converting charity to CLG - Duties of Directors</t>
+  </si>
+  <si>
+    <t>Charity to CLG conversion</t>
+  </si>
+  <si>
+    <t>Social Service Sector Roadmap, 9am-1pm, NCSS Ulu Pandan Community Building</t>
+  </si>
+  <si>
+    <t>NCSS Roadmap refresh</t>
   </si>
 </sst>
 </file>
@@ -2619,7 +2631,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -2677,7 +2689,7 @@
         <v>46023</v>
       </c>
       <c r="B3" s="32" t="str">
-        <f t="shared" ref="B3:B86" si="0">TEXT($A3,"ddd")</f>
+        <f t="shared" ref="B3:B88" si="0">TEXT($A3,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C3" s="33" t="s">
@@ -4341,1164 +4353,1204 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="12">
+        <f>DATE(2026,10,16)</f>
+        <v>46311</v>
+      </c>
+      <c r="B80" s="13" t="str">
+        <f>TEXT($A80,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C80" s="40" t="s">
+        <v>596</v>
+      </c>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="F80" s="44" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="12">
         <f>DATE(2026,10,19)</f>
         <v>46314</v>
       </c>
-      <c r="B80" s="13" t="str">
+      <c r="B81" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C81" s="16" t="s">
         <v>576</v>
       </c>
-      <c r="D80" s="16" t="s">
+      <c r="D81" s="16" t="s">
         <v>579</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E81" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F80" s="25" t="s">
+      <c r="F81" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A81" s="12">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="12">
         <f>DATE(2026,10,20)</f>
         <v>46315</v>
       </c>
-      <c r="B81" s="42" t="str">
-        <f>TEXT($A81,"ddd")</f>
+      <c r="B82" s="42" t="str">
+        <f>TEXT($A82,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C81" s="25" t="s">
+      <c r="C82" s="25" t="s">
         <v>549</v>
       </c>
-      <c r="D81" s="25" t="s">
+      <c r="D82" s="25" t="s">
         <v>550</v>
       </c>
-      <c r="E81" s="25" t="s">
+      <c r="E82" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="F81" s="25" t="s">
+      <c r="F82" s="25" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" s="12">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="12">
         <f>DATE(2026,10,21)</f>
         <v>46316</v>
       </c>
-      <c r="B82" s="13" t="str">
+      <c r="B83" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C82" s="16" t="s">
+      <c r="C83" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="D82" s="16" t="s">
+      <c r="D83" s="16" t="s">
         <v>586</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="E83" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F82" s="25" t="s">
+      <c r="F83" s="25" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" s="12">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="12">
+        <f>DATE(2026,10,21)</f>
+        <v>46316</v>
+      </c>
+      <c r="B84" s="13" t="str">
+        <f>TEXT($A84,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C84" s="40" t="s">
+        <v>598</v>
+      </c>
+      <c r="D84" s="37"/>
+      <c r="E84" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="F84" s="44" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="12">
         <f>DATE(2026,10,23)</f>
         <v>46318</v>
       </c>
-      <c r="B83" s="13" t="str">
+      <c r="B85" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C83" s="16" t="s">
+      <c r="C85" s="16" t="s">
         <v>577</v>
       </c>
-      <c r="D83" s="16" t="s">
+      <c r="D85" s="16" t="s">
         <v>580</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E85" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F83" s="25" t="s">
+      <c r="F85" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="12">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="12">
         <f>DATE(2026,10,24)</f>
         <v>46319</v>
       </c>
-      <c r="B84" s="13" t="str">
+      <c r="B86" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C84" s="16" t="s">
+      <c r="C86" s="16" t="s">
         <v>578</v>
       </c>
-      <c r="D84" s="16" t="s">
+      <c r="D86" s="16" t="s">
         <v>581</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="E86" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F84" s="25" t="s">
+      <c r="F86" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="12">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="12">
         <f>DATE(2026,10,26)</f>
         <v>46321</v>
       </c>
-      <c r="B85" s="42" t="str">
+      <c r="B87" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C85" s="25" t="s">
+      <c r="C87" s="25" t="s">
         <v>559</v>
       </c>
-      <c r="D85" s="25" t="s">
+      <c r="D87" s="25" t="s">
         <v>558</v>
       </c>
-      <c r="E85" s="25" t="s">
+      <c r="E87" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="F85" s="25" t="s">
+      <c r="F87" s="25" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="12">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="12">
         <f>DATE(2026,10,27)</f>
         <v>46322</v>
       </c>
-      <c r="B86" s="42" t="str">
+      <c r="B88" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C86" s="25" t="s">
+      <c r="C88" s="25" t="s">
         <v>561</v>
       </c>
-      <c r="D86" s="25"/>
-      <c r="E86" s="25" t="s">
+      <c r="D88" s="25"/>
+      <c r="E88" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="F86" s="25" t="s">
+      <c r="F88" s="25" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="35">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
       </c>
-      <c r="B87" s="36" t="str">
-        <f t="shared" ref="B87:B131" si="2">TEXT($A87,"ddd")</f>
+      <c r="B89" s="36" t="str">
+        <f t="shared" ref="B89:B133" si="2">TEXT($A89,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C87" s="40" t="s">
+      <c r="C89" s="40" t="s">
         <v>575</v>
       </c>
-      <c r="D87" s="40" t="s">
+      <c r="D89" s="40" t="s">
         <v>574</v>
       </c>
-      <c r="E87" s="37" t="s">
+      <c r="E89" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F87" s="25" t="s">
+      <c r="F89" s="25" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="35">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
       </c>
-      <c r="B88" s="36" t="str">
+      <c r="B90" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C88" s="40" t="s">
+      <c r="C90" s="40" t="s">
         <v>592</v>
       </c>
-      <c r="D88" s="40" t="s">
+      <c r="D90" s="40" t="s">
         <v>593</v>
       </c>
-      <c r="E88" s="37" t="s">
+      <c r="E90" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F88" s="44" t="s">
+      <c r="F90" s="44" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="35">
         <f>DATE(2026,11,7)</f>
         <v>46333</v>
       </c>
-      <c r="B89" s="36" t="str">
+      <c r="B91" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C89" s="40" t="s">
+      <c r="C91" s="40" t="s">
         <v>595</v>
       </c>
-      <c r="D89" s="40" t="s">
+      <c r="D91" s="40" t="s">
         <v>593</v>
       </c>
-      <c r="E89" s="37" t="s">
+      <c r="E91" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F89" s="44" t="s">
+      <c r="F91" s="44" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="35">
         <f>DATE(2026,11,8)</f>
         <v>46334</v>
       </c>
-      <c r="B90" s="36" t="str">
-        <f>TEXT($A90,"ddd")</f>
+      <c r="B92" s="36" t="str">
+        <f>TEXT($A92,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C90" s="37" t="s">
+      <c r="C92" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="D90" s="37" t="s">
+      <c r="D92" s="37" t="s">
         <v>453</v>
       </c>
-      <c r="E90" s="39" t="s">
+      <c r="E92" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F90" s="25" t="s">
+      <c r="F92" s="25" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="12">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="12">
         <f>DATE(2026,11,9)</f>
         <v>46335</v>
       </c>
-      <c r="B91" s="13" t="str">
-        <f>TEXT($A91,"ddd")</f>
+      <c r="B93" s="13" t="str">
+        <f>TEXT($A93,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C93" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="D91" s="11" t="s">
+      <c r="D93" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="E91" s="38" t="s">
+      <c r="E93" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F91" s="25" t="s">
+      <c r="F93" s="25" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="12">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="12">
         <f>DATE(2026,11,19)</f>
         <v>46345</v>
       </c>
-      <c r="B92" s="13" t="str">
-        <f>TEXT($A92,"ddd")</f>
+      <c r="B94" s="13" t="str">
+        <f>TEXT($A94,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C92" s="16" t="s">
+      <c r="C94" s="16" t="s">
         <v>588</v>
       </c>
-      <c r="D92" s="16" t="s">
+      <c r="D94" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="E92" s="46" t="s">
+      <c r="E94" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="F92" s="44" t="s">
+      <c r="F94" s="44" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="31">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="31">
         <f>DATE(2026,11,28)</f>
         <v>46354</v>
       </c>
-      <c r="B93" s="32" t="str">
+      <c r="B95" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C93" s="43" t="s">
+      <c r="C95" s="43" t="s">
         <v>573</v>
       </c>
-      <c r="D93" s="33"/>
-      <c r="E93" s="33" t="s">
+      <c r="D95" s="33"/>
+      <c r="E95" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F93" s="25" t="s">
+      <c r="F95" s="25" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="35">
         <f>DATE(2026,12,7)</f>
         <v>46363</v>
       </c>
-      <c r="B94" s="36" t="str">
+      <c r="B96" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C94" s="40" t="s">
+      <c r="C96" s="40" t="s">
         <v>569</v>
       </c>
-      <c r="D94" s="40" t="s">
+      <c r="D96" s="40" t="s">
         <v>570</v>
       </c>
-      <c r="E94" s="40" t="s">
+      <c r="E96" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="F94" s="40" t="s">
+      <c r="F96" s="40" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="35">
         <f>DATE(2026,12,7)</f>
         <v>46363</v>
       </c>
-      <c r="B95" s="36" t="str">
+      <c r="B97" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C95" s="40" t="s">
+      <c r="C97" s="40" t="s">
         <v>571</v>
       </c>
-      <c r="D95" s="40"/>
-      <c r="E95" s="40" t="s">
+      <c r="D97" s="40"/>
+      <c r="E97" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="F95" s="40" t="s">
+      <c r="F97" s="40" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="35">
         <f>DATE(2026,12,11)</f>
         <v>46367</v>
       </c>
-      <c r="B96" s="36" t="str">
+      <c r="B98" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C96" s="40" t="s">
+      <c r="C98" s="40" t="s">
         <v>565</v>
       </c>
-      <c r="D96" s="40" t="s">
+      <c r="D98" s="40" t="s">
         <v>566</v>
       </c>
-      <c r="E96" s="40" t="s">
+      <c r="E98" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="F96" s="44" t="s">
+      <c r="F98" s="44" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="35">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B97" s="36" t="str">
+      <c r="B99" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C97" s="40" t="s">
+      <c r="C99" s="40" t="s">
         <v>445</v>
       </c>
-      <c r="D97" s="40" t="s">
+      <c r="D99" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E97" s="37" t="s">
+      <c r="E99" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F97" s="25" t="s">
+      <c r="F99" s="25" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="35">
         <f>DATE(2026,12,25)</f>
         <v>46381</v>
       </c>
-      <c r="B98" s="36" t="str">
-        <f>TEXT($A98,"ddd")</f>
+      <c r="B100" s="36" t="str">
+        <f>TEXT($A100,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C98" s="37" t="s">
+      <c r="C100" s="37" t="s">
         <v>449</v>
       </c>
-      <c r="D98" s="37" t="s">
+      <c r="D100" s="37" t="s">
         <v>450</v>
       </c>
-      <c r="E98" s="39" t="s">
+      <c r="E100" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F98" s="25" t="s">
+      <c r="F100" s="25" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="12">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B99" s="13" t="str">
-        <f>TEXT($A99,"ddd")</f>
+      <c r="B101" s="13" t="str">
+        <f>TEXT($A101,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C99" s="11" t="s">
+      <c r="C101" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="D99" s="11" t="s">
+      <c r="D101" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="E99" s="38" t="s">
+      <c r="E101" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="F101" s="25" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="31">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="31">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B100" s="32" t="str">
+      <c r="B102" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C100" s="43" t="s">
+      <c r="C102" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="D100" s="33" t="s">
+      <c r="D102" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="E100" s="33" t="s">
+      <c r="E102" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F100" s="25" t="s">
+      <c r="F102" s="25" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="35">
         <f>DATE(2027,1,15)</f>
         <v>46402</v>
       </c>
-      <c r="B101" s="36" t="str">
+      <c r="B103" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C101" s="40" t="s">
+      <c r="C103" s="40" t="s">
         <v>590</v>
       </c>
-      <c r="D101" s="40" t="s">
+      <c r="D103" s="40" t="s">
         <v>591</v>
       </c>
-      <c r="E101" s="37" t="s">
+      <c r="E103" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F101" s="25"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="35">
+      <c r="F103" s="25"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="35">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B102" s="36" t="str">
+      <c r="B104" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C102" s="37" t="s">
+      <c r="C104" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="D102" s="37" t="s">
+      <c r="D104" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E102" s="37" t="s">
+      <c r="E104" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F102" s="25" t="s">
+      <c r="F104" s="25" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="35">
         <f>DATE(2027,2,6)</f>
         <v>46424</v>
       </c>
-      <c r="B103" s="36" t="str">
-        <f>TEXT($A103,"ddd")</f>
+      <c r="B105" s="36" t="str">
+        <f>TEXT($A105,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C103" s="37" t="s">
+      <c r="C105" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="D103" s="37" t="s">
+      <c r="D105" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="E103" s="39" t="s">
+      <c r="E105" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F103" s="25" t="s">
+      <c r="F105" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="35">
         <f>DATE(2027,2,7)</f>
         <v>46425</v>
       </c>
-      <c r="B104" s="36" t="str">
-        <f>TEXT($A104,"ddd")</f>
+      <c r="B106" s="36" t="str">
+        <f>TEXT($A106,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C104" s="37" t="s">
+      <c r="C106" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="D104" s="37" t="s">
+      <c r="D106" s="37" t="s">
         <v>470</v>
       </c>
-      <c r="E104" s="39" t="s">
+      <c r="E106" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F104" s="25" t="s">
+      <c r="F106" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="12">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B105" s="13" t="str">
-        <f>TEXT($A105,"ddd")</f>
+      <c r="B107" s="13" t="str">
+        <f>TEXT($A107,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C107" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="D105" s="11" t="s">
+      <c r="D107" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="E105" s="38" t="s">
+      <c r="E107" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F105" s="25" t="s">
+      <c r="F107" s="25" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="41">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B106" s="42" t="str">
+      <c r="B108" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C106" s="25" t="s">
+      <c r="C108" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="D106" s="25" t="s">
+      <c r="D108" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="E106" s="25" t="s">
+      <c r="E108" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="F106" s="26" t="s">
+      <c r="F108" s="26" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="12">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="12">
         <f>DATE(2027,3,6)</f>
         <v>46452</v>
       </c>
-      <c r="B107" s="13" t="str">
-        <f>TEXT($A107,"ddd")</f>
+      <c r="B109" s="13" t="str">
+        <f>TEXT($A109,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C109" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="D107" s="11" t="s">
+      <c r="D109" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="E107" s="11" t="s">
+      <c r="E109" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F107" s="25" t="s">
+      <c r="F109" s="25" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="12">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="12">
         <f>DATE(2027,3,10)</f>
         <v>46456</v>
       </c>
-      <c r="B108" s="13" t="str">
-        <f>TEXT($A108,"ddd")</f>
+      <c r="B110" s="13" t="str">
+        <f>TEXT($A110,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C110" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="D108" s="11" t="s">
+      <c r="D110" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="E108" s="38" t="s">
+      <c r="E110" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F108" s="25" t="s">
+      <c r="F110" s="25" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="31">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="31">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B109" s="32" t="str">
+      <c r="B111" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C109" s="33" t="s">
+      <c r="C111" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D109" s="33" t="s">
+      <c r="D111" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E109" s="33" t="s">
+      <c r="E111" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F109" s="26" t="s">
+      <c r="F111" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="35">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B110" s="36" t="str">
+      <c r="B112" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C110" s="37" t="s">
+      <c r="C112" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D110" s="37" t="s">
+      <c r="D112" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="E110" s="37" t="s">
+      <c r="E112" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F110" s="26" t="s">
+      <c r="F112" s="26" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="12">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="12">
         <f>DATE(2027,3,26)</f>
         <v>46472</v>
       </c>
-      <c r="B111" s="13" t="str">
-        <f>TEXT($A111,"ddd")</f>
+      <c r="B113" s="13" t="str">
+        <f>TEXT($A113,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C113" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D111" s="11" t="s">
+      <c r="D113" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="E111" s="38" t="s">
+      <c r="E113" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F111" s="25" t="s">
+      <c r="F113" s="25" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="31">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="31">
         <f>DATE(2027,4,17)</f>
         <v>46494</v>
       </c>
-      <c r="B112" s="32" t="str">
-        <f>TEXT($A112,"ddd")</f>
+      <c r="B114" s="32" t="str">
+        <f>TEXT($A114,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C112" s="43" t="s">
+      <c r="C114" s="43" t="s">
         <v>582</v>
       </c>
-      <c r="D112" s="43" t="s">
+      <c r="D114" s="43" t="s">
         <v>583</v>
       </c>
-      <c r="E112" s="43" t="s">
+      <c r="E114" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F112" s="45" t="s">
+      <c r="F114" s="45" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="35">
         <f>DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="B113" s="36" t="str">
-        <f>TEXT($A113,"ddd")</f>
+      <c r="B115" s="36" t="str">
+        <f>TEXT($A115,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C113" s="37" t="s">
+      <c r="C115" s="37" t="s">
         <v>458</v>
       </c>
-      <c r="D113" s="37" t="s">
+      <c r="D115" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="E113" s="39" t="s">
+      <c r="E115" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F113" s="25" t="s">
+      <c r="F115" s="25" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="12">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="12">
         <f>DATE(2027,5,17)</f>
         <v>46524</v>
       </c>
-      <c r="B114" s="13" t="str">
-        <f>TEXT($A114,"ddd")</f>
+      <c r="B116" s="13" t="str">
+        <f>TEXT($A116,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C114" s="11" t="s">
+      <c r="C116" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D114" s="11" t="s">
+      <c r="D116" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="E114" s="38" t="s">
+      <c r="E116" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F114" s="25" t="s">
+      <c r="F116" s="25" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="41">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="41">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B115" s="42" t="str">
+      <c r="B117" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C115" s="25" t="s">
+      <c r="C117" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="D115" s="25" t="s">
+      <c r="D117" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="E115" s="25" t="s">
+      <c r="E117" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="F115" s="26" t="s">
+      <c r="F117" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="12">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B116" s="13" t="str">
-        <f>TEXT($A116,"ddd")</f>
+      <c r="B118" s="13" t="str">
+        <f>TEXT($A118,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C118" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="D116" s="11" t="s">
+      <c r="D118" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="E116" s="38" t="s">
+      <c r="E118" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F116" s="25" t="s">
+      <c r="F118" s="25" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="31">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="31">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B117" s="32" t="str">
+      <c r="B119" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C117" s="33" t="s">
+      <c r="C119" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="D117" s="33" t="s">
+      <c r="D119" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="E117" s="33" t="s">
+      <c r="E119" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F117" s="26" t="s">
+      <c r="F119" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="12">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B118" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C118" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E118" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
-      </c>
-      <c r="B119" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="E119" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F119" s="26" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
       </c>
       <c r="B120" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>124</v>
+        <v>218</v>
       </c>
       <c r="F120" s="26" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B121" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C121" s="16" t="s">
+      <c r="C121" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E121" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F121" s="26" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="12">
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
+      </c>
+      <c r="B122" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="12">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B123" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C123" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="D121" s="11" t="s">
+      <c r="D123" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E121" s="11" t="s">
+      <c r="E123" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F121" s="25" t="s">
+      <c r="F123" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="35">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B122" s="36" t="str">
+      <c r="B124" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C122" s="37" t="s">
+      <c r="C124" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="D122" s="37" t="s">
+      <c r="D124" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="E122" s="37" t="s">
+      <c r="E124" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F122" s="26" t="s">
+      <c r="F124" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="12">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="12">
         <f>DATE(2027,8,9)</f>
         <v>46608</v>
       </c>
-      <c r="B123" s="13" t="str">
-        <f>TEXT($A123,"ddd")</f>
+      <c r="B125" s="13" t="str">
+        <f>TEXT($A125,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C125" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="D123" s="11" t="s">
+      <c r="D125" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="E123" s="38" t="s">
+      <c r="E125" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F123" s="25" t="s">
+      <c r="F125" s="25" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="31">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="31">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B124" s="32" t="str">
+      <c r="B126" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C124" s="33" t="s">
+      <c r="C126" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="D124" s="33" t="s">
+      <c r="D126" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E124" s="33" t="s">
+      <c r="E126" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F124" s="26" t="s">
+      <c r="F126" s="26" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="12">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
       </c>
-      <c r="B125" s="13" t="str">
+      <c r="B127" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C125" s="11" t="s">
+      <c r="C127" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D125" s="11" t="s">
+      <c r="D127" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E125" s="11" t="s">
+      <c r="E127" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F125" s="26" t="s">
+      <c r="F127" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="12">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B126" s="13" t="str">
+      <c r="B128" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C126" s="11" t="s">
+      <c r="C128" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D126" s="11" t="s">
+      <c r="D128" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E126" s="11" t="s">
+      <c r="E128" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F126" s="26" t="s">
+      <c r="F128" s="26" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="35">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B127" s="36" t="str">
+      <c r="B129" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C127" s="37" t="s">
+      <c r="C129" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="D127" s="37" t="s">
+      <c r="D129" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="E127" s="37" t="s">
+      <c r="E129" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F127" s="26" t="s">
+      <c r="F129" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="12">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="12">
         <f>DATE(2027,10,28)</f>
         <v>46688</v>
       </c>
-      <c r="B128" s="13" t="str">
-        <f>TEXT($A128,"ddd")</f>
+      <c r="B130" s="13" t="str">
+        <f>TEXT($A130,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C130" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D130" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="E128" s="38" t="s">
+      <c r="E130" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F128" s="25" t="s">
+      <c r="F130" s="25" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" s="31">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="31">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B129" s="32" t="str">
+      <c r="B131" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C129" s="33" t="s">
+      <c r="C131" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D129" s="33" t="s">
+      <c r="D131" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E129" s="33" t="s">
+      <c r="E131" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F129" s="26" t="s">
+      <c r="F131" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" s="12">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B130" s="13" t="str">
+      <c r="B132" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C130" s="16" t="s">
+      <c r="C132" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="D130" s="11" t="s">
+      <c r="D132" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E130" s="11" t="s">
+      <c r="E132" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F130" s="25" t="s">
+      <c r="F132" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A131" s="35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B131" s="36" t="str">
+      <c r="B133" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C131" s="37" t="s">
+      <c r="C133" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D131" s="40" t="s">
+      <c r="D133" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E131" s="37" t="s">
+      <c r="E133" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F131" s="26" t="s">
+      <c r="F133" s="26" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A132" s="12">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B132" s="13" t="str">
-        <f>TEXT($A132,"ddd")</f>
+      <c r="B134" s="13" t="str">
+        <f>TEXT($A134,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C132" s="11" t="s">
+      <c r="C134" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D132" s="11" t="s">
+      <c r="D134" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="E132" s="38" t="s">
+      <c r="E134" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F132" s="25" t="s">
+      <c r="F134" s="25" t="s">
         <v>493</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E132" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E134" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -7566,7 +7618,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7591,14 +7643,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7843,23 +7893,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7885,9 +7932,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1941" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62359A9E-1228-4689-B3FC-99BA4E4E6820}"/>
+  <xr:revisionPtr revIDLastSave="1943" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE70E2BD-574F-4EF1-A324-459D6BA58432}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -2689,7 +2689,7 @@
         <v>46023</v>
       </c>
       <c r="B3" s="32" t="str">
-        <f t="shared" ref="B3:B88" si="0">TEXT($A3,"ddd")</f>
+        <f t="shared" ref="B3:B87" si="0">TEXT($A3,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C3" s="33" t="s">
@@ -4421,56 +4421,56 @@
         <v>46316</v>
       </c>
       <c r="B83" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT($A83,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C83" s="16" t="s">
-        <v>585</v>
-      </c>
-      <c r="D83" s="16" t="s">
-        <v>586</v>
-      </c>
-      <c r="E83" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F83" s="25" t="s">
-        <v>397</v>
+      <c r="C83" s="40" t="s">
+        <v>598</v>
+      </c>
+      <c r="D83" s="37"/>
+      <c r="E83" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="F83" s="44" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="12">
-        <f>DATE(2026,10,21)</f>
-        <v>46316</v>
+        <f>DATE(2026,10,23)</f>
+        <v>46318</v>
       </c>
       <c r="B84" s="13" t="str">
-        <f>TEXT($A84,"ddd")</f>
-        <v>Wed</v>
-      </c>
-      <c r="C84" s="40" t="s">
-        <v>598</v>
-      </c>
-      <c r="D84" s="37"/>
-      <c r="E84" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="F84" s="44" t="s">
-        <v>599</v>
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>580</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F84" s="25" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="12">
-        <f>DATE(2026,10,23)</f>
-        <v>46318</v>
+        <f>DATE(2026,10,24)</f>
+        <v>46319</v>
       </c>
       <c r="B85" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E85" s="11" t="s">
         <v>218</v>
@@ -4481,66 +4481,66 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="12">
-        <f>DATE(2026,10,24)</f>
-        <v>46319</v>
-      </c>
-      <c r="B86" s="13" t="str">
+        <f>DATE(2026,10,26)</f>
+        <v>46321</v>
+      </c>
+      <c r="B86" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
-      </c>
-      <c r="C86" s="16" t="s">
-        <v>578</v>
-      </c>
-      <c r="D86" s="16" t="s">
-        <v>581</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>218</v>
+        <v>Mon</v>
+      </c>
+      <c r="C86" s="25" t="s">
+        <v>559</v>
+      </c>
+      <c r="D86" s="25" t="s">
+        <v>558</v>
+      </c>
+      <c r="E86" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="12">
-        <f>DATE(2026,10,26)</f>
-        <v>46321</v>
+        <f>DATE(2026,10,27)</f>
+        <v>46322</v>
       </c>
       <c r="B87" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>559</v>
-      </c>
-      <c r="D87" s="25" t="s">
-        <v>558</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="D87" s="25"/>
       <c r="E87" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="12">
-        <f>DATE(2026,10,27)</f>
-        <v>46322</v>
-      </c>
-      <c r="B88" s="42" t="str">
-        <f t="shared" si="0"/>
+      <c r="A88" s="35">
+        <f>DATE(2026,11,3)</f>
+        <v>46329</v>
+      </c>
+      <c r="B88" s="36" t="str">
+        <f t="shared" ref="B88:B133" si="2">TEXT($A88,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C88" s="25" t="s">
-        <v>561</v>
-      </c>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25" t="s">
-        <v>124</v>
+      <c r="C88" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="D88" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="E88" s="37" t="s">
+        <v>121</v>
       </c>
       <c r="F88" s="25" t="s">
-        <v>562</v>
+        <v>427</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -4549,33 +4549,33 @@
         <v>46329</v>
       </c>
       <c r="B89" s="36" t="str">
-        <f t="shared" ref="B89:B133" si="2">TEXT($A89,"ddd")</f>
+        <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C89" s="40" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="E89" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F89" s="25" t="s">
-        <v>427</v>
+      <c r="F89" s="44" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="35">
-        <f>DATE(2026,11,3)</f>
-        <v>46329</v>
+        <f>DATE(2026,11,7)</f>
+        <v>46333</v>
       </c>
       <c r="B90" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>Tue</v>
+        <v>Sat</v>
       </c>
       <c r="C90" s="40" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D90" s="40" t="s">
         <v>593</v>
@@ -4589,90 +4589,90 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="35">
-        <f>DATE(2026,11,7)</f>
-        <v>46333</v>
-      </c>
-      <c r="B91" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C91" s="40" t="s">
-        <v>595</v>
-      </c>
-      <c r="D91" s="40" t="s">
-        <v>593</v>
-      </c>
-      <c r="E91" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F91" s="44" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="35">
         <f>DATE(2026,11,8)</f>
         <v>46334</v>
       </c>
-      <c r="B92" s="36" t="str">
+      <c r="B91" s="36" t="str">
+        <f>TEXT($A91,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C91" s="37" t="s">
+        <v>452</v>
+      </c>
+      <c r="D91" s="37" t="s">
+        <v>453</v>
+      </c>
+      <c r="E91" s="39" t="s">
+        <v>451</v>
+      </c>
+      <c r="F91" s="25" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="12">
+        <f>DATE(2026,11,9)</f>
+        <v>46335</v>
+      </c>
+      <c r="B92" s="13" t="str">
         <f>TEXT($A92,"ddd")</f>
-        <v>Sun</v>
-      </c>
-      <c r="C92" s="37" t="s">
-        <v>452</v>
-      </c>
-      <c r="D92" s="37" t="s">
-        <v>453</v>
-      </c>
-      <c r="E92" s="39" t="s">
+        <v>Mon</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="E92" s="38" t="s">
         <v>451</v>
       </c>
       <c r="F92" s="25" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="12">
-        <f>DATE(2026,11,9)</f>
-        <v>46335</v>
+        <f>DATE(2026,11,19)</f>
+        <v>46345</v>
       </c>
       <c r="B93" s="13" t="str">
         <f>TEXT($A93,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>475</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>476</v>
-      </c>
-      <c r="E93" s="38" t="s">
-        <v>451</v>
-      </c>
-      <c r="F93" s="25" t="s">
-        <v>492</v>
+        <v>Thu</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="D93" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="E93" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="F93" s="44" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="12">
-        <f>DATE(2026,11,19)</f>
-        <v>46345</v>
+        <f>DATE(2026,11,25)</f>
+        <v>46351</v>
       </c>
       <c r="B94" s="13" t="str">
         <f>TEXT($A94,"ddd")</f>
-        <v>Thu</v>
+        <v>Wed</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="E94" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="F94" s="44" t="s">
-        <v>589</v>
+        <v>586</v>
+      </c>
+      <c r="E94" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F94" s="25" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7643,12 +7643,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7893,20 +7895,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7932,14 +7937,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1943" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE70E2BD-574F-4EF1-A324-459D6BA58432}"/>
+  <xr:revisionPtr revIDLastSave="1953" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{594CAA58-B530-4E67-B546-7F96A01AAF02}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$135</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="602">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1842,6 +1842,12 @@
   </si>
   <si>
     <t>NCSS Roadmap refresh</t>
+  </si>
+  <si>
+    <t>Hai Nam Sua temple - 171 year celebration</t>
+  </si>
+  <si>
+    <t>海南山天公神壇</t>
   </si>
 </sst>
 </file>
@@ -2631,7 +2637,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -2689,7 +2695,7 @@
         <v>46023</v>
       </c>
       <c r="B3" s="32" t="str">
-        <f t="shared" ref="B3:B87" si="0">TEXT($A3,"ddd")</f>
+        <f t="shared" ref="B3:B88" si="0">TEXT($A3,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C3" s="33" t="s">
@@ -4522,25 +4528,25 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="35">
-        <f>DATE(2026,11,3)</f>
-        <v>46329</v>
-      </c>
-      <c r="B88" s="36" t="str">
-        <f t="shared" ref="B88:B133" si="2">TEXT($A88,"ddd")</f>
-        <v>Tue</v>
-      </c>
-      <c r="C88" s="40" t="s">
-        <v>575</v>
-      </c>
-      <c r="D88" s="40" t="s">
-        <v>574</v>
-      </c>
-      <c r="E88" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F88" s="25" t="s">
-        <v>427</v>
+      <c r="A88" s="12">
+        <f>DATE(2026,10,28)</f>
+        <v>46323</v>
+      </c>
+      <c r="B88" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="C88" s="44" t="s">
+        <v>600</v>
+      </c>
+      <c r="D88" s="44" t="s">
+        <v>601</v>
+      </c>
+      <c r="E88" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="F88" s="44" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -4549,172 +4555,172 @@
         <v>46329</v>
       </c>
       <c r="B89" s="36" t="str">
+        <f t="shared" ref="B89:B134" si="2">TEXT($A89,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C89" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="D89" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F89" s="25" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="35">
+        <f>DATE(2026,11,3)</f>
+        <v>46329</v>
+      </c>
+      <c r="B90" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C89" s="40" t="s">
+      <c r="C90" s="40" t="s">
         <v>592</v>
       </c>
-      <c r="D89" s="40" t="s">
+      <c r="D90" s="40" t="s">
         <v>593</v>
       </c>
-      <c r="E89" s="37" t="s">
+      <c r="E90" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F89" s="44" t="s">
+      <c r="F90" s="44" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="35">
         <f>DATE(2026,11,7)</f>
         <v>46333</v>
       </c>
-      <c r="B90" s="36" t="str">
+      <c r="B91" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C90" s="40" t="s">
+      <c r="C91" s="40" t="s">
         <v>595</v>
       </c>
-      <c r="D90" s="40" t="s">
+      <c r="D91" s="40" t="s">
         <v>593</v>
       </c>
-      <c r="E90" s="37" t="s">
+      <c r="E91" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F90" s="44" t="s">
+      <c r="F91" s="44" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="35">
         <f>DATE(2026,11,8)</f>
         <v>46334</v>
       </c>
-      <c r="B91" s="36" t="str">
-        <f>TEXT($A91,"ddd")</f>
+      <c r="B92" s="36" t="str">
+        <f>TEXT($A92,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C91" s="37" t="s">
+      <c r="C92" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="D91" s="37" t="s">
+      <c r="D92" s="37" t="s">
         <v>453</v>
       </c>
-      <c r="E91" s="39" t="s">
+      <c r="E92" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F91" s="25" t="s">
+      <c r="F92" s="25" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="12">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="12">
         <f>DATE(2026,11,9)</f>
         <v>46335</v>
       </c>
-      <c r="B92" s="13" t="str">
-        <f>TEXT($A92,"ddd")</f>
+      <c r="B93" s="13" t="str">
+        <f>TEXT($A93,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C93" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D93" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="E92" s="38" t="s">
+      <c r="E93" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F92" s="25" t="s">
+      <c r="F93" s="25" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="12">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="12">
         <f>DATE(2026,11,19)</f>
         <v>46345</v>
       </c>
-      <c r="B93" s="13" t="str">
-        <f>TEXT($A93,"ddd")</f>
+      <c r="B94" s="13" t="str">
+        <f>TEXT($A94,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C93" s="16" t="s">
+      <c r="C94" s="16" t="s">
         <v>588</v>
       </c>
-      <c r="D93" s="16" t="s">
+      <c r="D94" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="E93" s="46" t="s">
+      <c r="E94" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="F93" s="44" t="s">
+      <c r="F94" s="44" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="12">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="12">
         <f>DATE(2026,11,25)</f>
         <v>46351</v>
       </c>
-      <c r="B94" s="13" t="str">
-        <f>TEXT($A94,"ddd")</f>
+      <c r="B95" s="13" t="str">
+        <f>TEXT($A95,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C94" s="16" t="s">
+      <c r="C95" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="D94" s="16" t="s">
+      <c r="D95" s="16" t="s">
         <v>586</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E95" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F94" s="25" t="s">
+      <c r="F95" s="25" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="31">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="31">
         <f>DATE(2026,11,28)</f>
         <v>46354</v>
       </c>
-      <c r="B95" s="32" t="str">
+      <c r="B96" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C95" s="43" t="s">
+      <c r="C96" s="43" t="s">
         <v>573</v>
       </c>
-      <c r="D95" s="33"/>
-      <c r="E95" s="33" t="s">
+      <c r="D96" s="33"/>
+      <c r="E96" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F95" s="25" t="s">
+      <c r="F96" s="25" t="s">
         <v>428</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="35">
-        <f>DATE(2026,12,7)</f>
-        <v>46363</v>
-      </c>
-      <c r="B96" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Mon</v>
-      </c>
-      <c r="C96" s="40" t="s">
-        <v>569</v>
-      </c>
-      <c r="D96" s="40" t="s">
-        <v>570</v>
-      </c>
-      <c r="E96" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="F96" s="40" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
@@ -4727,830 +4733,852 @@
         <v>Mon</v>
       </c>
       <c r="C97" s="40" t="s">
-        <v>571</v>
-      </c>
-      <c r="D97" s="40"/>
+        <v>569</v>
+      </c>
+      <c r="D97" s="40" t="s">
+        <v>570</v>
+      </c>
       <c r="E97" s="40" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="F97" s="40" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="35">
+        <f>DATE(2026,12,7)</f>
+        <v>46363</v>
+      </c>
+      <c r="B98" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C98" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="D98" s="40"/>
+      <c r="E98" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="F98" s="40" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="35">
         <f>DATE(2026,12,11)</f>
         <v>46367</v>
       </c>
-      <c r="B98" s="36" t="str">
+      <c r="B99" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C98" s="40" t="s">
+      <c r="C99" s="40" t="s">
         <v>565</v>
       </c>
-      <c r="D98" s="40" t="s">
+      <c r="D99" s="40" t="s">
         <v>566</v>
       </c>
-      <c r="E98" s="40" t="s">
+      <c r="E99" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="F98" s="44" t="s">
+      <c r="F99" s="44" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="35">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B99" s="36" t="str">
+      <c r="B100" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C99" s="40" t="s">
+      <c r="C100" s="40" t="s">
         <v>445</v>
       </c>
-      <c r="D99" s="40" t="s">
+      <c r="D100" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E99" s="37" t="s">
+      <c r="E100" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F99" s="25" t="s">
+      <c r="F100" s="25" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="35">
         <f>DATE(2026,12,25)</f>
         <v>46381</v>
       </c>
-      <c r="B100" s="36" t="str">
-        <f>TEXT($A100,"ddd")</f>
+      <c r="B101" s="36" t="str">
+        <f>TEXT($A101,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C100" s="37" t="s">
+      <c r="C101" s="37" t="s">
         <v>449</v>
       </c>
-      <c r="D100" s="37" t="s">
+      <c r="D101" s="37" t="s">
         <v>450</v>
       </c>
-      <c r="E100" s="39" t="s">
+      <c r="E101" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F100" s="25" t="s">
+      <c r="F101" s="25" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="12">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B101" s="13" t="str">
-        <f>TEXT($A101,"ddd")</f>
+      <c r="B102" s="13" t="str">
+        <f>TEXT($A102,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C102" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="D101" s="11" t="s">
+      <c r="D102" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="E101" s="38" t="s">
+      <c r="E102" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F101" s="25" t="s">
+      <c r="F102" s="25" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="31">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="31">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B102" s="32" t="str">
+      <c r="B103" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C102" s="43" t="s">
+      <c r="C103" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="D102" s="33" t="s">
+      <c r="D103" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="E102" s="33" t="s">
+      <c r="E103" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F102" s="25" t="s">
+      <c r="F103" s="25" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="35">
         <f>DATE(2027,1,15)</f>
         <v>46402</v>
       </c>
-      <c r="B103" s="36" t="str">
+      <c r="B104" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C103" s="40" t="s">
+      <c r="C104" s="40" t="s">
         <v>590</v>
       </c>
-      <c r="D103" s="40" t="s">
+      <c r="D104" s="40" t="s">
         <v>591</v>
       </c>
-      <c r="E103" s="37" t="s">
+      <c r="E104" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F103" s="25"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="35">
+      <c r="F104" s="25"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="35">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B104" s="36" t="str">
+      <c r="B105" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C104" s="37" t="s">
+      <c r="C105" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="D104" s="37" t="s">
+      <c r="D105" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E104" s="37" t="s">
+      <c r="E105" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F104" s="25" t="s">
+      <c r="F105" s="25" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="35">
         <f>DATE(2027,2,6)</f>
         <v>46424</v>
       </c>
-      <c r="B105" s="36" t="str">
-        <f>TEXT($A105,"ddd")</f>
+      <c r="B106" s="36" t="str">
+        <f>TEXT($A106,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C105" s="37" t="s">
+      <c r="C106" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="D105" s="37" t="s">
+      <c r="D106" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="E105" s="39" t="s">
+      <c r="E106" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F105" s="25" t="s">
+      <c r="F106" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="35">
         <f>DATE(2027,2,7)</f>
         <v>46425</v>
       </c>
-      <c r="B106" s="36" t="str">
-        <f>TEXT($A106,"ddd")</f>
+      <c r="B107" s="36" t="str">
+        <f>TEXT($A107,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C106" s="37" t="s">
+      <c r="C107" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="D106" s="37" t="s">
+      <c r="D107" s="37" t="s">
         <v>470</v>
       </c>
-      <c r="E106" s="39" t="s">
+      <c r="E107" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F106" s="25" t="s">
+      <c r="F107" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="12">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B107" s="13" t="str">
-        <f>TEXT($A107,"ddd")</f>
+      <c r="B108" s="13" t="str">
+        <f>TEXT($A108,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C108" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="D107" s="11" t="s">
+      <c r="D108" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="E107" s="38" t="s">
+      <c r="E108" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F107" s="25" t="s">
+      <c r="F108" s="25" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="41">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B108" s="42" t="str">
+      <c r="B109" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C108" s="25" t="s">
+      <c r="C109" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="D108" s="25" t="s">
+      <c r="D109" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="E108" s="25" t="s">
+      <c r="E109" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="F108" s="26" t="s">
+      <c r="F109" s="26" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="12">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="12">
         <f>DATE(2027,3,6)</f>
         <v>46452</v>
       </c>
-      <c r="B109" s="13" t="str">
-        <f>TEXT($A109,"ddd")</f>
+      <c r="B110" s="13" t="str">
+        <f>TEXT($A110,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C110" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="D109" s="11" t="s">
+      <c r="D110" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="E109" s="11" t="s">
+      <c r="E110" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F109" s="25" t="s">
+      <c r="F110" s="25" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="12">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="12">
         <f>DATE(2027,3,10)</f>
         <v>46456</v>
       </c>
-      <c r="B110" s="13" t="str">
-        <f>TEXT($A110,"ddd")</f>
+      <c r="B111" s="13" t="str">
+        <f>TEXT($A111,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C111" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="D110" s="11" t="s">
+      <c r="D111" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="E110" s="38" t="s">
+      <c r="E111" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F110" s="25" t="s">
+      <c r="F111" s="25" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="31">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="31">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B111" s="32" t="str">
+      <c r="B112" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C111" s="33" t="s">
+      <c r="C112" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D111" s="33" t="s">
+      <c r="D112" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E111" s="33" t="s">
+      <c r="E112" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F111" s="26" t="s">
+      <c r="F112" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="35">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B112" s="36" t="str">
+      <c r="B113" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C112" s="37" t="s">
+      <c r="C113" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D112" s="37" t="s">
+      <c r="D113" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="E112" s="37" t="s">
+      <c r="E113" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F112" s="26" t="s">
+      <c r="F113" s="26" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="12">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="12">
         <f>DATE(2027,3,26)</f>
         <v>46472</v>
       </c>
-      <c r="B113" s="13" t="str">
-        <f>TEXT($A113,"ddd")</f>
+      <c r="B114" s="13" t="str">
+        <f>TEXT($A114,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C113" s="11" t="s">
+      <c r="C114" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D113" s="11" t="s">
+      <c r="D114" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="E113" s="38" t="s">
+      <c r="E114" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F113" s="25" t="s">
+      <c r="F114" s="25" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="31">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="31">
         <f>DATE(2027,4,17)</f>
         <v>46494</v>
       </c>
-      <c r="B114" s="32" t="str">
-        <f>TEXT($A114,"ddd")</f>
+      <c r="B115" s="32" t="str">
+        <f>TEXT($A115,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C114" s="43" t="s">
+      <c r="C115" s="43" t="s">
         <v>582</v>
       </c>
-      <c r="D114" s="43" t="s">
+      <c r="D115" s="43" t="s">
         <v>583</v>
       </c>
-      <c r="E114" s="43" t="s">
+      <c r="E115" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F114" s="45" t="s">
+      <c r="F115" s="45" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="35">
         <f>DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="B115" s="36" t="str">
-        <f>TEXT($A115,"ddd")</f>
+      <c r="B116" s="36" t="str">
+        <f>TEXT($A116,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C115" s="37" t="s">
+      <c r="C116" s="37" t="s">
         <v>458</v>
       </c>
-      <c r="D115" s="37" t="s">
+      <c r="D116" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="E115" s="39" t="s">
+      <c r="E116" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="F115" s="25" t="s">
+      <c r="F116" s="25" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="12">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="12">
         <f>DATE(2027,5,17)</f>
         <v>46524</v>
       </c>
-      <c r="B116" s="13" t="str">
-        <f>TEXT($A116,"ddd")</f>
+      <c r="B117" s="13" t="str">
+        <f>TEXT($A117,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C117" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D116" s="11" t="s">
+      <c r="D117" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="E116" s="38" t="s">
+      <c r="E117" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="F116" s="25" t="s">
+      <c r="F117" s="25" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="41">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="41">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B117" s="42" t="str">
+      <c r="B118" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C117" s="25" t="s">
+      <c r="C118" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="D117" s="25" t="s">
+      <c r="D118" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="E117" s="25" t="s">
+      <c r="E118" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="F117" s="26" t="s">
+      <c r="F118" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="12">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B118" s="13" t="str">
-        <f>TEXT($A118,"ddd")</f>
+      <c r="B119" s="13" t="str">
+        <f>TEXT($A119,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C119" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="D118" s="11" t="s">
+      <c r="D119" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="E118" s="38" t="s">
+      <c r="E119" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F118" s="25" t="s">
+      <c r="F119" s="25" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="31">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="31">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B119" s="32" t="str">
+      <c r="B120" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C119" s="33" t="s">
+      <c r="C120" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="D119" s="33" t="s">
+      <c r="D120" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="E119" s="33" t="s">
+      <c r="E120" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F119" s="26" t="s">
+      <c r="F120" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="12">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B120" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D120" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E120" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="F120" s="26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B121" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B122" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B123" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C123" s="16" t="s">
-        <v>437</v>
+      <c r="C123" s="11" t="s">
+        <v>236</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>438</v>
+        <v>198</v>
       </c>
       <c r="E123" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F123" s="25" t="s">
+      <c r="F123" s="26" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="12">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B124" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="E124" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F124" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="35">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B124" s="36" t="str">
+      <c r="B125" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C124" s="37" t="s">
+      <c r="C125" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="D124" s="37" t="s">
+      <c r="D125" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="E124" s="37" t="s">
+      <c r="E125" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F124" s="26" t="s">
+      <c r="F125" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="12">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="12">
         <f>DATE(2027,8,9)</f>
         <v>46608</v>
       </c>
-      <c r="B125" s="13" t="str">
-        <f>TEXT($A125,"ddd")</f>
+      <c r="B126" s="13" t="str">
+        <f>TEXT($A126,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C125" s="11" t="s">
+      <c r="C126" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="D125" s="11" t="s">
+      <c r="D126" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="E125" s="38" t="s">
+      <c r="E126" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F125" s="25" t="s">
+      <c r="F126" s="25" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="31">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="31">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B126" s="32" t="str">
+      <c r="B127" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C126" s="33" t="s">
+      <c r="C127" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="D126" s="33" t="s">
+      <c r="D127" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E126" s="33" t="s">
+      <c r="E127" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F126" s="26" t="s">
+      <c r="F127" s="26" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="12">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
       </c>
-      <c r="B127" s="13" t="str">
+      <c r="B128" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C127" s="11" t="s">
+      <c r="C128" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D127" s="11" t="s">
+      <c r="D128" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E127" s="11" t="s">
+      <c r="E128" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F127" s="26" t="s">
+      <c r="F128" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="12">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B128" s="13" t="str">
+      <c r="B129" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C129" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D129" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E128" s="11" t="s">
+      <c r="E129" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F128" s="26" t="s">
+      <c r="F129" s="26" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" s="35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="35">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B129" s="36" t="str">
+      <c r="B130" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C129" s="37" t="s">
+      <c r="C130" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="D129" s="37" t="s">
+      <c r="D130" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="E129" s="37" t="s">
+      <c r="E130" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F129" s="26" t="s">
+      <c r="F130" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" s="12">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="12">
         <f>DATE(2027,10,28)</f>
         <v>46688</v>
       </c>
-      <c r="B130" s="13" t="str">
-        <f>TEXT($A130,"ddd")</f>
+      <c r="B131" s="13" t="str">
+        <f>TEXT($A131,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C130" s="11" t="s">
+      <c r="C131" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D130" s="11" t="s">
+      <c r="D131" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="E130" s="38" t="s">
+      <c r="E131" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F130" s="25" t="s">
+      <c r="F131" s="25" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A131" s="31">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" s="31">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B131" s="32" t="str">
+      <c r="B132" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C131" s="33" t="s">
+      <c r="C132" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D131" s="33" t="s">
+      <c r="D132" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E131" s="33" t="s">
+      <c r="E132" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F131" s="26" t="s">
+      <c r="F132" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A132" s="12">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B132" s="13" t="str">
+      <c r="B133" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C132" s="16" t="s">
+      <c r="C133" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="D132" s="11" t="s">
+      <c r="D133" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E132" s="11" t="s">
+      <c r="E133" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F132" s="25" t="s">
+      <c r="F133" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A133" s="35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B133" s="36" t="str">
+      <c r="B134" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C133" s="37" t="s">
+      <c r="C134" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D133" s="40" t="s">
+      <c r="D134" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E133" s="37" t="s">
+      <c r="E134" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F133" s="26" t="s">
+      <c r="F134" s="26" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A134" s="12">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B134" s="13" t="str">
-        <f>TEXT($A134,"ddd")</f>
+      <c r="B135" s="13" t="str">
+        <f>TEXT($A135,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C134" s="11" t="s">
+      <c r="C135" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D134" s="11" t="s">
+      <c r="D135" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="E134" s="38" t="s">
+      <c r="E135" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="F134" s="25" t="s">
+      <c r="F135" s="25" t="s">
         <v>493</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E134" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E135" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1953" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{594CAA58-B530-4E67-B546-7F96A01AAF02}"/>
+  <xr:revisionPtr revIDLastSave="2054" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B8C2866-5C32-44E6-97A6-FD8342A1D348}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$149</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="617">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1379,9 +1379,6 @@
     <t>Nam Hong Charity Concert 2026 (Location: Tzu Chi Humanistic Youth Centre). (In charge: Bryan, Chi Hwee)</t>
   </si>
   <si>
-    <t>[Tentative] Sponsor a HUG Campaign (Physical Launch Closer to Christmas). (In charge: Chi Hwee, Jin Hoa)</t>
-  </si>
-  <si>
     <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon dinner for NHWSS elderly (200 pax) - all to arrive by 7pm</t>
   </si>
   <si>
@@ -1848,6 +1845,54 @@
   </si>
   <si>
     <t>海南山天公神壇</t>
+  </si>
+  <si>
+    <t>Nine Emperor Gods Festival</t>
+  </si>
+  <si>
+    <t>九皇爷诞</t>
+  </si>
+  <si>
+    <t>SG Assist</t>
+  </si>
+  <si>
+    <t>Visit to SG Assist, 4-5pm</t>
+  </si>
+  <si>
+    <t>职员培训: 急救培训</t>
+  </si>
+  <si>
+    <t>Staff training : First-Aid</t>
+  </si>
+  <si>
+    <t>Staff Training - First-Aid. 职员培训: 急救培训</t>
+  </si>
+  <si>
+    <t>Sponsor a HUG Campaign (official launch). (In charge: Chi Hwee, Jin Hoa)</t>
+  </si>
+  <si>
+    <t>[Tentative] Wishing Tree</t>
+  </si>
+  <si>
+    <t>Wishing Tree</t>
+  </si>
+  <si>
+    <t>[Tentative] Sunrise Charity Walk 2028</t>
+  </si>
+  <si>
+    <t>日出义走2028</t>
+  </si>
+  <si>
+    <t>[Tentative] Charity Concert 2028</t>
+  </si>
+  <si>
+    <t>[Tentative] Charity Golf 2028</t>
+  </si>
+  <si>
+    <t>Charity Golf</t>
+  </si>
+  <si>
+    <t>[Tentative] Sponsor a HUG Campaign</t>
   </si>
 </sst>
 </file>
@@ -2637,7 +2682,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -2677,16 +2722,16 @@
         <v>Thu</v>
       </c>
       <c r="C2" s="30" t="s">
+        <v>472</v>
+      </c>
+      <c r="D2" s="30" t="s">
         <v>473</v>
       </c>
-      <c r="D2" s="30" t="s">
-        <v>474</v>
-      </c>
       <c r="E2" s="34" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2721,16 +2766,16 @@
         <v>Sun</v>
       </c>
       <c r="C4" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="D4" s="44" t="s">
         <v>551</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>552</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2765,16 +2810,16 @@
         <v>Tue</v>
       </c>
       <c r="C6" s="37" t="s">
+        <v>466</v>
+      </c>
+      <c r="D6" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="D6" s="37" t="s">
-        <v>468</v>
-      </c>
       <c r="E6" s="39" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2787,16 +2832,16 @@
         <v>Wed</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>470</v>
-      </c>
       <c r="E7" s="38" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2897,16 +2942,16 @@
         <v>Sat</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2919,16 +2964,16 @@
         <v>Sat</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -3007,16 +3052,16 @@
         <v>Fri</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>464</v>
-      </c>
       <c r="E17" s="38" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -3051,16 +3096,16 @@
         <v>Fri</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>458</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>459</v>
-      </c>
       <c r="E19" s="38" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -3098,7 +3143,7 @@
         <v>147</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>131</v>
@@ -3161,16 +3206,16 @@
         <v>Wed</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>496</v>
-      </c>
       <c r="E24" s="38" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -3227,16 +3272,16 @@
         <v>Sun</v>
       </c>
       <c r="C27" s="37" t="s">
+        <v>455</v>
+      </c>
+      <c r="D27" s="37" t="s">
         <v>456</v>
       </c>
-      <c r="D27" s="37" t="s">
-        <v>457</v>
-      </c>
       <c r="E27" s="39" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3249,16 +3294,16 @@
         <v>Mon</v>
       </c>
       <c r="C28" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>480</v>
-      </c>
       <c r="E28" s="38" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -3403,16 +3448,16 @@
         <v>Mon</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -3557,16 +3602,16 @@
         <v>Sun</v>
       </c>
       <c r="C42" s="37" t="s">
+        <v>453</v>
+      </c>
+      <c r="D42" s="37" t="s">
         <v>454</v>
       </c>
-      <c r="D42" s="37" t="s">
-        <v>455</v>
-      </c>
       <c r="E42" s="39" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3579,16 +3624,16 @@
         <v>Mon</v>
       </c>
       <c r="C43" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="D43" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="D43" s="11" t="s">
-        <v>478</v>
-      </c>
       <c r="E43" s="38" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3601,10 +3646,10 @@
         <v>Fri</v>
       </c>
       <c r="C44" s="33" t="s">
+        <v>504</v>
+      </c>
+      <c r="D44" s="43" t="s">
         <v>505</v>
-      </c>
-      <c r="D44" s="43" t="s">
-        <v>506</v>
       </c>
       <c r="E44" s="33" t="s">
         <v>218</v>
@@ -3667,10 +3712,10 @@
         <v>Sun</v>
       </c>
       <c r="C47" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="D47" s="11" t="s">
         <v>497</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>498</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>218</v>
@@ -3777,14 +3822,14 @@
         <v>Tue</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="11" t="s">
         <v>226</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3797,10 +3842,10 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="D53" s="16" t="s">
         <v>507</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>508</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>218</v>
@@ -3841,10 +3886,10 @@
         <v>Thu</v>
       </c>
       <c r="C55" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D55" s="16" t="s">
         <v>509</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>510</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>218</v>
@@ -3863,10 +3908,10 @@
         <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>218</v>
@@ -3885,14 +3930,14 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="11" t="s">
         <v>226</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3905,7 +3950,7 @@
         <v>Sat</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>162</v>
@@ -3928,14 +3973,14 @@
         <v>Sat</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11" t="s">
         <v>226</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G59" s="19"/>
     </row>
@@ -3949,10 +3994,10 @@
         <v>Mon</v>
       </c>
       <c r="C60" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="D60" s="16" t="s">
         <v>542</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>543</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>218</v>
@@ -3971,7 +4016,7 @@
         <v>Tue</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D61" s="16" t="s">
         <v>214</v>
@@ -3980,7 +4025,7 @@
         <v>218</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3993,14 +4038,14 @@
         <v>Tue</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="11" t="s">
         <v>226</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -4013,10 +4058,10 @@
         <v>Wed</v>
       </c>
       <c r="C63" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="D63" s="16" t="s">
         <v>540</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>541</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>218</v>
@@ -4035,14 +4080,14 @@
         <v>Wed</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -4077,14 +4122,14 @@
         <v>Wed</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -4097,14 +4142,14 @@
         <v>Thu</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -4137,14 +4182,14 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4157,16 +4202,16 @@
         <v>Sat</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -4179,16 +4224,16 @@
         <v>Sat</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -4201,7 +4246,7 @@
         <v>Sun</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>163</v>
@@ -4210,7 +4255,7 @@
         <v>124</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -4223,14 +4268,14 @@
         <v>Wed</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -4243,14 +4288,14 @@
         <v>Wed</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -4263,14 +4308,14 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="F75" s="25" t="s">
         <v>544</v>
-      </c>
-      <c r="F75" s="25" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="51" x14ac:dyDescent="0.35">
@@ -4327,14 +4372,14 @@
         <v>Mon</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D78" s="11"/>
       <c r="E78" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -4347,14 +4392,14 @@
         <v>Thu</v>
       </c>
       <c r="C79" s="40" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D79" s="37"/>
       <c r="E79" s="37" t="s">
         <v>226</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -4367,14 +4412,14 @@
         <v>Fri</v>
       </c>
       <c r="C80" s="40" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D80" s="37"/>
       <c r="E80" s="37" t="s">
         <v>226</v>
       </c>
       <c r="F80" s="44" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -4387,10 +4432,10 @@
         <v>Mon</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>218</v>
@@ -4409,16 +4454,16 @@
         <v>Tue</v>
       </c>
       <c r="C82" s="25" t="s">
+        <v>548</v>
+      </c>
+      <c r="D82" s="25" t="s">
         <v>549</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>550</v>
       </c>
       <c r="E82" s="25" t="s">
         <v>129</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
@@ -4431,14 +4476,14 @@
         <v>Wed</v>
       </c>
       <c r="C83" s="40" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D83" s="37"/>
       <c r="E83" s="37" t="s">
         <v>226</v>
       </c>
       <c r="F83" s="44" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
@@ -4451,10 +4496,10 @@
         <v>Fri</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E84" s="11" t="s">
         <v>218</v>
@@ -4473,10 +4518,10 @@
         <v>Sat</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E85" s="11" t="s">
         <v>218</v>
@@ -4495,16 +4540,16 @@
         <v>Mon</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E86" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -4517,14 +4562,14 @@
         <v>Tue</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D87" s="25"/>
       <c r="E87" s="25" t="s">
         <v>124</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
@@ -4537,16 +4582,16 @@
         <v>Wed</v>
       </c>
       <c r="C88" s="44" t="s">
+        <v>599</v>
+      </c>
+      <c r="D88" s="44" t="s">
         <v>600</v>
-      </c>
-      <c r="D88" s="44" t="s">
-        <v>601</v>
       </c>
       <c r="E88" s="44" t="s">
         <v>218</v>
       </c>
       <c r="F88" s="44" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -4555,14 +4600,14 @@
         <v>46329</v>
       </c>
       <c r="B89" s="36" t="str">
-        <f t="shared" ref="B89:B134" si="2">TEXT($A89,"ddd")</f>
+        <f t="shared" ref="B89:B147" si="2">TEXT($A89,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="C89" s="40" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E89" s="37" t="s">
         <v>121</v>
@@ -4581,1004 +4626,1606 @@
         <v>Tue</v>
       </c>
       <c r="C90" s="40" t="s">
+        <v>591</v>
+      </c>
+      <c r="D90" s="40" t="s">
         <v>592</v>
-      </c>
-      <c r="D90" s="40" t="s">
-        <v>593</v>
       </c>
       <c r="E90" s="37" t="s">
         <v>121</v>
       </c>
       <c r="F90" s="44" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="35">
+        <f>DATE(2026,11,4)</f>
+        <v>46330</v>
+      </c>
+      <c r="B91" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Wed</v>
+      </c>
+      <c r="C91" s="40" t="s">
+        <v>606</v>
+      </c>
+      <c r="D91" s="40" t="s">
+        <v>605</v>
+      </c>
+      <c r="E91" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="F91" s="44" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="35">
+        <f>DATE(2026,11,4)</f>
+        <v>46330</v>
+      </c>
+      <c r="B92" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Wed</v>
+      </c>
+      <c r="C92" s="40" t="s">
+        <v>604</v>
+      </c>
+      <c r="D92" s="40"/>
+      <c r="E92" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="F92" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="35">
         <f>DATE(2026,11,7)</f>
         <v>46333</v>
       </c>
-      <c r="B91" s="36" t="str">
+      <c r="B93" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C91" s="40" t="s">
-        <v>595</v>
-      </c>
-      <c r="D91" s="40" t="s">
+      <c r="C93" s="40" t="s">
+        <v>594</v>
+      </c>
+      <c r="D93" s="40" t="s">
+        <v>592</v>
+      </c>
+      <c r="E93" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F93" s="44" t="s">
         <v>593</v>
       </c>
-      <c r="E91" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F91" s="44" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="35">
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="35">
         <f>DATE(2026,11,8)</f>
         <v>46334</v>
       </c>
-      <c r="B92" s="36" t="str">
-        <f>TEXT($A92,"ddd")</f>
+      <c r="B94" s="36" t="str">
+        <f>TEXT($A94,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C92" s="37" t="s">
+      <c r="C94" s="37" t="s">
+        <v>451</v>
+      </c>
+      <c r="D94" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="D92" s="37" t="s">
-        <v>453</v>
-      </c>
-      <c r="E92" s="39" t="s">
-        <v>451</v>
-      </c>
-      <c r="F92" s="25" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="12">
+      <c r="E94" s="39" t="s">
+        <v>450</v>
+      </c>
+      <c r="F94" s="25" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="12">
         <f>DATE(2026,11,9)</f>
         <v>46335</v>
       </c>
-      <c r="B93" s="13" t="str">
-        <f>TEXT($A93,"ddd")</f>
+      <c r="B95" s="13" t="str">
+        <f>TEXT($A95,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C95" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="D95" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="D93" s="11" t="s">
-        <v>476</v>
-      </c>
-      <c r="E93" s="38" t="s">
-        <v>451</v>
-      </c>
-      <c r="F93" s="25" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="12">
+      <c r="E95" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="F95" s="25" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="12">
         <f>DATE(2026,11,19)</f>
         <v>46345</v>
       </c>
-      <c r="B94" s="13" t="str">
-        <f>TEXT($A94,"ddd")</f>
+      <c r="B96" s="13" t="str">
+        <f>TEXT($A96,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C94" s="16" t="s">
+      <c r="C96" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="D96" s="16" t="s">
+        <v>586</v>
+      </c>
+      <c r="E96" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="F96" s="44" t="s">
         <v>588</v>
       </c>
-      <c r="D94" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="E94" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="F94" s="44" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="12">
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="12">
         <f>DATE(2026,11,25)</f>
         <v>46351</v>
       </c>
-      <c r="B95" s="13" t="str">
-        <f>TEXT($A95,"ddd")</f>
+      <c r="B97" s="13" t="str">
+        <f>TEXT($A97,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C95" s="16" t="s">
+      <c r="C97" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="D97" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="D95" s="16" t="s">
-        <v>586</v>
-      </c>
-      <c r="E95" s="11" t="s">
+      <c r="E97" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F95" s="25" t="s">
+      <c r="F97" s="25" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="31">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="31">
         <f>DATE(2026,11,28)</f>
         <v>46354</v>
       </c>
-      <c r="B96" s="32" t="str">
+      <c r="B98" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C96" s="43" t="s">
-        <v>573</v>
-      </c>
-      <c r="D96" s="33"/>
-      <c r="E96" s="33" t="s">
+      <c r="C98" s="43" t="s">
+        <v>572</v>
+      </c>
+      <c r="D98" s="33"/>
+      <c r="E98" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F96" s="25" t="s">
+      <c r="F98" s="25" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="35">
         <f>DATE(2026,12,7)</f>
         <v>46363</v>
       </c>
-      <c r="B97" s="36" t="str">
+      <c r="B99" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C97" s="40" t="s">
+      <c r="C99" s="40" t="s">
+        <v>568</v>
+      </c>
+      <c r="D99" s="40" t="s">
         <v>569</v>
       </c>
-      <c r="D97" s="40" t="s">
-        <v>570</v>
-      </c>
-      <c r="E97" s="40" t="s">
+      <c r="E99" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="F97" s="40" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="35">
+      <c r="F99" s="40" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="35">
         <f>DATE(2026,12,7)</f>
         <v>46363</v>
       </c>
-      <c r="B98" s="36" t="str">
+      <c r="B100" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C98" s="40" t="s">
+      <c r="C100" s="40" t="s">
+        <v>570</v>
+      </c>
+      <c r="D100" s="40"/>
+      <c r="E100" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="F100" s="40" t="s">
         <v>571</v>
       </c>
-      <c r="D98" s="40"/>
-      <c r="E98" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F98" s="40" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="35">
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="35">
         <f>DATE(2026,12,11)</f>
         <v>46367</v>
       </c>
-      <c r="B99" s="36" t="str">
+      <c r="B101" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C99" s="40" t="s">
+      <c r="C101" s="40" t="s">
+        <v>564</v>
+      </c>
+      <c r="D101" s="40" t="s">
         <v>565</v>
       </c>
-      <c r="D99" s="40" t="s">
+      <c r="E101" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="F101" s="44" t="s">
         <v>566</v>
       </c>
-      <c r="E99" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="F99" s="44" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="35">
-        <f>DATE(2026,12,16)</f>
-        <v>46372</v>
-      </c>
-      <c r="B100" s="36" t="str">
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="35">
+        <f>DATE(2026,12,25)</f>
+        <v>46381</v>
+      </c>
+      <c r="B102" s="36" t="str">
+        <f>TEXT($A102,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C102" s="40" t="s">
+        <v>609</v>
+      </c>
+      <c r="D102" s="37"/>
+      <c r="E102" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F102" s="44" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="35">
+        <f>DATE(2026,12,25)</f>
+        <v>46381</v>
+      </c>
+      <c r="B103" s="36" t="str">
+        <f>TEXT($A103,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C103" s="37" t="s">
+        <v>448</v>
+      </c>
+      <c r="D103" s="37" t="s">
+        <v>449</v>
+      </c>
+      <c r="E103" s="39" t="s">
+        <v>450</v>
+      </c>
+      <c r="F103" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="12">
+        <f>DATE(2027,1,1)</f>
+        <v>46388</v>
+      </c>
+      <c r="B104" s="13" t="str">
+        <f>TEXT($A104,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="D104" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="E104" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="F104" s="25" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="31">
+        <f>DATE(2027,1,1)</f>
+        <v>46388</v>
+      </c>
+      <c r="B105" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C105" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="D105" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="E105" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F105" s="25" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="35">
+        <f>DATE(2027,1,15)</f>
+        <v>46402</v>
+      </c>
+      <c r="B106" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C106" s="40" t="s">
+        <v>589</v>
+      </c>
+      <c r="D106" s="40" t="s">
+        <v>590</v>
+      </c>
+      <c r="E106" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F106" s="25"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="35">
+        <f>DATE(2027,1,30)</f>
+        <v>46417</v>
+      </c>
+      <c r="B107" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="C107" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="D107" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="E107" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F107" s="25" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="35">
+        <f>DATE(2027,2,6)</f>
+        <v>46424</v>
+      </c>
+      <c r="B108" s="36" t="str">
+        <f>TEXT($A108,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C108" s="37" t="s">
+        <v>466</v>
+      </c>
+      <c r="D108" s="37" t="s">
+        <v>467</v>
+      </c>
+      <c r="E108" s="39" t="s">
+        <v>450</v>
+      </c>
+      <c r="F108" s="25" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="35">
+        <f>DATE(2027,2,7)</f>
+        <v>46425</v>
+      </c>
+      <c r="B109" s="36" t="str">
+        <f>TEXT($A109,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C109" s="37" t="s">
+        <v>468</v>
+      </c>
+      <c r="D109" s="37" t="s">
+        <v>469</v>
+      </c>
+      <c r="E109" s="39" t="s">
+        <v>450</v>
+      </c>
+      <c r="F109" s="25" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="12">
+        <f>DATE(2027,2,8)</f>
+        <v>46426</v>
+      </c>
+      <c r="B110" s="13" t="str">
+        <f>TEXT($A110,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C110" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="E110" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="F110" s="25" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="41">
+        <f>DATE(2027,2,18)</f>
+        <v>46436</v>
+      </c>
+      <c r="B111" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C111" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="D111" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="E111" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="F111" s="26" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="12">
+        <f>DATE(2027,3,6)</f>
+        <v>46452</v>
+      </c>
+      <c r="B112" s="13" t="str">
+        <f>TEXT($A112,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="E112" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F112" s="25" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="12">
+        <f>DATE(2027,3,10)</f>
+        <v>46456</v>
+      </c>
+      <c r="B113" s="13" t="str">
+        <f>TEXT($A113,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="E113" s="38" t="s">
+        <v>461</v>
+      </c>
+      <c r="F113" s="25" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="31">
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
+      </c>
+      <c r="B114" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C114" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="D114" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="E114" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="F114" s="26" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="35">
+        <f>DATE(2027,3,25)</f>
+        <v>46471</v>
+      </c>
+      <c r="B115" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C115" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="D115" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="E115" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F115" s="26" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="12">
+        <f>DATE(2027,3,26)</f>
+        <v>46472</v>
+      </c>
+      <c r="B116" s="13" t="str">
+        <f>TEXT($A116,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="E116" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="F116" s="25" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="31">
+        <f>DATE(2027,4,17)</f>
+        <v>46494</v>
+      </c>
+      <c r="B117" s="36" t="str">
+        <f>TEXT($A117,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C117" s="40" t="s">
+        <v>608</v>
+      </c>
+      <c r="D117" s="40"/>
+      <c r="E117" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F117" s="25" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="31">
+        <f>DATE(2027,4,17)</f>
+        <v>46494</v>
+      </c>
+      <c r="B118" s="32" t="str">
+        <f>TEXT($A118,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C118" s="43" t="s">
+        <v>581</v>
+      </c>
+      <c r="D118" s="43" t="s">
+        <v>582</v>
+      </c>
+      <c r="E118" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="F118" s="45" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="35">
+        <f>DATE(2027,5,1)</f>
+        <v>46508</v>
+      </c>
+      <c r="B119" s="36" t="str">
+        <f>TEXT($A119,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C119" s="37" t="s">
+        <v>457</v>
+      </c>
+      <c r="D119" s="37" t="s">
+        <v>458</v>
+      </c>
+      <c r="E119" s="39" t="s">
+        <v>450</v>
+      </c>
+      <c r="F119" s="25" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="12">
+        <f>DATE(2027,5,17)</f>
+        <v>46524</v>
+      </c>
+      <c r="B120" s="13" t="str">
+        <f>TEXT($A120,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="E120" s="38" t="s">
+        <v>461</v>
+      </c>
+      <c r="F120" s="25" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="41">
+        <f>DATE(2027,5,19)</f>
+        <v>46526</v>
+      </c>
+      <c r="B121" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C100" s="40" t="s">
-        <v>445</v>
-      </c>
-      <c r="D100" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="E100" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="F100" s="25" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="35">
-        <f>DATE(2026,12,25)</f>
-        <v>46381</v>
-      </c>
-      <c r="B101" s="36" t="str">
-        <f>TEXT($A101,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C101" s="37" t="s">
-        <v>449</v>
-      </c>
-      <c r="D101" s="37" t="s">
+      <c r="C121" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="D121" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="E121" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="F121" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="12">
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
+      </c>
+      <c r="B122" s="13" t="str">
+        <f>TEXT($A122,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="E122" s="38" t="s">
         <v>450</v>
       </c>
-      <c r="E101" s="39" t="s">
-        <v>451</v>
-      </c>
-      <c r="F101" s="25" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="12">
-        <f>DATE(2027,1,1)</f>
-        <v>46388</v>
-      </c>
-      <c r="B102" s="13" t="str">
-        <f>TEXT($A102,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>473</v>
-      </c>
-      <c r="D102" s="11" t="s">
-        <v>474</v>
-      </c>
-      <c r="E102" s="38" t="s">
-        <v>451</v>
-      </c>
-      <c r="F102" s="25" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="31">
-        <f>DATE(2027,1,1)</f>
-        <v>46388</v>
-      </c>
-      <c r="B103" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C103" s="43" t="s">
-        <v>217</v>
-      </c>
-      <c r="D103" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="E103" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="F103" s="25" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="35">
-        <f>DATE(2027,1,15)</f>
-        <v>46402</v>
-      </c>
-      <c r="B104" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C104" s="40" t="s">
-        <v>590</v>
-      </c>
-      <c r="D104" s="40" t="s">
-        <v>591</v>
-      </c>
-      <c r="E104" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F104" s="25"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="35">
-        <f>DATE(2027,1,30)</f>
-        <v>46417</v>
-      </c>
-      <c r="B105" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C105" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="D105" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="E105" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F105" s="25" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="35">
-        <f>DATE(2027,2,6)</f>
-        <v>46424</v>
-      </c>
-      <c r="B106" s="36" t="str">
-        <f>TEXT($A106,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C106" s="37" t="s">
-        <v>467</v>
-      </c>
-      <c r="D106" s="37" t="s">
-        <v>468</v>
-      </c>
-      <c r="E106" s="39" t="s">
-        <v>451</v>
-      </c>
-      <c r="F106" s="25" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="35">
-        <f>DATE(2027,2,7)</f>
-        <v>46425</v>
-      </c>
-      <c r="B107" s="36" t="str">
-        <f>TEXT($A107,"ddd")</f>
-        <v>Sun</v>
-      </c>
-      <c r="C107" s="37" t="s">
-        <v>469</v>
-      </c>
-      <c r="D107" s="37" t="s">
-        <v>470</v>
-      </c>
-      <c r="E107" s="39" t="s">
-        <v>451</v>
-      </c>
-      <c r="F107" s="25" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="12">
-        <f>DATE(2027,2,8)</f>
-        <v>46426</v>
-      </c>
-      <c r="B108" s="13" t="str">
-        <f>TEXT($A108,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="D108" s="11" t="s">
-        <v>472</v>
-      </c>
-      <c r="E108" s="38" t="s">
-        <v>451</v>
-      </c>
-      <c r="F108" s="25" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="41">
-        <f>DATE(2027,2,18)</f>
-        <v>46436</v>
-      </c>
-      <c r="B109" s="42" t="str">
+      <c r="F122" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="31">
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
+      </c>
+      <c r="B123" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C109" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="D109" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="E109" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="F109" s="26" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="12">
-        <f>DATE(2027,3,6)</f>
-        <v>46452</v>
-      </c>
-      <c r="B110" s="13" t="str">
-        <f>TEXT($A110,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C110" s="11" t="s">
-        <v>518</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="E110" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F110" s="25" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="12">
-        <f>DATE(2027,3,10)</f>
-        <v>46456</v>
-      </c>
-      <c r="B111" s="13" t="str">
-        <f>TEXT($A111,"ddd")</f>
-        <v>Wed</v>
-      </c>
-      <c r="C111" s="11" t="s">
-        <v>465</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>466</v>
-      </c>
-      <c r="E111" s="38" t="s">
-        <v>462</v>
-      </c>
-      <c r="F111" s="25" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="31">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
-      </c>
-      <c r="B112" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C112" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="D112" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="E112" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="F112" s="26" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="35">
-        <f>DATE(2027,3,25)</f>
-        <v>46471</v>
-      </c>
-      <c r="B113" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C113" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="D113" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="E113" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F113" s="26" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="12">
-        <f>DATE(2027,3,26)</f>
-        <v>46472</v>
-      </c>
-      <c r="B114" s="13" t="str">
-        <f>TEXT($A114,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>463</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>464</v>
-      </c>
-      <c r="E114" s="38" t="s">
-        <v>451</v>
-      </c>
-      <c r="F114" s="25" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="31">
-        <f>DATE(2027,4,17)</f>
-        <v>46494</v>
-      </c>
-      <c r="B115" s="32" t="str">
-        <f>TEXT($A115,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C115" s="43" t="s">
-        <v>582</v>
-      </c>
-      <c r="D115" s="43" t="s">
-        <v>583</v>
-      </c>
-      <c r="E115" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="F115" s="45" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="35">
-        <f>DATE(2027,5,1)</f>
-        <v>46508</v>
-      </c>
-      <c r="B116" s="36" t="str">
-        <f>TEXT($A116,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C116" s="37" t="s">
-        <v>458</v>
-      </c>
-      <c r="D116" s="37" t="s">
-        <v>459</v>
-      </c>
-      <c r="E116" s="39" t="s">
-        <v>451</v>
-      </c>
-      <c r="F116" s="25" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="12">
-        <f>DATE(2027,5,17)</f>
-        <v>46524</v>
-      </c>
-      <c r="B117" s="13" t="str">
-        <f>TEXT($A117,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>460</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>461</v>
-      </c>
-      <c r="E117" s="38" t="s">
-        <v>462</v>
-      </c>
-      <c r="F117" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="41">
-        <f>DATE(2027,5,19)</f>
-        <v>46526</v>
-      </c>
-      <c r="B118" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Wed</v>
-      </c>
-      <c r="C118" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="D118" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="E118" s="25" t="s">
+      <c r="C123" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="D123" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="E123" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F118" s="26" t="s">
+      <c r="F123" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="12">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
-      </c>
-      <c r="B119" s="13" t="str">
-        <f>TEXT($A119,"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>456</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>457</v>
-      </c>
-      <c r="E119" s="38" t="s">
-        <v>451</v>
-      </c>
-      <c r="F119" s="25" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="31">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
-      </c>
-      <c r="B120" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C120" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="D120" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E120" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="F120" s="26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="12">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B121" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C121" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D121" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E121" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="F121" s="26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
-      </c>
-      <c r="B122" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C122" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D122" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="E122" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F122" s="26" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
-      </c>
-      <c r="B123" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C123" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="D123" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="E123" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F123" s="26" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
       </c>
       <c r="B124" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C124" s="16" t="s">
+      <c r="C124" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E124" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F124" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="12">
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
+      </c>
+      <c r="B125" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E125" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F125" s="26" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="12">
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
+      </c>
+      <c r="B126" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E126" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F126" s="26" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="12">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B127" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C127" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="D124" s="11" t="s">
+      <c r="D127" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E124" s="11" t="s">
+      <c r="E127" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F124" s="25" t="s">
+      <c r="F127" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="35">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B125" s="36" t="str">
+      <c r="B128" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C125" s="37" t="s">
+      <c r="C128" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="D125" s="37" t="s">
+      <c r="D128" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="E125" s="37" t="s">
+      <c r="E128" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F125" s="26" t="s">
+      <c r="F128" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="12">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="12">
         <f>DATE(2027,8,9)</f>
         <v>46608</v>
       </c>
-      <c r="B126" s="13" t="str">
-        <f>TEXT($A126,"ddd")</f>
+      <c r="B129" s="13" t="str">
+        <f>TEXT($A129,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C126" s="11" t="s">
+      <c r="C129" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="D129" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="D126" s="11" t="s">
-        <v>455</v>
-      </c>
-      <c r="E126" s="38" t="s">
-        <v>451</v>
-      </c>
-      <c r="F126" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="31">
+      <c r="E129" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="F129" s="25" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="31">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B127" s="32" t="str">
+      <c r="B130" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C127" s="33" t="s">
+      <c r="C130" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="D127" s="33" t="s">
+      <c r="D130" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E127" s="33" t="s">
+      <c r="E130" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F127" s="26" t="s">
+      <c r="F130" s="26" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="12">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
       </c>
-      <c r="B128" s="13" t="str">
+      <c r="B131" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C131" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D131" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E128" s="11" t="s">
+      <c r="E131" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F128" s="26" t="s">
+      <c r="F131" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" s="12">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B129" s="13" t="str">
+      <c r="B132" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C129" s="11" t="s">
+      <c r="C132" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D129" s="11" t="s">
+      <c r="D132" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E129" s="11" t="s">
+      <c r="E132" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F129" s="26" t="s">
+      <c r="F132" s="26" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" s="35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" s="12">
+        <f>DATE(2027,9,30)</f>
+        <v>46660</v>
+      </c>
+      <c r="B133" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C133" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D133" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E133" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F133" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" s="12">
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
+      </c>
+      <c r="B134" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D134" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E134" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F134" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" s="12">
+        <f>DATE(2027,10,2)</f>
+        <v>46662</v>
+      </c>
+      <c r="B135" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D135" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E135" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F135" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" s="12">
+        <f>DATE(2027,10,3)</f>
+        <v>46663</v>
+      </c>
+      <c r="B136" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Sun</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D136" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E136" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F136" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137" s="12">
+        <f>DATE(2027,10,4)</f>
+        <v>46664</v>
+      </c>
+      <c r="B137" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C137" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D137" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E137" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F137" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A138" s="12">
+        <f>DATE(2027,10,5)</f>
+        <v>46665</v>
+      </c>
+      <c r="B138" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D138" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E138" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F138" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A139" s="12">
+        <f>DATE(2027,10,6)</f>
+        <v>46666</v>
+      </c>
+      <c r="B139" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Wed</v>
+      </c>
+      <c r="C139" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D139" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E139" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F139" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A140" s="12">
+        <f>DATE(2027,10,7)</f>
+        <v>46667</v>
+      </c>
+      <c r="B140" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C140" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D140" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E140" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F140" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A141" s="12">
+        <f>DATE(2027,10,8)</f>
+        <v>46668</v>
+      </c>
+      <c r="B141" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C141" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D141" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E141" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F141" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A142" s="35">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B130" s="36" t="str">
+      <c r="B142" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C130" s="37" t="s">
+      <c r="C142" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="D130" s="37" t="s">
+      <c r="D142" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="E130" s="37" t="s">
+      <c r="E142" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F130" s="26" t="s">
+      <c r="F142" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A131" s="12">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" s="12">
         <f>DATE(2027,10,28)</f>
         <v>46688</v>
       </c>
-      <c r="B131" s="13" t="str">
-        <f>TEXT($A131,"ddd")</f>
+      <c r="B143" s="13" t="str">
+        <f>TEXT($A143,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C131" s="11" t="s">
+      <c r="C143" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="D143" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D131" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="E131" s="38" t="s">
-        <v>451</v>
-      </c>
-      <c r="F131" s="25" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A132" s="31">
+      <c r="E143" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="F143" s="25" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A144" s="31">
+        <f>DATE(2027,11,1)</f>
+        <v>46692</v>
+      </c>
+      <c r="B144" s="36" t="str">
+        <f>TEXT($A144,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C144" s="40" t="s">
+        <v>616</v>
+      </c>
+      <c r="D144" s="40"/>
+      <c r="E144" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F144" s="25" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A145" s="31">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B132" s="32" t="str">
+      <c r="B145" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C132" s="33" t="s">
+      <c r="C145" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D132" s="33" t="s">
+      <c r="D145" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E132" s="33" t="s">
+      <c r="E145" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F132" s="26" t="s">
+      <c r="F145" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A133" s="12">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A146" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B133" s="13" t="str">
+      <c r="B146" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C133" s="16" t="s">
+      <c r="C146" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="D133" s="11" t="s">
+      <c r="D146" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E133" s="11" t="s">
+      <c r="E146" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F133" s="25" t="s">
+      <c r="F146" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A134" s="35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B134" s="36" t="str">
+      <c r="B147" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C134" s="37" t="s">
+      <c r="C147" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D134" s="40" t="s">
+      <c r="D147" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E134" s="37" t="s">
+      <c r="E147" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F134" s="26" t="s">
+      <c r="F147" s="26" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A135" s="12">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148" s="12">
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B135" s="13" t="str">
-        <f>TEXT($A135,"ddd")</f>
+      <c r="B148" s="36" t="str">
+        <f>TEXT($A148,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C135" s="11" t="s">
+      <c r="C148" s="40" t="s">
+        <v>609</v>
+      </c>
+      <c r="D148" s="37"/>
+      <c r="E148" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F148" s="44" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149" s="12">
+        <f>DATE(2027,12,25)</f>
+        <v>46746</v>
+      </c>
+      <c r="B149" s="13" t="str">
+        <f>TEXT($A149,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C149" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="D149" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D135" s="11" t="s">
+      <c r="E149" s="38" t="s">
         <v>450</v>
       </c>
-      <c r="E135" s="38" t="s">
-        <v>451</v>
-      </c>
-      <c r="F135" s="25" t="s">
-        <v>493</v>
+      <c r="F149" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A150" s="12">
+        <f>DATE(2028,1,1)</f>
+        <v>46753</v>
+      </c>
+      <c r="B150" s="13" t="str">
+        <f>TEXT($A150,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C150" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="E150" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="F150" s="25" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A151" s="12">
+        <f>DATE(2028,4,1)</f>
+        <v>46844</v>
+      </c>
+      <c r="B151" s="32" t="str">
+        <f>TEXT($A151,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C151" s="43" t="s">
+        <v>611</v>
+      </c>
+      <c r="D151" s="43" t="s">
+        <v>612</v>
+      </c>
+      <c r="E151" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="F151" s="45" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A152" s="12">
+        <f>DATE(2028,9,1)</f>
+        <v>46997</v>
+      </c>
+      <c r="B152" s="13" t="str">
+        <f t="shared" ref="B152:B153" si="3">TEXT($A152,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C152" s="16" t="s">
+        <v>613</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E152" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F152" s="26" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A153" s="12">
+        <f>DATE(2028,10,1)</f>
+        <v>47027</v>
+      </c>
+      <c r="B153" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>Sun</v>
+      </c>
+      <c r="C153" s="16" t="s">
+        <v>614</v>
+      </c>
+      <c r="D153" s="11"/>
+      <c r="E153" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F153" s="45" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A154" s="12">
+        <f>DATE(2028,10,18)</f>
+        <v>47044</v>
+      </c>
+      <c r="B154" s="13" t="str">
+        <f>TEXT($A154,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C154" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D154" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E154" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F154" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A155" s="12">
+        <f>DATE(2028,10,19)</f>
+        <v>47045</v>
+      </c>
+      <c r="B155" s="13" t="str">
+        <f>TEXT($A155,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C155" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D155" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E155" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F155" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A156" s="12">
+        <f>DATE(2028,10,20)</f>
+        <v>47046</v>
+      </c>
+      <c r="B156" s="13" t="str">
+        <f>TEXT($A156,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C156" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D156" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E156" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F156" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A157" s="12">
+        <f>DATE(2028,10,21)</f>
+        <v>47047</v>
+      </c>
+      <c r="B157" s="13" t="str">
+        <f>TEXT($A157,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C157" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D157" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E157" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F157" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A158" s="12">
+        <f>DATE(2028,10,22)</f>
+        <v>47048</v>
+      </c>
+      <c r="B158" s="13" t="str">
+        <f>TEXT($A158,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C158" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D158" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E158" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F158" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A159" s="12">
+        <f>DATE(2028,10,23)</f>
+        <v>47049</v>
+      </c>
+      <c r="B159" s="13" t="str">
+        <f>TEXT($A159,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C159" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D159" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E159" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F159" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A160" s="12">
+        <f>DATE(2028,10,24)</f>
+        <v>47050</v>
+      </c>
+      <c r="B160" s="13" t="str">
+        <f>TEXT($A160,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C160" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D160" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E160" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F160" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A161" s="12">
+        <f>DATE(2028,10,25)</f>
+        <v>47051</v>
+      </c>
+      <c r="B161" s="13" t="str">
+        <f>TEXT($A161,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C161" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D161" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E161" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F161" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A162" s="12">
+        <f>DATE(2028,10,26)</f>
+        <v>47052</v>
+      </c>
+      <c r="B162" s="13" t="str">
+        <f>TEXT($A162,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D162" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E162" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F162" s="25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A163" s="12">
+        <f>DATE(2028,11,1)</f>
+        <v>47058</v>
+      </c>
+      <c r="B163" s="36" t="str">
+        <f>TEXT($A163,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C163" s="40" t="s">
+        <v>616</v>
+      </c>
+      <c r="D163" s="40"/>
+      <c r="E163" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F163" s="25" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E135" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E149" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -7646,7 +8293,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7671,17 +8318,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -7922,6 +8558,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -7932,19 +8579,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7964,6 +8598,19 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2054" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B8C2866-5C32-44E6-97A6-FD8342A1D348}"/>
+  <xr:revisionPtr revIDLastSave="2062" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD592395-3E1F-4B57-A902-BDB46110BE38}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$150</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="619">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1893,6 +1893,12 @@
   </si>
   <si>
     <t>[Tentative] Sponsor a HUG Campaign</t>
+  </si>
+  <si>
+    <t>Chong Pang Deepavali Dinner</t>
+  </si>
+  <si>
+    <t>Chong Pang Deepavali Dinner, 6.30pm. GOH: Mr K Shanmugam</t>
   </si>
 </sst>
 </file>
@@ -2682,7 +2688,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -4600,7 +4606,7 @@
         <v>46329</v>
       </c>
       <c r="B89" s="36" t="str">
-        <f t="shared" ref="B89:B147" si="2">TEXT($A89,"ddd")</f>
+        <f t="shared" ref="B89:B148" si="2">TEXT($A89,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="C89" s="40" t="s">
@@ -4748,88 +4754,86 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="12">
+        <f>DATE(2026,11,13)</f>
+        <v>46339</v>
+      </c>
+      <c r="B96" s="13" t="str">
+        <f>TEXT($A96,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>618</v>
+      </c>
+      <c r="D96" s="16"/>
+      <c r="E96" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="F96" s="44" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="12">
         <f>DATE(2026,11,19)</f>
         <v>46345</v>
       </c>
-      <c r="B96" s="13" t="str">
-        <f>TEXT($A96,"ddd")</f>
+      <c r="B97" s="13" t="str">
+        <f>TEXT($A97,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C96" s="16" t="s">
+      <c r="C97" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="D96" s="16" t="s">
+      <c r="D97" s="16" t="s">
         <v>586</v>
       </c>
-      <c r="E96" s="46" t="s">
+      <c r="E97" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="F96" s="44" t="s">
+      <c r="F97" s="44" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="12">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="12">
         <f>DATE(2026,11,25)</f>
         <v>46351</v>
       </c>
-      <c r="B97" s="13" t="str">
-        <f>TEXT($A97,"ddd")</f>
+      <c r="B98" s="13" t="str">
+        <f>TEXT($A98,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C97" s="16" t="s">
+      <c r="C98" s="16" t="s">
         <v>584</v>
       </c>
-      <c r="D97" s="16" t="s">
+      <c r="D98" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="E97" s="11" t="s">
+      <c r="E98" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F97" s="25" t="s">
+      <c r="F98" s="25" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="31">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="31">
         <f>DATE(2026,11,28)</f>
         <v>46354</v>
       </c>
-      <c r="B98" s="32" t="str">
+      <c r="B99" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C98" s="43" t="s">
+      <c r="C99" s="43" t="s">
         <v>572</v>
       </c>
-      <c r="D98" s="33"/>
-      <c r="E98" s="33" t="s">
+      <c r="D99" s="33"/>
+      <c r="E99" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F98" s="25" t="s">
+      <c r="F99" s="25" t="s">
         <v>428</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="35">
-        <f>DATE(2026,12,7)</f>
-        <v>46363</v>
-      </c>
-      <c r="B99" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>Mon</v>
-      </c>
-      <c r="C99" s="40" t="s">
-        <v>568</v>
-      </c>
-      <c r="D99" s="40" t="s">
-        <v>569</v>
-      </c>
-      <c r="E99" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="F99" s="40" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
@@ -4842,56 +4846,58 @@
         <v>Mon</v>
       </c>
       <c r="C100" s="40" t="s">
-        <v>570</v>
-      </c>
-      <c r="D100" s="40"/>
+        <v>568</v>
+      </c>
+      <c r="D100" s="40" t="s">
+        <v>569</v>
+      </c>
       <c r="E100" s="40" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="F100" s="40" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="35">
+        <f>DATE(2026,12,7)</f>
+        <v>46363</v>
+      </c>
+      <c r="B101" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C101" s="40" t="s">
+        <v>570</v>
+      </c>
+      <c r="D101" s="40"/>
+      <c r="E101" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="F101" s="40" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="35">
         <f>DATE(2026,12,11)</f>
         <v>46367</v>
       </c>
-      <c r="B101" s="36" t="str">
+      <c r="B102" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C101" s="40" t="s">
+      <c r="C102" s="40" t="s">
         <v>564</v>
       </c>
-      <c r="D101" s="40" t="s">
+      <c r="D102" s="40" t="s">
         <v>565</v>
       </c>
-      <c r="E101" s="40" t="s">
+      <c r="E102" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="F101" s="44" t="s">
+      <c r="F102" s="44" t="s">
         <v>566</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="35">
-        <f>DATE(2026,12,25)</f>
-        <v>46381</v>
-      </c>
-      <c r="B102" s="36" t="str">
-        <f>TEXT($A102,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C102" s="40" t="s">
-        <v>609</v>
-      </c>
-      <c r="D102" s="37"/>
-      <c r="E102" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="F102" s="44" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
@@ -4903,321 +4909,321 @@
         <f>TEXT($A103,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C103" s="37" t="s">
+      <c r="C103" s="40" t="s">
+        <v>609</v>
+      </c>
+      <c r="D103" s="37"/>
+      <c r="E103" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F103" s="44" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="35">
+        <f>DATE(2026,12,25)</f>
+        <v>46381</v>
+      </c>
+      <c r="B104" s="36" t="str">
+        <f>TEXT($A104,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C104" s="37" t="s">
         <v>448</v>
       </c>
-      <c r="D103" s="37" t="s">
+      <c r="D104" s="37" t="s">
         <v>449</v>
       </c>
-      <c r="E103" s="39" t="s">
+      <c r="E104" s="39" t="s">
         <v>450</v>
       </c>
-      <c r="F103" s="25" t="s">
+      <c r="F104" s="25" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="12">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B104" s="13" t="str">
-        <f>TEXT($A104,"ddd")</f>
+      <c r="B105" s="13" t="str">
+        <f>TEXT($A105,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C105" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="D104" s="11" t="s">
+      <c r="D105" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="E104" s="38" t="s">
+      <c r="E105" s="38" t="s">
         <v>450</v>
       </c>
-      <c r="F104" s="25" t="s">
+      <c r="F105" s="25" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="31">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="31">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B105" s="32" t="str">
+      <c r="B106" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C105" s="43" t="s">
+      <c r="C106" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="D105" s="33" t="s">
+      <c r="D106" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="E105" s="33" t="s">
+      <c r="E106" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F105" s="25" t="s">
+      <c r="F106" s="25" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="35">
         <f>DATE(2027,1,15)</f>
         <v>46402</v>
       </c>
-      <c r="B106" s="36" t="str">
+      <c r="B107" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C106" s="40" t="s">
+      <c r="C107" s="40" t="s">
         <v>589</v>
       </c>
-      <c r="D106" s="40" t="s">
+      <c r="D107" s="40" t="s">
         <v>590</v>
       </c>
-      <c r="E106" s="37" t="s">
+      <c r="E107" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F106" s="25"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="35">
+      <c r="F107" s="25"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="35">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B107" s="36" t="str">
+      <c r="B108" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C107" s="37" t="s">
+      <c r="C108" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="D107" s="37" t="s">
+      <c r="D108" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E107" s="37" t="s">
+      <c r="E108" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F107" s="25" t="s">
+      <c r="F108" s="25" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="35">
         <f>DATE(2027,2,6)</f>
         <v>46424</v>
       </c>
-      <c r="B108" s="36" t="str">
-        <f>TEXT($A108,"ddd")</f>
+      <c r="B109" s="36" t="str">
+        <f>TEXT($A109,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C108" s="37" t="s">
+      <c r="C109" s="37" t="s">
         <v>466</v>
       </c>
-      <c r="D108" s="37" t="s">
+      <c r="D109" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="E108" s="39" t="s">
+      <c r="E109" s="39" t="s">
         <v>450</v>
       </c>
-      <c r="F108" s="25" t="s">
+      <c r="F109" s="25" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="35">
         <f>DATE(2027,2,7)</f>
         <v>46425</v>
       </c>
-      <c r="B109" s="36" t="str">
-        <f>TEXT($A109,"ddd")</f>
+      <c r="B110" s="36" t="str">
+        <f>TEXT($A110,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C109" s="37" t="s">
+      <c r="C110" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="D109" s="37" t="s">
+      <c r="D110" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="E109" s="39" t="s">
+      <c r="E110" s="39" t="s">
         <v>450</v>
       </c>
-      <c r="F109" s="25" t="s">
+      <c r="F110" s="25" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="12">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="12">
         <f>DATE(2027,2,8)</f>
         <v>46426</v>
       </c>
-      <c r="B110" s="13" t="str">
-        <f>TEXT($A110,"ddd")</f>
+      <c r="B111" s="13" t="str">
+        <f>TEXT($A111,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C111" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="D110" s="11" t="s">
+      <c r="D111" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="E110" s="38" t="s">
+      <c r="E111" s="38" t="s">
         <v>450</v>
       </c>
-      <c r="F110" s="25" t="s">
+      <c r="F111" s="25" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="41">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="41">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B111" s="42" t="str">
+      <c r="B112" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C111" s="25" t="s">
+      <c r="C112" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="D111" s="25" t="s">
+      <c r="D112" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="E111" s="25" t="s">
+      <c r="E112" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="F111" s="26" t="s">
+      <c r="F112" s="26" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="12">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="12">
         <f>DATE(2027,3,6)</f>
         <v>46452</v>
       </c>
-      <c r="B112" s="13" t="str">
-        <f>TEXT($A112,"ddd")</f>
+      <c r="B113" s="13" t="str">
+        <f>TEXT($A113,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C113" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="D112" s="11" t="s">
+      <c r="D113" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="E112" s="11" t="s">
+      <c r="E113" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F112" s="25" t="s">
+      <c r="F113" s="25" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="12">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="12">
         <f>DATE(2027,3,10)</f>
         <v>46456</v>
       </c>
-      <c r="B113" s="13" t="str">
-        <f>TEXT($A113,"ddd")</f>
+      <c r="B114" s="13" t="str">
+        <f>TEXT($A114,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C113" s="11" t="s">
+      <c r="C114" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="D113" s="11" t="s">
+      <c r="D114" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="E113" s="38" t="s">
+      <c r="E114" s="38" t="s">
         <v>461</v>
       </c>
-      <c r="F113" s="25" t="s">
+      <c r="F114" s="25" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="31">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="31">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B114" s="32" t="str">
+      <c r="B115" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C114" s="33" t="s">
+      <c r="C115" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D114" s="33" t="s">
+      <c r="D115" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E114" s="33" t="s">
+      <c r="E115" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F114" s="26" t="s">
+      <c r="F115" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="35">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B115" s="36" t="str">
+      <c r="B116" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C115" s="37" t="s">
+      <c r="C116" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="D115" s="37" t="s">
+      <c r="D116" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="E115" s="37" t="s">
+      <c r="E116" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F115" s="26" t="s">
+      <c r="F116" s="26" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="12">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="12">
         <f>DATE(2027,3,26)</f>
         <v>46472</v>
       </c>
-      <c r="B116" s="13" t="str">
-        <f>TEXT($A116,"ddd")</f>
+      <c r="B117" s="13" t="str">
+        <f>TEXT($A117,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C117" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="D116" s="11" t="s">
+      <c r="D117" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="E116" s="38" t="s">
+      <c r="E117" s="38" t="s">
         <v>450</v>
       </c>
-      <c r="F116" s="25" t="s">
+      <c r="F117" s="25" t="s">
         <v>483</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="31">
-        <f>DATE(2027,4,17)</f>
-        <v>46494</v>
-      </c>
-      <c r="B117" s="36" t="str">
-        <f>TEXT($A117,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C117" s="40" t="s">
-        <v>608</v>
-      </c>
-      <c r="D117" s="40"/>
-      <c r="E117" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="F117" s="25" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
@@ -5225,677 +5231,677 @@
         <f>DATE(2027,4,17)</f>
         <v>46494</v>
       </c>
-      <c r="B118" s="32" t="str">
+      <c r="B118" s="36" t="str">
         <f>TEXT($A118,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C118" s="43" t="s">
+      <c r="C118" s="40" t="s">
+        <v>608</v>
+      </c>
+      <c r="D118" s="40"/>
+      <c r="E118" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F118" s="25" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="31">
+        <f>DATE(2027,4,17)</f>
+        <v>46494</v>
+      </c>
+      <c r="B119" s="32" t="str">
+        <f>TEXT($A119,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C119" s="43" t="s">
         <v>581</v>
       </c>
-      <c r="D118" s="43" t="s">
+      <c r="D119" s="43" t="s">
         <v>582</v>
       </c>
-      <c r="E118" s="43" t="s">
+      <c r="E119" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F118" s="45" t="s">
+      <c r="F119" s="45" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="35">
         <f>DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="B119" s="36" t="str">
-        <f>TEXT($A119,"ddd")</f>
+      <c r="B120" s="36" t="str">
+        <f>TEXT($A120,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C119" s="37" t="s">
+      <c r="C120" s="37" t="s">
         <v>457</v>
       </c>
-      <c r="D119" s="37" t="s">
+      <c r="D120" s="37" t="s">
         <v>458</v>
       </c>
-      <c r="E119" s="39" t="s">
+      <c r="E120" s="39" t="s">
         <v>450</v>
       </c>
-      <c r="F119" s="25" t="s">
+      <c r="F120" s="25" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="12">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="12">
         <f>DATE(2027,5,17)</f>
         <v>46524</v>
       </c>
-      <c r="B120" s="13" t="str">
-        <f>TEXT($A120,"ddd")</f>
+      <c r="B121" s="13" t="str">
+        <f>TEXT($A121,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C120" s="11" t="s">
+      <c r="C121" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="D120" s="11" t="s">
+      <c r="D121" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="E120" s="38" t="s">
+      <c r="E121" s="38" t="s">
         <v>461</v>
       </c>
-      <c r="F120" s="25" t="s">
+      <c r="F121" s="25" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="41">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="41">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B121" s="42" t="str">
+      <c r="B122" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C121" s="25" t="s">
+      <c r="C122" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="D121" s="25" t="s">
+      <c r="D122" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="E121" s="25" t="s">
+      <c r="E122" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="F121" s="26" t="s">
+      <c r="F122" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="12">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B122" s="13" t="str">
-        <f>TEXT($A122,"ddd")</f>
+      <c r="B123" s="13" t="str">
+        <f>TEXT($A123,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C123" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="D122" s="11" t="s">
+      <c r="D123" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="E122" s="38" t="s">
+      <c r="E123" s="38" t="s">
         <v>450</v>
       </c>
-      <c r="F122" s="25" t="s">
+      <c r="F123" s="25" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="31">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="31">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B123" s="32" t="str">
+      <c r="B124" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C123" s="33" t="s">
+      <c r="C124" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="D123" s="33" t="s">
+      <c r="D124" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="E123" s="33" t="s">
+      <c r="E124" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F123" s="26" t="s">
+      <c r="F124" s="26" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="12">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B124" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D124" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E124" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="F124" s="26" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B125" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B126" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B127" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C127" s="16" t="s">
-        <v>437</v>
+      <c r="C127" s="11" t="s">
+        <v>236</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>438</v>
+        <v>198</v>
       </c>
       <c r="E127" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F127" s="25" t="s">
+      <c r="F127" s="26" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="12">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B128" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="E128" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F128" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="35">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B128" s="36" t="str">
+      <c r="B129" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C128" s="37" t="s">
+      <c r="C129" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="D128" s="37" t="s">
+      <c r="D129" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="E128" s="37" t="s">
+      <c r="E129" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F128" s="26" t="s">
+      <c r="F129" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" s="12">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="12">
         <f>DATE(2027,8,9)</f>
         <v>46608</v>
       </c>
-      <c r="B129" s="13" t="str">
-        <f>TEXT($A129,"ddd")</f>
+      <c r="B130" s="13" t="str">
+        <f>TEXT($A130,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C129" s="11" t="s">
+      <c r="C130" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="D129" s="11" t="s">
+      <c r="D130" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="E129" s="38" t="s">
+      <c r="E130" s="38" t="s">
         <v>450</v>
       </c>
-      <c r="F129" s="25" t="s">
+      <c r="F130" s="25" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" s="31">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="31">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B130" s="32" t="str">
+      <c r="B131" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C130" s="33" t="s">
+      <c r="C131" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="D130" s="33" t="s">
+      <c r="D131" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E130" s="33" t="s">
+      <c r="E131" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F130" s="26" t="s">
+      <c r="F131" s="26" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A131" s="12">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
       </c>
-      <c r="B131" s="13" t="str">
+      <c r="B132" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C131" s="11" t="s">
+      <c r="C132" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D131" s="11" t="s">
+      <c r="D132" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E131" s="11" t="s">
+      <c r="E132" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F131" s="26" t="s">
+      <c r="F132" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A132" s="12">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B132" s="13" t="str">
+      <c r="B133" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C132" s="11" t="s">
+      <c r="C133" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D132" s="11" t="s">
+      <c r="D133" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E132" s="11" t="s">
+      <c r="E133" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F132" s="26" t="s">
+      <c r="F133" s="26" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A133" s="12">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" s="12">
         <f>DATE(2027,9,30)</f>
         <v>46660</v>
       </c>
-      <c r="B133" s="13" t="str">
+      <c r="B134" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C133" s="16" t="s">
+      <c r="C134" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D133" s="16" t="s">
+      <c r="D134" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E133" s="11" t="s">
+      <c r="E134" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F133" s="25" t="s">
+      <c r="F134" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A134" s="12">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
       </c>
-      <c r="B134" s="13" t="str">
+      <c r="B135" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C134" s="16" t="s">
+      <c r="C135" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D134" s="16" t="s">
+      <c r="D135" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E134" s="11" t="s">
+      <c r="E135" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F134" s="25" t="s">
+      <c r="F135" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A135" s="12">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" s="12">
         <f>DATE(2027,10,2)</f>
         <v>46662</v>
       </c>
-      <c r="B135" s="13" t="str">
+      <c r="B136" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C135" s="16" t="s">
+      <c r="C136" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D135" s="16" t="s">
+      <c r="D136" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E135" s="11" t="s">
+      <c r="E136" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F135" s="25" t="s">
+      <c r="F136" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A136" s="12">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137" s="12">
         <f>DATE(2027,10,3)</f>
         <v>46663</v>
       </c>
-      <c r="B136" s="13" t="str">
+      <c r="B137" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sun</v>
       </c>
-      <c r="C136" s="16" t="s">
+      <c r="C137" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D136" s="16" t="s">
+      <c r="D137" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E136" s="11" t="s">
+      <c r="E137" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F136" s="25" t="s">
+      <c r="F137" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A137" s="12">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A138" s="12">
         <f>DATE(2027,10,4)</f>
         <v>46664</v>
       </c>
-      <c r="B137" s="13" t="str">
+      <c r="B138" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C137" s="16" t="s">
+      <c r="C138" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D137" s="16" t="s">
+      <c r="D138" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E137" s="11" t="s">
+      <c r="E138" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F137" s="25" t="s">
+      <c r="F138" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A138" s="12">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A139" s="12">
         <f>DATE(2027,10,5)</f>
         <v>46665</v>
       </c>
-      <c r="B138" s="13" t="str">
+      <c r="B139" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C138" s="16" t="s">
+      <c r="C139" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D138" s="16" t="s">
+      <c r="D139" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E138" s="11" t="s">
+      <c r="E139" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F138" s="25" t="s">
+      <c r="F139" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A139" s="12">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A140" s="12">
         <f>DATE(2027,10,6)</f>
         <v>46666</v>
       </c>
-      <c r="B139" s="13" t="str">
+      <c r="B140" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C139" s="16" t="s">
+      <c r="C140" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D139" s="16" t="s">
+      <c r="D140" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E139" s="11" t="s">
+      <c r="E140" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F139" s="25" t="s">
+      <c r="F140" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A140" s="12">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A141" s="12">
         <f>DATE(2027,10,7)</f>
         <v>46667</v>
       </c>
-      <c r="B140" s="13" t="str">
+      <c r="B141" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C140" s="16" t="s">
+      <c r="C141" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D140" s="16" t="s">
+      <c r="D141" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E140" s="11" t="s">
+      <c r="E141" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F140" s="25" t="s">
+      <c r="F141" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A141" s="12">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A142" s="12">
         <f>DATE(2027,10,8)</f>
         <v>46668</v>
       </c>
-      <c r="B141" s="13" t="str">
+      <c r="B142" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C141" s="16" t="s">
+      <c r="C142" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D141" s="16" t="s">
+      <c r="D142" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E141" s="11" t="s">
+      <c r="E142" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F141" s="25" t="s">
+      <c r="F142" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A142" s="35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" s="35">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B142" s="36" t="str">
+      <c r="B143" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C142" s="37" t="s">
+      <c r="C143" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="D142" s="37" t="s">
+      <c r="D143" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="E142" s="37" t="s">
+      <c r="E143" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F142" s="26" t="s">
+      <c r="F143" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A143" s="12">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A144" s="12">
         <f>DATE(2027,10,28)</f>
         <v>46688</v>
       </c>
-      <c r="B143" s="13" t="str">
-        <f>TEXT($A143,"ddd")</f>
+      <c r="B144" s="13" t="str">
+        <f>TEXT($A144,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C143" s="11" t="s">
+      <c r="C144" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="D143" s="11" t="s">
+      <c r="D144" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="E143" s="38" t="s">
+      <c r="E144" s="38" t="s">
         <v>450</v>
       </c>
-      <c r="F143" s="25" t="s">
+      <c r="F144" s="25" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A144" s="31">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A145" s="31">
         <f>DATE(2027,11,1)</f>
         <v>46692</v>
       </c>
-      <c r="B144" s="36" t="str">
-        <f>TEXT($A144,"ddd")</f>
+      <c r="B145" s="36" t="str">
+        <f>TEXT($A145,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C144" s="40" t="s">
+      <c r="C145" s="40" t="s">
         <v>616</v>
       </c>
-      <c r="D144" s="40"/>
-      <c r="E144" s="37" t="s">
+      <c r="D145" s="40"/>
+      <c r="E145" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F144" s="25" t="s">
+      <c r="F145" s="25" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A145" s="31">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A146" s="31">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B145" s="32" t="str">
+      <c r="B146" s="32" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C145" s="33" t="s">
+      <c r="C146" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="D145" s="33" t="s">
+      <c r="D146" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E145" s="33" t="s">
+      <c r="E146" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F145" s="26" t="s">
+      <c r="F146" s="26" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A146" s="12">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B146" s="13" t="str">
+      <c r="B147" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C146" s="16" t="s">
+      <c r="C147" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="D146" s="11" t="s">
+      <c r="D147" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E146" s="11" t="s">
+      <c r="E147" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F146" s="25" t="s">
+      <c r="F147" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A147" s="35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148" s="35">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B147" s="36" t="str">
+      <c r="B148" s="36" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C147" s="37" t="s">
+      <c r="C148" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="D147" s="40" t="s">
+      <c r="D148" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E147" s="37" t="s">
+      <c r="E148" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F147" s="26" t="s">
+      <c r="F148" s="26" t="s">
         <v>429</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A148" s="12">
-        <f>DATE(2027,12,25)</f>
-        <v>46746</v>
-      </c>
-      <c r="B148" s="36" t="str">
-        <f>TEXT($A148,"ddd")</f>
-        <v>Sat</v>
-      </c>
-      <c r="C148" s="40" t="s">
-        <v>609</v>
-      </c>
-      <c r="D148" s="37"/>
-      <c r="E148" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="F148" s="44" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
@@ -5903,329 +5909,349 @@
         <f>DATE(2027,12,25)</f>
         <v>46746</v>
       </c>
-      <c r="B149" s="13" t="str">
+      <c r="B149" s="36" t="str">
         <f>TEXT($A149,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C149" s="11" t="s">
-        <v>448</v>
-      </c>
-      <c r="D149" s="11" t="s">
-        <v>449</v>
-      </c>
-      <c r="E149" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="F149" s="25" t="s">
-        <v>492</v>
+      <c r="C149" s="40" t="s">
+        <v>609</v>
+      </c>
+      <c r="D149" s="37"/>
+      <c r="E149" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F149" s="44" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="12">
-        <f>DATE(2028,1,1)</f>
-        <v>46753</v>
+        <f>DATE(2027,12,25)</f>
+        <v>46746</v>
       </c>
       <c r="B150" s="13" t="str">
         <f>TEXT($A150,"ddd")</f>
         <v>Sat</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="E150" s="38" t="s">
         <v>450</v>
       </c>
       <c r="F150" s="25" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="12">
+        <f>DATE(2028,1,1)</f>
+        <v>46753</v>
+      </c>
+      <c r="B151" s="13" t="str">
+        <f>TEXT($A151,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="E151" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="F151" s="25" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A152" s="12">
         <f>DATE(2028,4,1)</f>
         <v>46844</v>
       </c>
-      <c r="B151" s="32" t="str">
-        <f>TEXT($A151,"ddd")</f>
+      <c r="B152" s="32" t="str">
+        <f>TEXT($A152,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C151" s="43" t="s">
+      <c r="C152" s="43" t="s">
         <v>611</v>
       </c>
-      <c r="D151" s="43" t="s">
+      <c r="D152" s="43" t="s">
         <v>612</v>
       </c>
-      <c r="E151" s="43" t="s">
+      <c r="E152" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="F151" s="45" t="s">
+      <c r="F152" s="45" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A152" s="12">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A153" s="12">
         <f>DATE(2028,9,1)</f>
         <v>46997</v>
       </c>
-      <c r="B152" s="13" t="str">
-        <f t="shared" ref="B152:B153" si="3">TEXT($A152,"ddd")</f>
+      <c r="B153" s="13" t="str">
+        <f t="shared" ref="B153:B154" si="3">TEXT($A153,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C152" s="16" t="s">
+      <c r="C153" s="16" t="s">
         <v>613</v>
       </c>
-      <c r="D152" s="11" t="s">
+      <c r="D153" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E152" s="11" t="s">
+      <c r="E153" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F152" s="26" t="s">
+      <c r="F153" s="26" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A153" s="12">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A154" s="12">
         <f>DATE(2028,10,1)</f>
         <v>47027</v>
       </c>
-      <c r="B153" s="13" t="str">
+      <c r="B154" s="13" t="str">
         <f t="shared" si="3"/>
         <v>Sun</v>
       </c>
-      <c r="C153" s="16" t="s">
+      <c r="C154" s="16" t="s">
         <v>614</v>
       </c>
-      <c r="D153" s="11"/>
-      <c r="E153" s="11" t="s">
+      <c r="D154" s="11"/>
+      <c r="E154" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F153" s="45" t="s">
+      <c r="F154" s="45" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A154" s="12">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A155" s="12">
         <f>DATE(2028,10,18)</f>
         <v>47044</v>
       </c>
-      <c r="B154" s="13" t="str">
-        <f>TEXT($A154,"ddd")</f>
+      <c r="B155" s="13" t="str">
+        <f t="shared" ref="B155:B164" si="4">TEXT($A155,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C154" s="16" t="s">
+      <c r="C155" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D154" s="16" t="s">
+      <c r="D155" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E154" s="11" t="s">
+      <c r="E155" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F154" s="25" t="s">
+      <c r="F155" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A155" s="12">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A156" s="12">
         <f>DATE(2028,10,19)</f>
         <v>47045</v>
       </c>
-      <c r="B155" s="13" t="str">
-        <f>TEXT($A155,"ddd")</f>
+      <c r="B156" s="13" t="str">
+        <f t="shared" si="4"/>
         <v>Thu</v>
       </c>
-      <c r="C155" s="16" t="s">
+      <c r="C156" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D155" s="16" t="s">
+      <c r="D156" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E155" s="11" t="s">
+      <c r="E156" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F155" s="25" t="s">
+      <c r="F156" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A156" s="12">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A157" s="12">
         <f>DATE(2028,10,20)</f>
         <v>47046</v>
       </c>
-      <c r="B156" s="13" t="str">
-        <f>TEXT($A156,"ddd")</f>
+      <c r="B157" s="13" t="str">
+        <f t="shared" si="4"/>
         <v>Fri</v>
       </c>
-      <c r="C156" s="16" t="s">
+      <c r="C157" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D156" s="16" t="s">
+      <c r="D157" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E156" s="11" t="s">
+      <c r="E157" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F156" s="25" t="s">
+      <c r="F157" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A157" s="12">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A158" s="12">
         <f>DATE(2028,10,21)</f>
         <v>47047</v>
       </c>
-      <c r="B157" s="13" t="str">
-        <f>TEXT($A157,"ddd")</f>
+      <c r="B158" s="13" t="str">
+        <f t="shared" si="4"/>
         <v>Sat</v>
       </c>
-      <c r="C157" s="16" t="s">
+      <c r="C158" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D157" s="16" t="s">
+      <c r="D158" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E157" s="11" t="s">
+      <c r="E158" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F157" s="25" t="s">
+      <c r="F158" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A158" s="12">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A159" s="12">
         <f>DATE(2028,10,22)</f>
         <v>47048</v>
       </c>
-      <c r="B158" s="13" t="str">
-        <f>TEXT($A158,"ddd")</f>
+      <c r="B159" s="13" t="str">
+        <f t="shared" si="4"/>
         <v>Sun</v>
       </c>
-      <c r="C158" s="16" t="s">
+      <c r="C159" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D158" s="16" t="s">
+      <c r="D159" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E158" s="11" t="s">
+      <c r="E159" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F158" s="25" t="s">
+      <c r="F159" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A159" s="12">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A160" s="12">
         <f>DATE(2028,10,23)</f>
         <v>47049</v>
       </c>
-      <c r="B159" s="13" t="str">
-        <f>TEXT($A159,"ddd")</f>
+      <c r="B160" s="13" t="str">
+        <f t="shared" si="4"/>
         <v>Mon</v>
       </c>
-      <c r="C159" s="16" t="s">
+      <c r="C160" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D159" s="16" t="s">
+      <c r="D160" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E159" s="11" t="s">
+      <c r="E160" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F159" s="25" t="s">
+      <c r="F160" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A160" s="12">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A161" s="12">
         <f>DATE(2028,10,24)</f>
         <v>47050</v>
       </c>
-      <c r="B160" s="13" t="str">
-        <f>TEXT($A160,"ddd")</f>
+      <c r="B161" s="13" t="str">
+        <f t="shared" si="4"/>
         <v>Tue</v>
       </c>
-      <c r="C160" s="16" t="s">
+      <c r="C161" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D160" s="16" t="s">
+      <c r="D161" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E160" s="11" t="s">
+      <c r="E161" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F160" s="25" t="s">
+      <c r="F161" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A161" s="12">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A162" s="12">
         <f>DATE(2028,10,25)</f>
         <v>47051</v>
       </c>
-      <c r="B161" s="13" t="str">
-        <f>TEXT($A161,"ddd")</f>
+      <c r="B162" s="13" t="str">
+        <f t="shared" si="4"/>
         <v>Wed</v>
       </c>
-      <c r="C161" s="16" t="s">
+      <c r="C162" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D161" s="16" t="s">
+      <c r="D162" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E161" s="11" t="s">
+      <c r="E162" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F161" s="25" t="s">
+      <c r="F162" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A162" s="12">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A163" s="12">
         <f>DATE(2028,10,26)</f>
         <v>47052</v>
       </c>
-      <c r="B162" s="13" t="str">
-        <f>TEXT($A162,"ddd")</f>
+      <c r="B163" s="13" t="str">
+        <f t="shared" si="4"/>
         <v>Thu</v>
       </c>
-      <c r="C162" s="16" t="s">
+      <c r="C163" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D162" s="16" t="s">
+      <c r="D163" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="E162" s="11" t="s">
+      <c r="E163" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F162" s="25" t="s">
+      <c r="F163" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A163" s="12">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A164" s="12">
         <f>DATE(2028,11,1)</f>
         <v>47058</v>
       </c>
-      <c r="B163" s="36" t="str">
-        <f>TEXT($A163,"ddd")</f>
+      <c r="B164" s="36" t="str">
+        <f t="shared" si="4"/>
         <v>Wed</v>
       </c>
-      <c r="C163" s="40" t="s">
+      <c r="C164" s="40" t="s">
         <v>616</v>
       </c>
-      <c r="D163" s="40"/>
-      <c r="E163" s="37" t="s">
+      <c r="D164" s="40"/>
+      <c r="E164" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F163" s="25" t="s">
+      <c r="F164" s="25" t="s">
         <v>429</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E149" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E150" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -8293,7 +8319,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46321</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -8318,6 +8344,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -8558,42 +8604,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8612,9 +8626,21 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2062" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD592395-3E1F-4B57-A902-BDB46110BE38}"/>
+  <xr:revisionPtr revIDLastSave="2073" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{499D16F0-E823-4994-8DE6-BEDA0B5A4A58}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="620">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -230,12 +230,6 @@
     <t>Ng Chuan Seng (Tony)</t>
   </si>
   <si>
-    <t>Ng Jie Ying (Cecil) PBM</t>
-  </si>
-  <si>
-    <t>黄洁滢</t>
-  </si>
-  <si>
     <t>吴荣豪</t>
   </si>
   <si>
@@ -353,9 +347,6 @@
     <t>Ilman.jpg</t>
   </si>
   <si>
-    <t>Cecil.jpg</t>
-  </si>
-  <si>
     <t>Lawrence.jpg</t>
   </si>
   <si>
@@ -1899,6 +1890,18 @@
   </si>
   <si>
     <t>Chong Pang Deepavali Dinner, 6.30pm. GOH: Mr K Shanmugam</t>
+  </si>
+  <si>
+    <t>Bretran.jpg</t>
+  </si>
+  <si>
+    <t>Bretran Chia Chwee Peng</t>
+  </si>
+  <si>
+    <t>谢沝玶</t>
+  </si>
+  <si>
+    <t>Special Committee Member</t>
   </si>
 </sst>
 </file>
@@ -2578,7 +2581,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2703,7 +2706,7 @@
         <v>30</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>31</v>
@@ -2712,10 +2715,10 @@
         <v>32</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2728,16 +2731,16 @@
         <v>Thu</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2750,16 +2753,16 @@
         <v>Thu</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2772,16 +2775,16 @@
         <v>Sun</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2794,16 +2797,16 @@
         <v>Sun</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2816,16 +2819,16 @@
         <v>Tue</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2838,16 +2841,16 @@
         <v>Wed</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2860,16 +2863,16 @@
         <v>Thu</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2882,16 +2885,16 @@
         <v>Fri</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2904,16 +2907,16 @@
         <v>Sat</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2926,16 +2929,16 @@
         <v>Fri</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2948,16 +2951,16 @@
         <v>Sat</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2970,16 +2973,16 @@
         <v>Sat</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2992,16 +2995,16 @@
         <v>Mon</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -3014,16 +3017,16 @@
         <v>Tue</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -3036,16 +3039,16 @@
         <v>Fri</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -3058,16 +3061,16 @@
         <v>Fri</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -3080,16 +3083,16 @@
         <v>Mon</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -3102,16 +3105,16 @@
         <v>Fri</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -3124,16 +3127,16 @@
         <v>Mon</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3146,16 +3149,16 @@
         <v>Fri</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3168,16 +3171,16 @@
         <v>Sun</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -3190,16 +3193,16 @@
         <v>Mon</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -3212,16 +3215,16 @@
         <v>Wed</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -3234,16 +3237,16 @@
         <v>Fri</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -3256,16 +3259,16 @@
         <v>Sat</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -3278,16 +3281,16 @@
         <v>Sun</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3300,16 +3303,16 @@
         <v>Mon</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -3322,16 +3325,16 @@
         <v>Sun</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -3344,16 +3347,16 @@
         <v>Mon</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -3366,16 +3369,16 @@
         <v>Fri</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -3388,16 +3391,16 @@
         <v>Sat</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -3410,16 +3413,16 @@
         <v>Sat</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -3432,16 +3435,16 @@
         <v>Fri</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -3454,16 +3457,16 @@
         <v>Mon</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -3476,16 +3479,16 @@
         <v>Fri</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3498,16 +3501,16 @@
         <v>Fri</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3520,16 +3523,16 @@
         <v>Sat</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3542,16 +3545,16 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3564,16 +3567,16 @@
         <v>Wed</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -3586,16 +3589,16 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3608,16 +3611,16 @@
         <v>Sun</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3630,16 +3633,16 @@
         <v>Mon</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3652,16 +3655,16 @@
         <v>Fri</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3674,16 +3677,16 @@
         <v>Sat</v>
       </c>
       <c r="C45" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="E45" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="D45" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>226</v>
-      </c>
       <c r="F45" s="25" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3696,16 +3699,16 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3718,16 +3721,16 @@
         <v>Sun</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3740,16 +3743,16 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3762,16 +3765,16 @@
         <v>Sat</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -3784,16 +3787,16 @@
         <v>Sat</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3806,16 +3809,16 @@
         <v>Mon</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3828,14 +3831,14 @@
         <v>Tue</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3848,16 +3851,16 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -3870,16 +3873,16 @@
         <v>Thu</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3892,16 +3895,16 @@
         <v>Thu</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3914,16 +3917,16 @@
         <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3936,14 +3939,14 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3956,16 +3959,16 @@
         <v>Sat</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="G58" s="19"/>
     </row>
@@ -3979,14 +3982,14 @@
         <v>Sat</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="G59" s="19"/>
     </row>
@@ -4000,16 +4003,16 @@
         <v>Mon</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -4022,16 +4025,16 @@
         <v>Tue</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -4044,14 +4047,14 @@
         <v>Tue</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -4064,16 +4067,16 @@
         <v>Wed</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -4086,14 +4089,14 @@
         <v>Wed</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -4106,16 +4109,16 @@
         <v>Wed</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -4128,14 +4131,14 @@
         <v>Wed</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -4148,14 +4151,14 @@
         <v>Thu</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -4168,14 +4171,14 @@
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F68" s="25" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4188,14 +4191,14 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4208,16 +4211,16 @@
         <v>Sat</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -4230,16 +4233,16 @@
         <v>Sat</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -4252,16 +4255,16 @@
         <v>Sun</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -4274,14 +4277,14 @@
         <v>Wed</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -4294,14 +4297,14 @@
         <v>Wed</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -4314,14 +4317,14 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="11" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F75" s="25" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="51" x14ac:dyDescent="0.35">
@@ -4334,16 +4337,16 @@
         <v>Fri</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
@@ -4356,16 +4359,16 @@
         <v>Sat</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -4378,14 +4381,14 @@
         <v>Mon</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D78" s="11"/>
       <c r="E78" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -4398,14 +4401,14 @@
         <v>Thu</v>
       </c>
       <c r="C79" s="40" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D79" s="37"/>
       <c r="E79" s="37" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -4418,14 +4421,14 @@
         <v>Fri</v>
       </c>
       <c r="C80" s="40" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D80" s="37"/>
       <c r="E80" s="37" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F80" s="44" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -4438,16 +4441,16 @@
         <v>Mon</v>
       </c>
       <c r="C81" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="D81" s="16" t="s">
         <v>575</v>
       </c>
-      <c r="D81" s="16" t="s">
-        <v>578</v>
-      </c>
       <c r="E81" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
@@ -4460,16 +4463,16 @@
         <v>Tue</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E82" s="25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
@@ -4482,14 +4485,14 @@
         <v>Wed</v>
       </c>
       <c r="C83" s="40" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D83" s="37"/>
       <c r="E83" s="37" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F83" s="44" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
@@ -4502,16 +4505,16 @@
         <v>Fri</v>
       </c>
       <c r="C84" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="D84" s="16" t="s">
         <v>576</v>
       </c>
-      <c r="D84" s="16" t="s">
-        <v>579</v>
-      </c>
       <c r="E84" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
@@ -4524,16 +4527,16 @@
         <v>Sat</v>
       </c>
       <c r="C85" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="D85" s="16" t="s">
         <v>577</v>
       </c>
-      <c r="D85" s="16" t="s">
-        <v>580</v>
-      </c>
       <c r="E85" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -4546,16 +4549,16 @@
         <v>Mon</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E86" s="25" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -4568,14 +4571,14 @@
         <v>Tue</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D87" s="25"/>
       <c r="E87" s="25" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
@@ -4588,16 +4591,16 @@
         <v>Wed</v>
       </c>
       <c r="C88" s="44" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D88" s="44" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E88" s="44" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F88" s="44" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -4610,16 +4613,16 @@
         <v>Tue</v>
       </c>
       <c r="C89" s="40" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E89" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F89" s="25" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
@@ -4632,16 +4635,16 @@
         <v>Tue</v>
       </c>
       <c r="C90" s="40" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D90" s="40" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E90" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F90" s="44" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
@@ -4654,16 +4657,16 @@
         <v>Wed</v>
       </c>
       <c r="C91" s="40" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F91" s="44" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
@@ -4676,14 +4679,14 @@
         <v>Wed</v>
       </c>
       <c r="C92" s="40" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D92" s="40"/>
       <c r="E92" s="37" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F92" s="44" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
@@ -4696,16 +4699,16 @@
         <v>Sat</v>
       </c>
       <c r="C93" s="40" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E93" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F93" s="44" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
@@ -4718,16 +4721,16 @@
         <v>Sun</v>
       </c>
       <c r="C94" s="37" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D94" s="37" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E94" s="39" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -4740,16 +4743,16 @@
         <v>Mon</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E95" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
@@ -4762,14 +4765,14 @@
         <v>Fri</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D96" s="16"/>
       <c r="E96" s="46" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F96" s="44" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
@@ -4782,16 +4785,16 @@
         <v>Thu</v>
       </c>
       <c r="C97" s="16" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E97" s="46" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F97" s="44" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
@@ -4804,16 +4807,16 @@
         <v>Wed</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
@@ -4826,14 +4829,14 @@
         <v>Sat</v>
       </c>
       <c r="C99" s="43" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D99" s="33"/>
       <c r="E99" s="33" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
@@ -4846,16 +4849,16 @@
         <v>Mon</v>
       </c>
       <c r="C100" s="40" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D100" s="40" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="E100" s="40" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F100" s="40" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
@@ -4868,14 +4871,14 @@
         <v>Mon</v>
       </c>
       <c r="C101" s="40" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D101" s="40"/>
       <c r="E101" s="40" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F101" s="40" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
@@ -4888,16 +4891,16 @@
         <v>Fri</v>
       </c>
       <c r="C102" s="40" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D102" s="40" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E102" s="40" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F102" s="44" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
@@ -4910,14 +4913,14 @@
         <v>Fri</v>
       </c>
       <c r="C103" s="40" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D103" s="37"/>
       <c r="E103" s="33" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F103" s="44" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
@@ -4930,16 +4933,16 @@
         <v>Fri</v>
       </c>
       <c r="C104" s="37" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D104" s="37" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E104" s="39" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F104" s="25" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
@@ -4952,16 +4955,16 @@
         <v>Fri</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E105" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
@@ -4974,16 +4977,16 @@
         <v>Fri</v>
       </c>
       <c r="C106" s="43" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D106" s="33" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E106" s="33" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F106" s="25" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
@@ -4996,13 +4999,13 @@
         <v>Fri</v>
       </c>
       <c r="C107" s="40" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D107" s="40" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E107" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F107" s="25"/>
     </row>
@@ -5016,16 +5019,16 @@
         <v>Sat</v>
       </c>
       <c r="C108" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D108" s="37" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E108" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F108" s="25" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -5038,16 +5041,16 @@
         <v>Sat</v>
       </c>
       <c r="C109" s="37" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D109" s="37" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E109" s="39" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F109" s="25" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -5060,16 +5063,16 @@
         <v>Sun</v>
       </c>
       <c r="C110" s="37" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D110" s="37" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E110" s="39" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F110" s="25" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -5082,16 +5085,16 @@
         <v>Mon</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E111" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F111" s="25" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
@@ -5104,16 +5107,16 @@
         <v>Thu</v>
       </c>
       <c r="C112" s="25" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D112" s="25" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E112" s="25" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -5126,16 +5129,16 @@
         <v>Sat</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F113" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
@@ -5148,16 +5151,16 @@
         <v>Wed</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E114" s="38" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F114" s="25" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
@@ -5170,16 +5173,16 @@
         <v>Fri</v>
       </c>
       <c r="C115" s="33" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D115" s="33" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E115" s="33" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
@@ -5192,16 +5195,16 @@
         <v>Thu</v>
       </c>
       <c r="C116" s="37" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D116" s="37" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E116" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
@@ -5214,16 +5217,16 @@
         <v>Fri</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E117" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F117" s="25" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
@@ -5236,14 +5239,14 @@
         <v>Sat</v>
       </c>
       <c r="C118" s="40" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D118" s="40"/>
       <c r="E118" s="37" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F118" s="25" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
@@ -5256,16 +5259,16 @@
         <v>Sat</v>
       </c>
       <c r="C119" s="43" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D119" s="43" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E119" s="43" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F119" s="45" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
@@ -5278,16 +5281,16 @@
         <v>Sat</v>
       </c>
       <c r="C120" s="37" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D120" s="37" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E120" s="39" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F120" s="25" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
@@ -5300,16 +5303,16 @@
         <v>Mon</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E121" s="38" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F121" s="25" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
@@ -5322,16 +5325,16 @@
         <v>Wed</v>
       </c>
       <c r="C122" s="25" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D122" s="25" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
@@ -5344,16 +5347,16 @@
         <v>Thu</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E123" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F123" s="25" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -5366,16 +5369,16 @@
         <v>Thu</v>
       </c>
       <c r="C124" s="33" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D124" s="33" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E124" s="33" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -5388,16 +5391,16 @@
         <v>Fri</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
@@ -5410,16 +5413,16 @@
         <v>Fri</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5432,16 +5435,16 @@
         <v>Fri</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F127" s="26" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5454,16 +5457,16 @@
         <v>Fri</v>
       </c>
       <c r="C128" s="16" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F128" s="25" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5476,16 +5479,16 @@
         <v>Fri</v>
       </c>
       <c r="C129" s="37" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D129" s="37" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E129" s="37" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
@@ -5498,16 +5501,16 @@
         <v>Mon</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E130" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F130" s="25" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
@@ -5520,16 +5523,16 @@
         <v>Mon</v>
       </c>
       <c r="C131" s="33" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D131" s="33" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E131" s="33" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
@@ -5542,16 +5545,16 @@
         <v>Fri</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F132" s="26" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
@@ -5564,16 +5567,16 @@
         <v>Sat</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
@@ -5586,16 +5589,16 @@
         <v>Thu</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F134" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
@@ -5608,16 +5611,16 @@
         <v>Fri</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F135" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
@@ -5630,16 +5633,16 @@
         <v>Sat</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F136" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
@@ -5652,16 +5655,16 @@
         <v>Sun</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F137" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
@@ -5674,16 +5677,16 @@
         <v>Mon</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E138" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F138" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
@@ -5696,16 +5699,16 @@
         <v>Tue</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E139" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F139" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
@@ -5718,16 +5721,16 @@
         <v>Wed</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E140" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F140" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
@@ -5740,16 +5743,16 @@
         <v>Thu</v>
       </c>
       <c r="C141" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E141" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F141" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
@@ -5762,16 +5765,16 @@
         <v>Fri</v>
       </c>
       <c r="C142" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D142" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F142" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
@@ -5784,16 +5787,16 @@
         <v>Fri</v>
       </c>
       <c r="C143" s="37" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D143" s="37" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E143" s="37" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
@@ -5806,16 +5809,16 @@
         <v>Thu</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E144" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F144" s="25" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
@@ -5828,14 +5831,14 @@
         <v>Mon</v>
       </c>
       <c r="C145" s="40" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D145" s="40"/>
       <c r="E145" s="37" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F145" s="25" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
@@ -5848,16 +5851,16 @@
         <v>Fri</v>
       </c>
       <c r="C146" s="33" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D146" s="33" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E146" s="33" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
@@ -5870,16 +5873,16 @@
         <v>Fri</v>
       </c>
       <c r="C147" s="16" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E147" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F147" s="25" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.35">
@@ -5892,16 +5895,16 @@
         <v>Thu</v>
       </c>
       <c r="C148" s="37" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D148" s="40" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E148" s="37" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
@@ -5914,14 +5917,14 @@
         <v>Sat</v>
       </c>
       <c r="C149" s="40" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D149" s="37"/>
       <c r="E149" s="33" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F149" s="44" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
@@ -5934,16 +5937,16 @@
         <v>Sat</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E150" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F150" s="25" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
@@ -5956,16 +5959,16 @@
         <v>Sat</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E151" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F151" s="25" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
@@ -5978,16 +5981,16 @@
         <v>Sat</v>
       </c>
       <c r="C152" s="43" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D152" s="43" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E152" s="43" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F152" s="45" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
@@ -6000,16 +6003,16 @@
         <v>Fri</v>
       </c>
       <c r="C153" s="16" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E153" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F153" s="26" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
@@ -6022,14 +6025,14 @@
         <v>Sun</v>
       </c>
       <c r="C154" s="16" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D154" s="11"/>
       <c r="E154" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F154" s="45" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
@@ -6042,16 +6045,16 @@
         <v>Wed</v>
       </c>
       <c r="C155" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D155" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E155" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F155" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
@@ -6064,16 +6067,16 @@
         <v>Thu</v>
       </c>
       <c r="C156" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D156" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E156" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F156" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
@@ -6086,16 +6089,16 @@
         <v>Fri</v>
       </c>
       <c r="C157" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D157" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E157" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F157" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
@@ -6108,16 +6111,16 @@
         <v>Sat</v>
       </c>
       <c r="C158" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D158" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E158" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F158" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
@@ -6130,16 +6133,16 @@
         <v>Sun</v>
       </c>
       <c r="C159" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D159" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E159" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F159" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.35">
@@ -6152,16 +6155,16 @@
         <v>Mon</v>
       </c>
       <c r="C160" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D160" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E160" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F160" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
@@ -6174,16 +6177,16 @@
         <v>Tue</v>
       </c>
       <c r="C161" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D161" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E161" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F161" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.35">
@@ -6196,16 +6199,16 @@
         <v>Wed</v>
       </c>
       <c r="C162" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D162" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E162" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F162" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
@@ -6218,16 +6221,16 @@
         <v>Thu</v>
       </c>
       <c r="C163" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D163" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E163" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F163" s="25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
@@ -6240,14 +6243,14 @@
         <v>Wed</v>
       </c>
       <c r="C164" s="40" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D164" s="40"/>
       <c r="E164" s="37" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F164" s="25" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -6265,7 +6268,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.08984375" customWidth="1"/>
@@ -6299,7 +6302,7 @@
         <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6313,7 +6316,7 @@
         <v>40</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6327,7 +6330,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6341,7 +6344,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6355,7 +6358,7 @@
         <v>46</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6369,7 +6372,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6383,7 +6386,7 @@
         <v>50</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6397,7 +6400,7 @@
         <v>52</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6411,7 +6414,7 @@
         <v>54</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6425,7 +6428,7 @@
         <v>56</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6437,7 +6440,7 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6449,7 +6452,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6463,7 +6466,7 @@
         <v>60</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6474,10 +6477,10 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6485,13 +6488,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="D16" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6499,13 +6502,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>176</v>
+        <v>63</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>64</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6519,7 +6522,7 @@
         <v>66</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6533,7 +6536,7 @@
         <v>68</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6547,7 +6550,7 @@
         <v>70</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6561,7 +6564,7 @@
         <v>72</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6575,7 +6578,7 @@
         <v>74</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6589,7 +6592,7 @@
         <v>76</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6603,7 +6606,7 @@
         <v>78</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6617,21 +6620,27 @@
         <v>80</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="4">
-        <v>25</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>92</v>
+      <c r="A26" s="4"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>619</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>618</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -6666,7 +6675,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>21</v>
@@ -6689,7 +6698,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -6703,13 +6712,13 @@
         <v>48</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -6723,13 +6732,13 @@
         <v>42</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -6743,13 +6752,13 @@
         <v>46</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -6763,13 +6772,13 @@
         <v>50</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -6783,13 +6792,13 @@
         <v>56</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -6797,19 +6806,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -6817,19 +6826,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -6837,19 +6846,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -6857,19 +6866,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -6877,19 +6886,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -6937,10 +6946,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -6955,15 +6964,15 @@
         <v>28</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -6976,38 +6985,38 @@
         <v>29</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -7020,61 +7029,61 @@
         <v>29</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -7089,61 +7098,61 @@
         <v>29</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F9" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -7158,15 +7167,15 @@
         <v>28</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -7175,21 +7184,21 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -7204,15 +7213,15 @@
         <v>29</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -7227,15 +7236,15 @@
         <v>29</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -7250,153 +7259,153 @@
         <v>28</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>62</v>
+        <v>617</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>63</v>
+        <v>618</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>103</v>
+        <v>616</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F19" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F20" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F21" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -7411,7 +7420,7 @@
         <v>29</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -7446,7 +7455,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>21</v>
@@ -7454,839 +7463,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D6" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D7" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B8" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H8" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D9" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H9" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C10" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D10" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D11" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H11" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C12" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D12" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H12" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B13" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C13" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D13" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H13" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B14" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D14" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E14" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
       <c r="G14" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B15" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C15" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D15" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E15" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
       <c r="G15" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="H15" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B16" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C16" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D16" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E16" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
       <c r="G16" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H16" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C17" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D17" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E17" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
       <c r="G17" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H17" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B18" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C18" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D18" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E18" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
       <c r="G18" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H18" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B19" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C19" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D19" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E19" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
       <c r="G19" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H19" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C20" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D20" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E20" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
       <c r="G20" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H20" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B21" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C21" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D21" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E21" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
       <c r="G21" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H21" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C22" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D22" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E22" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
       <c r="G22" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H22" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C23" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D23" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E23" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
       <c r="G23" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H23" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B24" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D24" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E24" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
       <c r="G24" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H24" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B25" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C25" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D25" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geokchin.jpg</v>
       </c>
       <c r="G25" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="H25" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B26" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D26" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laysiew.jpg</v>
       </c>
       <c r="G26" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H26" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B27" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C27" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D27" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>waiyee.jpg</v>
       </c>
       <c r="G27" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="H27" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B28" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C28" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D28" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>carol.jpg</v>
       </c>
       <c r="G28" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="H28" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B29" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C29" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D29" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F29" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yokewant.jpg</v>
       </c>
       <c r="G29" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H29" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C30" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D30" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F30" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pohcheng.jpg</v>
       </c>
       <c r="G30" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="H30" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B31" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C31" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D31" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F31" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geoklan.jpg</v>
       </c>
       <c r="G31" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="H31" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B32" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C32" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D32" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F32" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laichee.jpg</v>
       </c>
       <c r="G32" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="H32" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B33" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C33" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D33" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F33" s="4" t="str">
         <f t="shared" si="0"/>
         <v>beechoo.jpg</v>
       </c>
       <c r="G33" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="H33" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -8319,7 +8328,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -8327,15 +8336,15 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -8344,26 +8353,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -8604,10 +8593,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8626,21 +8647,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>